--- a/reports/2026-08-01/blotter_report.xlsx
+++ b/reports/2026-08-01/blotter_report.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$299</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$161</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1076,21 +1076,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>147</v>
+        <v>9</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>31</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>471.3</v>
+      </c>
       <c r="K14" s="3" t="n">
         <v>46233</v>
       </c>
@@ -1636,30 +1638,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>71878728447</t>
+          <t>2620701835</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46230.4375</v>
+        <v>46229</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1669,26 +1671,26 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>Assault Offenses</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>16XX BLOCK OF N 105TH ST</t>
+          <t>4000 S LAWRENCE ST</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>47.70504225</v>
+        <v>47.219421</v>
       </c>
       <c r="K8" t="n">
-        <v>-122.338094779232</v>
+        <v>-122.478428</v>
       </c>
       <c r="L8" t="n">
-        <v>938.8</v>
+        <v>853.4</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 26, 2026, 853 m from Tacoma Mall (4000 S LAWRENCE ST). Case #2620701835 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -1710,15 +1712,15 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>71894237115</t>
+          <t>71878728447</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46231.20833333334</v>
+        <v>46230.4375</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1733,51 +1735,51 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>16XX BLOCK OF N 105TH ST</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>47.70668788</v>
+        <v>47.70504225</v>
       </c>
       <c r="K9" t="n">
-        <v>-122.311189997702</v>
+        <v>-122.338094779232</v>
       </c>
       <c r="L9" t="n">
-        <v>1145.7</v>
+        <v>938.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>71889871382</t>
+          <t>2621000152</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46231.00625</v>
+        <v>46232</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Simple Assault</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1787,56 +1789,56 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ALL OTHER</t>
+          <t>Assault Offenses</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>3500 S 45TH ST</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>47.70668788</v>
+        <v>47.216421</v>
       </c>
       <c r="K10" t="n">
-        <v>-122.311189997702</v>
+        <v>-122.482428</v>
       </c>
       <c r="L10" t="n">
-        <v>1145.7</v>
+        <v>1074.3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 29, 2026, 1074 m from Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>26C142249</t>
+          <t>71894237115</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46230.75</v>
+        <v>46231.20833333334</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BATTERY ABW</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1846,56 +1848,56 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SIM_ASSAULT</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S MISSION RD</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>37.6756469679485</v>
+        <v>47.70668788</v>
       </c>
       <c r="K11" t="n">
-        <v>-97.25850032865422</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L11" t="n">
-        <v>1251.5</v>
+        <v>1145.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>096140526</t>
+          <t>71889871382</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46232</v>
+        <v>46231.00625</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1905,56 +1907,56 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13A</t>
+          <t>ALL OTHER</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1900-1999 POST OAK PARK DR</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>29.74712522681273</v>
+        <v>47.70668788</v>
       </c>
       <c r="K12" t="n">
-        <v>-95.45374747370188</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L12" t="n">
-        <v>1323.4</v>
+        <v>1145.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 29, 2026, 1323 m from Houston Galleria (1900-1999 POST OAK PARK DR). Case #096140526 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675136         </t>
+          <t>26C142249</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46228.97847222222</v>
+        <v>46230.75</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
+          <t>BATTERY ABW</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1962,54 +1964,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>SIM_ASSAULT</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5XXX S HARDY DR</t>
+          <t>700 BLOCK OF S MISSION RD</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>33.3757495513233</v>
+        <v>37.6756469679485</v>
       </c>
       <c r="K13" t="n">
-        <v>-111.9531832468173</v>
+        <v>-97.25850032865422</v>
       </c>
       <c r="L13" t="n">
-        <v>1345.1</v>
+        <v>1251.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>[13b] assault on Jul 25, 2026, 1345 m from Arizona Mills (5XXX S HARDY DR). Case #TE202675136          (use for a records request — full narratives are not published in open data).</t>
+          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2621102285</t>
+          <t>096140526</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2019,50 +2025,56 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>13A</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5100 S 58TH ST</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+          <t>1900-1999 POST OAK PARK DR</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>29.74712522681273</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-95.45374747370188</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1323.4</v>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 30, 2026, Tacoma Mall (5100 S 58TH ST). Case #2621102285 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 29, 2026, 1323 m from Houston Galleria (1900-1999 POST OAK PARK DR). Case #096140526 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2621101093</t>
+          <t xml:space="preserve">TE202675136         </t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46233</v>
+        <v>46228.97847222222</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Assault Aggravated</t>
+          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2070,22 +2082,24 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8400 PACIFIC AVE</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+          <t>5XXX S HARDY DR</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>33.3757495513233</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-111.9531832468173</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1345.1</v>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Assault aggravated on Jul 30, 2026, Tacoma Mall (8400 PACIFIC AVE). Case #2621101093 (use for a records request — full narratives are not published in open data).</t>
+          <t>[13b] assault on Jul 25, 2026, 1345 m from Arizona Mills (5XXX S HARDY DR). Case #TE202675136          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2121,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2621101249</t>
+          <t>2621102013</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -2115,7 +2129,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Assault Aggravated</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2130,545 +2144,611 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>400 S 23RD ST</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+          <t>5400 SOUTH TACOMA WAY</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>47.206421</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-122.483428</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1578</v>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Assault aggravated on Jul 30, 2026, Tacoma Mall (400 S 23RD ST). Case #2621101249 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 30, 2026, 1578 m from Tacoma Mall (5400 SOUTH TACOMA WAY). Case #2621102013 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2621102013</t>
+          <t>DP2026415473230300</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46233</v>
+        <v>46231.47916666666</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>larceny</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5400 SOUTH TACOMA WAY</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+          <t>15 S STEELE ST</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>39.7162154712797</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-104.9512928115626</v>
+      </c>
+      <c r="L17" t="n">
+        <v>144.7</v>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 30, 2026, Tacoma Mall (5400 SOUTH TACOMA WAY). Case #2621102013 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 28, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026415473 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2621100265</t>
+          <t>DP2026413358260700</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46233</v>
+        <v>46230.47013888889</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Assault Aggravated</t>
+          <t>fraud-by-telephone</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>white-collar-crime</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2000 6TH AVE</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+          <t>15 S STEELE ST</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>39.7162154712797</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-104.9512928115626</v>
+      </c>
+      <c r="L18" t="n">
+        <v>144.7</v>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Assault aggravated on Jul 30, 2026, Tacoma Mall (2000 6TH AVE). Case #2621100265 (use for a records request — full narratives are not published in open data).</t>
+          <t>Fraud-by-telephone on Jul 27, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026413358 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2621101020</t>
+          <t>71913162555</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46232</v>
+        <v>46232.82986111111</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3400 S 19TH ST</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>47.7086028</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-122.324615154453</v>
+      </c>
+      <c r="L19" t="n">
+        <v>145.2</v>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 29, 2026, Tacoma Mall (3400 S 19TH ST). Case #2621101020 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 29, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-222878 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2621001950</t>
+          <t>71898889573</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46232</v>
+        <v>46231.625</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Assault Aggravated</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1700 S J ST</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>47.7086028</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-122.324615154453</v>
+      </c>
+      <c r="L20" t="n">
+        <v>145.2</v>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Assault aggravated on Jul 29, 2026, Tacoma Mall (1700 S J ST). Case #2621001950 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221387 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2621001913</t>
+          <t>71899277060</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46232</v>
+        <v>46231.47569444445</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7200 PACIFIC AVE</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>47.7086028</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-122.324615154454</v>
+      </c>
+      <c r="L21" t="n">
+        <v>145.2</v>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 29, 2026, Tacoma Mall (7200 PACIFIC AVE). Case #2621001913 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221174 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Property</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2621001005</t>
+          <t>096475026</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1900 S 72ND ST</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+          <t>5100-5199 ALABAMA ST W</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>29.73799058803365</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-95.46478253884783</v>
+      </c>
+      <c r="L22" t="n">
+        <v>163.5</v>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 29, 2026, Tacoma Mall (1900 S 72ND ST). Case #2621001005 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 30, 2026, 163 m from Houston Galleria (5100-5199 ALABAMA ST W). Case #096475026 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Property</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2621001310</t>
+          <t>095621926</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Assault Aggravated</t>
+          <t>Theft from motor vehicle</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>23F</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>600 N JACKSON AVE</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+          <t>5100-5199 ALABAMA ST W</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>29.73799058803365</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-95.46478253884783</v>
+      </c>
+      <c r="L23" t="n">
+        <v>163.5</v>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Assault aggravated on Jul 29, 2026, Tacoma Mall (600 N JACKSON AVE). Case #2621001310 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft from motor vehicle on Jul 28, 2026, 163 m from Houston Galleria (5100-5199 ALABAMA ST W). Case #095621926 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Property</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2621000152</t>
+          <t>095601426</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3500 S 45TH ST</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+          <t>5100-5199 ALABAMA ST W</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>29.73799058803365</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-95.46478253884783</v>
+      </c>
+      <c r="L24" t="n">
+        <v>163.5</v>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 29, 2026, Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 163 m from Houston Galleria (5100-5199 ALABAMA ST W). Case #095601426 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2621000914</t>
+          <t>20260728-1130-01</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46232</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1600 MARTIN LUTHER KING JR WAY</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L25" t="n">
+        <v>178.9</v>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 29, 2026, Tacoma Mall (1600 MARTIN LUTHER KING JR WAY). Case #2621000914 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1130-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2621100025</t>
+          <t>20260728-1922-01</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46232</v>
+        <v>46231.16666666666</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Assault Aggravated</t>
+          <t>Shoplifting</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>23C</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2500 PACIFIC AVE</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+          <t>4400 SHARON RD</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>35.15120046375475</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-80.82867375349484</v>
+      </c>
+      <c r="L26" t="n">
+        <v>178.9</v>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Assault aggravated on Jul 29, 2026, Tacoma Mall (2500 PACIFIC AVE). Case #2621100025 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1922-01 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M299"/>
+  <dimension ref="A1:M161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2694,8 +2774,8 @@
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="53" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="49" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -11580,38 +11660,44 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2621001842</t>
+          <t>2620701835</t>
         </is>
       </c>
       <c r="E153" s="3" t="n">
-        <v>46232</v>
+        <v>46229</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Loitering/Vagrancy</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Loitering/Vagrancy</t>
+          <t>Assault Offenses</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>E 25TH ST &amp; E M ST</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
+          <t>4000 S LAWRENCE ST</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
+        <v>47.219421</v>
+      </c>
+      <c r="K153" t="n">
+        <v>-122.478428</v>
+      </c>
+      <c r="L153" t="n">
+        <v>853.4</v>
+      </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Loitering/vagrancy on Jul 29, 2026, Tacoma Mall (E 25TH ST &amp; E M ST). Case #2621001842 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 26, 2026, 853 m from Tacoma Mall (4000 S LAWRENCE ST). Case #2620701835 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -11633,38 +11719,44 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2621000741</t>
+          <t>2620700788</t>
         </is>
       </c>
       <c r="E154" s="3" t="n">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Destruction/Damage/Vandalism</t>
+          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Destruction/Damage/Vandalism</t>
+          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>1900 FAWCETT AVE</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
+          <t>TACOMA MALL BLVD &amp; S 48TH ST</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
+        <v>47.213421</v>
+      </c>
+      <c r="K154" t="n">
+        <v>-122.463428</v>
+      </c>
+      <c r="L154" t="n">
+        <v>471.3</v>
+      </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Destruction/damage/vandalism on Jul 27, 2026, Tacoma Mall (1900 FAWCETT AVE). Case #2621000741 (use for a records request — full narratives are not published in open data).</t>
+          <t>Traffic accident/collision - non fatal - injury on Jul 26, 2026, 471 m from Tacoma Mall (TACOMA MALL BLVD &amp; S 48TH ST). Case #2620700788 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -11686,7 +11778,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2620802264</t>
+          <t>2620801268</t>
         </is>
       </c>
       <c r="E155" s="3" t="n">
@@ -11694,30 +11786,36 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Larceny Theft</t>
+          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Larceny/Theft Offenses</t>
+          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>700 S 56TH ST</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
+          <t>S 48TH ST &amp; TACOMA MALL BLVD</t>
+        </is>
+      </c>
+      <c r="J155" t="n">
+        <v>47.213421</v>
+      </c>
+      <c r="K155" t="n">
+        <v>-122.463428</v>
+      </c>
+      <c r="L155" t="n">
+        <v>471.3</v>
+      </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (700 S 56TH ST). Case #2620802264 (use for a records request — full narratives are not published in open data).</t>
+          <t>Traffic accident/collision - non fatal - injury on Jul 27, 2026, 471 m from Tacoma Mall (S 48TH ST &amp; TACOMA MALL BLVD). Case #2620801268 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -11739,15 +11837,15 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2621100741</t>
+          <t>2621001325</t>
         </is>
       </c>
       <c r="E156" s="3" t="n">
-        <v>46233</v>
+        <v>46231</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Destruction/Damage/Vandalism</t>
+          <t>Motor Vehicle Theft</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11757,20 +11855,26 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Destruction/Damage/Vandalism</t>
+          <t>Motor Vehicle Theft</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2200 N PEARL ST</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
+          <t>S UNION AVE &amp; S 47TH ST</t>
+        </is>
+      </c>
+      <c r="J156" t="n">
+        <v>47.214421</v>
+      </c>
+      <c r="K156" t="n">
+        <v>-122.483428</v>
+      </c>
+      <c r="L156" t="n">
+        <v>1165.2</v>
+      </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Destruction/damage/vandalism on Jul 30, 2026, Tacoma Mall (2200 N PEARL ST). Case #2621100741 (use for a records request — full narratives are not published in open data).</t>
+          <t>Motor vehicle theft on Jul 28, 2026, 1165 m from Tacoma Mall (S UNION AVE &amp; S 47TH ST). Case #2621001325 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -11792,7 +11896,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2621000943</t>
+          <t>2621000811</t>
         </is>
       </c>
       <c r="E157" s="3" t="n">
@@ -11800,7 +11904,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Destruction/Damage/Vandalism</t>
+          <t>Fraud</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11810,20 +11914,26 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Destruction/Damage/Vandalism</t>
+          <t>Fraud Offenses</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>3800 N WATERVIEW ST</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
+          <t>3100 S 45TH ST</t>
+        </is>
+      </c>
+      <c r="J157" t="n">
+        <v>47.216421</v>
+      </c>
+      <c r="K157" t="n">
+        <v>-122.477428</v>
+      </c>
+      <c r="L157" t="n">
+        <v>696.9</v>
+      </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Destruction/damage/vandalism on Jul 29, 2026, Tacoma Mall (3800 N WATERVIEW ST). Case #2621000943 (use for a records request — full narratives are not published in open data).</t>
+          <t>Fraud on Jul 29, 2026, 697 m from Tacoma Mall (3100 S 45TH ST). Case #2621000811 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -11845,38 +11955,44 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2621109059</t>
+          <t>2621102013</t>
         </is>
       </c>
       <c r="E158" s="3" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Larceny Theft</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Larceny/Theft Offenses</t>
+          <t>Assault Offenses</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2100 S SHERIDAN AVE</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
+          <t>5400 SOUTH TACOMA WAY</t>
+        </is>
+      </c>
+      <c r="J158" t="n">
+        <v>47.206421</v>
+      </c>
+      <c r="K158" t="n">
+        <v>-122.483428</v>
+      </c>
+      <c r="L158" t="n">
+        <v>1578</v>
+      </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Larceny theft on Jul 28, 2026, Tacoma Mall (2100 S SHERIDAN AVE). Case #2621109059 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 30, 2026, 1578 m from Tacoma Mall (5400 SOUTH TACOMA WAY). Case #2621102013 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -11898,7 +12014,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2620702146</t>
+          <t>2620800399</t>
         </is>
       </c>
       <c r="E159" s="3" t="n">
@@ -11906,7 +12022,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Destruction/Damage/Vandalism</t>
+          <t>Motor Vehicle Theft</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11916,20 +12032,26 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Destruction/Damage/Vandalism</t>
+          <t>Motor Vehicle Theft</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>700 S 56TH ST</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
+          <t>4800 S M ST</t>
+        </is>
+      </c>
+      <c r="J159" t="n">
+        <v>47.212421</v>
+      </c>
+      <c r="K159" t="n">
+        <v>-122.451428</v>
+      </c>
+      <c r="L159" t="n">
+        <v>1333.5</v>
+      </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Destruction/damage/vandalism on Jul 26, 2026, Tacoma Mall (700 S 56TH ST). Case #2620702146 (use for a records request — full narratives are not published in open data).</t>
+          <t>Motor vehicle theft on Jul 26, 2026, 1333 m from Tacoma Mall (4800 S M ST). Case #2620800399 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -11951,38 +12073,44 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2621109010</t>
+          <t>2621000152</t>
         </is>
       </c>
       <c r="E160" s="3" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Larceny Theft</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Larceny/Theft Offenses</t>
+          <t>Assault Offenses</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>7000 S 12TH ST</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
+          <t>3500 S 45TH ST</t>
+        </is>
+      </c>
+      <c r="J160" t="n">
+        <v>47.216421</v>
+      </c>
+      <c r="K160" t="n">
+        <v>-122.482428</v>
+      </c>
+      <c r="L160" t="n">
+        <v>1074.3</v>
+      </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (7000 S 12TH ST). Case #2621109010 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 29, 2026, 1074 m from Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -12004,7357 +12132,49 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2621101504</t>
+          <t>2620901147</t>
         </is>
       </c>
       <c r="E161" s="3" t="n">
-        <v>46233</v>
+        <v>46231</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Larceny Theft</t>
+          <t>Extortion (Blackmail)</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Larceny/Theft Offenses</t>
+          <t>Extortion (Blackmail)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>400 S 23RD ST</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
+          <t>5400 S STEELE ST</t>
+        </is>
+      </c>
+      <c r="J161" t="n">
+        <v>47.206421</v>
+      </c>
+      <c r="K161" t="n">
+        <v>-122.467428</v>
+      </c>
+      <c r="L161" t="n">
+        <v>1082.7</v>
+      </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Larceny theft on Jul 30, 2026, Tacoma Mall (400 S 23RD ST). Case #2621101504 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>2621101060</t>
-        </is>
-      </c>
-      <c r="E162" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>LAKEWOOD DR W &amp; 68TH ST W</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 30, 2026, Tacoma Mall (LAKEWOOD DR W &amp; 68TH ST W). Case #2621101060 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>2621109060</t>
-        </is>
-      </c>
-      <c r="E163" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>700 S M ST</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 29, 2026, Tacoma Mall (700 S M ST). Case #2621109060 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>2621100865</t>
-        </is>
-      </c>
-      <c r="E164" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>COMMERCE ST &amp; S 11TH ST</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - injury on Jul 30, 2026, Tacoma Mall (COMMERCE ST &amp; S 11TH ST). Case #2621100865 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2621001342</t>
-        </is>
-      </c>
-      <c r="E165" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>E 25TH ST &amp; MCKINLEY AVE</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 29, 2026, Tacoma Mall (E 25TH ST &amp; MCKINLEY AVE). Case #2621001342 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>2620701835</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>4000 S LAWRENCE ST</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 26, 2026, Tacoma Mall (4000 S LAWRENCE ST). Case #2620701835 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>2620900912</t>
-        </is>
-      </c>
-      <c r="E167" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>S 12TH ST &amp; S PINE ST</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 28, 2026, Tacoma Mall (S 12TH ST &amp; S PINE ST). Case #2620900912 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>2621109027</t>
-        </is>
-      </c>
-      <c r="E168" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>2300 FREMONT ST</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 30, 2026, Tacoma Mall (2300 FREMONT ST). Case #2621109027 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>2620700133</t>
-        </is>
-      </c>
-      <c r="E169" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>Drug/Narcotics Violations</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>QUALITY_OF_LIFE</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Drug/Narcotics Violations</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>S ASH ST &amp; 96TH ST S</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>Drug/narcotics violations on Jul 26, 2026, Tacoma Mall (S ASH ST &amp; 96TH ST S). Case #2620700133 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>2621101383</t>
-        </is>
-      </c>
-      <c r="E170" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>Arson</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Arson</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>200 N I ST</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>Arson on Jul 30, 2026, Tacoma Mall (200 N I ST). Case #2621101383 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>2620900213</t>
-        </is>
-      </c>
-      <c r="E171" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>Burglary</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Burglary/Breaking &amp; Entering</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>1900 YAKIMA AVE</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>Burglary on Jul 28, 2026, Tacoma Mall (1900 YAKIMA AVE). Case #2620900213 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>2621109013</t>
-        </is>
-      </c>
-      <c r="E172" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>1000 S PUGET SOUND AVE</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 28, 2026, Tacoma Mall (1000 S PUGET SOUND AVE). Case #2621109013 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>2620801701</t>
-        </is>
-      </c>
-      <c r="E173" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>S 8TH ST &amp; S FIFE ST</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 27, 2026, Tacoma Mall (S 8TH ST &amp; S FIFE ST). Case #2620801701 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>2621109019</t>
-        </is>
-      </c>
-      <c r="E174" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>6300 N 26TH ST</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 28, 2026, Tacoma Mall (6300 N 26TH ST). Case #2621109019 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>2620800717</t>
-        </is>
-      </c>
-      <c r="E175" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Fraud Offenses</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>5000 N 29TH ST</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>Fraud on Jul 27, 2026, Tacoma Mall (5000 N 29TH ST). Case #2620800717 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>2620700788</t>
-        </is>
-      </c>
-      <c r="E176" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>TACOMA MALL BLVD &amp; S 48TH ST</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - injury on Jul 26, 2026, Tacoma Mall (TACOMA MALL BLVD &amp; S 48TH ST). Case #2620700788 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>2620701357</t>
-        </is>
-      </c>
-      <c r="E177" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>1600 NORPOINT WAY NE</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 26, 2026, Tacoma Mall (1600 NORPOINT WAY NE). Case #2620701357 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>2620809029</t>
-        </is>
-      </c>
-      <c r="E178" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>4500 S J ST</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (4500 S J ST). Case #2620809029 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>2620902305</t>
-        </is>
-      </c>
-      <c r="E179" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>8400 PACIFIC AVE</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 28, 2026, Tacoma Mall (8400 PACIFIC AVE). Case #2620902305 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>2620901622</t>
-        </is>
-      </c>
-      <c r="E180" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>S J ST &amp; 6TH AVE</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - injury on Jul 28, 2026, Tacoma Mall (S J ST &amp; 6TH AVE). Case #2620901622 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>2620701372</t>
-        </is>
-      </c>
-      <c r="E181" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>S STEELE ST &amp; S 96TH ST</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 26, 2026, Tacoma Mall (S STEELE ST &amp; S 96TH ST). Case #2620701372 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>2620800590</t>
-        </is>
-      </c>
-      <c r="E182" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>7000 S OAKES ST</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - injury on Jul 27, 2026, Tacoma Mall (7000 S OAKES ST). Case #2620800590 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>2620702095</t>
-        </is>
-      </c>
-      <c r="E183" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>S 25TH ST &amp; JEFFERSON AVE</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - injury on Jul 26, 2026, Tacoma Mall (S 25TH ST &amp; JEFFERSON AVE). Case #2620702095 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>2620802464</t>
-        </is>
-      </c>
-      <c r="E184" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>1000 S L ST</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 27, 2026, Tacoma Mall (1000 S L ST). Case #2620802464 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>2620901957</t>
-        </is>
-      </c>
-      <c r="E185" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>2400 RUSTON WAY</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 28, 2026, Tacoma Mall (2400 RUSTON WAY). Case #2620901957 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>2621109043</t>
-        </is>
-      </c>
-      <c r="E186" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>1700 MARKET ST</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 27, 2026, Tacoma Mall (1700 MARKET ST). Case #2621109043 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>2621102285</t>
-        </is>
-      </c>
-      <c r="E187" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>5100 S 58TH ST</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 30, 2026, Tacoma Mall (5100 S 58TH ST). Case #2621102285 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>2621109021</t>
-        </is>
-      </c>
-      <c r="E188" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>5600 N 37TH ST</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (5600 N 37TH ST). Case #2621109021 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>2621109058</t>
-        </is>
-      </c>
-      <c r="E189" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>1900 LINCOLN AVE</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 28, 2026, Tacoma Mall (1900 LINCOLN AVE). Case #2621109058 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>2621101020</t>
-        </is>
-      </c>
-      <c r="E190" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>3400 S 19TH ST</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 29, 2026, Tacoma Mall (3400 S 19TH ST). Case #2621101020 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>2620801790</t>
-        </is>
-      </c>
-      <c r="E191" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>400 SOUTH TACOMA WAY</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - injury on Jul 27, 2026, Tacoma Mall (400 SOUTH TACOMA WAY). Case #2620801790 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>2621109063</t>
-        </is>
-      </c>
-      <c r="E192" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>700 S M ST</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 26, 2026, Tacoma Mall (700 S M ST). Case #2621109063 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>2621109049</t>
-        </is>
-      </c>
-      <c r="E193" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>1700 TACOMA AVE S</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 29, 2026, Tacoma Mall (1700 TACOMA AVE S). Case #2621109049 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>2621109042</t>
-        </is>
-      </c>
-      <c r="E194" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>2300 S J ST</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 26, 2026, Tacoma Mall (2300 S J ST). Case #2621109042 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>2620800685</t>
-        </is>
-      </c>
-      <c r="E195" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>2500 N PROCTOR ST</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (2500 N PROCTOR ST). Case #2620800685 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>2620801268</t>
-        </is>
-      </c>
-      <c r="E196" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>S 48TH ST &amp; TACOMA MALL BLVD</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - injury on Jul 27, 2026, Tacoma Mall (S 48TH ST &amp; TACOMA MALL BLVD). Case #2620801268 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>2621101391</t>
-        </is>
-      </c>
-      <c r="E197" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>2600 WESTRIDGE AVE W</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - injury on Jul 30, 2026, Tacoma Mall (2600 WESTRIDGE AVE W). Case #2621101391 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>2621109007</t>
-        </is>
-      </c>
-      <c r="E198" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>3200 N 30TH ST</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 27, 2026, Tacoma Mall (3200 N 30TH ST). Case #2621109007 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>2621001950</t>
-        </is>
-      </c>
-      <c r="E199" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>Assault Aggravated</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>1700 S J ST</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>Assault aggravated on Jul 29, 2026, Tacoma Mall (1700 S J ST). Case #2621001950 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>2621109057</t>
-        </is>
-      </c>
-      <c r="E200" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>1400 TACOMA AVE S</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 26, 2026, Tacoma Mall (1400 TACOMA AVE S). Case #2621109057 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>2620709006</t>
-        </is>
-      </c>
-      <c r="E201" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>600 N K ST</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr"/>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 26, 2026, Tacoma Mall (600 N K ST). Case #2620709006 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>2621100946</t>
-        </is>
-      </c>
-      <c r="E202" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>Burglary</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Burglary/Breaking &amp; Entering</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>1400 S SHERIDAN AVE</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>Burglary on Jul 30, 2026, Tacoma Mall (1400 S SHERIDAN AVE). Case #2621100946 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>2621109018</t>
-        </is>
-      </c>
-      <c r="E203" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>600 S SHIRLEY ST</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (600 S SHIRLEY ST). Case #2621109018 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>2621101093</t>
-        </is>
-      </c>
-      <c r="E204" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>Assault Aggravated</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>8400 PACIFIC AVE</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>Assault aggravated on Jul 30, 2026, Tacoma Mall (8400 PACIFIC AVE). Case #2621101093 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>2621101249</t>
-        </is>
-      </c>
-      <c r="E205" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>Assault Aggravated</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>400 S 23RD ST</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>Assault aggravated on Jul 30, 2026, Tacoma Mall (400 S 23RD ST). Case #2621101249 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>2620902083</t>
-        </is>
-      </c>
-      <c r="E206" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>SOUTH TACOMA WAY &amp; S FIFE ST</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (SOUTH TACOMA WAY &amp; S FIFE ST). Case #2620902083 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>2620801976</t>
-        </is>
-      </c>
-      <c r="E207" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>E 25TH ST &amp; E C ST</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 26, 2026, Tacoma Mall (E 25TH ST &amp; E C ST). Case #2620801976 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>2620800472</t>
-        </is>
-      </c>
-      <c r="E208" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>600 N PUGET SOUND AVE</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>Motor vehicle theft on Jul 27, 2026, Tacoma Mall (600 N PUGET SOUND AVE). Case #2620800472 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>2621001913</t>
-        </is>
-      </c>
-      <c r="E209" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>7200 PACIFIC AVE</t>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr"/>
-      <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr"/>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 29, 2026, Tacoma Mall (7200 PACIFIC AVE). Case #2621001913 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>2620900180</t>
-        </is>
-      </c>
-      <c r="E210" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>Weapon Law Violation</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Weapon Law Violations</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>1700 S 95TH ST</t>
-        </is>
-      </c>
-      <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
-      <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>Weapon law violation on Jul 28, 2026, Tacoma Mall (1700 S 95TH ST). Case #2620900180 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>2621109048</t>
-        </is>
-      </c>
-      <c r="E211" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>700 YAKIMA AVE</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 26, 2026, Tacoma Mall (700 YAKIMA AVE). Case #2621109048 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>2620900934</t>
-        </is>
-      </c>
-      <c r="E212" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>3500 CENTER ST</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 28, 2026, Tacoma Mall (3500 CENTER ST). Case #2620900934 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>2620701371</t>
-        </is>
-      </c>
-      <c r="E213" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>900 FAWCETT AVE</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>Motor vehicle theft on Jul 26, 2026, Tacoma Mall (900 FAWCETT AVE). Case #2620701371 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>2621109022</t>
-        </is>
-      </c>
-      <c r="E214" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>3600 N ORCHARD ST</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 29, 2026, Tacoma Mall (3600 N ORCHARD ST). Case #2621109022 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>2620700857</t>
-        </is>
-      </c>
-      <c r="E215" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>Extortion (Blackmail)</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Extortion (Blackmail)</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>400 E 56TH ST</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr"/>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>Extortion (blackmail) on Jul 26, 2026, Tacoma Mall (400 E 56TH ST). Case #2620700857 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>2621001325</t>
-        </is>
-      </c>
-      <c r="E216" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>S UNION AVE &amp; S 47TH ST</t>
-        </is>
-      </c>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr"/>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>Motor vehicle theft on Jul 28, 2026, Tacoma Mall (S UNION AVE &amp; S 47TH ST). Case #2621001325 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>2620700384</t>
-        </is>
-      </c>
-      <c r="E217" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>CENTER ST &amp; S LAWRENCE ST</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 26, 2026, Tacoma Mall (CENTER ST &amp; S LAWRENCE ST). Case #2620700384 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>2620700156</t>
-        </is>
-      </c>
-      <c r="E218" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>1100 BROADWAY</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 26, 2026, Tacoma Mall (1100 BROADWAY). Case #2620700156 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>2621109061</t>
-        </is>
-      </c>
-      <c r="E219" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>2300 YAKIMA CT</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 28, 2026, Tacoma Mall (2300 YAKIMA CT). Case #2621109061 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>2621000233</t>
-        </is>
-      </c>
-      <c r="E220" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>1600 E 32ND ST</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 29, 2026, Tacoma Mall (1600 E 32ND ST). Case #2621000233 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>2621100101</t>
-        </is>
-      </c>
-      <c r="E221" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>Traffic - DUI (Liquor)</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>QUALITY_OF_LIFE</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Traffic - DUI (Liquor)</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>S HOSMER ST &amp; S STEELE ST</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>Traffic - dui (liquor) on Jul 30, 2026, Tacoma Mall (S HOSMER ST &amp; S STEELE ST). Case #2621100101 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>2620700268</t>
-        </is>
-      </c>
-      <c r="E222" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>Assault Aggravated</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>900 PACIFIC AVE</t>
-        </is>
-      </c>
-      <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>Assault aggravated on Jul 26, 2026, Tacoma Mall (900 PACIFIC AVE). Case #2620700268 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>2620702070</t>
-        </is>
-      </c>
-      <c r="E223" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>2700 E D ST</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr"/>
-      <c r="K223" t="inlineStr"/>
-      <c r="L223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>Motor vehicle theft on Jul 26, 2026, Tacoma Mall (2700 E D ST). Case #2620702070 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>2621100925</t>
-        </is>
-      </c>
-      <c r="E224" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Fraud Offenses</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>6400 S L ST</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr"/>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>Fraud on Jul 27, 2026, Tacoma Mall (6400 S L ST). Case #2621100925 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>2621100159</t>
-        </is>
-      </c>
-      <c r="E225" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>3500 PACIFIC AVE</t>
-        </is>
-      </c>
-      <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr"/>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 30, 2026, Tacoma Mall (3500 PACIFIC AVE). Case #2621100159 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>2621001005</t>
-        </is>
-      </c>
-      <c r="E226" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>1900 S 72ND ST</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr"/>
-      <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr"/>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 29, 2026, Tacoma Mall (1900 S 72ND ST). Case #2621001005 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>2621109052</t>
-        </is>
-      </c>
-      <c r="E227" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>4900 32ND ST NE</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
-      <c r="L227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 28, 2026, Tacoma Mall (4900 32ND ST NE). Case #2621109052 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>2621000811</t>
-        </is>
-      </c>
-      <c r="E228" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Fraud Offenses</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>3100 S 45TH ST</t>
-        </is>
-      </c>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="L228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>Fraud on Jul 29, 2026, Tacoma Mall (3100 S 45TH ST). Case #2621000811 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>2620700581</t>
-        </is>
-      </c>
-      <c r="E229" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Injury</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>S 99TH ST &amp; PACIFIC AVE</t>
-        </is>
-      </c>
-      <c r="J229" t="inlineStr"/>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - injury on Jul 26, 2026, Tacoma Mall (S 99TH ST &amp; PACIFIC AVE). Case #2620700581 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>2621102013</t>
-        </is>
-      </c>
-      <c r="E230" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>5400 SOUTH TACOMA WAY</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr"/>
-      <c r="K230" t="inlineStr"/>
-      <c r="L230" t="inlineStr"/>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 30, 2026, Tacoma Mall (5400 SOUTH TACOMA WAY). Case #2621102013 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>2620900401</t>
-        </is>
-      </c>
-      <c r="E231" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>3200 N 27TH ST</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr"/>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>Motor vehicle theft on Jul 28, 2026, Tacoma Mall (3200 N 27TH ST). Case #2620900401 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>2620901923</t>
-        </is>
-      </c>
-      <c r="E232" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>Fraud Offenses</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>6400 S 10TH ST</t>
-        </is>
-      </c>
-      <c r="J232" t="inlineStr"/>
-      <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr"/>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>Fraud on Jul 27, 2026, Tacoma Mall (6400 S 10TH ST). Case #2620901923 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>2621109005</t>
-        </is>
-      </c>
-      <c r="E233" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>5800 N 35TH ST</t>
-        </is>
-      </c>
-      <c r="J233" t="inlineStr"/>
-      <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr"/>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (5800 N 35TH ST). Case #2621109005 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>2620701616</t>
-        </is>
-      </c>
-      <c r="E234" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>Assault Aggravated</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>N PEARL ST &amp; N 44TH ST</t>
-        </is>
-      </c>
-      <c r="J234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>Assault aggravated on Jul 26, 2026, Tacoma Mall (N PEARL ST &amp; N 44TH ST). Case #2620701616 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>2620700320</t>
-        </is>
-      </c>
-      <c r="E235" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>Traffic - DUI (Drugs)</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>QUALITY_OF_LIFE</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>Traffic - DUI (Drugs)</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>3700 PACIFIC AVE</t>
-        </is>
-      </c>
-      <c r="J235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>Traffic - dui (drugs) on Jul 26, 2026, Tacoma Mall (3700 PACIFIC AVE). Case #2620700320 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>2620809022</t>
-        </is>
-      </c>
-      <c r="E236" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>4300 CENTER ST</t>
-        </is>
-      </c>
-      <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 27, 2026, Tacoma Mall (4300 CENTER ST). Case #2620809022 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>2620802455</t>
-        </is>
-      </c>
-      <c r="E237" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>Traffic - DUI (Liquor)</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>QUALITY_OF_LIFE</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>Traffic - DUI (Liquor)</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>S 4TH ST &amp; S STADIUM WAY</t>
-        </is>
-      </c>
-      <c r="J237" t="inlineStr"/>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>Traffic - dui (liquor) on Jul 27, 2026, Tacoma Mall (S 4TH ST &amp; S STADIUM WAY). Case #2620802455 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>2621101760</t>
-        </is>
-      </c>
-      <c r="E238" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>1200 S 56TH ST</t>
-        </is>
-      </c>
-      <c r="J238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 30, 2026, Tacoma Mall (1200 S 56TH ST). Case #2621101760 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>2620801516</t>
-        </is>
-      </c>
-      <c r="E239" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>400 S I ST</t>
-        </is>
-      </c>
-      <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 27, 2026, Tacoma Mall (400 S I ST). Case #2620801516 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>2621000630</t>
-        </is>
-      </c>
-      <c r="E240" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr">
-        <is>
-          <t>5100 N 26TH ST</t>
-        </is>
-      </c>
-      <c r="J240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 29, 2026, Tacoma Mall (5100 N 26TH ST). Case #2621000630 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>2621100265</t>
-        </is>
-      </c>
-      <c r="E241" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>Assault Aggravated</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t>2000 6TH AVE</t>
-        </is>
-      </c>
-      <c r="J241" t="inlineStr"/>
-      <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>Assault aggravated on Jul 30, 2026, Tacoma Mall (2000 6TH AVE). Case #2621100265 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>2620800399</t>
-        </is>
-      </c>
-      <c r="E242" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>4800 S M ST</t>
-        </is>
-      </c>
-      <c r="J242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>Motor vehicle theft on Jul 26, 2026, Tacoma Mall (4800 S M ST). Case #2620800399 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>2620902259</t>
-        </is>
-      </c>
-      <c r="E243" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>5800 N 33RD ST</t>
-        </is>
-      </c>
-      <c r="J243" t="inlineStr"/>
-      <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 26, 2026, Tacoma Mall (5800 N 33RD ST). Case #2620902259 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>2620901027</t>
-        </is>
-      </c>
-      <c r="E244" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>8000 S D ST</t>
-        </is>
-      </c>
-      <c r="J244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
-      <c r="L244" t="inlineStr"/>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 28, 2026, Tacoma Mall (8000 S D ST). Case #2620901027 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>2621000212</t>
-        </is>
-      </c>
-      <c r="E245" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I245" t="inlineStr">
-        <is>
-          <t>1200 E 72ND ST</t>
-        </is>
-      </c>
-      <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
-      <c r="L245" t="inlineStr"/>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 28, 2026, Tacoma Mall (1200 E 72ND ST). Case #2621000212 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>2620900849</t>
-        </is>
-      </c>
-      <c r="E246" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>3500 S AINSWORTH AVE</t>
-        </is>
-      </c>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 28, 2026, Tacoma Mall (3500 S AINSWORTH AVE). Case #2620900849 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>2620701211</t>
-        </is>
-      </c>
-      <c r="E247" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t>1400 YAKIMA AVE</t>
-        </is>
-      </c>
-      <c r="J247" t="inlineStr"/>
-      <c r="K247" t="inlineStr"/>
-      <c r="L247" t="inlineStr"/>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 26, 2026, Tacoma Mall (1400 YAKIMA AVE). Case #2620701211 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>2621001592</t>
-        </is>
-      </c>
-      <c r="E248" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t>4000 S TYLER ST</t>
-        </is>
-      </c>
-      <c r="J248" t="inlineStr"/>
-      <c r="K248" t="inlineStr"/>
-      <c r="L248" t="inlineStr"/>
-      <c r="M248" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 29, 2026, Tacoma Mall (4000 S TYLER ST). Case #2621001592 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>2620701587</t>
-        </is>
-      </c>
-      <c r="E249" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>Burglary</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>Burglary/Breaking &amp; Entering</t>
-        </is>
-      </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t>7400 ORCHARD ST W</t>
-        </is>
-      </c>
-      <c r="J249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>Burglary on Jul 26, 2026, Tacoma Mall (7400 ORCHARD ST W). Case #2620701587 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>2620700804</t>
-        </is>
-      </c>
-      <c r="E250" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>PACIFIC AVE &amp; S 99TH ST</t>
-        </is>
-      </c>
-      <c r="J250" t="inlineStr"/>
-      <c r="K250" t="inlineStr"/>
-      <c r="L250" t="inlineStr"/>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>Motor vehicle theft on Jul 26, 2026, Tacoma Mall (PACIFIC AVE &amp; S 99TH ST). Case #2620700804 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>2621000176</t>
-        </is>
-      </c>
-      <c r="E251" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>Traffic - DUI (Liquor)</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>QUALITY_OF_LIFE</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>Traffic - DUI (Liquor)</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>S 60TH ST &amp; SOUTH TACOMA WAY</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr"/>
-      <c r="K251" t="inlineStr"/>
-      <c r="L251" t="inlineStr"/>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>Traffic - dui (liquor) on Jul 29, 2026, Tacoma Mall (S 60TH ST &amp; SOUTH TACOMA WAY). Case #2621000176 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>2620809026</t>
-        </is>
-      </c>
-      <c r="E252" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I252" t="inlineStr">
-        <is>
-          <t>3200 S MASON AVE</t>
-        </is>
-      </c>
-      <c r="J252" t="inlineStr"/>
-      <c r="K252" t="inlineStr"/>
-      <c r="L252" t="inlineStr"/>
-      <c r="M252" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (3200 S MASON AVE). Case #2620809026 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>2621101033</t>
-        </is>
-      </c>
-      <c r="E253" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I253" t="inlineStr">
-        <is>
-          <t>2300 YAKIMA CT</t>
-        </is>
-      </c>
-      <c r="J253" t="inlineStr"/>
-      <c r="K253" t="inlineStr"/>
-      <c r="L253" t="inlineStr"/>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 29, 2026, Tacoma Mall (2300 YAKIMA CT). Case #2621101033 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>2620801035</t>
-        </is>
-      </c>
-      <c r="E254" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>S PEARL ST &amp; S 12TH ST</t>
-        </is>
-      </c>
-      <c r="J254" t="inlineStr"/>
-      <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr"/>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 27, 2026, Tacoma Mall (S PEARL ST &amp; S 12TH ST). Case #2620801035 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>2620801833</t>
-        </is>
-      </c>
-      <c r="E255" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>900 MARKET ST</t>
-        </is>
-      </c>
-      <c r="J255" t="inlineStr"/>
-      <c r="K255" t="inlineStr"/>
-      <c r="L255" t="inlineStr"/>
-      <c r="M255" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 27, 2026, Tacoma Mall (900 MARKET ST). Case #2620801833 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>2620801416</t>
-        </is>
-      </c>
-      <c r="E256" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>2100 N 30TH ST</t>
-        </is>
-      </c>
-      <c r="J256" t="inlineStr"/>
-      <c r="K256" t="inlineStr"/>
-      <c r="L256" t="inlineStr"/>
-      <c r="M256" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 27, 2026, Tacoma Mall (2100 N 30TH ST). Case #2620801416 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>2621109024</t>
-        </is>
-      </c>
-      <c r="E257" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t>1100 S HIGHLAND AVE</t>
-        </is>
-      </c>
-      <c r="J257" t="inlineStr"/>
-      <c r="K257" t="inlineStr"/>
-      <c r="L257" t="inlineStr"/>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 28, 2026, Tacoma Mall (1100 S HIGHLAND AVE). Case #2621109024 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>2620802228</t>
-        </is>
-      </c>
-      <c r="E258" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Theft</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>EARNEST S BRAZILL ST &amp; MARTIN LUTHER KING JR WAY</t>
-        </is>
-      </c>
-      <c r="J258" t="inlineStr"/>
-      <c r="K258" t="inlineStr"/>
-      <c r="L258" t="inlineStr"/>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>Motor vehicle theft on Jul 27, 2026, Tacoma Mall (EARNEST S BRAZILL ST &amp; MARTIN LUTHER KING JR WAY). Case #2620802228 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>2620809021</t>
-        </is>
-      </c>
-      <c r="E259" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t>3700 N 8TH ST</t>
-        </is>
-      </c>
-      <c r="J259" t="inlineStr"/>
-      <c r="K259" t="inlineStr"/>
-      <c r="L259" t="inlineStr"/>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 26, 2026, Tacoma Mall (3700 N 8TH ST). Case #2620809021 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>2620701921</t>
-        </is>
-      </c>
-      <c r="E260" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>Weapon Law Violation</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>Weapon Law Violations</t>
-        </is>
-      </c>
-      <c r="I260" t="inlineStr">
-        <is>
-          <t>400 E DIVISION LN</t>
-        </is>
-      </c>
-      <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>Weapon law violation on Jul 26, 2026, Tacoma Mall (400 E DIVISION LN). Case #2620701921 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>2620702008</t>
-        </is>
-      </c>
-      <c r="E261" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>S 10TH ST &amp; S JUNETT ST</t>
-        </is>
-      </c>
-      <c r="J261" t="inlineStr"/>
-      <c r="K261" t="inlineStr"/>
-      <c r="L261" t="inlineStr"/>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 26, 2026, Tacoma Mall (S 10TH ST &amp; S JUNETT ST). Case #2620702008 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>2620700660</t>
-        </is>
-      </c>
-      <c r="E262" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>Assault Aggravated</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>800 E 25TH ST</t>
-        </is>
-      </c>
-      <c r="J262" t="inlineStr"/>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr"/>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t>Assault aggravated on Jul 26, 2026, Tacoma Mall (800 E 25TH ST). Case #2620700660 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>2621001973</t>
-        </is>
-      </c>
-      <c r="E263" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>1900 S UNION AVE</t>
-        </is>
-      </c>
-      <c r="J263" t="inlineStr"/>
-      <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr"/>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 29, 2026, Tacoma Mall (1900 S UNION AVE). Case #2621001973 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>2620802008</t>
-        </is>
-      </c>
-      <c r="E264" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>Assault Aggravated</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>5500 6TH AVE</t>
-        </is>
-      </c>
-      <c r="J264" t="inlineStr"/>
-      <c r="K264" t="inlineStr"/>
-      <c r="L264" t="inlineStr"/>
-      <c r="M264" t="inlineStr">
-        <is>
-          <t>Assault aggravated on Jul 27, 2026, Tacoma Mall (5500 6TH AVE). Case #2620802008 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>2621102344</t>
-        </is>
-      </c>
-      <c r="E265" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>S 74TH ST &amp; SOUTH TACOMA WAY</t>
-        </is>
-      </c>
-      <c r="J265" t="inlineStr"/>
-      <c r="K265" t="inlineStr"/>
-      <c r="L265" t="inlineStr"/>
-      <c r="M265" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 30, 2026, Tacoma Mall (S 74TH ST &amp; SOUTH TACOMA WAY). Case #2621102344 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>2620900726</t>
-        </is>
-      </c>
-      <c r="E266" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I266" t="inlineStr">
-        <is>
-          <t>3600 6TH AVE</t>
-        </is>
-      </c>
-      <c r="J266" t="inlineStr"/>
-      <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr"/>
-      <c r="M266" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 28, 2026, Tacoma Mall (3600 6TH AVE). Case #2620900726 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>2621109009</t>
-        </is>
-      </c>
-      <c r="E267" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>3800 N PEARL ST</t>
-        </is>
-      </c>
-      <c r="J267" t="inlineStr"/>
-      <c r="K267" t="inlineStr"/>
-      <c r="L267" t="inlineStr"/>
-      <c r="M267" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (3800 N PEARL ST). Case #2621109009 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>2621001310</t>
-        </is>
-      </c>
-      <c r="E268" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>Assault Aggravated</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>600 N JACKSON AVE</t>
-        </is>
-      </c>
-      <c r="J268" t="inlineStr"/>
-      <c r="K268" t="inlineStr"/>
-      <c r="L268" t="inlineStr"/>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>Assault aggravated on Jul 29, 2026, Tacoma Mall (600 N JACKSON AVE). Case #2621001310 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>2620701678</t>
-        </is>
-      </c>
-      <c r="E269" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>4000 RUSTON WAY</t>
-        </is>
-      </c>
-      <c r="J269" t="inlineStr"/>
-      <c r="K269" t="inlineStr"/>
-      <c r="L269" t="inlineStr"/>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 26, 2026, Tacoma Mall (4000 RUSTON WAY). Case #2620701678 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>2621101218</t>
-        </is>
-      </c>
-      <c r="E270" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>8000 S HOSMER ST</t>
-        </is>
-      </c>
-      <c r="J270" t="inlineStr"/>
-      <c r="K270" t="inlineStr"/>
-      <c r="L270" t="inlineStr"/>
-      <c r="M270" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 30, 2026, Tacoma Mall (8000 S HOSMER ST). Case #2621101218 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>2621109023</t>
-        </is>
-      </c>
-      <c r="E271" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>1500 S FIFE ST</t>
-        </is>
-      </c>
-      <c r="J271" t="inlineStr"/>
-      <c r="K271" t="inlineStr"/>
-      <c r="L271" t="inlineStr"/>
-      <c r="M271" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 28, 2026, Tacoma Mall (1500 S FIFE ST). Case #2621109023 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>2621109045</t>
-        </is>
-      </c>
-      <c r="E272" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>1900 E D ST</t>
-        </is>
-      </c>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 28, 2026, Tacoma Mall (1900 E D ST). Case #2621109045 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>2620801831</t>
-        </is>
-      </c>
-      <c r="E273" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>S 62ND ST &amp; S GOVE ST</t>
-        </is>
-      </c>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 27, 2026, Tacoma Mall (S 62ND ST &amp; S GOVE ST). Case #2620801831 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>2621109055</t>
-        </is>
-      </c>
-      <c r="E274" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>2100 S SHERIDAN AVE</t>
-        </is>
-      </c>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 28, 2026, Tacoma Mall (2100 S SHERIDAN AVE). Case #2621109055 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>2620700616</t>
-        </is>
-      </c>
-      <c r="E275" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>800 S PEARL ST</t>
-        </is>
-      </c>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 26, 2026, Tacoma Mall (800 S PEARL ST). Case #2620700616 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>2621102065</t>
-        </is>
-      </c>
-      <c r="E276" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>1900 S UNION AVE</t>
-        </is>
-      </c>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 30, 2026, Tacoma Mall (1900 S UNION AVE). Case #2621102065 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>2621001907</t>
-        </is>
-      </c>
-      <c r="E277" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>Drug/Narcotics Violations</t>
-        </is>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>QUALITY_OF_LIFE</t>
-        </is>
-      </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>Drug/Narcotics Violations</t>
-        </is>
-      </c>
-      <c r="I277" t="inlineStr">
-        <is>
-          <t>200 E 64TH ST</t>
-        </is>
-      </c>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="inlineStr">
-        <is>
-          <t>Drug/narcotics violations on Jul 29, 2026, Tacoma Mall (200 E 64TH ST). Case #2621001907 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>2621000152</t>
-        </is>
-      </c>
-      <c r="E278" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>3500 S 45TH ST</t>
-        </is>
-      </c>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 29, 2026, Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>2621109062</t>
-        </is>
-      </c>
-      <c r="E279" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>2300 YAKIMA CT</t>
-        </is>
-      </c>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 26, 2026, Tacoma Mall (2300 YAKIMA CT). Case #2621109062 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>2620701081</t>
-        </is>
-      </c>
-      <c r="E280" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>Counterfeiting/Forgery</t>
-        </is>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>Counterfeiting/Forgery</t>
-        </is>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>3200 S 23RD ST</t>
-        </is>
-      </c>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="inlineStr">
-        <is>
-          <t>Counterfeiting/forgery on Jul 26, 2026, Tacoma Mall (3200 S 23RD ST). Case #2620701081 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>2621101834</t>
-        </is>
-      </c>
-      <c r="E281" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>19TH ST W &amp; MILDRED ST W</t>
-        </is>
-      </c>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 30, 2026, Tacoma Mall (19TH ST W &amp; MILDRED ST W). Case #2621101834 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>2620701703</t>
-        </is>
-      </c>
-      <c r="E282" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>Drug/Narcotics Violations</t>
-        </is>
-      </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>QUALITY_OF_LIFE</t>
-        </is>
-      </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>Drug/Narcotics Violations</t>
-        </is>
-      </c>
-      <c r="I282" t="inlineStr">
-        <is>
-          <t>S 74TH ST &amp; SOUTH TACOMA WAY</t>
-        </is>
-      </c>
-      <c r="J282" t="inlineStr"/>
-      <c r="K282" t="inlineStr"/>
-      <c r="L282" t="inlineStr"/>
-      <c r="M282" t="inlineStr">
-        <is>
-          <t>Drug/narcotics violations on Jul 26, 2026, Tacoma Mall (S 74TH ST &amp; SOUTH TACOMA WAY). Case #2620701703 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>2621002172</t>
-        </is>
-      </c>
-      <c r="E283" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Fatal</t>
-        </is>
-      </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Fatal</t>
-        </is>
-      </c>
-      <c r="I283" t="inlineStr">
-        <is>
-          <t>500 N SCHUSTER PKWY</t>
-        </is>
-      </c>
-      <c r="J283" t="inlineStr"/>
-      <c r="K283" t="inlineStr"/>
-      <c r="L283" t="inlineStr"/>
-      <c r="M283" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - fatal on Jul 29, 2026, Tacoma Mall (500 N SCHUSTER PKWY). Case #2621002172 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>2620701263</t>
-        </is>
-      </c>
-      <c r="E284" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I284" t="inlineStr">
-        <is>
-          <t>400 S I ST</t>
-        </is>
-      </c>
-      <c r="J284" t="inlineStr"/>
-      <c r="K284" t="inlineStr"/>
-      <c r="L284" t="inlineStr"/>
-      <c r="M284" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 26, 2026, Tacoma Mall (400 S I ST). Case #2620701263 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>2620901147</t>
-        </is>
-      </c>
-      <c r="E285" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>Extortion (Blackmail)</t>
-        </is>
-      </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>Extortion (Blackmail)</t>
-        </is>
-      </c>
-      <c r="I285" t="inlineStr">
-        <is>
-          <t>5400 S STEELE ST</t>
-        </is>
-      </c>
-      <c r="J285" t="inlineStr"/>
-      <c r="K285" t="inlineStr"/>
-      <c r="L285" t="inlineStr"/>
-      <c r="M285" t="inlineStr">
-        <is>
-          <t>Extortion (blackmail) on Jul 28, 2026, Tacoma Mall (5400 S STEELE ST). Case #2620901147 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>2621109015</t>
-        </is>
-      </c>
-      <c r="E286" s="3" t="n">
-        <v>46231</v>
-      </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I286" t="inlineStr">
-        <is>
-          <t>3200 S 23RD ST</t>
-        </is>
-      </c>
-      <c r="J286" t="inlineStr"/>
-      <c r="K286" t="inlineStr"/>
-      <c r="L286" t="inlineStr"/>
-      <c r="M286" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 28, 2026, Tacoma Mall (3200 S 23RD ST). Case #2621109015 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>2621000914</t>
-        </is>
-      </c>
-      <c r="E287" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I287" t="inlineStr">
-        <is>
-          <t>1600 MARTIN LUTHER KING JR WAY</t>
-        </is>
-      </c>
-      <c r="J287" t="inlineStr"/>
-      <c r="K287" t="inlineStr"/>
-      <c r="L287" t="inlineStr"/>
-      <c r="M287" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 29, 2026, Tacoma Mall (1600 MARTIN LUTHER KING JR WAY). Case #2621000914 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>2620800264</t>
-        </is>
-      </c>
-      <c r="E288" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>Assault Simple</t>
-        </is>
-      </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I288" t="inlineStr">
-        <is>
-          <t>3500 S 56TH ST</t>
-        </is>
-      </c>
-      <c r="J288" t="inlineStr"/>
-      <c r="K288" t="inlineStr"/>
-      <c r="L288" t="inlineStr"/>
-      <c r="M288" t="inlineStr">
-        <is>
-          <t>Assault simple on Jul 27, 2026, Tacoma Mall (3500 S 56TH ST). Case #2620800264 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>2621109047</t>
-        </is>
-      </c>
-      <c r="E289" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H289" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I289" t="inlineStr">
-        <is>
-          <t>800 S 15TH ST</t>
-        </is>
-      </c>
-      <c r="J289" t="inlineStr"/>
-      <c r="K289" t="inlineStr"/>
-      <c r="L289" t="inlineStr"/>
-      <c r="M289" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 26, 2026, Tacoma Mall (800 S 15TH ST). Case #2621109047 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>2621109006</t>
-        </is>
-      </c>
-      <c r="E290" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I290" t="inlineStr">
-        <is>
-          <t>3300 S 23RD ST</t>
-        </is>
-      </c>
-      <c r="J290" t="inlineStr"/>
-      <c r="K290" t="inlineStr"/>
-      <c r="L290" t="inlineStr"/>
-      <c r="M290" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (3300 S 23RD ST). Case #2621109006 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>2620809033</t>
-        </is>
-      </c>
-      <c r="E291" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H291" t="inlineStr">
-        <is>
-          <t>Destruction/Damage/Vandalism</t>
-        </is>
-      </c>
-      <c r="I291" t="inlineStr">
-        <is>
-          <t>8600 S PARK AVE</t>
-        </is>
-      </c>
-      <c r="J291" t="inlineStr"/>
-      <c r="K291" t="inlineStr"/>
-      <c r="L291" t="inlineStr"/>
-      <c r="M291" t="inlineStr">
-        <is>
-          <t>Destruction/damage/vandalism on Jul 26, 2026, Tacoma Mall (8600 S PARK AVE). Case #2620809033 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>2620900833</t>
-        </is>
-      </c>
-      <c r="E292" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I292" t="inlineStr">
-        <is>
-          <t>2300 S G ST</t>
-        </is>
-      </c>
-      <c r="J292" t="inlineStr"/>
-      <c r="K292" t="inlineStr"/>
-      <c r="L292" t="inlineStr"/>
-      <c r="M292" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (2300 S G ST). Case #2620900833 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>2621109025</t>
-        </is>
-      </c>
-      <c r="E293" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>Larceny Theft</t>
-        </is>
-      </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t>Larceny/Theft Offenses</t>
-        </is>
-      </c>
-      <c r="I293" t="inlineStr">
-        <is>
-          <t>2300 WESTRIDGE AVE W</t>
-        </is>
-      </c>
-      <c r="J293" t="inlineStr"/>
-      <c r="K293" t="inlineStr"/>
-      <c r="L293" t="inlineStr"/>
-      <c r="M293" t="inlineStr">
-        <is>
-          <t>Larceny theft on Jul 27, 2026, Tacoma Mall (2300 WESTRIDGE AVE W). Case #2621109025 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>2621100025</t>
-        </is>
-      </c>
-      <c r="E294" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>Assault Aggravated</t>
-        </is>
-      </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t>2500 PACIFIC AVE</t>
-        </is>
-      </c>
-      <c r="J294" t="inlineStr"/>
-      <c r="K294" t="inlineStr"/>
-      <c r="L294" t="inlineStr"/>
-      <c r="M294" t="inlineStr">
-        <is>
-          <t>Assault aggravated on Jul 29, 2026, Tacoma Mall (2500 PACIFIC AVE). Case #2621100025 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>2620801622</t>
-        </is>
-      </c>
-      <c r="E295" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I295" t="inlineStr">
-        <is>
-          <t>S 9TH ST &amp; S ADAMS ST</t>
-        </is>
-      </c>
-      <c r="J295" t="inlineStr"/>
-      <c r="K295" t="inlineStr"/>
-      <c r="L295" t="inlineStr"/>
-      <c r="M295" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 27, 2026, Tacoma Mall (S 9TH ST &amp; S ADAMS ST). Case #2620801622 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>2621101599</t>
-        </is>
-      </c>
-      <c r="E296" s="3" t="n">
-        <v>46233</v>
-      </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I296" t="inlineStr">
-        <is>
-          <t>2600 CENTER ST</t>
-        </is>
-      </c>
-      <c r="J296" t="inlineStr"/>
-      <c r="K296" t="inlineStr"/>
-      <c r="L296" t="inlineStr"/>
-      <c r="M296" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 30, 2026, Tacoma Mall (2600 CENTER ST). Case #2621101599 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>2620700255</t>
-        </is>
-      </c>
-      <c r="E297" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>Assault Aggravated</t>
-        </is>
-      </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
-      <c r="I297" t="inlineStr">
-        <is>
-          <t>700 ST HELENS AVE</t>
-        </is>
-      </c>
-      <c r="J297" t="inlineStr"/>
-      <c r="K297" t="inlineStr"/>
-      <c r="L297" t="inlineStr"/>
-      <c r="M297" t="inlineStr">
-        <is>
-          <t>Assault aggravated on Jul 26, 2026, Tacoma Mall (700 ST HELENS AVE). Case #2620700255 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>2620701640</t>
-        </is>
-      </c>
-      <c r="E298" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t>Traffic Accident/Collision - Non Fatal - Non Injury</t>
-        </is>
-      </c>
-      <c r="I298" t="inlineStr">
-        <is>
-          <t>4000 RUSTON WAY</t>
-        </is>
-      </c>
-      <c r="J298" t="inlineStr"/>
-      <c r="K298" t="inlineStr"/>
-      <c r="L298" t="inlineStr"/>
-      <c r="M298" t="inlineStr">
-        <is>
-          <t>Traffic accident/collision - non fatal - non injury on Jul 26, 2026, Tacoma Mall (4000 RUSTON WAY). Case #2620701640 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>TACOMAMALL</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>Tacoma Mall</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>2621000769</t>
-        </is>
-      </c>
-      <c r="E299" s="3" t="n">
-        <v>46232</v>
-      </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>Extortion (Blackmail)</t>
-        </is>
-      </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t>Extortion (Blackmail)</t>
-        </is>
-      </c>
-      <c r="I299" t="inlineStr">
-        <is>
-          <t>5800 S PUGET SOUND AVE</t>
-        </is>
-      </c>
-      <c r="J299" t="inlineStr"/>
-      <c r="K299" t="inlineStr"/>
-      <c r="L299" t="inlineStr"/>
-      <c r="M299" t="inlineStr">
-        <is>
-          <t>Extortion (blackmail) on Jul 29, 2026, Tacoma Mall (5800 S PUGET SOUND AVE). Case #2621000769 (use for a records request — full narratives are not published in open data).</t>
+          <t>Extortion (blackmail) on Jul 28, 2026, 1083 m from Tacoma Mall (5400 S STEELE ST). Case #2620901147 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M299"/>
+  <autoFilter ref="A1:M161"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19392,7 +12212,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 04:19:08.436322+00:00</t>
+          <t>2026-08-01 04:21:05.180533+00:00</t>
         </is>
       </c>
     </row>
@@ -19424,7 +12244,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 04:19:08.436322+00:00</t>
+          <t>2026-07-25 04:21:05.180533+00:00</t>
         </is>
       </c>
     </row>
@@ -19435,7 +12255,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>298</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7">
@@ -19445,7 +12265,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">

--- a/reports/2026-08-01/blotter_report.xlsx
+++ b/reports/2026-08-01/blotter_report.xlsx
@@ -13,10 +13,10 @@
     <sheet name="Run Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$161</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$285</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,10 +443,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="57" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -747,17 +747,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>CLEARFORK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>The Shops at Clearfork</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2126 Abbott Martin Road, Nashville, TN 37215</t>
+          <t>5188 Monahans Avenue Fort Worth TX 76109</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -780,8 +780,12 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>1086.4</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>46228.59375</v>
+      </c>
       <c r="L7" t="b">
         <v>0</v>
       </c>
@@ -789,17 +793,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5085 Westheimer Houston TX 77056</t>
+          <t>5000 Empire Mall Sioux Falls SD 57106</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -808,25 +812,25 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>57</v>
+        <v>123</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="J8" t="n">
-        <v>163.5</v>
+        <v>315.5</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>46233</v>
+        <v>46234.24527777778</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
@@ -835,17 +839,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INTLPLAZA</t>
+          <t>GREENHILLS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>International Plaza</t>
+          <t>The Mall at Green Hills</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
+          <t>2126 Abbott Martin Road, Nashville, TN 37215</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -854,13 +858,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -868,12 +872,8 @@
       <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="n">
-        <v>1534.5</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>46232.16666666666</v>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="b">
         <v>0</v>
       </c>
@@ -881,41 +881,45 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LENOX</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lenox Square</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>5085 Westheimer Houston TX 77056</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
+        <v>57</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>163.5</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>46233</v>
+      </c>
       <c r="L10" t="b">
         <v>0</v>
       </c>
@@ -923,17 +927,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>INTLPLAZA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>International Plaza</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>401 Northeast Northgate Way Seattle WA 98125</t>
+          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -942,25 +946,25 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>14</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>145.2</v>
+        <v>1534.5</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>46233.28194444445</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
@@ -969,22 +973,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>LENOX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Lenox Square</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>433 Opry Mills Drive Nashville TN 37214</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1011,17 +1015,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>MALLATMILLENIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>The Mall at Millenia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4400 Sharon Road Charlotte NC 28211</t>
+          <t>4200 Conroy Road, Orlando, FL 32839</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1030,26 +1034,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>178.9</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>46232.16666666666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="b">
         <v>0</v>
       </c>
@@ -1057,17 +1057,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4502 South Steele Street Tacoma WA 98409</t>
+          <t>401 Northeast Northgate Way Seattle WA 98125</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1076,25 +1076,25 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>471.3</v>
+        <v>145.2</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>46233</v>
+        <v>46233.28194444445</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
@@ -1103,22 +1103,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>THEDOMAIN</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Domain</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>11410 Century Oaks Terrace Austin TX 78758</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>433 Opry Mills Drive Nashville TN 37214</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1145,17 +1145,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7700 East Kellogg Wichita KS 67207</t>
+          <t>4400 Sharon Road Charlotte NC 28211</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1164,32 +1164,208 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="n">
-        <v>23</v>
-      </c>
       <c r="J16" t="n">
-        <v>288.9</v>
+        <v>178.9</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>46233.7625</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="L16" t="b">
         <v>0</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TACOMAMALL</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tacoma Mall</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4502 South Steele Street Tacoma WA 98409</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>9</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>471.3</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="L17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>THEDOMAIN</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>The Domain</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>11410 Century Oaks Terrace Austin TX 78758</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>7700 East Kellogg Wichita KS 67207</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>33</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>23</v>
+      </c>
+      <c r="J19" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>46233.7625</v>
+      </c>
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>UNIVPARKVILLAGE</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>University Park Village</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1612 South University Drive Fort Worth TX 76107</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L16"/>
+  <autoFilter ref="A1:L20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1205,7 +1381,7 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
@@ -1520,30 +1696,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DP2026411044131300</t>
+          <t>CFS26-161839</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46229.1125</v>
+        <v>46231.00275462963</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>assault-simple</t>
+          <t>Assault P3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1553,56 +1729,56 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>other-crimes-against-persons</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3200 BLOCK E CHERRY CREEK S DR</t>
+          <t>W 47TH ST &amp; S WESTPORT AVE</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>39.71130989687384</v>
+        <v>43.50940131405472</v>
       </c>
       <c r="K6" t="n">
-        <v>-104.9490029653731</v>
+        <v>-96.76746570282992</v>
       </c>
       <c r="L6" t="n">
-        <v>696.3</v>
+        <v>678.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault p3 on Jul 28, 2026, 678 m from Empire Mall (W 47TH ST &amp; S WESTPORT AVE). Case #CFS26-161839 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20260729-1600-11</t>
+          <t>DP2026411044131300</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46232.16666666666</v>
+        <v>46229.1125</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Simple Assault</t>
+          <t>assault-simple</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1612,56 +1788,56 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>13B</t>
+          <t>other-crimes-against-persons</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4700 PIEDMONT ROW DR</t>
+          <t>3200 BLOCK E CHERRY CREEK S DR</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>35.15196312662653</v>
+        <v>39.71130989687384</v>
       </c>
       <c r="K7" t="n">
-        <v>-80.83980651357408</v>
+        <v>-104.9490029653731</v>
       </c>
       <c r="L7" t="n">
-        <v>850.6</v>
+        <v>696.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 29, 2026, 851 m from Southpark (4700 PIEDMONT ROW DR). Status: Open. Case #20260729-1600-11 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2620701835</t>
+          <t>CFS26-161603</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46229</v>
+        <v>46230.83325231481</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1671,56 +1847,56 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4000 S LAWRENCE ST</t>
+          <t>S WESTPORT AVE &amp; W 41ST ST</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>47.219421</v>
+        <v>43.51485103457241</v>
       </c>
       <c r="K8" t="n">
-        <v>-122.478428</v>
+        <v>-96.76794119445807</v>
       </c>
       <c r="L8" t="n">
-        <v>853.4</v>
+        <v>808.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 26, 2026, 853 m from Tacoma Mall (4000 S LAWRENCE ST). Case #2620701835 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 27, 2026, 809 m from Empire Mall (S WESTPORT AVE &amp; W 41ST ST). Case #CFS26-161603 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>71878728447</t>
+          <t>20260729-1600-11</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46230.4375</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1730,26 +1906,26 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>13B</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>16XX BLOCK OF N 105TH ST</t>
+          <t>4700 PIEDMONT ROW DR</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>47.70504225</v>
+        <v>35.15196312662653</v>
       </c>
       <c r="K9" t="n">
-        <v>-122.338094779232</v>
+        <v>-80.83980651357408</v>
       </c>
       <c r="L9" t="n">
-        <v>938.8</v>
+        <v>850.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 29, 2026, 851 m from Southpark (4700 PIEDMONT ROW DR). Status: Open. Case #20260729-1600-11 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -1771,11 +1947,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2621000152</t>
+          <t>2620701835</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46232</v>
+        <v>46229</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1794,21 +1970,21 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3500 S 45TH ST</t>
+          <t>4000 S LAWRENCE ST</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>47.216421</v>
+        <v>47.219421</v>
       </c>
       <c r="K10" t="n">
-        <v>-122.482428</v>
+        <v>-122.478428</v>
       </c>
       <c r="L10" t="n">
-        <v>1074.3</v>
+        <v>853.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 29, 2026, 1074 m from Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 26, 2026, 853 m from Tacoma Mall (4000 S LAWRENCE ST). Case #2620701835 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -1830,15 +2006,15 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>71894237115</t>
+          <t>71878728447</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46231.20833333334</v>
+        <v>46230.4375</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1853,51 +2029,51 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>16XX BLOCK OF N 105TH ST</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>47.70668788</v>
+        <v>47.70504225</v>
       </c>
       <c r="K11" t="n">
-        <v>-122.311189997702</v>
+        <v>-122.338094779232</v>
       </c>
       <c r="L11" t="n">
-        <v>1145.7</v>
+        <v>938.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>71889871382</t>
+          <t>2621000152</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46231.00625</v>
+        <v>46232</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Simple Assault</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1907,56 +2083,56 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ALL OTHER</t>
+          <t>Assault Offenses</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>3500 S 45TH ST</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>47.70668788</v>
+        <v>47.216421</v>
       </c>
       <c r="K12" t="n">
-        <v>-122.311189997702</v>
+        <v>-122.482428</v>
       </c>
       <c r="L12" t="n">
-        <v>1145.7</v>
+        <v>1074.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 29, 2026, 1074 m from Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>26C142249</t>
+          <t>71894237115</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46230.75</v>
+        <v>46231.20833333334</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BATTERY ABW</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1966,56 +2142,56 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SIM_ASSAULT</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S MISSION RD</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>37.6756469679485</v>
+        <v>47.70668788</v>
       </c>
       <c r="K13" t="n">
-        <v>-97.25850032865422</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L13" t="n">
-        <v>1251.5</v>
+        <v>1145.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>096140526</t>
+          <t>71889871382</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46232</v>
+        <v>46231.00625</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2025,56 +2201,56 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>13A</t>
+          <t>ALL OTHER</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1900-1999 POST OAK PARK DR</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>29.74712522681273</v>
+        <v>47.70668788</v>
       </c>
       <c r="K14" t="n">
-        <v>-95.45374747370188</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L14" t="n">
-        <v>1323.4</v>
+        <v>1145.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 29, 2026, 1323 m from Houston Galleria (1900-1999 POST OAK PARK DR). Case #096140526 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675136         </t>
+          <t>26C142249</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46228.97847222222</v>
+        <v>46230.75</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
+          <t>BATTERY ABW</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2082,54 +2258,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>SIM_ASSAULT</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5XXX S HARDY DR</t>
+          <t>700 BLOCK OF S MISSION RD</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>33.3757495513233</v>
+        <v>37.6756469679485</v>
       </c>
       <c r="K15" t="n">
-        <v>-111.9531832468173</v>
+        <v>-97.25850032865422</v>
       </c>
       <c r="L15" t="n">
-        <v>1345.1</v>
+        <v>1251.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>[13b] assault on Jul 25, 2026, 1345 m from Arizona Mills (5XXX S HARDY DR). Case #TE202675136          (use for a records request — full narratives are not published in open data).</t>
+          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2621102013</t>
+          <t>CFS26-164521</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46233</v>
+        <v>46234.03421296296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2139,351 +2319,347 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5400 SOUTH TACOMA WAY</t>
+          <t>S MARION RD &amp; W 41ST ST</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>47.206421</v>
+        <v>43.51481738299845</v>
       </c>
       <c r="K16" t="n">
-        <v>-122.483428</v>
+        <v>-96.79096028032072</v>
       </c>
       <c r="L16" t="n">
-        <v>1578</v>
+        <v>1322.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 30, 2026, 1578 m from Tacoma Mall (5400 SOUTH TACOMA WAY). Case #2621102013 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 31, 2026, 1322 m from Empire Mall (S MARION RD &amp; W 41ST ST). Case #CFS26-164521 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DP2026415473230300</t>
+          <t>096140526</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46231.47916666666</v>
+        <v>46232</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>larceny</t>
+          <t>13A</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15 S STEELE ST</t>
+          <t>1900-1999 POST OAK PARK DR</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>39.7162154712797</v>
+        <v>29.74712522681273</v>
       </c>
       <c r="K17" t="n">
-        <v>-104.9512928115626</v>
+        <v>-95.45374747370188</v>
       </c>
       <c r="L17" t="n">
-        <v>144.7</v>
+        <v>1323.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 28, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026415473 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 29, 2026, 1323 m from Houston Galleria (1900-1999 POST OAK PARK DR). Case #096140526 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DP2026413358260700</t>
+          <t xml:space="preserve">TE202675136         </t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46230.47013888889</v>
+        <v>46228.97847222222</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>fraud-by-telephone</t>
+          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>white-collar-crime</t>
-        </is>
-      </c>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>15 S STEELE ST</t>
+          <t>5XXX S HARDY DR</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>39.7162154712797</v>
+        <v>33.3757495513233</v>
       </c>
       <c r="K18" t="n">
-        <v>-104.9512928115626</v>
+        <v>-111.9531832468173</v>
       </c>
       <c r="L18" t="n">
-        <v>144.7</v>
+        <v>1345.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Fraud-by-telephone on Jul 27, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026413358 (use for a records request — full narratives are not published in open data).</t>
+          <t>[13b] assault on Jul 25, 2026, 1345 m from Arizona Mills (5XXX S HARDY DR). Case #TE202675136          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>71913162555</t>
+          <t>CFS26-164393</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46232.82986111111</v>
+        <v>46233.93733796296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>47.7086028</v>
+        <v>43.51319846254545</v>
       </c>
       <c r="K19" t="n">
-        <v>-122.324615154453</v>
+        <v>-96.79336119066248</v>
       </c>
       <c r="L19" t="n">
-        <v>145.2</v>
+        <v>1453.4</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 29, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-222878 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 30, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-164393 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>71898889573</t>
+          <t>CFS26-159792</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46231.625</v>
+        <v>46229.12712962963</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Weapons Violations</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>Weapons</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>47.7086028</v>
+        <v>43.51319846254545</v>
       </c>
       <c r="K20" t="n">
-        <v>-122.324615154453</v>
+        <v>-96.79336119066248</v>
       </c>
       <c r="L20" t="n">
-        <v>145.2</v>
+        <v>1453.4</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221387 (use for a records request — full narratives are not published in open data).</t>
+          <t>Weapons violations on Jul 26, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-159792 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>71899277060</t>
+          <t>2621102013</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46231.47569444445</v>
+        <v>46233</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>Assault Offenses</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>5400 SOUTH TACOMA WAY</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>47.7086028</v>
+        <v>47.206421</v>
       </c>
       <c r="K21" t="n">
-        <v>-122.324615154454</v>
+        <v>-122.483428</v>
       </c>
       <c r="L21" t="n">
-        <v>145.2</v>
+        <v>1578</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221174 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 30, 2026, 1578 m from Tacoma Mall (5400 SOUTH TACOMA WAY). Case #2621102013 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Property</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>096475026</t>
+          <t>DP2026415473230300</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46233</v>
+        <v>46231.47916666666</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>theft-shoplift</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2493,56 +2669,56 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>larceny</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5100-5199 ALABAMA ST W</t>
+          <t>15 S STEELE ST</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>29.73799058803365</v>
+        <v>39.7162154712797</v>
       </c>
       <c r="K22" t="n">
-        <v>-95.46478253884783</v>
+        <v>-104.9512928115626</v>
       </c>
       <c r="L22" t="n">
-        <v>163.5</v>
+        <v>144.7</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 30, 2026, 163 m from Houston Galleria (5100-5199 ALABAMA ST W). Case #096475026 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft-shoplift on Jul 28, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026415473 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Property</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>095621926</t>
+          <t>DP2026413358260700</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46231</v>
+        <v>46230.47013888889</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Theft from motor vehicle</t>
+          <t>fraud-by-telephone</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2552,52 +2728,52 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>23F</t>
+          <t>white-collar-crime</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5100-5199 ALABAMA ST W</t>
+          <t>15 S STEELE ST</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>29.73799058803365</v>
+        <v>39.7162154712797</v>
       </c>
       <c r="K23" t="n">
-        <v>-95.46478253884783</v>
+        <v>-104.9512928115626</v>
       </c>
       <c r="L23" t="n">
-        <v>163.5</v>
+        <v>144.7</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Theft from motor vehicle on Jul 28, 2026, 163 m from Houston Galleria (5100-5199 ALABAMA ST W). Case #095621926 (use for a records request — full narratives are not published in open data).</t>
+          <t>Fraud-by-telephone on Jul 27, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026413358 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Property</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>095601426</t>
+          <t>71913162555</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46231</v>
+        <v>46232.82986111111</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2611,52 +2787,52 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5100-5199 ALABAMA ST W</t>
+          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>29.73799058803365</v>
+        <v>47.7086028</v>
       </c>
       <c r="K24" t="n">
-        <v>-95.46478253884783</v>
+        <v>-122.324615154453</v>
       </c>
       <c r="L24" t="n">
-        <v>163.5</v>
+        <v>145.2</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 163 m from Houston Galleria (5100-5199 ALABAMA ST W). Case #095601426 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 29, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-222878 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>20260728-1130-01</t>
+          <t>71898889573</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46231.16666666666</v>
+        <v>46231.625</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2670,52 +2846,52 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>35.15120046375475</v>
+        <v>47.7086028</v>
       </c>
       <c r="K25" t="n">
-        <v>-80.82867375349484</v>
+        <v>-122.324615154453</v>
       </c>
       <c r="L25" t="n">
-        <v>178.9</v>
+        <v>145.2</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1130-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221387 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>20260728-1922-01</t>
+          <t>71899277060</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46231.16666666666</v>
+        <v>46231.47569444445</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2729,26 +2905,26 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>23C</t>
+          <t>PROPERTY CRIME</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4400 SHARON RD</t>
+          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>35.15120046375475</v>
+        <v>47.7086028</v>
       </c>
       <c r="K26" t="n">
-        <v>-80.82867375349484</v>
+        <v>-122.324615154454</v>
       </c>
       <c r="L26" t="n">
-        <v>178.9</v>
+        <v>145.2</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 179 m from Southpark (4400 SHARON RD). Status: Open. Case #20260728-1922-01 (use for a records request — full narratives are not published in open data).</t>
+          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221174 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2764,18 +2940,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M161"/>
+  <dimension ref="A1:M285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="49" customWidth="1" min="8" max="8"/>
-    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="53" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -12173,8 +12349,7324 @@
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>CLEARFORK</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>The Shops at Clearfork</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>CLEARFORK:Fort Worth PD Crime Data</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>260318151</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>46228.59375</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>PC 31.03(E)(3)   Theft prop&gt;=$750&lt;$2500</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>THEFT</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>2500 RIVER PARK DR</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
+        <v>32.70776370720614</v>
+      </c>
+      <c r="K162" t="n">
+        <v>-97.41184118183627</v>
+      </c>
+      <c r="L162" t="n">
+        <v>1086.4</v>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>Pc 31.03(e)(3)   theft prop&gt;=$750&lt;$2500 on Jul 25, 2026, 1086 m from The Shops at Clearfork (2500 RIVER PARK DR). Premises: 20. Case #260318151 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>CFS26-159019</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>46228.31771990741</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Hit &amp; Run</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>S SOLBERG AVE &amp; W CHIPPEWA CIR</t>
+        </is>
+      </c>
+      <c r="J163" t="n">
+        <v>43.50469043243786</v>
+      </c>
+      <c r="K163" t="n">
+        <v>-96.7809382470065</v>
+      </c>
+      <c r="L163" t="n">
+        <v>750.9</v>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>Hit &amp; run on Jul 25, 2026, 751 m from Empire Mall (S SOLBERG AVE &amp; W CHIPPEWA CIR). Case #CFS26-159019 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>CFS26-160102</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>46229.22534722222</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Hit &amp; Run</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>S SHIRLEY AVE &amp; W 41ST ST &amp; W EMPIRE PL</t>
+        </is>
+      </c>
+      <c r="J164" t="n">
+        <v>43.51484546427315</v>
+      </c>
+      <c r="K164" t="n">
+        <v>-96.77443635605863</v>
+      </c>
+      <c r="L164" t="n">
+        <v>515.4</v>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>Hit &amp; run on Jul 26, 2026, 515 m from Empire Mall (S SHIRLEY AVE &amp; W 41ST ST &amp; W EMPIRE PL). Case #CFS26-160102 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>CFS26-159451</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>46228.90921296296</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Injury Accident P2</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>S MARION RD &amp; W 44TH ST</t>
+        </is>
+      </c>
+      <c r="J165" t="n">
+        <v>43.51236607235115</v>
+      </c>
+      <c r="K165" t="n">
+        <v>-96.7909260097226</v>
+      </c>
+      <c r="L165" t="n">
+        <v>1242.3</v>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Injury accident p2 on Jul 25, 2026, 1242 m from Empire Mall (S MARION RD &amp; W 44TH ST). Case #CFS26-159451 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>CFS26-159511</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>46228.96453703703</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Check Wellbeing</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>W EMPIRE PL &amp; W EMPIRE PL &amp; W EMPIRE PL</t>
+        </is>
+      </c>
+      <c r="J166" t="n">
+        <v>43.51307477335324</v>
+      </c>
+      <c r="K166" t="n">
+        <v>-96.7766862668114</v>
+      </c>
+      <c r="L166" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>Check wellbeing on Jul 25, 2026, 316 m from Empire Mall (W EMPIRE PL &amp; W EMPIRE PL &amp; W EMPIRE PL). Case #CFS26-159511 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>CFS26-159454</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>46228.91143518518</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Check Wellbeing</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>S GATEWAY LN &amp; S GATEWAY BLVD</t>
+        </is>
+      </c>
+      <c r="J167" t="n">
+        <v>43.51281290360509</v>
+      </c>
+      <c r="K167" t="n">
+        <v>-96.7832464577892</v>
+      </c>
+      <c r="L167" t="n">
+        <v>662.9</v>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Check wellbeing on Jul 25, 2026, 663 m from Empire Mall (S GATEWAY LN &amp; S GATEWAY BLVD). Case #CFS26-159454 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>CFS26-158981</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>46228.27228009259</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Check Wellbeing</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>S GOLDEN CREEK PL &amp; S WESTPORT AVE</t>
+        </is>
+      </c>
+      <c r="J168" t="n">
+        <v>43.51126427380821</v>
+      </c>
+      <c r="K168" t="n">
+        <v>-96.76791435426648</v>
+      </c>
+      <c r="L168" t="n">
+        <v>643.3</v>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Check wellbeing on Jul 25, 2026, 643 m from Empire Mall (S GOLDEN CREEK PL &amp; S WESTPORT AVE). Case #CFS26-158981 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>CFS26-159792</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>46229.12712962963</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Weapons Violations</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Weapons</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>43.51319846254545</v>
+      </c>
+      <c r="K169" t="n">
+        <v>-96.79336119066248</v>
+      </c>
+      <c r="L169" t="n">
+        <v>1453.4</v>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>Weapons violations on Jul 26, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-159792 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>CFS26-159074</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>46228.47578703704</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Noise Disturbance</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>S MAYFAIR DR &amp; W 38TH ST</t>
+        </is>
+      </c>
+      <c r="J170" t="n">
+        <v>43.51704606425148</v>
+      </c>
+      <c r="K170" t="n">
+        <v>-96.78170076795006</v>
+      </c>
+      <c r="L170" t="n">
+        <v>887.7</v>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>Noise disturbance on Jul 25, 2026, 888 m from Empire Mall (S MAYFAIR DR &amp; W 38TH ST). Case #CFS26-159074 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>CFS26-159523</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>46228.97929398148</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Larceny</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Theft</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>S CAROLYN AVE &amp; W 38TH ST</t>
+        </is>
+      </c>
+      <c r="J171" t="n">
+        <v>43.51777966412532</v>
+      </c>
+      <c r="K171" t="n">
+        <v>-96.77850989695047</v>
+      </c>
+      <c r="L171" t="n">
+        <v>858.8</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>Larceny on Jul 25, 2026, 859 m from Empire Mall (S CAROLYN AVE &amp; W 38TH ST). Case #CFS26-159523 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>CFS26-158990</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>46228.28158564815</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Protection Order Violation</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>I 29 RAMP &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J172" t="n">
+        <v>43.51483782368534</v>
+      </c>
+      <c r="K172" t="n">
+        <v>-96.77936822734073</v>
+      </c>
+      <c r="L172" t="n">
+        <v>580.2</v>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>Protection order violation on Jul 25, 2026, 580 m from Empire Mall (I 29 RAMP &amp; W 41ST ST). Case #CFS26-158990 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>CFS26-159352</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="n">
+        <v>46228.84677083333</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Stalled Vehicle</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J173" t="n">
+        <v>43.51480707435041</v>
+      </c>
+      <c r="K173" t="n">
+        <v>-96.77110350565825</v>
+      </c>
+      <c r="L173" t="n">
+        <v>626.1</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>Stalled vehicle on Jul 25, 2026, 626 m from Empire Mall (S LOUISE AVE &amp; W 41ST ST). Case #CFS26-159352 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>CFS26-159379</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>46228.86439814815</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Man Down</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>S SHIRLEY AVE &amp; W 41ST ST &amp; W EMPIRE PL</t>
+        </is>
+      </c>
+      <c r="J174" t="n">
+        <v>43.51484546427315</v>
+      </c>
+      <c r="K174" t="n">
+        <v>-96.77443635605863</v>
+      </c>
+      <c r="L174" t="n">
+        <v>515.4</v>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>Man down on Jul 25, 2026, 515 m from Empire Mall (S SHIRLEY AVE &amp; W 41ST ST &amp; W EMPIRE PL). Case #CFS26-159379 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>CFS26-159552</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>46229.0159375</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Liquor Law Violation</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Drugs/Alcohol</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>S SOLBERG AVE &amp; W VALHALLA BLVD</t>
+        </is>
+      </c>
+      <c r="J175" t="n">
+        <v>43.50623018207514</v>
+      </c>
+      <c r="K175" t="n">
+        <v>-96.77990236625163</v>
+      </c>
+      <c r="L175" t="n">
+        <v>562.7</v>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>Liquor law violation on Jul 26, 2026, 563 m from Empire Mall (S SOLBERG AVE &amp; W VALHALLA BLVD). Case #CFS26-159552 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>CFS26-160038</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>46229.18260416666</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Suspicious Subject</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
+        </is>
+      </c>
+      <c r="J176" t="n">
+        <v>43.51319846254545</v>
+      </c>
+      <c r="K176" t="n">
+        <v>-96.79336119066248</v>
+      </c>
+      <c r="L176" t="n">
+        <v>1453.4</v>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>Suspicious subject on Jul 26, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-160038 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>CFS26-159326</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="n">
+        <v>46228.81621527778</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>S KIWANIS AVE &amp; W 49TH ST</t>
+        </is>
+      </c>
+      <c r="J177" t="n">
+        <v>43.50841031406458</v>
+      </c>
+      <c r="K177" t="n">
+        <v>-96.75802133136874</v>
+      </c>
+      <c r="L177" t="n">
+        <v>1447.9</v>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>Accident on Jul 25, 2026, 1448 m from Empire Mall (S KIWANIS AVE &amp; W 49TH ST). Case #CFS26-159326 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>CFS26-159498</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="n">
+        <v>46228.95116898148</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Shoplifting</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Theft</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>S WESTPORT AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J178" t="n">
+        <v>43.51485103457241</v>
+      </c>
+      <c r="K178" t="n">
+        <v>-96.76794119445807</v>
+      </c>
+      <c r="L178" t="n">
+        <v>808.9</v>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 25, 2026, 809 m from Empire Mall (S WESTPORT AVE &amp; W 41ST ST). Case #CFS26-159498 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>CFS26-160064</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="n">
+        <v>46229.19341435185</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Loitering</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>W 41ST ST &amp; W EMPIRE PL</t>
+        </is>
+      </c>
+      <c r="J179" t="n">
+        <v>43.51484419416143</v>
+      </c>
+      <c r="K179" t="n">
+        <v>-96.77669360636062</v>
+      </c>
+      <c r="L179" t="n">
+        <v>509.1</v>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>Loitering on Jul 26, 2026, 509 m from Empire Mall (W 41ST ST &amp; W EMPIRE PL). Case #CFS26-160064 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>CFS26-159225</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>46228.71445601852</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>S MARION RD &amp; W 44TH ST</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v>43.51236607235115</v>
+      </c>
+      <c r="K180" t="n">
+        <v>-96.7909260097226</v>
+      </c>
+      <c r="L180" t="n">
+        <v>1242.3</v>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 25, 2026, 1242 m from Empire Mall (S MARION RD &amp; W 44TH ST). Case #CFS26-159225 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>CFS26-159217</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="n">
+        <v>46228.70810185185</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>S MARION RD &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J181" t="n">
+        <v>43.51481738299845</v>
+      </c>
+      <c r="K181" t="n">
+        <v>-96.79096028032072</v>
+      </c>
+      <c r="L181" t="n">
+        <v>1322.4</v>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 25, 2026, 1322 m from Empire Mall (S MARION RD &amp; W 41ST ST). Case #CFS26-159217 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>CFS26-159290</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="n">
+        <v>46228.79174768519</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>W 41ST ST &amp; W EMPIRE PL</t>
+        </is>
+      </c>
+      <c r="J182" t="n">
+        <v>43.51484419416143</v>
+      </c>
+      <c r="K182" t="n">
+        <v>-96.77669360636062</v>
+      </c>
+      <c r="L182" t="n">
+        <v>509.1</v>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 25, 2026, 509 m from Empire Mall (W 41ST ST &amp; W EMPIRE PL). Case #CFS26-159290 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>CFS26-159410</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="n">
+        <v>46228.88324074074</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
+        </is>
+      </c>
+      <c r="J183" t="n">
+        <v>43.51319846254545</v>
+      </c>
+      <c r="K183" t="n">
+        <v>-96.79336119066248</v>
+      </c>
+      <c r="L183" t="n">
+        <v>1453.4</v>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 25, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-159410 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>CFS26-159608</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="n">
+        <v>46229.05333333334</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
+        </is>
+      </c>
+      <c r="J184" t="n">
+        <v>43.51319846254545</v>
+      </c>
+      <c r="K184" t="n">
+        <v>-96.79336119066248</v>
+      </c>
+      <c r="L184" t="n">
+        <v>1453.4</v>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 26, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-159608 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>CFS26-159063</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="n">
+        <v>46228.43545138889</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Family Dispute</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>S GATEWAY BLVD &amp; S TERRY AVE</t>
+        </is>
+      </c>
+      <c r="J185" t="n">
+        <v>43.51220536263347</v>
+      </c>
+      <c r="K185" t="n">
+        <v>-96.7859525684798</v>
+      </c>
+      <c r="L185" t="n">
+        <v>846.7</v>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>Family dispute on Jul 25, 2026, 847 m from Empire Mall (S GATEWAY BLVD &amp; S TERRY AVE). Case #CFS26-159063 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>CFS26-159009</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="n">
+        <v>46228.30119212963</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Intoxicated Subject</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Drugs/Alcohol</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>S GATEWAY LN &amp; S GATEWAY BLVD</t>
+        </is>
+      </c>
+      <c r="J186" t="n">
+        <v>43.51281290360509</v>
+      </c>
+      <c r="K186" t="n">
+        <v>-96.7832464577892</v>
+      </c>
+      <c r="L186" t="n">
+        <v>662.9</v>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>Intoxicated subject on Jul 25, 2026, 663 m from Empire Mall (S GATEWAY LN &amp; S GATEWAY BLVD). Case #CFS26-159009 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>CFS26-160089</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="n">
+        <v>46229.21228009259</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Traffic Hazard</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>S TERRY AVE &amp; W 38TH ST</t>
+        </is>
+      </c>
+      <c r="J187" t="n">
+        <v>43.51704515371051</v>
+      </c>
+      <c r="K187" t="n">
+        <v>-96.78631726005253</v>
+      </c>
+      <c r="L187" t="n">
+        <v>1132.2</v>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>Traffic hazard on Jul 26, 2026, 1132 m from Empire Mall (S TERRY AVE &amp; W 38TH ST). Case #CFS26-160089 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>CFS26-159914</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="n">
+        <v>46229.14921296296</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Traffic Hazard</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>W 35TH ST &amp; W THURMAN DR</t>
+        </is>
+      </c>
+      <c r="J188" t="n">
+        <v>43.51960763359122</v>
+      </c>
+      <c r="K188" t="n">
+        <v>-96.7878127897683</v>
+      </c>
+      <c r="L188" t="n">
+        <v>1417.4</v>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>Traffic hazard on Jul 26, 2026, 1417 m from Empire Mall (W 35TH ST &amp; W THURMAN DR). Case #CFS26-159914 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>CFS26-160048</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="n">
+        <v>46229.18739583333</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Child Custody Dispute</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>PARK SERVICE RD &amp; S OXBOW AVE &amp; W 53RD ST</t>
+        </is>
+      </c>
+      <c r="J189" t="n">
+        <v>43.50489764292522</v>
+      </c>
+      <c r="K189" t="n">
+        <v>-96.76589799216201</v>
+      </c>
+      <c r="L189" t="n">
+        <v>999.1</v>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>Child custody dispute on Jul 26, 2026, 999 m from Empire Mall (PARK SERVICE RD &amp; S OXBOW AVE &amp; W 53RD ST). Case #CFS26-160048 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>CFS26-159581</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="n">
+        <v>46229.03685185185</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Reckless Driver</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W 49TH ST</t>
+        </is>
+      </c>
+      <c r="J190" t="n">
+        <v>43.50759974361088</v>
+      </c>
+      <c r="K190" t="n">
+        <v>-96.77103685388698</v>
+      </c>
+      <c r="L190" t="n">
+        <v>487.4</v>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>Reckless driver on Jul 26, 2026, 487 m from Empire Mall (S LOUISE AVE &amp; W 49TH ST). Case #CFS26-159581 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>CFS26-160716</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="n">
+        <v>46229.90825231482</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Check Wellbeing</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>S TECHNOPOLIS DR &amp; S NEVADA AVE &amp; W 57TH ST</t>
+        </is>
+      </c>
+      <c r="J191" t="n">
+        <v>43.5003427218675</v>
+      </c>
+      <c r="K191" t="n">
+        <v>-96.77458843355284</v>
+      </c>
+      <c r="L191" t="n">
+        <v>1112.9</v>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>Check wellbeing on Jul 26, 2026, 1113 m from Empire Mall (S TECHNOPOLIS DR &amp; S NEVADA AVE &amp; W 57TH ST). Case #CFS26-160716 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>CFS26-160779</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="n">
+        <v>46229.96965277778</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Public Assist</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>S TENNIS LN &amp; W 55TH ST</t>
+        </is>
+      </c>
+      <c r="J192" t="n">
+        <v>43.50200894302012</v>
+      </c>
+      <c r="K192" t="n">
+        <v>-96.76842992223241</v>
+      </c>
+      <c r="L192" t="n">
+        <v>1097.5</v>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>Public assist on Jul 26, 2026, 1097 m from Empire Mall (S TENNIS LN &amp; W 55TH ST). Case #CFS26-160779 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>CFS26-160342</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="n">
+        <v>46229.62094907407</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Suspicious Activity</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>I 29 &amp; I 29 RAMP</t>
+        </is>
+      </c>
+      <c r="J193" t="n">
+        <v>43.52358822521935</v>
+      </c>
+      <c r="K193" t="n">
+        <v>-96.78066507908444</v>
+      </c>
+      <c r="L193" t="n">
+        <v>1527.6</v>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>Suspicious activity on Jul 26, 2026, 1528 m from Empire Mall (I 29 &amp; I 29 RAMP). Case #CFS26-160342 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>CFS26-160736</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="n">
+        <v>46229.93079861111</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Suspicious Subject</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>I 29 &amp; I 29 RAMP</t>
+        </is>
+      </c>
+      <c r="J194" t="n">
+        <v>43.52358822521935</v>
+      </c>
+      <c r="K194" t="n">
+        <v>-96.78066507908444</v>
+      </c>
+      <c r="L194" t="n">
+        <v>1527.6</v>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>Suspicious subject on Jul 26, 2026, 1528 m from Empire Mall (I 29 &amp; I 29 RAMP). Case #CFS26-160736 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>CFS26-160505</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="n">
+        <v>46229.75098379629</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Family Dispute</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
+        </is>
+      </c>
+      <c r="J195" t="n">
+        <v>43.51319846254545</v>
+      </c>
+      <c r="K195" t="n">
+        <v>-96.79336119066248</v>
+      </c>
+      <c r="L195" t="n">
+        <v>1453.4</v>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>Family dispute on Jul 26, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-160505 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>CFS26-160511</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="n">
+        <v>46229.75467592593</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Family Dispute</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
+        </is>
+      </c>
+      <c r="J196" t="n">
+        <v>43.51319846254545</v>
+      </c>
+      <c r="K196" t="n">
+        <v>-96.79336119066248</v>
+      </c>
+      <c r="L196" t="n">
+        <v>1453.4</v>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>Family dispute on Jul 26, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-160511 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>CFS26-160288</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="n">
+        <v>46229.56722222222</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Check Security</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>S WESTPORT AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J197" t="n">
+        <v>43.51485103457241</v>
+      </c>
+      <c r="K197" t="n">
+        <v>-96.76794119445807</v>
+      </c>
+      <c r="L197" t="n">
+        <v>808.9</v>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>Check security on Jul 26, 2026, 809 m from Empire Mall (S WESTPORT AVE &amp; W 41ST ST). Case #CFS26-160288 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>CFS26-160875</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="n">
+        <v>46230.0453587963</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Family Dispute</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>S GATEWAY LN &amp; S GATEWAY BLVD</t>
+        </is>
+      </c>
+      <c r="J198" t="n">
+        <v>43.51281290360509</v>
+      </c>
+      <c r="K198" t="n">
+        <v>-96.7832464577892</v>
+      </c>
+      <c r="L198" t="n">
+        <v>662.9</v>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>Family dispute on Jul 27, 2026, 663 m from Empire Mall (S GATEWAY LN &amp; S GATEWAY BLVD). Case #CFS26-160875 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>CFS26-160633</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="n">
+        <v>46229.85539351852</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Suspicious Vehicle</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>S GRAND CIR &amp; W 59TH ST</t>
+        </is>
+      </c>
+      <c r="J199" t="n">
+        <v>43.49854222157047</v>
+      </c>
+      <c r="K199" t="n">
+        <v>-96.7727172028677</v>
+      </c>
+      <c r="L199" t="n">
+        <v>1332.1</v>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>Suspicious vehicle on Jul 26, 2026, 1332 m from Empire Mall (S GRAND CIR &amp; W 59TH ST). Case #CFS26-160633 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>CFS26-160199</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="n">
+        <v>46229.36001157408</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Family Dispute</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>S GOLDEN CREEK PL &amp; S WESTPORT AVE</t>
+        </is>
+      </c>
+      <c r="J200" t="n">
+        <v>43.51126427380821</v>
+      </c>
+      <c r="K200" t="n">
+        <v>-96.76791435426648</v>
+      </c>
+      <c r="L200" t="n">
+        <v>643.3</v>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>Family dispute on Jul 26, 2026, 643 m from Empire Mall (S GOLDEN CREEK PL &amp; S WESTPORT AVE). Case #CFS26-160199 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>CFS26-160492</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="n">
+        <v>46229.74104166667</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Reckless Driver</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>S MEADOW AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J201" t="n">
+        <v>43.51483469375145</v>
+      </c>
+      <c r="K201" t="n">
+        <v>-96.78305741794478</v>
+      </c>
+      <c r="L201" t="n">
+        <v>772.5</v>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>Reckless driver on Jul 26, 2026, 773 m from Empire Mall (S MEADOW AVE &amp; W 41ST ST). Case #CFS26-160492 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>CFS26-161737</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="n">
+        <v>46230.9250925926</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Larceny</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Theft</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>S MARION RD &amp; W 44TH ST</t>
+        </is>
+      </c>
+      <c r="J202" t="n">
+        <v>43.51236607235115</v>
+      </c>
+      <c r="K202" t="n">
+        <v>-96.7909260097226</v>
+      </c>
+      <c r="L202" t="n">
+        <v>1242.3</v>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>Larceny on Jul 27, 2026, 1242 m from Empire Mall (S MARION RD &amp; W 44TH ST). Case #CFS26-161737 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>CFS26-161544</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="n">
+        <v>46230.79988425926</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Larceny</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Theft</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>S TERRY AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J203" t="n">
+        <v>43.51482816316226</v>
+      </c>
+      <c r="K203" t="n">
+        <v>-96.78634901931601</v>
+      </c>
+      <c r="L203" t="n">
+        <v>988.9</v>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>Larceny on Jul 27, 2026, 989 m from Empire Mall (S TERRY AVE &amp; W 41ST ST). Case #CFS26-161544 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>CFS26-161498</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="n">
+        <v>46230.76065972223</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Hit &amp; Run</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>S SHIRLEY AVE &amp; W 38TH ST</t>
+        </is>
+      </c>
+      <c r="J204" t="n">
+        <v>43.51777845484326</v>
+      </c>
+      <c r="K204" t="n">
+        <v>-96.77437979679537</v>
+      </c>
+      <c r="L204" t="n">
+        <v>837.7</v>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>Hit &amp; run on Jul 27, 2026, 838 m from Empire Mall (S SHIRLEY AVE &amp; W 38TH ST). Case #CFS26-161498 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>CFS26-161973</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="n">
+        <v>46231.13439814815</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>S ARIZONA DR &amp; S ROLLING GREEN AVE</t>
+        </is>
+      </c>
+      <c r="J205" t="n">
+        <v>43.49801125109279</v>
+      </c>
+      <c r="K205" t="n">
+        <v>-96.77724004489316</v>
+      </c>
+      <c r="L205" t="n">
+        <v>1373.1</v>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 28, 2026, 1373 m from Empire Mall (S ARIZONA DR &amp; S ROLLING GREEN AVE). Case #CFS26-161973 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>CFS26-161649</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="n">
+        <v>46230.8672337963</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Injury Accident P3</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J206" t="n">
+        <v>43.51480707435041</v>
+      </c>
+      <c r="K206" t="n">
+        <v>-96.77110350565825</v>
+      </c>
+      <c r="L206" t="n">
+        <v>626.1</v>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>Injury accident p3 on Jul 27, 2026, 626 m from Empire Mall (S LOUISE AVE &amp; W 41ST ST). Case #CFS26-161649 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>CFS26-161603</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="n">
+        <v>46230.83325231481</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Assault</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Assault</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>S WESTPORT AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J207" t="n">
+        <v>43.51485103457241</v>
+      </c>
+      <c r="K207" t="n">
+        <v>-96.76794119445807</v>
+      </c>
+      <c r="L207" t="n">
+        <v>808.9</v>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>Assault on Jul 27, 2026, 809 m from Empire Mall (S WESTPORT AVE &amp; W 41ST ST). Case #CFS26-161603 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>CFS26-161727</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="n">
+        <v>46230.92016203704</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Family Dispute</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>S GOLDEN CREEK PL &amp; S WESTPORT AVE</t>
+        </is>
+      </c>
+      <c r="J208" t="n">
+        <v>43.51126427380821</v>
+      </c>
+      <c r="K208" t="n">
+        <v>-96.76791435426648</v>
+      </c>
+      <c r="L208" t="n">
+        <v>643.3</v>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>Family dispute on Jul 27, 2026, 643 m from Empire Mall (S GOLDEN CREEK PL &amp; S WESTPORT AVE). Case #CFS26-161727 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>CFS26-161531</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="n">
+        <v>46230.79126157407</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Family Dispute</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>W ROYAL ST &amp; W COTTAGE TRL</t>
+        </is>
+      </c>
+      <c r="J209" t="n">
+        <v>43.50235624174632</v>
+      </c>
+      <c r="K209" t="n">
+        <v>-96.78809349742139</v>
+      </c>
+      <c r="L209" t="n">
+        <v>1330</v>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>Family dispute on Jul 27, 2026, 1330 m from Empire Mall (W ROYAL ST &amp; W COTTAGE TRL). Case #CFS26-161531 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>CFS26-161096</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="n">
+        <v>46230.29450231481</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Family Dispute</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>S MADELYN AVE &amp; W 40TH ST</t>
+        </is>
+      </c>
+      <c r="J210" t="n">
+        <v>43.51538966329255</v>
+      </c>
+      <c r="K210" t="n">
+        <v>-96.78441883878321</v>
+      </c>
+      <c r="L210" t="n">
+        <v>896.4</v>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>Family dispute on Jul 27, 2026, 896 m from Empire Mall (S MADELYN AVE &amp; W 40TH ST). Case #CFS26-161096 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>CFS26-161785</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="n">
+        <v>46230.95932870371</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Child Custody Dispute</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>S TECHNOLOGY DR &amp; W VALHALLA BLVD</t>
+        </is>
+      </c>
+      <c r="J211" t="n">
+        <v>43.50660996268574</v>
+      </c>
+      <c r="K211" t="n">
+        <v>-96.77575207566703</v>
+      </c>
+      <c r="L211" t="n">
+        <v>411.9</v>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>Child custody dispute on Jul 27, 2026, 412 m from Empire Mall (S TECHNOLOGY DR &amp; W VALHALLA BLVD). Case #CFS26-161785 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>CFS26-161660</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="n">
+        <v>46230.87556712963</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Child Custody Dispute</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>W ST JAMES CIR &amp; W ST JAMES DR &amp; W VICTORIA DR</t>
+        </is>
+      </c>
+      <c r="J212" t="n">
+        <v>43.50653056252924</v>
+      </c>
+      <c r="K212" t="n">
+        <v>-96.78533738843498</v>
+      </c>
+      <c r="L212" t="n">
+        <v>877.9</v>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>Child custody dispute on Jul 27, 2026, 878 m from Empire Mall (W ST JAMES CIR &amp; W ST JAMES DR &amp; W VICTORIA DR). Case #CFS26-161660 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>CFS26-162016</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="n">
+        <v>46231.18817129629</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Noise Disturbance</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
+        </is>
+      </c>
+      <c r="J213" t="n">
+        <v>43.51319846254545</v>
+      </c>
+      <c r="K213" t="n">
+        <v>-96.79336119066248</v>
+      </c>
+      <c r="L213" t="n">
+        <v>1453.4</v>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>Noise disturbance on Jul 28, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-162016 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>CFS26-161878</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="n">
+        <v>46231.03434027778</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Noise Disturbance</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
+        </is>
+      </c>
+      <c r="J214" t="n">
+        <v>43.51319846254545</v>
+      </c>
+      <c r="K214" t="n">
+        <v>-96.79336119066248</v>
+      </c>
+      <c r="L214" t="n">
+        <v>1453.4</v>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>Noise disturbance on Jul 28, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-161878 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>CFS26-161852</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="n">
+        <v>46231.01834490741</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Customer Dispute</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>S TECHLINK CIR &amp; S TECHNOLOGY DR &amp; W 53RD ST</t>
+        </is>
+      </c>
+      <c r="J215" t="n">
+        <v>43.504010843024</v>
+      </c>
+      <c r="K215" t="n">
+        <v>-96.77367136420254</v>
+      </c>
+      <c r="L215" t="n">
+        <v>721.3</v>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>Customer dispute on Jul 28, 2026, 721 m from Empire Mall (S TECHLINK CIR &amp; S TECHNOLOGY DR &amp; W 53RD ST). Case #CFS26-161852 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>CFS26-161905</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="n">
+        <v>46231.05966435185</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Suspicious Vehicle</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>S GATEWAY LN &amp; S GATEWAY BLVD</t>
+        </is>
+      </c>
+      <c r="J216" t="n">
+        <v>43.51281290360509</v>
+      </c>
+      <c r="K216" t="n">
+        <v>-96.7832464577892</v>
+      </c>
+      <c r="L216" t="n">
+        <v>662.9</v>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>Suspicious vehicle on Jul 28, 2026, 663 m from Empire Mall (S GATEWAY LN &amp; S GATEWAY BLVD). Case #CFS26-161905 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>CFS26-161839</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="n">
+        <v>46231.00275462963</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Assault P3</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Assault</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>W 47TH ST &amp; S WESTPORT AVE</t>
+        </is>
+      </c>
+      <c r="J217" t="n">
+        <v>43.50940131405472</v>
+      </c>
+      <c r="K217" t="n">
+        <v>-96.76746570282992</v>
+      </c>
+      <c r="L217" t="n">
+        <v>678.4</v>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>Assault p3 on Jul 28, 2026, 678 m from Empire Mall (W 47TH ST &amp; S WESTPORT AVE). Case #CFS26-161839 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>CFS26-161599</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="n">
+        <v>46230.83100694444</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Public Assist</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>S MARION RD &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J218" t="n">
+        <v>43.51481738299845</v>
+      </c>
+      <c r="K218" t="n">
+        <v>-96.79096028032072</v>
+      </c>
+      <c r="L218" t="n">
+        <v>1322.4</v>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>Public assist on Jul 27, 2026, 1322 m from Empire Mall (S MARION RD &amp; W 41ST ST). Case #CFS26-161599 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>CFS26-161152</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="n">
+        <v>46230.51356481481</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Burglary Alarm</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Burglary</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W KENTUCKY PL</t>
+        </is>
+      </c>
+      <c r="J219" t="n">
+        <v>43.51601560446141</v>
+      </c>
+      <c r="K219" t="n">
+        <v>-96.77111077469445</v>
+      </c>
+      <c r="L219" t="n">
+        <v>737.5</v>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>Burglary alarm on Jul 27, 2026, 737 m from Empire Mall (S LOUISE AVE &amp; W KENTUCKY PL). Case #CFS26-161152 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>CFS26-161167</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="n">
+        <v>46230.53862268518</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Burglary Alarm</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Burglary</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>PARK SERVICE RD &amp; PARK SERVICE RD &amp; PARK SERVICE RD</t>
+        </is>
+      </c>
+      <c r="J220" t="n">
+        <v>43.5063858340459</v>
+      </c>
+      <c r="K220" t="n">
+        <v>-96.7618683317002</v>
+      </c>
+      <c r="L220" t="n">
+        <v>1204.2</v>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>Burglary alarm on Jul 27, 2026, 1204 m from Empire Mall (PARK SERVICE RD &amp; PARK SERVICE RD &amp; PARK SERVICE RD). Case #CFS26-161167 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>CFS26-161121</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="n">
+        <v>46230.38135416667</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Standby To Pick Up Property</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>S GATEWAY LN &amp; S GATEWAY BLVD</t>
+        </is>
+      </c>
+      <c r="J221" t="n">
+        <v>43.51281290360509</v>
+      </c>
+      <c r="K221" t="n">
+        <v>-96.7832464577892</v>
+      </c>
+      <c r="L221" t="n">
+        <v>662.9</v>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>Standby to pick up property on Jul 27, 2026, 663 m from Empire Mall (S GATEWAY LN &amp; S GATEWAY BLVD). Case #CFS26-161121 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>CFS26-161158</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="n">
+        <v>46230.52385416667</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Traffic Control</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>S OXBOW AVE &amp; W 57TH ST</t>
+        </is>
+      </c>
+      <c r="J222" t="n">
+        <v>43.50034566225657</v>
+      </c>
+      <c r="K222" t="n">
+        <v>-96.76586341187955</v>
+      </c>
+      <c r="L222" t="n">
+        <v>1367</v>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>Traffic control on Jul 27, 2026, 1367 m from Empire Mall (S OXBOW AVE &amp; W 57TH ST). Case #CFS26-161158 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>CFS26-161654</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="n">
+        <v>46230.86913194445</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Traffic Control</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>S KIWANIS AVE &amp; W 49TH ST</t>
+        </is>
+      </c>
+      <c r="J223" t="n">
+        <v>43.50841031406458</v>
+      </c>
+      <c r="K223" t="n">
+        <v>-96.75802133136874</v>
+      </c>
+      <c r="L223" t="n">
+        <v>1447.9</v>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>Traffic control on Jul 27, 2026, 1448 m from Empire Mall (S KIWANIS AVE &amp; W 49TH ST). Case #CFS26-161654 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>CFS26-161756</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="n">
+        <v>46230.94164351852</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Reckless Driver</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>S MARION RD &amp; W COTTAGE TRL</t>
+        </is>
+      </c>
+      <c r="J224" t="n">
+        <v>43.501643341026</v>
+      </c>
+      <c r="K224" t="n">
+        <v>-96.79084966877771</v>
+      </c>
+      <c r="L224" t="n">
+        <v>1551.2</v>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>Reckless driver on Jul 27, 2026, 1551 m from Empire Mall (S MARION RD &amp; W COTTAGE TRL). Case #CFS26-161756 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>CFS26-161851</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="n">
+        <v>46231.01702546296</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>W 41ST ST &amp; W EMPIRE PL</t>
+        </is>
+      </c>
+      <c r="J225" t="n">
+        <v>43.51484419416143</v>
+      </c>
+      <c r="K225" t="n">
+        <v>-96.77669360636062</v>
+      </c>
+      <c r="L225" t="n">
+        <v>509.1</v>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>Accident on Jul 28, 2026, 509 m from Empire Mall (W 41ST ST &amp; W EMPIRE PL). Case #CFS26-161851 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>CFS26-162280</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="n">
+        <v>46231.63763888889</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Man Down</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W KENTUCKY PL</t>
+        </is>
+      </c>
+      <c r="J226" t="n">
+        <v>43.51601560446141</v>
+      </c>
+      <c r="K226" t="n">
+        <v>-96.77111077469445</v>
+      </c>
+      <c r="L226" t="n">
+        <v>737.5</v>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>Man down on Jul 28, 2026, 737 m from Empire Mall (S LOUISE AVE &amp; W KENTUCKY PL). Case #CFS26-162280 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>CFS26-162861</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="n">
+        <v>46232.11736111111</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Man Down</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>W ST JAMES CIR &amp; W ST JAMES DR &amp; W VICTORIA DR</t>
+        </is>
+      </c>
+      <c r="J227" t="n">
+        <v>43.50653056252924</v>
+      </c>
+      <c r="K227" t="n">
+        <v>-96.78533738843498</v>
+      </c>
+      <c r="L227" t="n">
+        <v>877.9</v>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>Man down on Jul 29, 2026, 878 m from Empire Mall (W ST JAMES CIR &amp; W ST JAMES DR &amp; W VICTORIA DR). Case #CFS26-162861 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>CFS26-162901</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="n">
+        <v>46232.16435185185</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Abandoned Vehicles</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>S TERRY AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J228" t="n">
+        <v>43.51482816316226</v>
+      </c>
+      <c r="K228" t="n">
+        <v>-96.78634901931601</v>
+      </c>
+      <c r="L228" t="n">
+        <v>988.9</v>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>Abandoned vehicles on Jul 29, 2026, 989 m from Empire Mall (S TERRY AVE &amp; W 41ST ST). Case #CFS26-162901 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>CFS26-162736</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="n">
+        <v>46231.9900462963</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Hit &amp; Run</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>S MARION RD &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J229" t="n">
+        <v>43.51481738299845</v>
+      </c>
+      <c r="K229" t="n">
+        <v>-96.79096028032072</v>
+      </c>
+      <c r="L229" t="n">
+        <v>1322.4</v>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>Hit &amp; run on Jul 28, 2026, 1322 m from Empire Mall (S MARION RD &amp; W 41ST ST). Case #CFS26-162736 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>CFS26-162920</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="n">
+        <v>46232.18731481482</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>W CHIPPEWA PL &amp; W CHIPPEWA CIR</t>
+        </is>
+      </c>
+      <c r="J230" t="n">
+        <v>43.50415214191399</v>
+      </c>
+      <c r="K230" t="n">
+        <v>-96.78340912722523</v>
+      </c>
+      <c r="L230" t="n">
+        <v>920.7</v>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 29, 2026, 921 m from Empire Mall (W CHIPPEWA PL &amp; W CHIPPEWA CIR). Case #CFS26-162920 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>CFS26-162449</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="n">
+        <v>46231.78344907407</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Burglary</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Burglary</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>S MADELYN AVE &amp; W 40TH ST</t>
+        </is>
+      </c>
+      <c r="J231" t="n">
+        <v>43.51538966329255</v>
+      </c>
+      <c r="K231" t="n">
+        <v>-96.78441883878321</v>
+      </c>
+      <c r="L231" t="n">
+        <v>896.4</v>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>Burglary on Jul 28, 2026, 896 m from Empire Mall (S MADELYN AVE &amp; W 40TH ST). Case #CFS26-162449 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>CFS26-162689</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="n">
+        <v>46231.94540509259</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Check Wellbeing</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>S GATEWAY LN &amp; S GATEWAY BLVD</t>
+        </is>
+      </c>
+      <c r="J232" t="n">
+        <v>43.51281290360509</v>
+      </c>
+      <c r="K232" t="n">
+        <v>-96.7832464577892</v>
+      </c>
+      <c r="L232" t="n">
+        <v>662.9</v>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>Check wellbeing on Jul 28, 2026, 663 m from Empire Mall (S GATEWAY LN &amp; S GATEWAY BLVD). Case #CFS26-162689 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>CFS26-162800</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="n">
+        <v>46232.04965277778</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Check Wellbeing</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>S KIWANIS AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J233" t="n">
+        <v>43.5148316053277</v>
+      </c>
+      <c r="K233" t="n">
+        <v>-96.76108050220627</v>
+      </c>
+      <c r="L233" t="n">
+        <v>1287.6</v>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>Check wellbeing on Jul 29, 2026, 1288 m from Empire Mall (S KIWANIS AVE &amp; W 41ST ST). Case #CFS26-162800 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>CFS26-162937</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="n">
+        <v>46232.20616898148</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Suspicious Vehicle</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>S TECHNOPOLIS DR &amp; S NEVADA AVE &amp; W 57TH ST</t>
+        </is>
+      </c>
+      <c r="J234" t="n">
+        <v>43.5003427218675</v>
+      </c>
+      <c r="K234" t="n">
+        <v>-96.77458843355284</v>
+      </c>
+      <c r="L234" t="n">
+        <v>1112.9</v>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>Suspicious vehicle on Jul 29, 2026, 1113 m from Empire Mall (S TECHNOPOLIS DR &amp; S NEVADA AVE &amp; W 57TH ST). Case #CFS26-162937 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>CFS26-162812</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="n">
+        <v>46232.06216435185</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Neighbor Dispute</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>S BAHA AVE &amp; W 55TH ST</t>
+        </is>
+      </c>
+      <c r="J235" t="n">
+        <v>43.50196079221673</v>
+      </c>
+      <c r="K235" t="n">
+        <v>-96.76954183339693</v>
+      </c>
+      <c r="L235" t="n">
+        <v>1056.4</v>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>Neighbor dispute on Jul 29, 2026, 1056 m from Empire Mall (S BAHA AVE &amp; W 55TH ST). Case #CFS26-162812 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>CFS26-162458</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="n">
+        <v>46231.788125</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Family Dispute</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>S TECHNOPOLIS DR &amp; W 53RD ST</t>
+        </is>
+      </c>
+      <c r="J236" t="n">
+        <v>43.50364750236709</v>
+      </c>
+      <c r="K236" t="n">
+        <v>-96.7753931947034</v>
+      </c>
+      <c r="L236" t="n">
+        <v>742</v>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>Family dispute on Jul 28, 2026, 742 m from Empire Mall (S TECHNOPOLIS DR &amp; W 53RD ST). Case #CFS26-162458 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>CFS26-162677</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="n">
+        <v>46231.93572916667</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Intoxicated Subject</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Drugs/Alcohol</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W KENTUCKY PL</t>
+        </is>
+      </c>
+      <c r="J237" t="n">
+        <v>43.51601560446141</v>
+      </c>
+      <c r="K237" t="n">
+        <v>-96.77111077469445</v>
+      </c>
+      <c r="L237" t="n">
+        <v>737.5</v>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>Intoxicated subject on Jul 28, 2026, 737 m from Empire Mall (S LOUISE AVE &amp; W KENTUCKY PL). Case #CFS26-162677 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>CFS26-162423</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="n">
+        <v>46231.75775462963</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>S SHIRLEY AVE &amp; W SWENSON DR</t>
+        </is>
+      </c>
+      <c r="J238" t="n">
+        <v>43.52370102520238</v>
+      </c>
+      <c r="K238" t="n">
+        <v>-96.77699254769605</v>
+      </c>
+      <c r="L238" t="n">
+        <v>1491.8</v>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>Accident on Jul 28, 2026, 1492 m from Empire Mall (S SHIRLEY AVE &amp; W SWENSON DR). Case #CFS26-162423 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>CFS26-162896</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="n">
+        <v>46232.15972222222</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Stolen Vehicle</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Stolen Vehicles</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>S TECHNOPOLIS DR &amp; W 53RD ST</t>
+        </is>
+      </c>
+      <c r="J239" t="n">
+        <v>43.50364750236709</v>
+      </c>
+      <c r="K239" t="n">
+        <v>-96.7753931947034</v>
+      </c>
+      <c r="L239" t="n">
+        <v>742</v>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>Stolen vehicle on Jul 29, 2026, 742 m from Empire Mall (S TECHNOPOLIS DR &amp; W 53RD ST). Case #CFS26-162896 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>CFS26-162910</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="n">
+        <v>46232.17696759259</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Customer Dispute</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>S CAROLYN AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J240" t="n">
+        <v>43.51484141407607</v>
+      </c>
+      <c r="K240" t="n">
+        <v>-96.77853636764556</v>
+      </c>
+      <c r="L240" t="n">
+        <v>550.2</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>Customer dispute on Jul 29, 2026, 550 m from Empire Mall (S CAROLYN AVE &amp; W 41ST ST). Case #CFS26-162910 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>CFS26-162629</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="n">
+        <v>46231.90168981482</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W 55TH ST</t>
+        </is>
+      </c>
+      <c r="J241" t="n">
+        <v>43.50195752221772</v>
+      </c>
+      <c r="K241" t="n">
+        <v>-96.77102644399517</v>
+      </c>
+      <c r="L241" t="n">
+        <v>1005.3</v>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>Accident on Jul 28, 2026, 1005 m from Empire Mall (S LOUISE AVE &amp; W 55TH ST). Case #CFS26-162629 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>CFS26-163580</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="n">
+        <v>46232.96297453704</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Protection Order Violation</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>S COTTAGE CIR &amp; W ST JAMES DR</t>
+        </is>
+      </c>
+      <c r="J242" t="n">
+        <v>43.50478034152432</v>
+      </c>
+      <c r="K242" t="n">
+        <v>-96.78663732772262</v>
+      </c>
+      <c r="L242" t="n">
+        <v>1070</v>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>Protection order violation on Jul 29, 2026, 1070 m from Empire Mall (S COTTAGE CIR &amp; W ST JAMES DR). Case #CFS26-163580 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>CFS26-163692</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="n">
+        <v>46233.060625</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Stalled Vehicle</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W 59TH ST</t>
+        </is>
+      </c>
+      <c r="J243" t="n">
+        <v>43.49878851194642</v>
+      </c>
+      <c r="K243" t="n">
+        <v>-96.77094963245196</v>
+      </c>
+      <c r="L243" t="n">
+        <v>1339.6</v>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>Stalled vehicle on Jul 30, 2026, 1340 m from Empire Mall (S LOUISE AVE &amp; W 59TH ST). Case #CFS26-163692 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>CFS26-163539</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="n">
+        <v>46232.93219907407</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Check Wellbeing</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>S CAROLYN AVE &amp; W 38TH ST</t>
+        </is>
+      </c>
+      <c r="J244" t="n">
+        <v>43.51777966412532</v>
+      </c>
+      <c r="K244" t="n">
+        <v>-96.77850989695047</v>
+      </c>
+      <c r="L244" t="n">
+        <v>858.8</v>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>Check wellbeing on Jul 29, 2026, 859 m from Empire Mall (S CAROLYN AVE &amp; W 38TH ST). Case #CFS26-163539 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>CFS26-162972</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="n">
+        <v>46232.25686342592</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Intoxicated Subject</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Drugs/Alcohol</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>S MARION RD &amp; W 44TH ST</t>
+        </is>
+      </c>
+      <c r="J245" t="n">
+        <v>43.51236607235115</v>
+      </c>
+      <c r="K245" t="n">
+        <v>-96.7909260097226</v>
+      </c>
+      <c r="L245" t="n">
+        <v>1242.3</v>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>Intoxicated subject on Jul 29, 2026, 1242 m from Empire Mall (S MARION RD &amp; W 44TH ST). Case #CFS26-162972 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>CFS26-163689</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="n">
+        <v>46233.05902777778</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Injury Accident P3</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>W 41ST ST &amp; W EMPIRE PL</t>
+        </is>
+      </c>
+      <c r="J246" t="n">
+        <v>43.51484419416143</v>
+      </c>
+      <c r="K246" t="n">
+        <v>-96.77669360636062</v>
+      </c>
+      <c r="L246" t="n">
+        <v>509.1</v>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>Injury accident p3 on Jul 30, 2026, 509 m from Empire Mall (W 41ST ST &amp; W EMPIRE PL). Case #CFS26-163689 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>CFS26-162985</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="n">
+        <v>46232.27642361111</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>S SHIRLEY AVE &amp; W SHIRLEY PL</t>
+        </is>
+      </c>
+      <c r="J247" t="n">
+        <v>43.51586590399282</v>
+      </c>
+      <c r="K247" t="n">
+        <v>-96.77448526595956</v>
+      </c>
+      <c r="L247" t="n">
+        <v>626.1</v>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 29, 2026, 626 m from Empire Mall (S SHIRLEY AVE &amp; W SHIRLEY PL). Case #CFS26-162985 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>CFS26-163675</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="n">
+        <v>46233.04778935185</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>S MADELYN AVE &amp; W 40TH ST</t>
+        </is>
+      </c>
+      <c r="J248" t="n">
+        <v>43.51538966329255</v>
+      </c>
+      <c r="K248" t="n">
+        <v>-96.78441883878321</v>
+      </c>
+      <c r="L248" t="n">
+        <v>896.4</v>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 30, 2026, 896 m from Empire Mall (S MADELYN AVE &amp; W 40TH ST). Case #CFS26-163675 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>CFS26-163782</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="n">
+        <v>46233.15675925926</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>S MADELYN AVE &amp; W 40TH ST</t>
+        </is>
+      </c>
+      <c r="J249" t="n">
+        <v>43.51538966329255</v>
+      </c>
+      <c r="K249" t="n">
+        <v>-96.78441883878321</v>
+      </c>
+      <c r="L249" t="n">
+        <v>896.4</v>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 30, 2026, 896 m from Empire Mall (S MADELYN AVE &amp; W 40TH ST). Case #CFS26-163782 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>CFS26-163779</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="n">
+        <v>46233.15428240741</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>S TECHNOPOLIS DR &amp; W 53RD ST</t>
+        </is>
+      </c>
+      <c r="J250" t="n">
+        <v>43.50364750236709</v>
+      </c>
+      <c r="K250" t="n">
+        <v>-96.7753931947034</v>
+      </c>
+      <c r="L250" t="n">
+        <v>742</v>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 30, 2026, 742 m from Empire Mall (S TECHNOPOLIS DR &amp; W 53RD ST). Case #CFS26-163779 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>CFS26-163772</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="n">
+        <v>46233.1472337963</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>S WESTPORT AVE &amp; W 43RD ST</t>
+        </is>
+      </c>
+      <c r="J251" t="n">
+        <v>43.5130372443594</v>
+      </c>
+      <c r="K251" t="n">
+        <v>-96.76793865443652</v>
+      </c>
+      <c r="L251" t="n">
+        <v>701.3</v>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 30, 2026, 701 m from Empire Mall (S WESTPORT AVE &amp; W 43RD ST). Case #CFS26-163772 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>CFS26-163815</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="n">
+        <v>46233.19416666667</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Disorderly Phone Calls</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>W CHIPPEWA PL &amp; W CHIPPEWA CIR</t>
+        </is>
+      </c>
+      <c r="J252" t="n">
+        <v>43.50415214191399</v>
+      </c>
+      <c r="K252" t="n">
+        <v>-96.78340912722523</v>
+      </c>
+      <c r="L252" t="n">
+        <v>920.7</v>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>Disorderly phone calls on Jul 30, 2026, 921 m from Empire Mall (W CHIPPEWA PL &amp; W CHIPPEWA CIR). Case #CFS26-163815 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>CFS26-163515</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="n">
+        <v>46232.92128472222</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>S SHIRLEY AVE &amp; W 38TH ST</t>
+        </is>
+      </c>
+      <c r="J253" t="n">
+        <v>43.51777845484326</v>
+      </c>
+      <c r="K253" t="n">
+        <v>-96.77437979679537</v>
+      </c>
+      <c r="L253" t="n">
+        <v>837.7</v>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>Accident on Jul 29, 2026, 838 m from Empire Mall (S SHIRLEY AVE &amp; W 38TH ST). Case #CFS26-163515 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>CFS26-163812</t>
+        </is>
+      </c>
+      <c r="E254" s="3" t="n">
+        <v>46233.19130787037</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Suspicious Vehicle</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
+        </is>
+      </c>
+      <c r="J254" t="n">
+        <v>43.51319846254545</v>
+      </c>
+      <c r="K254" t="n">
+        <v>-96.79336119066248</v>
+      </c>
+      <c r="L254" t="n">
+        <v>1453.4</v>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>Suspicious vehicle on Jul 30, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-163812 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>CFS26-163677</t>
+        </is>
+      </c>
+      <c r="E255" s="3" t="n">
+        <v>46233.04851851852</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Customer Dispute</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W KENTUCKY PL</t>
+        </is>
+      </c>
+      <c r="J255" t="n">
+        <v>43.51601560446141</v>
+      </c>
+      <c r="K255" t="n">
+        <v>-96.77111077469445</v>
+      </c>
+      <c r="L255" t="n">
+        <v>737.5</v>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>Customer dispute on Jul 30, 2026, 737 m from Empire Mall (S LOUISE AVE &amp; W KENTUCKY PL). Case #CFS26-163677 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>CFS26-163900</t>
+        </is>
+      </c>
+      <c r="E256" s="3" t="n">
+        <v>46233.38151620371</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Burglary Alarm</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Burglary</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>S BUR OAK PL &amp; W 57TH ST</t>
+        </is>
+      </c>
+      <c r="J256" t="n">
+        <v>43.5003453731365</v>
+      </c>
+      <c r="K256" t="n">
+        <v>-96.76225601111084</v>
+      </c>
+      <c r="L256" t="n">
+        <v>1555.3</v>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>Burglary alarm on Jul 30, 2026, 1555 m from Empire Mall (S BUR OAK PL &amp; W 57TH ST). Case #CFS26-163900 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>CFS26-164551</t>
+        </is>
+      </c>
+      <c r="E257" s="3" t="n">
+        <v>46234.08541666667</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Check Wellbeing</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>S GATEWAY BLVD &amp; S MADELYN AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J257" t="n">
+        <v>43.51483006334468</v>
+      </c>
+      <c r="K257" t="n">
+        <v>-96.78442152875238</v>
+      </c>
+      <c r="L257" t="n">
+        <v>858.8</v>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>Check wellbeing on Jul 31, 2026, 859 m from Empire Mall (S GATEWAY BLVD &amp; S MADELYN AVE &amp; W 41ST ST). Case #CFS26-164551 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>CFS26-164565</t>
+        </is>
+      </c>
+      <c r="E258" s="3" t="n">
+        <v>46234.09699074074</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Check Wellbeing</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W 43RD ST &amp; W EMPIRE PL</t>
+        </is>
+      </c>
+      <c r="J258" t="n">
+        <v>43.51305131378995</v>
+      </c>
+      <c r="K258" t="n">
+        <v>-96.77107093496716</v>
+      </c>
+      <c r="L258" t="n">
+        <v>486.8</v>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>Check wellbeing on Jul 31, 2026, 487 m from Empire Mall (S LOUISE AVE &amp; W 43RD ST &amp; W EMPIRE PL). Case #CFS26-164565 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>CFS26-164420</t>
+        </is>
+      </c>
+      <c r="E259" s="3" t="n">
+        <v>46233.95097222222</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Check Wellbeing</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>S GATEWAY LN &amp; S GATEWAY BLVD</t>
+        </is>
+      </c>
+      <c r="J259" t="n">
+        <v>43.51281290360509</v>
+      </c>
+      <c r="K259" t="n">
+        <v>-96.7832464577892</v>
+      </c>
+      <c r="L259" t="n">
+        <v>662.9</v>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>Check wellbeing on Jul 30, 2026, 663 m from Empire Mall (S GATEWAY LN &amp; S GATEWAY BLVD). Case #CFS26-164420 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>CFS26-163938</t>
+        </is>
+      </c>
+      <c r="E260" s="3" t="n">
+        <v>46233.51668981482</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Intoxicated Subject</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Drugs/Alcohol</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>S SHIRLEY AVE &amp; W 38TH ST</t>
+        </is>
+      </c>
+      <c r="J260" t="n">
+        <v>43.51777845484326</v>
+      </c>
+      <c r="K260" t="n">
+        <v>-96.77437979679537</v>
+      </c>
+      <c r="L260" t="n">
+        <v>837.7</v>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>Intoxicated subject on Jul 30, 2026, 838 m from Empire Mall (S SHIRLEY AVE &amp; W 38TH ST). Case #CFS26-163938 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>CFS26-164198</t>
+        </is>
+      </c>
+      <c r="E261" s="3" t="n">
+        <v>46233.79908564815</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Check Wellbeing</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>S SHIRLEY AVE &amp; W 38TH ST</t>
+        </is>
+      </c>
+      <c r="J261" t="n">
+        <v>43.51777845484326</v>
+      </c>
+      <c r="K261" t="n">
+        <v>-96.77437979679537</v>
+      </c>
+      <c r="L261" t="n">
+        <v>837.7</v>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>Check wellbeing on Jul 30, 2026, 838 m from Empire Mall (S SHIRLEY AVE &amp; W 38TH ST). Case #CFS26-164198 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>CFS26-164532</t>
+        </is>
+      </c>
+      <c r="E262" s="3" t="n">
+        <v>46234.05094907407</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Disorderly Phone Calls</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>W 56TH ST &amp; W CREEKSIDE CIR &amp; W CREEKSIDE DR</t>
+        </is>
+      </c>
+      <c r="J262" t="n">
+        <v>43.50145532175087</v>
+      </c>
+      <c r="K262" t="n">
+        <v>-96.77903768516548</v>
+      </c>
+      <c r="L262" t="n">
+        <v>1019.4</v>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>Disorderly phone calls on Jul 31, 2026, 1019 m from Empire Mall (W 56TH ST &amp; W CREEKSIDE CIR &amp; W CREEKSIDE DR). Case #CFS26-164532 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>CFS26-164458</t>
+        </is>
+      </c>
+      <c r="E263" s="3" t="n">
+        <v>46233.97483796296</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Family Dispute</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
+        </is>
+      </c>
+      <c r="J263" t="n">
+        <v>43.51319846254545</v>
+      </c>
+      <c r="K263" t="n">
+        <v>-96.79336119066248</v>
+      </c>
+      <c r="L263" t="n">
+        <v>1453.4</v>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>Family dispute on Jul 30, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-164458 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>CFS26-164034</t>
+        </is>
+      </c>
+      <c r="E264" s="3" t="n">
+        <v>46233.6452199074</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Abandoned Vehicles</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>S GATEWAY LN &amp; S GATEWAY BLVD</t>
+        </is>
+      </c>
+      <c r="J264" t="n">
+        <v>43.51281290360509</v>
+      </c>
+      <c r="K264" t="n">
+        <v>-96.7832464577892</v>
+      </c>
+      <c r="L264" t="n">
+        <v>662.9</v>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>Abandoned vehicles on Jul 30, 2026, 663 m from Empire Mall (S GATEWAY LN &amp; S GATEWAY BLVD). Case #CFS26-164034 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>CFS26-164393</t>
+        </is>
+      </c>
+      <c r="E265" s="3" t="n">
+        <v>46233.93733796296</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Assault</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Assault</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
+        </is>
+      </c>
+      <c r="J265" t="n">
+        <v>43.51319846254545</v>
+      </c>
+      <c r="K265" t="n">
+        <v>-96.79336119066248</v>
+      </c>
+      <c r="L265" t="n">
+        <v>1453.4</v>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>Assault on Jul 30, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-164393 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>CFS26-163932</t>
+        </is>
+      </c>
+      <c r="E266" s="3" t="n">
+        <v>46233.4896875</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Larceny</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Theft</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>S GATEWAY BLVD &amp; S TERRY AVE</t>
+        </is>
+      </c>
+      <c r="J266" t="n">
+        <v>43.51220536263347</v>
+      </c>
+      <c r="K266" t="n">
+        <v>-96.7859525684798</v>
+      </c>
+      <c r="L266" t="n">
+        <v>846.7</v>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>Larceny on Jul 30, 2026, 847 m from Empire Mall (S GATEWAY BLVD &amp; S TERRY AVE). Case #CFS26-163932 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>CFS26-164418</t>
+        </is>
+      </c>
+      <c r="E267" s="3" t="n">
+        <v>46233.94917824074</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>S SHIRLEY AVE &amp; W 38TH ST</t>
+        </is>
+      </c>
+      <c r="J267" t="n">
+        <v>43.51777845484326</v>
+      </c>
+      <c r="K267" t="n">
+        <v>-96.77437979679537</v>
+      </c>
+      <c r="L267" t="n">
+        <v>837.7</v>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>Accident on Jul 30, 2026, 838 m from Empire Mall (S SHIRLEY AVE &amp; W 38TH ST). Case #CFS26-164418 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>CFS26-164353</t>
+        </is>
+      </c>
+      <c r="E268" s="3" t="n">
+        <v>46233.91128472222</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W 49TH ST</t>
+        </is>
+      </c>
+      <c r="J268" t="n">
+        <v>43.50759974361088</v>
+      </c>
+      <c r="K268" t="n">
+        <v>-96.77103685388698</v>
+      </c>
+      <c r="L268" t="n">
+        <v>487.4</v>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>Accident on Jul 30, 2026, 487 m from Empire Mall (S LOUISE AVE &amp; W 49TH ST). Case #CFS26-164353 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>CFS26-164234</t>
+        </is>
+      </c>
+      <c r="E269" s="3" t="n">
+        <v>46233.82494212963</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>S MARION RD &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J269" t="n">
+        <v>43.51481738299845</v>
+      </c>
+      <c r="K269" t="n">
+        <v>-96.79096028032072</v>
+      </c>
+      <c r="L269" t="n">
+        <v>1322.4</v>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>Accident on Jul 30, 2026, 1322 m from Empire Mall (S MARION RD &amp; W 41ST ST). Case #CFS26-164234 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>CFS26-163978</t>
+        </is>
+      </c>
+      <c r="E270" s="3" t="n">
+        <v>46233.59060185185</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>S KIWANIS AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J270" t="n">
+        <v>43.5148316053277</v>
+      </c>
+      <c r="K270" t="n">
+        <v>-96.76108050220627</v>
+      </c>
+      <c r="L270" t="n">
+        <v>1287.6</v>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>Accident on Jul 30, 2026, 1288 m from Empire Mall (S KIWANIS AVE &amp; W 41ST ST). Case #CFS26-163978 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>CFS26-164089</t>
+        </is>
+      </c>
+      <c r="E271" s="3" t="n">
+        <v>46233.70215277778</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Accident</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Traffic</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J271" t="n">
+        <v>43.51480707435041</v>
+      </c>
+      <c r="K271" t="n">
+        <v>-96.77110350565825</v>
+      </c>
+      <c r="L271" t="n">
+        <v>626.1</v>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>Accident on Jul 30, 2026, 626 m from Empire Mall (S LOUISE AVE &amp; W 41ST ST). Case #CFS26-164089 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>CFS26-164075</t>
+        </is>
+      </c>
+      <c r="E272" s="3" t="n">
+        <v>46233.69127314815</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Suspicious Subject</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>S KIWANIS AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J272" t="n">
+        <v>43.5148316053277</v>
+      </c>
+      <c r="K272" t="n">
+        <v>-96.76108050220627</v>
+      </c>
+      <c r="L272" t="n">
+        <v>1287.6</v>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>Suspicious subject on Jul 30, 2026, 1288 m from Empire Mall (S KIWANIS AVE &amp; W 41ST ST). Case #CFS26-164075 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>CFS26-164113</t>
+        </is>
+      </c>
+      <c r="E273" s="3" t="n">
+        <v>46233.72401620371</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J273" t="n">
+        <v>43.51480707435041</v>
+      </c>
+      <c r="K273" t="n">
+        <v>-96.77110350565825</v>
+      </c>
+      <c r="L273" t="n">
+        <v>626.1</v>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 30, 2026, 626 m from Empire Mall (S LOUISE AVE &amp; W 41ST ST). Case #CFS26-164113 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>CFS26-164293</t>
+        </is>
+      </c>
+      <c r="E274" s="3" t="n">
+        <v>46233.87532407408</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>W EMPIRE PL &amp; W EMPIRE PL &amp; W EMPIRE PL</t>
+        </is>
+      </c>
+      <c r="J274" t="n">
+        <v>43.51307477335324</v>
+      </c>
+      <c r="K274" t="n">
+        <v>-96.7766862668114</v>
+      </c>
+      <c r="L274" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 30, 2026, 316 m from Empire Mall (W EMPIRE PL &amp; W EMPIRE PL &amp; W EMPIRE PL). Case #CFS26-164293 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>CFS26-164668</t>
+        </is>
+      </c>
+      <c r="E275" s="3" t="n">
+        <v>46234.24527777778</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Disorderly Subjects</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>S GATEWAY LN &amp; S GATEWAY BLVD</t>
+        </is>
+      </c>
+      <c r="J275" t="n">
+        <v>43.51281290360509</v>
+      </c>
+      <c r="K275" t="n">
+        <v>-96.7832464577892</v>
+      </c>
+      <c r="L275" t="n">
+        <v>662.9</v>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>Disorderly subjects on Jul 31, 2026, 663 m from Empire Mall (S GATEWAY LN &amp; S GATEWAY BLVD). Case #CFS26-164668 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>CFS26-164564</t>
+        </is>
+      </c>
+      <c r="E276" s="3" t="n">
+        <v>46234.09667824074</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Found Child</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J276" t="n">
+        <v>43.51480707435041</v>
+      </c>
+      <c r="K276" t="n">
+        <v>-96.77110350565825</v>
+      </c>
+      <c r="L276" t="n">
+        <v>626.1</v>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>Found child on Jul 31, 2026, 626 m from Empire Mall (S LOUISE AVE &amp; W 41ST ST). Case #CFS26-164564 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>CFS26-164621</t>
+        </is>
+      </c>
+      <c r="E277" s="3" t="n">
+        <v>46234.17833333334</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Noise Disturbance</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>S SOLBERG AVE &amp; W CHIPPEWA CIR</t>
+        </is>
+      </c>
+      <c r="J277" t="n">
+        <v>43.50469043243786</v>
+      </c>
+      <c r="K277" t="n">
+        <v>-96.7809382470065</v>
+      </c>
+      <c r="L277" t="n">
+        <v>750.9</v>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>Noise disturbance on Jul 31, 2026, 751 m from Empire Mall (S SOLBERG AVE &amp; W CHIPPEWA CIR). Case #CFS26-164621 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>CFS26-164170</t>
+        </is>
+      </c>
+      <c r="E278" s="3" t="n">
+        <v>46233.77346064815</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Suspicious Subject</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>W EMPIRE PL &amp; W EMPIRE PL &amp; W EMPIRE PL</t>
+        </is>
+      </c>
+      <c r="J278" t="n">
+        <v>43.51307477335324</v>
+      </c>
+      <c r="K278" t="n">
+        <v>-96.7766862668114</v>
+      </c>
+      <c r="L278" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>Suspicious subject on Jul 30, 2026, 316 m from Empire Mall (W EMPIRE PL &amp; W EMPIRE PL &amp; W EMPIRE PL). Case #CFS26-164170 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>CFS26-164521</t>
+        </is>
+      </c>
+      <c r="E279" s="3" t="n">
+        <v>46234.03421296296</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Aggravated Assault</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Assault</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>S MARION RD &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J279" t="n">
+        <v>43.51481738299845</v>
+      </c>
+      <c r="K279" t="n">
+        <v>-96.79096028032072</v>
+      </c>
+      <c r="L279" t="n">
+        <v>1322.4</v>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>Aggravated assault on Jul 31, 2026, 1322 m from Empire Mall (S MARION RD &amp; W 41ST ST). Case #CFS26-164521 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>CFS26-163988</t>
+        </is>
+      </c>
+      <c r="E280" s="3" t="n">
+        <v>46233.60233796296</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Found Property</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>S GATEWAY LN &amp; S GATEWAY BLVD</t>
+        </is>
+      </c>
+      <c r="J280" t="n">
+        <v>43.51281290360509</v>
+      </c>
+      <c r="K280" t="n">
+        <v>-96.7832464577892</v>
+      </c>
+      <c r="L280" t="n">
+        <v>662.9</v>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>Found property on Jul 30, 2026, 663 m from Empire Mall (S GATEWAY LN &amp; S GATEWAY BLVD). Case #CFS26-163988 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>CFS26-164120</t>
+        </is>
+      </c>
+      <c r="E281" s="3" t="n">
+        <v>46233.72950231482</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Man Down</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W KENTUCKY PL</t>
+        </is>
+      </c>
+      <c r="J281" t="n">
+        <v>43.51601560446141</v>
+      </c>
+      <c r="K281" t="n">
+        <v>-96.77111077469445</v>
+      </c>
+      <c r="L281" t="n">
+        <v>737.5</v>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>Man down on Jul 30, 2026, 737 m from Empire Mall (S LOUISE AVE &amp; W KENTUCKY PL). Case #CFS26-164120 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>CFS26-164224</t>
+        </is>
+      </c>
+      <c r="E282" s="3" t="n">
+        <v>46233.81635416667</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Man Down</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>S LOUISE AVE &amp; W 41ST ST</t>
+        </is>
+      </c>
+      <c r="J282" t="n">
+        <v>43.51480707435041</v>
+      </c>
+      <c r="K282" t="n">
+        <v>-96.77110350565825</v>
+      </c>
+      <c r="L282" t="n">
+        <v>626.1</v>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>Man down on Jul 30, 2026, 626 m from Empire Mall (S LOUISE AVE &amp; W 41ST ST). Case #CFS26-164224 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>CFS26-163961</t>
+        </is>
+      </c>
+      <c r="E283" s="3" t="n">
+        <v>46233.55917824074</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Man Down</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>S OXBOW AVE &amp; W 49TH ST</t>
+        </is>
+      </c>
+      <c r="J283" t="n">
+        <v>43.50760687329769</v>
+      </c>
+      <c r="K283" t="n">
+        <v>-96.76591290307073</v>
+      </c>
+      <c r="L283" t="n">
+        <v>851</v>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>Man down on Jul 30, 2026, 851 m from Empire Mall (S OXBOW AVE &amp; W 49TH ST). Case #CFS26-163961 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>CFS26-163882</t>
+        </is>
+      </c>
+      <c r="E284" s="3" t="n">
+        <v>46233.329375</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Man Down</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>S RACKET DR &amp; W 49TH ST</t>
+        </is>
+      </c>
+      <c r="J284" t="n">
+        <v>43.50761161336476</v>
+      </c>
+      <c r="K284" t="n">
+        <v>-96.76881681294817</v>
+      </c>
+      <c r="L284" t="n">
+        <v>637.1</v>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>Man down on Jul 30, 2026, 637 m from Empire Mall (S RACKET DR &amp; W 49TH ST). Case #CFS26-163882 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Empire Mall</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>CFS26-164060</t>
+        </is>
+      </c>
+      <c r="E285" s="3" t="n">
+        <v>46233.67805555555</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Suspicious Vehicle</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Disorderly Conduct</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>W CHIPPEWA PL &amp; W CHIPPEWA CIR</t>
+        </is>
+      </c>
+      <c r="J285" t="n">
+        <v>43.50415214191399</v>
+      </c>
+      <c r="K285" t="n">
+        <v>-96.78340912722523</v>
+      </c>
+      <c r="L285" t="n">
+        <v>920.7</v>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>Suspicious vehicle on Jul 30, 2026, 921 m from Empire Mall (W CHIPPEWA PL &amp; W CHIPPEWA CIR). Case #CFS26-164060 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M161"/>
+  <autoFilter ref="A1:M285"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12185,7 +19677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="51" customWidth="1" min="1" max="1"/>
@@ -12212,7 +19704,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 04:21:05.180533+00:00</t>
+          <t>2026-08-01 04:22:40.060082+00:00</t>
         </is>
       </c>
     </row>
@@ -12244,7 +19736,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 04:21:05.180533+00:00</t>
+          <t>2026-07-25 04:22:40.060082+00:00</t>
         </is>
       </c>
     </row>
@@ -12255,7 +19747,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>160</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7">
@@ -12265,7 +19757,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -12472,8 +19964,56 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>source:CLEARFORK/Fort Worth PD Crime Data</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>OK fetched=1 truncated=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>source:UNIVPARKVILLAGE/Fort Worth PD Crime Data</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>OK fetched=0 truncated=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>source:EMPIRE/Sioux Falls PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>OK fetched=123 truncated=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>source:MALLATMILLENIA/Orlando PD Crimes</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>OK fetched=0 truncated=False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B24"/>
+  <autoFilter ref="A1:B28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/2026-08-01/blotter_report.xlsx
+++ b/reports/2026-08-01/blotter_report.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Run Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$285</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$28</definedName>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -655,45 +655,41 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CHARLOTTE</t>
+          <t>CASTLETON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Charlotte Premium Outlets</t>
+          <t>Castleton Square</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5404 New Fashion Way Charlotte NC 28278</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>6020 East 82nd Street Indianapolis IN 46250</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>232.6</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>46233.16666666666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="b">
         <v>0</v>
       </c>
@@ -701,17 +697,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Charlotte Premium Outlets</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3000 East 1st Avenue, Denver CO 80206</t>
+          <t>5404 New Fashion Way Charlotte NC 28278</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -720,25 +716,25 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>144.7</v>
+        <v>232.6</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>46231.83333333334</v>
+        <v>46233.16666666666</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -747,17 +743,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CLEARFORK</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Shops at Clearfork</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5188 Monahans Avenue Fort Worth TX 76109</t>
+          <t>3000 East 1st Avenue, Denver CO 80206</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -766,25 +762,25 @@
         </is>
       </c>
       <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>1086.4</v>
+        <v>144.7</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>46228.59375</v>
+        <v>46231.83333333334</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
@@ -793,17 +789,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>CLEARFORK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>The Shops at Clearfork</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5000 Empire Mall Sioux Falls SD 57106</t>
+          <t>5188 Monahans Avenue Fort Worth TX 76109</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -812,25 +808,25 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>123</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>315.5</v>
+        <v>1086.4</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>46234.24527777778</v>
+        <v>46228.59375</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
@@ -839,17 +835,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2126 Abbott Martin Road, Nashville, TN 37215</t>
+          <t>5000 Empire Mall Sioux Falls SD 57106</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -858,22 +854,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
+        <v>123</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+        <v>79</v>
+      </c>
+      <c r="J9" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>46234.24527777778</v>
+      </c>
       <c r="L9" t="b">
         <v>0</v>
       </c>
@@ -881,17 +881,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>GREENHILLS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>The Mall at Green Hills</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5085 Westheimer Houston TX 77056</t>
+          <t>2126 Abbott Martin Road, Nashville, TN 37215</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -900,26 +900,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>57</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>163.5</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>46233</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="b">
         <v>0</v>
       </c>
@@ -927,17 +923,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INTLPLAZA</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>International Plaza</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
+          <t>5085 Westheimer Houston TX 77056</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -946,25 +942,25 @@
         </is>
       </c>
       <c r="E11" t="n">
+        <v>57</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>43</v>
+      </c>
+      <c r="H11" t="n">
         <v>1</v>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>1534.5</v>
+        <v>163.5</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>46232.16666666666</v>
+        <v>46233</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
@@ -973,32 +969,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LENOX</t>
+          <t>INTLPLAZA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lenox Square</t>
+          <t>International Plaza</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1006,8 +1002,12 @@
       <c r="I12" t="n">
         <v>0</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>1534.5</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>46232.16666666666</v>
+      </c>
       <c r="L12" t="b">
         <v>0</v>
       </c>
@@ -1015,22 +1015,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MALLATMILLENIA</t>
+          <t>LENOX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Mall at Millenia</t>
+          <t>Lenox Square</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4200 Conroy Road, Orlando, FL 32839</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1057,17 +1057,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>MALLATMILLENIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>The Mall at Millenia</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>401 Northeast Northgate Way Seattle WA 98125</t>
+          <t>4200 Conroy Road, Orlando, FL 32839</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1076,26 +1076,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>14</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>145.2</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>46233.28194444445</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="b">
         <v>0</v>
       </c>
@@ -1103,17 +1099,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>433 Opry Mills Drive Nashville TN 37214</t>
+          <t>401 Northeast Northgate Way Seattle WA 98125</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1122,22 +1118,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>46233.28194444445</v>
+      </c>
       <c r="L15" t="b">
         <v>0</v>
       </c>
@@ -1145,17 +1145,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4400 Sharon Road Charlotte NC 28211</t>
+          <t>433 Opry Mills Drive Nashville TN 37214</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1164,26 +1164,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>178.9</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>46232.16666666666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="b">
         <v>0</v>
       </c>
@@ -1191,17 +1187,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4502 South Steele Street Tacoma WA 98409</t>
+          <t>4400 Sharon Road Charlotte NC 28211</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1210,25 +1206,25 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>471.3</v>
+        <v>178.9</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>46233</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="L17" t="b">
         <v>0</v>
@@ -1237,41 +1233,45 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>THEDOMAIN</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Domain</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>11410 Century Oaks Terrace Austin TX 78758</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>4502 South Steele Street Tacoma WA 98409</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>471.3</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>46233</v>
+      </c>
       <c r="L18" t="b">
         <v>0</v>
       </c>
@@ -1279,45 +1279,41 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>THEDOMAIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>The Domain</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7700 East Kellogg Wichita KS 67207</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>11410 Century Oaks Terrace Austin TX 78758</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>33</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>23</v>
-      </c>
-      <c r="J19" t="n">
-        <v>288.9</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>46233.7625</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="b">
         <v>0</v>
       </c>
@@ -1325,17 +1321,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UNIVPARKVILLAGE</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>University Park Village</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1612 South University Drive Fort Worth TX 76107</t>
+          <t>7700 East Kellogg Wichita KS 67207</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1344,28 +1340,74 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="J20" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>46233.7625</v>
+      </c>
       <c r="L20" t="b">
         <v>0</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>UNIVPARKVILLAGE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>University Park Village</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1612 South University Drive Fort Worth TX 76107</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L20"/>
+  <autoFilter ref="A1:L21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19704,7 +19746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 04:22:40.060082+00:00</t>
+          <t>2026-08-01 04:25:02.895488+00:00</t>
         </is>
       </c>
     </row>
@@ -19736,7 +19778,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 04:22:40.060082+00:00</t>
+          <t>2026-07-25 04:25:02.895488+00:00</t>
         </is>
       </c>
     </row>
@@ -19768,7 +19810,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LENOX, THEDOMAIN</t>
+          <t>CASTLETON, LENOX, THEDOMAIN</t>
         </is>
       </c>
     </row>

--- a/reports/2026-08-01/blotter_report.xlsx
+++ b/reports/2026-08-01/blotter_report.xlsx
@@ -19746,7 +19746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 04:25:02.895488+00:00</t>
+          <t>2026-08-01 04:32:25.991636+00:00</t>
         </is>
       </c>
     </row>
@@ -19778,7 +19778,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 04:25:02.895488+00:00</t>
+          <t>2026-07-25 04:32:25.991636+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/2026-08-01/blotter_report.xlsx
+++ b/reports/2026-08-01/blotter_report.xlsx
@@ -13,10 +13,10 @@
     <sheet name="Run Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$285</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$286</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -789,17 +789,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CLEARFORK</t>
+          <t>CLARKSBURG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Shops at Clearfork</t>
+          <t>Clarksburg Premium Outlets</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5188 Monahans Avenue Fort Worth TX 76109</t>
+          <t>22705 Clarksburg Rd Clarksburg MD 20871</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -814,19 +814,19 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>1086.4</v>
+        <v>1135.3</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>46228.59375</v>
+        <v>46232.38263888889</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
@@ -835,17 +835,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>CLEARFORK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>The Shops at Clearfork</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5000 Empire Mall Sioux Falls SD 57106</t>
+          <t>5188 Monahans Avenue Fort Worth TX 76109</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -854,25 +854,25 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>123</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>315.5</v>
+        <v>1086.4</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>46234.24527777778</v>
+        <v>46228.59375</v>
       </c>
       <c r="L9" t="b">
         <v>0</v>
@@ -881,17 +881,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2126 Abbott Martin Road, Nashville, TN 37215</t>
+          <t>5000 Empire Mall Sioux Falls SD 57106</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -900,22 +900,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
+        <v>123</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+        <v>79</v>
+      </c>
+      <c r="J10" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>46234.24527777778</v>
+      </c>
       <c r="L10" t="b">
         <v>0</v>
       </c>
@@ -923,17 +927,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>GREENHILLS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>The Mall at Green Hills</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5085 Westheimer Houston TX 77056</t>
+          <t>2126 Abbott Martin Road, Nashville, TN 37215</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -942,26 +946,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>57</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>163.5</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>46233</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="b">
         <v>0</v>
       </c>
@@ -969,17 +969,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INTLPLAZA</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>International Plaza</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
+          <t>5085 Westheimer Houston TX 77056</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -988,25 +988,25 @@
         </is>
       </c>
       <c r="E12" t="n">
+        <v>57</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>43</v>
+      </c>
+      <c r="H12" t="n">
         <v>1</v>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J12" t="n">
-        <v>1534.5</v>
+        <v>163.5</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>46232.16666666666</v>
+        <v>46233</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
@@ -1015,32 +1015,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LENOX</t>
+          <t>INTLPLAZA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lenox Square</t>
+          <t>International Plaza</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1048,8 +1048,12 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>1534.5</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>46232.16666666666</v>
+      </c>
       <c r="L13" t="b">
         <v>0</v>
       </c>
@@ -1057,22 +1061,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MALLATMILLENIA</t>
+          <t>LENOX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Mall at Millenia</t>
+          <t>Lenox Square</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4200 Conroy Road, Orlando, FL 32839</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1099,17 +1103,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>MALLATMILLENIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>The Mall at Millenia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>401 Northeast Northgate Way Seattle WA 98125</t>
+          <t>4200 Conroy Road, Orlando, FL 32839</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1118,26 +1122,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>14</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>145.2</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>46233.28194444445</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="b">
         <v>0</v>
       </c>
@@ -1145,17 +1145,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>433 Opry Mills Drive Nashville TN 37214</t>
+          <t>401 Northeast Northgate Way Seattle WA 98125</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1164,22 +1164,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>46233.28194444445</v>
+      </c>
       <c r="L16" t="b">
         <v>0</v>
       </c>
@@ -1187,17 +1191,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4400 Sharon Road Charlotte NC 28211</t>
+          <t>433 Opry Mills Drive Nashville TN 37214</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1206,26 +1210,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>178.9</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>46232.16666666666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="b">
         <v>0</v>
       </c>
@@ -1233,17 +1233,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4502 South Steele Street Tacoma WA 98409</t>
+          <t>4400 Sharon Road Charlotte NC 28211</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1252,25 +1252,25 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>471.3</v>
+        <v>178.9</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>46233</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
@@ -1279,41 +1279,45 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>THEDOMAIN</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Domain</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>11410 Century Oaks Terrace Austin TX 78758</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>4502 South Steele Street Tacoma WA 98409</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>471.3</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>46233</v>
+      </c>
       <c r="L19" t="b">
         <v>0</v>
       </c>
@@ -1321,45 +1325,41 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>THEDOMAIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>The Domain</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7700 East Kellogg Wichita KS 67207</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>11410 Century Oaks Terrace Austin TX 78758</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>33</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
-      </c>
-      <c r="J20" t="n">
-        <v>288.9</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>46233.7625</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="b">
         <v>0</v>
       </c>
@@ -1367,17 +1367,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UNIVPARKVILLAGE</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>University Park Village</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1612 South University Drive Fort Worth TX 76107</t>
+          <t>7700 East Kellogg Wichita KS 67207</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1386,28 +1386,74 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="J21" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>46233.7625</v>
+      </c>
       <c r="L21" t="b">
         <v>0</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>UNIVPARKVILLAGE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>University Park Village</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1612 South University Drive Fort Worth TX 76107</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L21"/>
+  <autoFilter ref="A1:L22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2982,7 +3028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M285"/>
+  <dimension ref="A1:M286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2992,7 +3038,7 @@
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="49" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
     <col width="53" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
@@ -19707,8 +19753,67 @@
         </is>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>CLARKSBURG</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Clarksburg Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>CLARKSBURG:icn6-v9z3</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>201584985</t>
+        </is>
+      </c>
+      <c r="E286" s="3" t="n">
+        <v>46232.38263888889</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Family Offenses, NonViolent</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>FAMILY OFFENSE - NEGLECT CHILD (INCLUDES NONSUPPOR</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>13400 BLK  BLUEBEARD TER</t>
+        </is>
+      </c>
+      <c r="J286" t="n">
+        <v>39.235</v>
+      </c>
+      <c r="K286" t="n">
+        <v>-77.27719999999999</v>
+      </c>
+      <c r="L286" t="n">
+        <v>1135.3</v>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>Family offenses, nonviolent on Jul 29, 2026, 1135 m from Clarksburg Premium Outlets (13400 BLK  BLUEBEARD TER). Case #201584985 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M285"/>
+  <autoFilter ref="A1:M286"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19719,7 +19824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="51" customWidth="1" min="1" max="1"/>
@@ -19746,7 +19851,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 04:32:25.991636+00:00</t>
+          <t>2026-08-01 04:35:44.705888+00:00</t>
         </is>
       </c>
     </row>
@@ -19778,7 +19883,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 04:32:25.991636+00:00</t>
+          <t>2026-07-25 04:35:44.705888+00:00</t>
         </is>
       </c>
     </row>
@@ -19789,7 +19894,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7">
@@ -20054,8 +20159,20 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>source:CLARKSBURG/Montgomery County Police Crime</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>OK fetched=1 truncated=False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B28"/>
+  <autoFilter ref="A1:B29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/2026-08-01/blotter_report.xlsx
+++ b/reports/2026-08-01/blotter_report.xlsx
@@ -19851,7 +19851,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 04:35:44.705888+00:00</t>
+          <t>2026-08-01 04:54:04.147095+00:00</t>
         </is>
       </c>
     </row>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 04:35:44.705888+00:00</t>
+          <t>2026-07-25 04:54:04.147095+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/2026-08-01/blotter_report.xlsx
+++ b/reports/2026-08-01/blotter_report.xlsx
@@ -19851,7 +19851,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 04:54:04.147095+00:00</t>
+          <t>2026-08-01 04:55:55.470379+00:00</t>
         </is>
       </c>
     </row>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 04:54:04.147095+00:00</t>
+          <t>2026-07-25 04:55:55.470379+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/2026-08-01/blotter_report.xlsx
+++ b/reports/2026-08-01/blotter_report.xlsx
@@ -13,10 +13,10 @@
     <sheet name="Run Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$286</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$288</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -789,26 +789,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CLARKSBURG</t>
+          <t>CHESTNUTHILL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Clarksburg Premium Outlets</t>
+          <t>The Shops at Chestnut Hill</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>22705 Clarksburg Rd Clarksburg MD 20871</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>199 Boylston Street Chestnut Hill MA 02467</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -820,14 +820,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1135.3</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>46232.38263888889</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="b">
         <v>0</v>
       </c>
@@ -835,17 +831,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CLEARFORK</t>
+          <t>CLARKSBURG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Shops at Clearfork</t>
+          <t>Clarksburg Premium Outlets</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5188 Monahans Avenue Fort Worth TX 76109</t>
+          <t>22705 Clarksburg Rd Clarksburg MD 20871</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -860,19 +856,19 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1086.4</v>
+        <v>1135.3</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>46228.59375</v>
+        <v>46232.38263888889</v>
       </c>
       <c r="L9" t="b">
         <v>0</v>
@@ -881,17 +877,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>CLEARFORK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>The Shops at Clearfork</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5000 Empire Mall Sioux Falls SD 57106</t>
+          <t>5188 Monahans Avenue Fort Worth TX 76109</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -900,25 +896,25 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>123</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>315.5</v>
+        <v>1086.4</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>46234.24527777778</v>
+        <v>46228.59375</v>
       </c>
       <c r="L10" t="b">
         <v>0</v>
@@ -927,22 +923,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2126 Abbott Martin Road, Nashville, TN 37215</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>2 Copley Place Boston MA 02116</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -969,17 +965,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5085 Westheimer Houston TX 77056</t>
+          <t>5000 Empire Mall Sioux Falls SD 57106</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -988,25 +984,25 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>57</v>
+        <v>123</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="J12" t="n">
-        <v>163.5</v>
+        <v>315.5</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>46233</v>
+        <v>46234.24527777778</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
@@ -1015,17 +1011,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INTLPLAZA</t>
+          <t>GREENHILLS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>International Plaza</t>
+          <t>The Mall at Green Hills</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
+          <t>2126 Abbott Martin Road, Nashville, TN 37215</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1034,13 +1030,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1048,12 +1044,8 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" t="n">
-        <v>1534.5</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>46232.16666666666</v>
-      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="b">
         <v>0</v>
       </c>
@@ -1061,41 +1053,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LENOX</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lenox Square</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>5085 Westheimer Houston TX 77056</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
+        <v>57</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>163.5</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>46233</v>
+      </c>
       <c r="L14" t="b">
         <v>0</v>
       </c>
@@ -1103,17 +1099,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MALLATMILLENIA</t>
+          <t>INTLPLAZA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Mall at Millenia</t>
+          <t>International Plaza</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4200 Conroy Road, Orlando, FL 32839</t>
+          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1122,13 +1118,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1136,8 +1132,12 @@
       <c r="I15" t="n">
         <v>0</v>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>1534.5</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>46232.16666666666</v>
+      </c>
       <c r="L15" t="b">
         <v>0</v>
       </c>
@@ -1145,45 +1145,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>LENOX</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Lenox Square</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>401 Northeast Northgate Way Seattle WA 98125</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>14</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>145.2</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>46233.28194444445</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="b">
         <v>0</v>
       </c>
@@ -1191,17 +1187,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>MALLATMILLENIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>The Mall at Millenia</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>433 Opry Mills Drive Nashville TN 37214</t>
+          <t>4200 Conroy Road, Orlando, FL 32839</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1233,17 +1229,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>NORFOLKPO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Norfolk Premium Outlets</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4400 Sharon Road Charlotte NC 28211</t>
+          <t>1600 Premium Outlets Boulevard Norfolk VA 23502</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1252,25 +1248,25 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>178.9</v>
+        <v>1118.9</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>46232.16666666666</v>
+        <v>46233</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
@@ -1279,17 +1275,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4502 South Steele Street Tacoma WA 98409</t>
+          <t>401 Northeast Northgate Way Seattle WA 98125</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1298,25 +1294,25 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>471.3</v>
+        <v>145.2</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>46233</v>
+        <v>46233.28194444445</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
@@ -1325,22 +1321,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>THEDOMAIN</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Domain</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>11410 Century Oaks Terrace Austin TX 78758</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>433 Opry Mills Drive Nashville TN 37214</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1367,17 +1363,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>7700 East Kellogg Wichita KS 67207</t>
+          <t>4400 Sharon Road Charlotte NC 28211</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1386,25 +1382,25 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>1</v>
       </c>
-      <c r="I21" t="n">
-        <v>23</v>
-      </c>
       <c r="J21" t="n">
-        <v>288.9</v>
+        <v>178.9</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>46233.7625</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
@@ -1413,17 +1409,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UNIVPARKVILLAGE</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>University Park Village</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1612 South University Drive Fort Worth TX 76107</t>
+          <t>4502 South Steele Street Tacoma WA 98409</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1432,28 +1428,162 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>471.3</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>46233</v>
+      </c>
       <c r="L22" t="b">
         <v>0</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>THEDOMAIN</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>The Domain</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>11410 Century Oaks Terrace Austin TX 78758</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>7700 East Kellogg Wichita KS 67207</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>33</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>23</v>
+      </c>
+      <c r="J24" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>46233.7625</v>
+      </c>
+      <c r="L24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>UNIVPARKVILLAGE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>University Park Village</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1612 South University Drive Fort Worth TX 76107</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L22"/>
+  <autoFilter ref="A1:L25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3028,7 +3158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M286"/>
+  <dimension ref="A1:M288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19812,8 +19942,118 @@
         </is>
       </c>
     </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>NORFOLKPO</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Norfolk Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>NORFOLKPO:r7bn-2egr</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>260730001961</t>
+        </is>
+      </c>
+      <c r="E287" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>SHOOT INTO OCCUPIED DWELLING</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>1400 DURE RD</t>
+        </is>
+      </c>
+      <c r="J287" t="n">
+        <v>36.872248203692</v>
+      </c>
+      <c r="K287" t="n">
+        <v>-76.209734788037</v>
+      </c>
+      <c r="L287" t="n">
+        <v>1387.8</v>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>Shoot into occupied dwelling on Jul 30, 2026, 1388 m from Norfolk Premium Outlets (1400 DURE RD). Case #260730001961 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>NORFOLKPO</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Norfolk Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>NORFOLKPO:r7bn-2egr</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>260730001974</t>
+        </is>
+      </c>
+      <c r="E288" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>HIT &amp; RUN - PERSONAL INJURY</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>2500 MILITARY HIGHWAY</t>
+        </is>
+      </c>
+      <c r="J288" t="n">
+        <v>36.879766119132</v>
+      </c>
+      <c r="K288" t="n">
+        <v>-76.212427576002</v>
+      </c>
+      <c r="L288" t="n">
+        <v>1118.9</v>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>Hit &amp; run - personal injury on Jul 30, 2026, 1119 m from Norfolk Premium Outlets (2500 MILITARY HIGHWAY). Case #260730001974 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M286"/>
+  <autoFilter ref="A1:M288"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19824,11 +20064,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="51" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19851,7 +20091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 04:55:55.470379+00:00</t>
+          <t>2026-08-01 04:58:47.637225+00:00</t>
         </is>
       </c>
     </row>
@@ -19883,7 +20123,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 04:55:55.470379+00:00</t>
+          <t>2026-07-25 04:58:47.637225+00:00</t>
         </is>
       </c>
     </row>
@@ -19894,7 +20134,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7">
@@ -20171,8 +20411,44 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>source:COPLEY/Boston PD Crime Incident Reports</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FAILED fetched=0 truncated=False CKAN fetch failed for b973d8cb-eeb2-4e7e-99da-c92938efc9c0: HTTP 403 for https://data.boston.gov/api/3/action/datastore_search_sql?sql=SELECT+%2A+FROM+%22b973d8cb-eeb2-4e7e-99da-c92938efc9c0%22+WHERE+CAST%28NULLIF%28%22Lat%22%2C+%27%27%29+AS+float8%29+BETWEEN+42.3332261543053+AND+42.3620044456947+AND+CAST%28NULLIF%28%22Long%22%2C+%27%27%29+AS+float8%29+BETWEEN+-71.09710221911952+AND+-71.05816378088049+AND+%22OCCURRED_ON_DATE%22+%3E%3D+%272026-07-25T04%3A58%3A47%27+LIMIT+5000 :: {"help": "https://data.boston.gov/api/3/action/help_show?name=datastore_search_sql", "error": {"__type": "Authorization Error", "message": "Access denied: {'permissions': ['Not authorized to call function NULLIF']}"}, "success": false}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>source:CHESTNUTHILL/Boston PD Crime Incident Reports (Boston-side only)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FAILED fetched=0 truncated=False CKAN fetch failed for b973d8cb-eeb2-4e7e-99da-c92938efc9c0: HTTP 403 for https://data.boston.gov/api/3/action/datastore_search_sql?sql=SELECT+%2A+FROM+%22b973d8cb-eeb2-4e7e-99da-c92938efc9c0%22+WHERE+CAST%28NULLIF%28%22Lat%22%2C+%27%27%29+AS+float8%29+BETWEEN+42.3071233543053+AND+42.3359016456947+AND+CAST%28NULLIF%28%22Long%22%2C+%27%27%29+AS+float8%29+BETWEEN+-71.19513294012805+AND+-71.15621065987196+AND+%22OCCURRED_ON_DATE%22+%3E%3D+%272026-07-25T04%3A58%3A47%27+LIMIT+5000 :: {"help": "https://data.boston.gov/api/3/action/help_show?name=datastore_search_sql", "error": {"__type": "Authorization Error", "message": "Access denied: {'permissions': ['Not authorized to call function NULLIF']}"}, "success": false}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>source:NORFOLKPO/Norfolk Police Incident Reports</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>OK fetched=281 truncated=False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B29"/>
+  <autoFilter ref="A1:B32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/2026-08-01/blotter_report.xlsx
+++ b/reports/2026-08-01/blotter_report.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$288</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$350</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -802,9 +802,9 @@
           <t>199 Boylston Street Chestnut Hill MA 02467</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -936,28 +936,32 @@
           <t>2 Copley Place Boston MA 02116</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="J11" t="n">
+        <v>129.3</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>46230.89583333334</v>
+      </c>
       <c r="L11" t="b">
         <v>0</v>
       </c>
@@ -1248,7 +1252,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1260,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
         <v>1118.9</v>
@@ -1599,7 +1603,7 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
@@ -2032,30 +2036,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CFS26-161603</t>
+          <t>262064756</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46230.83325231481</v>
+        <v>46230.80347222222</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>ASSAULT - SIMPLE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2063,58 +2067,54 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Assault</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>S WESTPORT AVE &amp; W 41ST ST</t>
+          <t>MASSACHUSETTS AVE</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>43.51485103457241</v>
+        <v>42.34439568415441</v>
       </c>
       <c r="K8" t="n">
-        <v>-96.76794119445807</v>
+        <v>-71.08632016344815</v>
       </c>
       <c r="L8" t="n">
-        <v>808.9</v>
+        <v>798.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Assault on Jul 27, 2026, 809 m from Empire Mall (S WESTPORT AVE &amp; W 41ST ST). Case #CFS26-161603 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - simple on Jul 27, 2026, 799 m from Copley Place (MASSACHUSETTS AVE). Case #262064756 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20260729-1600-11</t>
+          <t>CFS26-161603</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46232.16666666666</v>
+        <v>46230.83325231481</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Simple Assault</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2124,56 +2124,56 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>13B</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4700 PIEDMONT ROW DR</t>
+          <t>S WESTPORT AVE &amp; W 41ST ST</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>35.15196312662653</v>
+        <v>43.51485103457241</v>
       </c>
       <c r="K9" t="n">
-        <v>-80.83980651357408</v>
+        <v>-96.76794119445807</v>
       </c>
       <c r="L9" t="n">
-        <v>850.6</v>
+        <v>808.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 29, 2026, 851 m from Southpark (4700 PIEDMONT ROW DR). Status: Open. Case #20260729-1600-11 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 27, 2026, 809 m from Empire Mall (S WESTPORT AVE &amp; W 41ST ST). Case #CFS26-161603 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2620701835</t>
+          <t>20260729-1600-11</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46229</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2183,56 +2183,56 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>13B</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4000 S LAWRENCE ST</t>
+          <t>4700 PIEDMONT ROW DR</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>47.219421</v>
+        <v>35.15196312662653</v>
       </c>
       <c r="K10" t="n">
-        <v>-122.478428</v>
+        <v>-80.83980651357408</v>
       </c>
       <c r="L10" t="n">
-        <v>853.4</v>
+        <v>850.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 26, 2026, 853 m from Tacoma Mall (4000 S LAWRENCE ST). Case #2620701835 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 29, 2026, 851 m from Southpark (4700 PIEDMONT ROW DR). Status: Open. Case #20260729-1600-11 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>71878728447</t>
+          <t>2620701835</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46230.4375</v>
+        <v>46229</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2242,56 +2242,56 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>Assault Offenses</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>16XX BLOCK OF N 105TH ST</t>
+          <t>4000 S LAWRENCE ST</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>47.70504225</v>
+        <v>47.219421</v>
       </c>
       <c r="K11" t="n">
-        <v>-122.338094779232</v>
+        <v>-122.478428</v>
       </c>
       <c r="L11" t="n">
-        <v>938.8</v>
+        <v>853.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 26, 2026, 853 m from Tacoma Mall (4000 S LAWRENCE ST). Case #2620701835 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2621000152</t>
+          <t>262064416</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46232</v>
+        <v>46229.87569444445</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>ASSAULT - AGGRAVATED</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2299,28 +2299,24 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3500 S 45TH ST</t>
+          <t>HUNTINGTON AVE</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>47.216421</v>
+        <v>42.34221543503831</v>
       </c>
       <c r="K12" t="n">
-        <v>-122.482428</v>
+        <v>-71.08577074656198</v>
       </c>
       <c r="L12" t="n">
-        <v>1074.3</v>
+        <v>898.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 29, 2026, 1074 m from Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - aggravated on Jul 26, 2026, 899 m from Copley Place (HUNTINGTON AVE). Case #262064416 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2342,15 +2338,15 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>71894237115</t>
+          <t>71878728447</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46231.20833333334</v>
+        <v>46230.4375</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2365,51 +2361,51 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>16XX BLOCK OF N 105TH ST</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>47.70668788</v>
+        <v>47.70504225</v>
       </c>
       <c r="K13" t="n">
-        <v>-122.311189997702</v>
+        <v>-122.338094779232</v>
       </c>
       <c r="L13" t="n">
-        <v>1145.7</v>
+        <v>938.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>71889871382</t>
+          <t>2621000152</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46231.00625</v>
+        <v>46232</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Simple Assault</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2419,56 +2415,56 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ALL OTHER</t>
+          <t>Assault Offenses</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>3500 S 45TH ST</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>47.70668788</v>
+        <v>47.216421</v>
       </c>
       <c r="K14" t="n">
-        <v>-122.311189997702</v>
+        <v>-122.482428</v>
       </c>
       <c r="L14" t="n">
-        <v>1145.7</v>
+        <v>1074.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 29, 2026, 1074 m from Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>26C142249</t>
+          <t>262064432</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46230.75</v>
+        <v>46229.91666666666</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BATTERY ABW</t>
+          <t>ROBBERY</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2476,58 +2472,54 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>SIM_ASSAULT</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S MISSION RD</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>37.6756469679485</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K15" t="n">
-        <v>-97.25850032865422</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L15" t="n">
-        <v>1251.5</v>
+        <v>1123.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064432 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CFS26-164521</t>
+          <t>262064298</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46234.03421296296</v>
+        <v>46229.08611111111</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>FIREARM/WEAPON - LOST</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2535,54 +2527,50 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Assault</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>S MARION RD &amp; W 41ST ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>43.51481738299845</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K16" t="n">
-        <v>-96.79096028032072</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L16" t="n">
-        <v>1322.4</v>
+        <v>1123.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 31, 2026, 1322 m from Empire Mall (S MARION RD &amp; W 41ST ST). Case #CFS26-164521 (use for a records request — full narratives are not published in open data).</t>
+          <t>Firearm/weapon - lost on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064298 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>096140526</t>
+          <t>71894237115</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46232</v>
+        <v>46231.20833333334</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2596,56 +2584,56 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>13A</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1900-1999 POST OAK PARK DR</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>29.74712522681273</v>
+        <v>47.70668788</v>
       </c>
       <c r="K17" t="n">
-        <v>-95.45374747370188</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L17" t="n">
-        <v>1323.4</v>
+        <v>1145.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 29, 2026, 1323 m from Houston Galleria (1900-1999 POST OAK PARK DR). Case #096140526 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675136         </t>
+          <t>71889871382</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46228.97847222222</v>
+        <v>46231.00625</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2653,54 +2641,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ALL OTHER</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5XXX S HARDY DR</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>33.3757495513233</v>
+        <v>47.70668788</v>
       </c>
       <c r="K18" t="n">
-        <v>-111.9531832468173</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L18" t="n">
-        <v>1345.1</v>
+        <v>1145.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>[13b] assault on Jul 25, 2026, 1345 m from Arizona Mills (5XXX S HARDY DR). Case #TE202675136          (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CFS26-164393</t>
+          <t>26C142249</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46233.93733796296</v>
+        <v>46230.75</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>BATTERY ABW</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2710,26 +2702,26 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>SIM_ASSAULT</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>S LARCH AVE &amp; W 43RD ST</t>
+          <t>700 BLOCK OF S MISSION RD</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>43.51319846254545</v>
+        <v>37.6756469679485</v>
       </c>
       <c r="K19" t="n">
-        <v>-96.79336119066248</v>
+        <v>-97.25850032865422</v>
       </c>
       <c r="L19" t="n">
-        <v>1453.4</v>
+        <v>1251.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Assault on Jul 30, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-164393 (use for a records request — full narratives are not published in open data).</t>
+          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2751,15 +2743,15 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CFS26-159792</t>
+          <t>CFS26-164521</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46229.12712962963</v>
+        <v>46234.03421296296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Weapons Violations</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2769,56 +2761,56 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Weapons</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>S LARCH AVE &amp; W 43RD ST</t>
+          <t>S MARION RD &amp; W 41ST ST</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>43.51319846254545</v>
+        <v>43.51481738299845</v>
       </c>
       <c r="K20" t="n">
-        <v>-96.79336119066248</v>
+        <v>-96.79096028032072</v>
       </c>
       <c r="L20" t="n">
-        <v>1453.4</v>
+        <v>1322.4</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Weapons violations on Jul 26, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-159792 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 31, 2026, 1322 m from Empire Mall (S MARION RD &amp; W 41ST ST). Case #CFS26-164521 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2621102013</t>
+          <t>096140526</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2828,321 +2820,309 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>13A</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5400 SOUTH TACOMA WAY</t>
+          <t>1900-1999 POST OAK PARK DR</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>47.206421</v>
+        <v>29.74712522681273</v>
       </c>
       <c r="K21" t="n">
-        <v>-122.483428</v>
+        <v>-95.45374747370188</v>
       </c>
       <c r="L21" t="n">
-        <v>1578</v>
+        <v>1323.4</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 30, 2026, 1578 m from Tacoma Mall (5400 SOUTH TACOMA WAY). Case #2621102013 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 29, 2026, 1323 m from Houston Galleria (1900-1999 POST OAK PARK DR). Case #096140526 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>ARZMILLS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Arizona Mills</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>ARZMILLS:Tempe PD General Offenses</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DP2026415473230300</t>
+          <t xml:space="preserve">TE202675136         </t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46231.47916666666</v>
+        <v>46228.97847222222</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>theft-shoplift</t>
+          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>larceny</t>
-        </is>
-      </c>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15 S STEELE ST</t>
+          <t>5XXX S HARDY DR</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>39.7162154712797</v>
+        <v>33.3757495513233</v>
       </c>
       <c r="K22" t="n">
-        <v>-104.9512928115626</v>
+        <v>-111.9531832468173</v>
       </c>
       <c r="L22" t="n">
-        <v>144.7</v>
+        <v>1345.1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Theft-shoplift on Jul 28, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026415473 (use for a records request — full narratives are not published in open data).</t>
+          <t>[13b] assault on Jul 25, 2026, 1345 m from Arizona Mills (5XXX S HARDY DR). Case #TE202675136          (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DP2026413358260700</t>
+          <t>262064339</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46230.47013888889</v>
+        <v>46229.63333333333</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>fraud-by-telephone</t>
+          <t>ASSAULT - AGGRAVATED</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>white-collar-crime</t>
-        </is>
-      </c>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15 S STEELE ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>39.7162154712797</v>
+        <v>42.33511903946613</v>
       </c>
       <c r="K23" t="n">
-        <v>-104.9512928115626</v>
+        <v>-71.07491709613726</v>
       </c>
       <c r="L23" t="n">
-        <v>144.7</v>
+        <v>1407.3</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Fraud-by-telephone on Jul 27, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP2026413358 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - aggravated on Jul 26, 2026, 1407 m from Copley Place (HARRISON AVE). Case #262064339 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>71913162555</t>
+          <t>CFS26-164393</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46232.82986111111</v>
+        <v>46233.93733796296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>47.7086028</v>
+        <v>43.51319846254545</v>
       </c>
       <c r="K24" t="n">
-        <v>-122.324615154453</v>
+        <v>-96.79336119066248</v>
       </c>
       <c r="L24" t="n">
-        <v>145.2</v>
+        <v>1453.4</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 29, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-222878 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 30, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-164393 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>71898889573</t>
+          <t>CFS26-159792</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46231.625</v>
+        <v>46229.12712962963</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>Weapons Violations</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>PROPERTY CRIME</t>
+          <t>Weapons</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>S LARCH AVE &amp; W 43RD ST</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>47.7086028</v>
+        <v>43.51319846254545</v>
       </c>
       <c r="K25" t="n">
-        <v>-122.324615154453</v>
+        <v>-96.79336119066248</v>
       </c>
       <c r="L25" t="n">
-        <v>145.2</v>
+        <v>1453.4</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221387 (use for a records request — full narratives are not published in open data).</t>
+          <t>Weapons violations on Jul 26, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-159792 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>71899277060</t>
+          <t>262064587</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46231.47569444445</v>
+        <v>46230.5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shoplifting</t>
+          <t>ASSAULT - AGGRAVATED</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>PROPERTY CRIME</t>
-        </is>
-      </c>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4XX BLOCK OF NE NORTHGATE WAY</t>
+          <t>MASSACHUSETTS AVE</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>47.7086028</v>
+        <v>42.3342194178955</v>
       </c>
       <c r="K26" t="n">
-        <v>-122.324615154454</v>
+        <v>-71.07434615707857</v>
       </c>
       <c r="L26" t="n">
-        <v>145.2</v>
+        <v>1513.9</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Shoplifting on Jul 28, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-221174 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - aggravated on Jul 27, 2026, 1514 m from Copley Place (MASSACHUSETTS AVE). Case #262064587 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -3158,12 +3138,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M288"/>
+  <dimension ref="A1:M350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
@@ -19945,30 +19925,30 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>NORFOLKPO</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Norfolk Premium Outlets</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>NORFOLKPO:r7bn-2egr</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>260730001961</t>
+          <t>262064284</t>
         </is>
       </c>
       <c r="E287" s="3" t="n">
-        <v>46233</v>
+        <v>46229.54305555556</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>SHOOT INTO OCCUPIED DWELLING</t>
+          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -19979,51 +19959,51 @@
       <c r="H287" t="inlineStr"/>
       <c r="I287" t="inlineStr">
         <is>
-          <t>1400 DURE RD</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J287" t="n">
-        <v>36.872248203692</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K287" t="n">
-        <v>-76.209734788037</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L287" t="n">
-        <v>1387.8</v>
+        <v>1123.7</v>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Shoot into occupied dwelling on Jul 30, 2026, 1388 m from Norfolk Premium Outlets (1400 DURE RD). Case #260730001961 (use for a records request — full narratives are not published in open data).</t>
+          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064284 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>NORFOLKPO</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Norfolk Premium Outlets</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>NORFOLKPO:r7bn-2egr</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>260730001974</t>
+          <t>262064275</t>
         </is>
       </c>
       <c r="E288" s="3" t="n">
-        <v>46233</v>
+        <v>46229.51111111111</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>HIT &amp; RUN - PERSONAL INJURY</t>
+          <t>FORGERY / COUNTERFEITING</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -20034,26 +20014,3468 @@
       <c r="H288" t="inlineStr"/>
       <c r="I288" t="inlineStr">
         <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J288" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K288" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L288" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>Forgery / counterfeiting on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064275 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>262064650</t>
+        </is>
+      </c>
+      <c r="E289" s="3" t="n">
+        <v>46230.61875</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>M/V ACCIDENT - INVOLVING BICYCLE - INJURY</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>MASSACHUSETTS AVE &amp; TREMONT ST
+BOSTON, MA 02118
+UN</t>
+        </is>
+      </c>
+      <c r="J289" t="n">
+        <v>42.33929095757131</v>
+      </c>
+      <c r="K289" t="n">
+        <v>-71.08041395047391</v>
+      </c>
+      <c r="L289" t="n">
+        <v>953.4</v>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>M/v accident - involving bicycle - injury on Jul 27, 2026, 953 m from Copley Place (MASSACHUSETTS AVE &amp; TREMONT ST
+BOSTON, MA 02118
+UN). Case #262064650 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>262064295</t>
+        </is>
+      </c>
+      <c r="E290" s="3" t="n">
+        <v>46229.54791666667</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J290" t="n">
+        <v>42.34862381555496</v>
+      </c>
+      <c r="K290" t="n">
+        <v>-71.08277637086411</v>
+      </c>
+      <c r="L290" t="n">
+        <v>437.3</v>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 26, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064295 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>262064382</t>
+        </is>
+      </c>
+      <c r="E291" s="3" t="n">
+        <v>46229.78680555556</v>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>VERBAL DISPUTE</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>HUDSON ST</t>
+        </is>
+      </c>
+      <c r="J291" t="n">
+        <v>42.34976401607222</v>
+      </c>
+      <c r="K291" t="n">
+        <v>-71.06045076420118</v>
+      </c>
+      <c r="L291" t="n">
+        <v>1432.1</v>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>Verbal dispute on Jul 26, 2026, 1432 m from Copley Place (HUDSON ST). Case #262064382 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>262064432</t>
+        </is>
+      </c>
+      <c r="E292" s="3" t="n">
+        <v>46229.91666666666</v>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>ROBBERY</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J292" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K292" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L292" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>Robbery on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064432 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>262064822</t>
+        </is>
+      </c>
+      <c r="E293" s="3" t="n">
+        <v>46230.83541666667</v>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PERSON</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>COLUMBUS SQ</t>
+        </is>
+      </c>
+      <c r="J293" t="n">
+        <v>42.34332879779392</v>
+      </c>
+      <c r="K293" t="n">
+        <v>-71.07788857963692</v>
+      </c>
+      <c r="L293" t="n">
+        <v>477.1</v>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>Investigate person on Jul 27, 2026, 477 m from Copley Place (COLUMBUS SQ). Case #262064822 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>262064697</t>
+        </is>
+      </c>
+      <c r="E294" s="3" t="n">
+        <v>46230.70277777778</v>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PERSON</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>MASSACHUSETTS AVE</t>
+        </is>
+      </c>
+      <c r="J294" t="n">
+        <v>42.34867437636976</v>
+      </c>
+      <c r="K294" t="n">
+        <v>-71.08841866225799</v>
+      </c>
+      <c r="L294" t="n">
+        <v>894.2</v>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>Investigate person on Jul 27, 2026, 894 m from Copley Place (MASSACHUSETTS AVE). Case #262064697 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>262064696</t>
+        </is>
+      </c>
+      <c r="E295" s="3" t="n">
+        <v>46230.57777777778</v>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>LARCENY THEFT FROM BUILDING</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr"/>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>LINCOLN ST</t>
+        </is>
+      </c>
+      <c r="J295" t="n">
+        <v>42.35043296884182</v>
+      </c>
+      <c r="K295" t="n">
+        <v>-71.05873157807835</v>
+      </c>
+      <c r="L295" t="n">
+        <v>1584.6</v>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>Larceny theft from building on Jul 27, 2026, 1585 m from Copley Place (LINCOLN ST). Case #262064696 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>262064796</t>
+        </is>
+      </c>
+      <c r="E296" s="3" t="n">
+        <v>46230.75</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>PROPERTY - LOST/ MISSING</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J296" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K296" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L296" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>Property - lost/ missing on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064796 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>262064756</t>
+        </is>
+      </c>
+      <c r="E297" s="3" t="n">
+        <v>46230.80347222222</v>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>ASSAULT - SIMPLE</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr"/>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>MASSACHUSETTS AVE</t>
+        </is>
+      </c>
+      <c r="J297" t="n">
+        <v>42.34439568415441</v>
+      </c>
+      <c r="K297" t="n">
+        <v>-71.08632016344815</v>
+      </c>
+      <c r="L297" t="n">
+        <v>798.7</v>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>Assault - simple on Jul 27, 2026, 799 m from Copley Place (MASSACHUSETTS AVE). Case #262064756 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>262064716</t>
+        </is>
+      </c>
+      <c r="E298" s="3" t="n">
+        <v>46230.72638888889</v>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>LARCENY SHOPLIFTING</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>NEWBURY ST</t>
+        </is>
+      </c>
+      <c r="J298" t="n">
+        <v>42.35059716982988</v>
+      </c>
+      <c r="K298" t="n">
+        <v>-71.07881030689927</v>
+      </c>
+      <c r="L298" t="n">
+        <v>345.4</v>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 27, 2026, 345 m from Copley Place (NEWBURY ST). Case #262064716 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>262064587</t>
+        </is>
+      </c>
+      <c r="E299" s="3" t="n">
+        <v>46230.5</v>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>ASSAULT - AGGRAVATED</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>MASSACHUSETTS AVE</t>
+        </is>
+      </c>
+      <c r="J299" t="n">
+        <v>42.3342194178955</v>
+      </c>
+      <c r="K299" t="n">
+        <v>-71.07434615707857</v>
+      </c>
+      <c r="L299" t="n">
+        <v>1513.9</v>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>Assault - aggravated on Jul 27, 2026, 1514 m from Copley Place (MASSACHUSETTS AVE). Case #262064587 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>262064392</t>
+        </is>
+      </c>
+      <c r="E300" s="3" t="n">
+        <v>46229.82222222222</v>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>M/V ACCIDENT - OTHER</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>TYLER ST</t>
+        </is>
+      </c>
+      <c r="J300" t="n">
+        <v>42.3509005960865</v>
+      </c>
+      <c r="K300" t="n">
+        <v>-71.06068690177561</v>
+      </c>
+      <c r="L300" t="n">
+        <v>1439.7</v>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>M/v accident - other on Jul 26, 2026, 1440 m from Copley Place (TYLER ST). Case #262064392 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>262064350</t>
+        </is>
+      </c>
+      <c r="E301" s="3" t="n">
+        <v>46229.70486111111</v>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PERSON</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>HUNTINGTON AVE</t>
+        </is>
+      </c>
+      <c r="J301" t="n">
+        <v>42.3473097976345</v>
+      </c>
+      <c r="K301" t="n">
+        <v>-71.0791516658207</v>
+      </c>
+      <c r="L301" t="n">
+        <v>129.3</v>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>Investigate person on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064350 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>262064616</t>
+        </is>
+      </c>
+      <c r="E302" s="3" t="n">
+        <v>46230.50347222222</v>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>DRUGS - POSSESSION/ SALE/ MANUFACTURING/ USE</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr"/>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>BOYLSTON SQ</t>
+        </is>
+      </c>
+      <c r="J302" t="n">
+        <v>42.35197501205302</v>
+      </c>
+      <c r="K302" t="n">
+        <v>-71.06332910808086</v>
+      </c>
+      <c r="L302" t="n">
+        <v>1271.5</v>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>Drugs - possession/ sale/ manufacturing/ use on Jul 27, 2026, 1272 m from Copley Place (BOYLSTON SQ). Case #262064616 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>262064640</t>
+        </is>
+      </c>
+      <c r="E303" s="3" t="n">
+        <v>46230.3125</v>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PERSON</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr"/>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J303" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K303" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L303" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>Investigate person on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064640 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>262064573</t>
+        </is>
+      </c>
+      <c r="E304" s="3" t="n">
+        <v>46230.45833333334</v>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>SICK ASSIST - DRUG RELATED ILLNESS</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr"/>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>ALBANY ST</t>
+        </is>
+      </c>
+      <c r="J304" t="n">
+        <v>42.33428840659414</v>
+      </c>
+      <c r="K304" t="n">
+        <v>-71.07239517543796</v>
+      </c>
+      <c r="L304" t="n">
+        <v>1543.1</v>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>Sick assist - drug related illness on Jul 27, 2026, 1543 m from Copley Place (ALBANY ST). Case #262064573 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>262064608</t>
+        </is>
+      </c>
+      <c r="E305" s="3" t="n">
+        <v>46230</v>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>THREATS TO DO BODILY HARM</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr"/>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J305" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K305" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L305" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>Threats to do bodily harm on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064608 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>262064378</t>
+        </is>
+      </c>
+      <c r="E306" s="3" t="n">
+        <v>46229.79097222222</v>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>LARCENY ALL OTHERS</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr"/>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>W CONCORD ST</t>
+        </is>
+      </c>
+      <c r="J306" t="n">
+        <v>42.33961961800693</v>
+      </c>
+      <c r="K306" t="n">
+        <v>-71.07699236739417</v>
+      </c>
+      <c r="L306" t="n">
+        <v>890.6</v>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>Larceny all others on Jul 26, 2026, 891 m from Copley Place (W CONCORD ST). Case #262064378 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>262064152</t>
+        </is>
+      </c>
+      <c r="E307" s="3" t="n">
+        <v>46229.01458333333</v>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>NOISY PARTY/RADIO-NO ARREST</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr"/>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>PHILLIPS ST</t>
+        </is>
+      </c>
+      <c r="J307" t="n">
+        <v>42.36027809483424</v>
+      </c>
+      <c r="K307" t="n">
+        <v>-71.06899804851336</v>
+      </c>
+      <c r="L307" t="n">
+        <v>1576.7</v>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>Noisy party/radio-no arrest on Jul 26, 2026, 1577 m from Copley Place (PHILLIPS ST). Case #262064152 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>262064312</t>
+        </is>
+      </c>
+      <c r="E308" s="3" t="n">
+        <v>46229.60625</v>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>SICK ASSIST - DRUG RELATED ILLNESS</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>ALBANY ST</t>
+        </is>
+      </c>
+      <c r="J308" t="n">
+        <v>42.33428840659414</v>
+      </c>
+      <c r="K308" t="n">
+        <v>-71.07239517543796</v>
+      </c>
+      <c r="L308" t="n">
+        <v>1543.1</v>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>Sick assist - drug related illness on Jul 26, 2026, 1543 m from Copley Place (ALBANY ST). Case #262064312 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>262064770</t>
+        </is>
+      </c>
+      <c r="E309" s="3" t="n">
+        <v>46230.52083333334</v>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>LARCENY THEFT FROM MV - NON-ACCESSORY</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J309" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K309" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L309" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>Larceny theft from mv - non-accessory on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064770 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>262064532</t>
+        </is>
+      </c>
+      <c r="E310" s="3" t="n">
+        <v>46230.29166666666</v>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>PROPERTY - LOST/ MISSING</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J310" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K310" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L310" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>Property - lost/ missing on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064532 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>262064590</t>
+        </is>
+      </c>
+      <c r="E311" s="3" t="n">
+        <v>46230.50625</v>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>LARCENY ALL OTHERS</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr"/>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>W BROOKLINE ST</t>
+        </is>
+      </c>
+      <c r="J311" t="n">
+        <v>42.34172590358821</v>
+      </c>
+      <c r="K311" t="n">
+        <v>-71.07501847816492</v>
+      </c>
+      <c r="L311" t="n">
+        <v>689.2</v>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>Larceny all others on Jul 27, 2026, 689 m from Copley Place (W BROOKLINE ST). Case #262064590 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>262064674</t>
+        </is>
+      </c>
+      <c r="E312" s="3" t="n">
+        <v>46229.33333333334</v>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>PROPERTY - LOST/ MISSING</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr"/>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J312" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K312" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L312" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>Property - lost/ missing on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064674 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>262064591</t>
+        </is>
+      </c>
+      <c r="E313" s="3" t="n">
+        <v>46229.77847222222</v>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PERSON</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr"/>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>AVERY ST</t>
+        </is>
+      </c>
+      <c r="J313" t="n">
+        <v>42.35327560751949</v>
+      </c>
+      <c r="K313" t="n">
+        <v>-71.06345772204415</v>
+      </c>
+      <c r="L313" t="n">
+        <v>1324</v>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>Investigate person on Jul 26, 2026, 1324 m from Copley Place (AVERY ST). Case #262064591 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>262064579</t>
+        </is>
+      </c>
+      <c r="E314" s="3" t="n">
+        <v>46230.43402777778</v>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>SICK/INJURED/MEDICAL - PERSON</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr"/>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>NORTHAMPTON ST</t>
+        </is>
+      </c>
+      <c r="J314" t="n">
+        <v>42.33395124839377</v>
+      </c>
+      <c r="K314" t="n">
+        <v>-71.07538938822692</v>
+      </c>
+      <c r="L314" t="n">
+        <v>1530.5</v>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>Sick/injured/medical - person on Jul 27, 2026, 1531 m from Copley Place (NORTHAMPTON ST). Case #262064579 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>262064357</t>
+        </is>
+      </c>
+      <c r="E315" s="3" t="n">
+        <v>46229.72638888889</v>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>LARCENY SHOPLIFTING</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr"/>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>HUNTINGTON AVE</t>
+        </is>
+      </c>
+      <c r="J315" t="n">
+        <v>42.3473097976345</v>
+      </c>
+      <c r="K315" t="n">
+        <v>-71.0791516658207</v>
+      </c>
+      <c r="L315" t="n">
+        <v>129.3</v>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064357 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>262064198</t>
+        </is>
+      </c>
+      <c r="E316" s="3" t="n">
+        <v>46229.16736111111</v>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>TOWED MOTOR VEHICLE</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr"/>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>STUART ST &amp; CHARLES ST S
+BOSTON, MA 02116
+UNITED S</t>
+        </is>
+      </c>
+      <c r="J316" t="n">
+        <v>42.35095701392956</v>
+      </c>
+      <c r="K316" t="n">
+        <v>-71.06685999332976</v>
+      </c>
+      <c r="L316" t="n">
+        <v>960.1</v>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>Towed motor vehicle on Jul 26, 2026, 960 m from Copley Place (STUART ST &amp; CHARLES ST S
+BOSTON, MA 02116
+UNITED S). Case #262064198 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>262064309</t>
+        </is>
+      </c>
+      <c r="E317" s="3" t="n">
+        <v>46229.39444444444</v>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PERSON</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>SAINT BOTOLPH ST</t>
+        </is>
+      </c>
+      <c r="J317" t="n">
+        <v>42.34617475544754</v>
+      </c>
+      <c r="K317" t="n">
+        <v>-71.07925920373032</v>
+      </c>
+      <c r="L317" t="n">
+        <v>208.6</v>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>Investigate person on Jul 26, 2026, 209 m from Copley Place (SAINT BOTOLPH ST). Case #262064309 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>262064283</t>
+        </is>
+      </c>
+      <c r="E318" s="3" t="n">
+        <v>46229.51736111111</v>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>LARCENY SHOPLIFTING</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>HUNTINGTON AVE</t>
+        </is>
+      </c>
+      <c r="J318" t="n">
+        <v>42.3473097976345</v>
+      </c>
+      <c r="K318" t="n">
+        <v>-71.0791516658207</v>
+      </c>
+      <c r="L318" t="n">
+        <v>129.3</v>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064283 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>262064226</t>
+        </is>
+      </c>
+      <c r="E319" s="3" t="n">
+        <v>46229.375</v>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>M/V ACCIDENT - PROPERTY DAMAGE</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>BERKELEY ST &amp; SAINT JAMES AVE
+BOSTON, MA 02116
+UNI</t>
+        </is>
+      </c>
+      <c r="J319" t="n">
+        <v>42.3504290420294</v>
+      </c>
+      <c r="K319" t="n">
+        <v>-71.07264798093048</v>
+      </c>
+      <c r="L319" t="n">
+        <v>515.5</v>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>M/v accident - property damage on Jul 26, 2026, 515 m from Copley Place (BERKELEY ST &amp; SAINT JAMES AVE
+BOSTON, MA 02116
+UNI). Case #262064226 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>262064268</t>
+        </is>
+      </c>
+      <c r="E320" s="3" t="n">
+        <v>46229.48680555556</v>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>LARCENY THEFT FROM BUILDING</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>REED ST &amp; E LENOX ST
+ROXBURY, MA 02118
+UNITED STAT</t>
+        </is>
+      </c>
+      <c r="J320" t="n">
+        <v>42.33406097367816</v>
+      </c>
+      <c r="K320" t="n">
+        <v>-71.07756301316894</v>
+      </c>
+      <c r="L320" t="n">
+        <v>1507.2</v>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>Larceny theft from building on Jul 26, 2026, 1507 m from Copley Place (REED ST &amp; E LENOX ST
+ROXBURY, MA 02118
+UNITED STAT). Case #262064268 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>262064394</t>
+        </is>
+      </c>
+      <c r="E321" s="3" t="n">
+        <v>46229.82152777778</v>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>M/V ACCIDENT - OTHER</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>HARRISON AVE &amp; PLYMPTON ST
+BOSTON, MA 02118
+UNITED</t>
+        </is>
+      </c>
+      <c r="J321" t="n">
+        <v>42.33973998780085</v>
+      </c>
+      <c r="K321" t="n">
+        <v>-71.0691099454142</v>
+      </c>
+      <c r="L321" t="n">
+        <v>1121.4</v>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>M/v accident - other on Jul 26, 2026, 1121 m from Copley Place (HARRISON AVE &amp; PLYMPTON ST
+BOSTON, MA 02118
+UNITED). Case #262064394 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>262064321</t>
+        </is>
+      </c>
+      <c r="E322" s="3" t="n">
+        <v>46229.59166666667</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>M/V - LEAVING SCENE - PROPERTY DAMAGE</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J322" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K322" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L322" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>M/v - leaving scene - property damage on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064321 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>262064179</t>
+        </is>
+      </c>
+      <c r="E323" s="3" t="n">
+        <v>46229.07361111111</v>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PROPERTY</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J323" t="n">
+        <v>42.35234109431519</v>
+      </c>
+      <c r="K323" t="n">
+        <v>-71.06432465046424</v>
+      </c>
+      <c r="L323" t="n">
+        <v>1213.3</v>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>Investigate property on Jul 26, 2026, 1213 m from Copley Place (BOYLSTON ST). Case #262064179 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>262064772</t>
+        </is>
+      </c>
+      <c r="E324" s="3" t="n">
+        <v>46230.82569444444</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>LARCENY SHOPLIFTING</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J324" t="n">
+        <v>42.34862381555496</v>
+      </c>
+      <c r="K324" t="n">
+        <v>-71.08277637086411</v>
+      </c>
+      <c r="L324" t="n">
+        <v>437.3</v>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 27, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064772 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>262064289</t>
+        </is>
+      </c>
+      <c r="E325" s="3" t="n">
+        <v>46229.54583333333</v>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>LARCENY SHOPLIFTING</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J325" t="n">
+        <v>42.35095908794595</v>
+      </c>
+      <c r="K325" t="n">
+        <v>-71.07412780075079</v>
+      </c>
+      <c r="L325" t="n">
+        <v>470.3</v>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 26, 2026, 470 m from Copley Place (BOYLSTON ST). Case #262064289 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>262064298</t>
+        </is>
+      </c>
+      <c r="E326" s="3" t="n">
+        <v>46229.08611111111</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>FIREARM/WEAPON - LOST</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr"/>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J326" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K326" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L326" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>Firearm/weapon - lost on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064298 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>262064416</t>
+        </is>
+      </c>
+      <c r="E327" s="3" t="n">
+        <v>46229.87569444445</v>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>ASSAULT - AGGRAVATED</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>HUNTINGTON AVE</t>
+        </is>
+      </c>
+      <c r="J327" t="n">
+        <v>42.34221543503831</v>
+      </c>
+      <c r="K327" t="n">
+        <v>-71.08577074656198</v>
+      </c>
+      <c r="L327" t="n">
+        <v>898.8</v>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>Assault - aggravated on Jul 26, 2026, 899 m from Copley Place (HUNTINGTON AVE). Case #262064416 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>262064700</t>
+        </is>
+      </c>
+      <c r="E328" s="3" t="n">
+        <v>46230.71458333333</v>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>BREAKING AND ENTERING (B&amp;E) MOTOR VEHICLE</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr"/>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J328" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K328" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L328" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>Breaking and entering (b&amp;e) motor vehicle on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064700 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>262064491</t>
+        </is>
+      </c>
+      <c r="E329" s="3" t="n">
+        <v>46230.22916666666</v>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>LARCENY ALL OTHERS</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>RUTLAND ST</t>
+        </is>
+      </c>
+      <c r="J329" t="n">
+        <v>42.34020387362647</v>
+      </c>
+      <c r="K329" t="n">
+        <v>-71.07645111113312</v>
+      </c>
+      <c r="L329" t="n">
+        <v>829.8</v>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>Larceny all others on Jul 27, 2026, 830 m from Copley Place (RUTLAND ST). Case #262064491 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>262064492</t>
+        </is>
+      </c>
+      <c r="E330" s="3" t="n">
+        <v>46230.10972222222</v>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>VANDALISM</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr"/>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>NORTHAMPTON ST</t>
+        </is>
+      </c>
+      <c r="J330" t="n">
+        <v>42.33798932384219</v>
+      </c>
+      <c r="K330" t="n">
+        <v>-71.08003745874711</v>
+      </c>
+      <c r="L330" t="n">
+        <v>1088.4</v>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>Vandalism on Jul 27, 2026, 1088 m from Copley Place (NORTHAMPTON ST). Case #262064492 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>262064766</t>
+        </is>
+      </c>
+      <c r="E331" s="3" t="n">
+        <v>46230.75416666667</v>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>PROPERTY - LOST/ MISSING</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>COLUMBUS AVE</t>
+        </is>
+      </c>
+      <c r="J331" t="n">
+        <v>42.34294800069079</v>
+      </c>
+      <c r="K331" t="n">
+        <v>-71.07888700104606</v>
+      </c>
+      <c r="L331" t="n">
+        <v>529.1</v>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>Property - lost/ missing on Jul 27, 2026, 529 m from Copley Place (COLUMBUS AVE). Case #262064766 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>262064548</t>
+        </is>
+      </c>
+      <c r="E332" s="3" t="n">
+        <v>46230.44236111111</v>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>M/V - LEAVING SCENE - PROPERTY DAMAGE</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr"/>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J332" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K332" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L332" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>M/v - leaving scene - property damage on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064548 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>262064504</t>
+        </is>
+      </c>
+      <c r="E333" s="3" t="n">
+        <v>46230.34791666667</v>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>LARCENY SHOPLIFTING</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr"/>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>CHARLES ST</t>
+        </is>
+      </c>
+      <c r="J333" t="n">
+        <v>42.36064469554803</v>
+      </c>
+      <c r="K333" t="n">
+        <v>-71.07086192011141</v>
+      </c>
+      <c r="L333" t="n">
+        <v>1552</v>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 27, 2026, 1552 m from Copley Place (CHARLES ST). Case #262064504 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>262064506</t>
+        </is>
+      </c>
+      <c r="E334" s="3" t="n">
+        <v>46230.34375</v>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr"/>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J334" t="n">
+        <v>42.35037869977646</v>
+      </c>
+      <c r="K334" t="n">
+        <v>-71.07626098382806</v>
+      </c>
+      <c r="L334" t="n">
+        <v>327.3</v>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 27, 2026, 327 m from Copley Place (BOYLSTON ST). Case #262064506 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>262064752</t>
+        </is>
+      </c>
+      <c r="E335" s="3" t="n">
+        <v>46230.79166666666</v>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>STOLEN PROPERTY - BUYING / RECEIVING / POSSESSING</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr"/>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>HUDSON ST</t>
+        </is>
+      </c>
+      <c r="J335" t="n">
+        <v>42.35074197291232</v>
+      </c>
+      <c r="K335" t="n">
+        <v>-71.06006134581432</v>
+      </c>
+      <c r="L335" t="n">
+        <v>1485.3</v>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>Stolen property - buying / receiving / possessing on Jul 27, 2026, 1485 m from Copley Place (HUDSON ST). Case #262064752 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>262064383</t>
+        </is>
+      </c>
+      <c r="E336" s="3" t="n">
+        <v>46229.79375</v>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr"/>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST &amp; DALTON ST
+BOSTON, MA 02115
+UNITED ST</t>
+        </is>
+      </c>
+      <c r="J336" t="n">
+        <v>42.34787097987171</v>
+      </c>
+      <c r="K336" t="n">
+        <v>-71.08556796747074</v>
+      </c>
+      <c r="L336" t="n">
+        <v>652.7</v>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 653 m from Copley Place (BOYLSTON ST &amp; DALTON ST
+BOSTON, MA 02115
+UNITED ST). Case #262064383 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>262064391</t>
+        </is>
+      </c>
+      <c r="E337" s="3" t="n">
+        <v>46229.83125</v>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>DRUGS - POSSESSION/ SALE/ MANUFACTURING/ USE</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr"/>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOYLSTON ST &amp; BOYLSTON SQ
+BOSTON, MA 02111
+UNITED </t>
+        </is>
+      </c>
+      <c r="J337" t="n">
+        <v>42.35231098936428</v>
+      </c>
+      <c r="K337" t="n">
+        <v>-71.06350996526169</v>
+      </c>
+      <c r="L337" t="n">
+        <v>1272.6</v>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>Drugs - possession/ sale/ manufacturing/ use on Jul 26, 2026, 1273 m from Copley Place (BOYLSTON ST &amp; BOYLSTON SQ
+BOSTON, MA 02111
+UNITED ). Case #262064391 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>262064802</t>
+        </is>
+      </c>
+      <c r="E338" s="3" t="n">
+        <v>46230.89583333334</v>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>LARCENY SHOPLIFTING</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr"/>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J338" t="n">
+        <v>42.34862381555496</v>
+      </c>
+      <c r="K338" t="n">
+        <v>-71.08277637086411</v>
+      </c>
+      <c r="L338" t="n">
+        <v>437.3</v>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 27, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064802 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>262064409</t>
+        </is>
+      </c>
+      <c r="E339" s="3" t="n">
+        <v>46229.85833333333</v>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>OXFORD ST</t>
+        </is>
+      </c>
+      <c r="J339" t="n">
+        <v>42.35193460488232</v>
+      </c>
+      <c r="K339" t="n">
+        <v>-71.06048592223925</v>
+      </c>
+      <c r="L339" t="n">
+        <v>1488.7</v>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 26, 2026, 1489 m from Copley Place (OXFORD ST). Case #262064409 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>262064318</t>
+        </is>
+      </c>
+      <c r="E340" s="3" t="n">
+        <v>46229.53958333333</v>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PERSON</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr"/>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>SHAWMUT AVE</t>
+        </is>
+      </c>
+      <c r="J340" t="n">
+        <v>42.34319452771496</v>
+      </c>
+      <c r="K340" t="n">
+        <v>-71.06880536524001</v>
+      </c>
+      <c r="L340" t="n">
+        <v>876.3</v>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>Investigate person on Jul 26, 2026, 876 m from Copley Place (SHAWMUT AVE). Case #262064318 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>262064412</t>
+        </is>
+      </c>
+      <c r="E341" s="3" t="n">
+        <v>46229.87638888889</v>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>SICK/INJURED/MEDICAL - PERSON</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr"/>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>TREMONT ST</t>
+        </is>
+      </c>
+      <c r="J341" t="n">
+        <v>42.35428377241487</v>
+      </c>
+      <c r="K341" t="n">
+        <v>-71.06380403747467</v>
+      </c>
+      <c r="L341" t="n">
+        <v>1356.9</v>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>Sick/injured/medical - person on Jul 26, 2026, 1357 m from Copley Place (TREMONT ST). Case #262064412 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>262064362</t>
+        </is>
+      </c>
+      <c r="E342" s="3" t="n">
+        <v>46229.64305555556</v>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr"/>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>DARTMOUTH ST</t>
+        </is>
+      </c>
+      <c r="J342" t="n">
+        <v>42.35029374297969</v>
+      </c>
+      <c r="K342" t="n">
+        <v>-71.07744671381569</v>
+      </c>
+      <c r="L342" t="n">
+        <v>298.2</v>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 298 m from Copley Place (DARTMOUTH ST). Case #262064362 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>262064307</t>
+        </is>
+      </c>
+      <c r="E343" s="3" t="n">
+        <v>46229.59027777778</v>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr"/>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>TREMONT ST &amp; TEMPLE PL
+BOSTON, MA 02111
+UNITED STA</t>
+        </is>
+      </c>
+      <c r="J343" t="n">
+        <v>42.35561100811422</v>
+      </c>
+      <c r="K343" t="n">
+        <v>-71.06289400004533</v>
+      </c>
+      <c r="L343" t="n">
+        <v>1502.5</v>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 26, 2026, 1502 m from Copley Place (TREMONT ST &amp; TEMPLE PL
+BOSTON, MA 02111
+UNITED STA). Case #262064307 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>262064419</t>
+        </is>
+      </c>
+      <c r="E344" s="3" t="n">
+        <v>46229.90138888889</v>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>HARASSMENT/ CRIMINAL HARASSMENT</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>NASSAU ST</t>
+        </is>
+      </c>
+      <c r="J344" t="n">
+        <v>42.34880604399623</v>
+      </c>
+      <c r="K344" t="n">
+        <v>-71.06285446968663</v>
+      </c>
+      <c r="L344" t="n">
+        <v>1221.7</v>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>Harassment/ criminal harassment on Jul 26, 2026, 1222 m from Copley Place (NASSAU ST). Case #262064419 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>262064339</t>
+        </is>
+      </c>
+      <c r="E345" s="3" t="n">
+        <v>46229.63333333333</v>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>ASSAULT - AGGRAVATED</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr"/>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J345" t="n">
+        <v>42.33511903946613</v>
+      </c>
+      <c r="K345" t="n">
+        <v>-71.07491709613726</v>
+      </c>
+      <c r="L345" t="n">
+        <v>1407.3</v>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>Assault - aggravated on Jul 26, 2026, 1407 m from Copley Place (HARRISON AVE). Case #262064339 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>262064236</t>
+        </is>
+      </c>
+      <c r="E346" s="3" t="n">
+        <v>46229.37638888889</v>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr"/>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>TREMONT ST</t>
+        </is>
+      </c>
+      <c r="J346" t="n">
+        <v>42.34470135794417</v>
+      </c>
+      <c r="K346" t="n">
+        <v>-71.0703760849388</v>
+      </c>
+      <c r="L346" t="n">
+        <v>678.7</v>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 26, 2026, 679 m from Copley Place (TREMONT ST). Case #262064236 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>262064234</t>
+        </is>
+      </c>
+      <c r="E347" s="3" t="n">
+        <v>46229.31944444445</v>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PERSON</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr"/>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>SAINT JAMES AVE</t>
+        </is>
+      </c>
+      <c r="J347" t="n">
+        <v>42.34947585701249</v>
+      </c>
+      <c r="K347" t="n">
+        <v>-71.07640149637847</v>
+      </c>
+      <c r="L347" t="n">
+        <v>230.3</v>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>Investigate person on Jul 26, 2026, 230 m from Copley Place (SAINT JAMES AVE). Case #262064234 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>NORFOLKPO</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Norfolk Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>NORFOLKPO:r7bn-2egr</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>260730001961</t>
+        </is>
+      </c>
+      <c r="E348" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>SHOOT INTO OCCUPIED DWELLING</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr"/>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>1400 DURE RD</t>
+        </is>
+      </c>
+      <c r="J348" t="n">
+        <v>36.872248203692</v>
+      </c>
+      <c r="K348" t="n">
+        <v>-76.209734788037</v>
+      </c>
+      <c r="L348" t="n">
+        <v>1387.8</v>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>Shoot into occupied dwelling on Jul 30, 2026, 1388 m from Norfolk Premium Outlets (1400 DURE RD). Case #260730001961 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>NORFOLKPO</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Norfolk Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>NORFOLKPO:r7bn-2egr</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>260730001974</t>
+        </is>
+      </c>
+      <c r="E349" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>HIT &amp; RUN - PERSONAL INJURY</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr"/>
+      <c r="I349" t="inlineStr">
+        <is>
           <t>2500 MILITARY HIGHWAY</t>
         </is>
       </c>
-      <c r="J288" t="n">
+      <c r="J349" t="n">
         <v>36.879766119132</v>
       </c>
-      <c r="K288" t="n">
+      <c r="K349" t="n">
         <v>-76.212427576002</v>
       </c>
-      <c r="L288" t="n">
+      <c r="L349" t="n">
         <v>1118.9</v>
       </c>
-      <c r="M288" t="inlineStr">
+      <c r="M349" t="inlineStr">
         <is>
           <t>Hit &amp; run - personal injury on Jul 30, 2026, 1119 m from Norfolk Premium Outlets (2500 MILITARY HIGHWAY). Case #260730001974 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>NORFOLKPO</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Norfolk Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>NORFOLKPO:r7bn-2egr</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>260726001633</t>
+        </is>
+      </c>
+      <c r="E350" s="3" t="n">
+        <v>46229</v>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>ABDUCTION</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr"/>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>1500 MILITARY HIGHWAY</t>
+        </is>
+      </c>
+      <c r="J350" t="n">
+        <v>36.875468779419</v>
+      </c>
+      <c r="K350" t="n">
+        <v>-76.210483896081</v>
+      </c>
+      <c r="L350" t="n">
+        <v>1176.8</v>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>Abduction on Jul 26, 2026, 1177 m from Norfolk Premium Outlets (1500 MILITARY HIGHWAY). Case #260726001633 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M288"/>
+  <autoFilter ref="A1:M350"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20068,7 +23490,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20091,7 +23513,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 04:58:47.637225+00:00</t>
+          <t>2026-08-01 05:00:58.075328+00:00</t>
         </is>
       </c>
     </row>
@@ -20123,7 +23545,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 04:58:47.637225+00:00</t>
+          <t>2026-07-25 05:00:58.075328+00:00</t>
         </is>
       </c>
     </row>
@@ -20134,7 +23556,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>287</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7">
@@ -20144,7 +23566,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
@@ -20419,7 +23841,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FAILED fetched=0 truncated=False CKAN fetch failed for b973d8cb-eeb2-4e7e-99da-c92938efc9c0: HTTP 403 for https://data.boston.gov/api/3/action/datastore_search_sql?sql=SELECT+%2A+FROM+%22b973d8cb-eeb2-4e7e-99da-c92938efc9c0%22+WHERE+CAST%28NULLIF%28%22Lat%22%2C+%27%27%29+AS+float8%29+BETWEEN+42.3332261543053+AND+42.3620044456947+AND+CAST%28NULLIF%28%22Long%22%2C+%27%27%29+AS+float8%29+BETWEEN+-71.09710221911952+AND+-71.05816378088049+AND+%22OCCURRED_ON_DATE%22+%3E%3D+%272026-07-25T04%3A58%3A47%27+LIMIT+5000 :: {"help": "https://data.boston.gov/api/3/action/help_show?name=datastore_search_sql", "error": {"__type": "Authorization Error", "message": "Access denied: {'permissions': ['Not authorized to call function NULLIF']}"}, "success": false}</t>
+          <t>OK fetched=67 truncated=False</t>
         </is>
       </c>
     </row>
@@ -20431,7 +23853,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FAILED fetched=0 truncated=False CKAN fetch failed for b973d8cb-eeb2-4e7e-99da-c92938efc9c0: HTTP 403 for https://data.boston.gov/api/3/action/datastore_search_sql?sql=SELECT+%2A+FROM+%22b973d8cb-eeb2-4e7e-99da-c92938efc9c0%22+WHERE+CAST%28NULLIF%28%22Lat%22%2C+%27%27%29+AS+float8%29+BETWEEN+42.3071233543053+AND+42.3359016456947+AND+CAST%28NULLIF%28%22Long%22%2C+%27%27%29+AS+float8%29+BETWEEN+-71.19513294012805+AND+-71.15621065987196+AND+%22OCCURRED_ON_DATE%22+%3E%3D+%272026-07-25T04%3A58%3A47%27+LIMIT+5000 :: {"help": "https://data.boston.gov/api/3/action/help_show?name=datastore_search_sql", "error": {"__type": "Authorization Error", "message": "Access denied: {'permissions': ['Not authorized to call function NULLIF']}"}, "success": false}</t>
+          <t>OK fetched=0 truncated=False</t>
         </is>
       </c>
     </row>

--- a/reports/2026-08-01/blotter_report.xlsx
+++ b/reports/2026-08-01/blotter_report.xlsx
@@ -19940,40 +19940,40 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>262064284</t>
+          <t>262064179</t>
         </is>
       </c>
       <c r="E287" s="3" t="n">
-        <v>46229.54305555556</v>
+        <v>46229.07361111111</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
+          <t>INVESTIGATE PROPERTY</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H287" t="inlineStr"/>
       <c r="I287" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>BOYLSTON ST</t>
         </is>
       </c>
       <c r="J287" t="n">
-        <v>42.33954198983015</v>
+        <v>42.35234109431519</v>
       </c>
       <c r="K287" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.06432465046424</v>
       </c>
       <c r="L287" t="n">
-        <v>1123.7</v>
+        <v>1213.3</v>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064284 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate property on Jul 26, 2026, 1213 m from Copley Place (BOYLSTON ST). Case #262064179 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -19995,15 +19995,15 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>262064275</t>
+          <t>262064284</t>
         </is>
       </c>
       <c r="E288" s="3" t="n">
-        <v>46229.51111111111</v>
+        <v>46229.54305555556</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>FORGERY / COUNTERFEITING</t>
+          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -20028,7 +20028,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Forgery / counterfeiting on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064275 (use for a records request — full narratives are not published in open data).</t>
+          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064284 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20050,15 +20050,15 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>262064650</t>
+          <t>262064275</t>
         </is>
       </c>
       <c r="E289" s="3" t="n">
-        <v>46230.61875</v>
+        <v>46229.51111111111</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>M/V ACCIDENT - INVOLVING BICYCLE - INJURY</t>
+          <t>FORGERY / COUNTERFEITING</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -20068,22 +20068,77 @@
       </c>
       <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J289" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K289" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L289" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>Forgery / counterfeiting on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064275 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>262064650</t>
+        </is>
+      </c>
+      <c r="E290" s="3" t="n">
+        <v>46230.61875</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>M/V ACCIDENT - INVOLVING BICYCLE - INJURY</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr">
         <is>
           <t>MASSACHUSETTS AVE &amp; TREMONT ST
 BOSTON, MA 02118
 UN</t>
         </is>
       </c>
-      <c r="J289" t="n">
+      <c r="J290" t="n">
         <v>42.33929095757131</v>
       </c>
-      <c r="K289" t="n">
+      <c r="K290" t="n">
         <v>-71.08041395047391</v>
       </c>
-      <c r="L289" t="n">
+      <c r="L290" t="n">
         <v>953.4</v>
       </c>
-      <c r="M289" t="inlineStr">
+      <c r="M290" t="inlineStr">
         <is>
           <t>M/v accident - involving bicycle - injury on Jul 27, 2026, 953 m from Copley Place (MASSACHUSETTS AVE &amp; TREMONT ST
 BOSTON, MA 02118
@@ -20091,61 +20146,6 @@
         </is>
       </c>
     </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>262064295</t>
-        </is>
-      </c>
-      <c r="E290" s="3" t="n">
-        <v>46229.54791666667</v>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>SICK ASSIST</t>
-        </is>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H290" t="inlineStr"/>
-      <c r="I290" t="inlineStr">
-        <is>
-          <t>BOYLSTON ST</t>
-        </is>
-      </c>
-      <c r="J290" t="n">
-        <v>42.34862381555496</v>
-      </c>
-      <c r="K290" t="n">
-        <v>-71.08277637086411</v>
-      </c>
-      <c r="L290" t="n">
-        <v>437.3</v>
-      </c>
-      <c r="M290" t="inlineStr">
-        <is>
-          <t>Sick assist on Jul 26, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064295 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
@@ -20164,15 +20164,15 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>262064382</t>
+          <t>262064295</t>
         </is>
       </c>
       <c r="E291" s="3" t="n">
-        <v>46229.78680555556</v>
+        <v>46229.54791666667</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>VERBAL DISPUTE</t>
+          <t>SICK ASSIST</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -20183,21 +20183,21 @@
       <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr">
         <is>
-          <t>HUDSON ST</t>
+          <t>BOYLSTON ST</t>
         </is>
       </c>
       <c r="J291" t="n">
-        <v>42.34976401607222</v>
+        <v>42.34862381555496</v>
       </c>
       <c r="K291" t="n">
-        <v>-71.06045076420118</v>
+        <v>-71.08277637086411</v>
       </c>
       <c r="L291" t="n">
-        <v>1432.1</v>
+        <v>437.3</v>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Verbal dispute on Jul 26, 2026, 1432 m from Copley Place (HUDSON ST). Case #262064382 (use for a records request — full narratives are not published in open data).</t>
+          <t>Sick assist on Jul 26, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064295 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20219,40 +20219,40 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>262064432</t>
+          <t>262064382</t>
         </is>
       </c>
       <c r="E292" s="3" t="n">
-        <v>46229.91666666666</v>
+        <v>46229.78680555556</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>ROBBERY</t>
+          <t>VERBAL DISPUTE</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>HUDSON ST</t>
         </is>
       </c>
       <c r="J292" t="n">
-        <v>42.33954198983015</v>
+        <v>42.34976401607222</v>
       </c>
       <c r="K292" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.06045076420118</v>
       </c>
       <c r="L292" t="n">
-        <v>1123.7</v>
+        <v>1432.1</v>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Robbery on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064432 (use for a records request — full narratives are not published in open data).</t>
+          <t>Verbal dispute on Jul 26, 2026, 1432 m from Copley Place (HUDSON ST). Case #262064382 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20274,40 +20274,40 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>262064822</t>
+          <t>262064432</t>
         </is>
       </c>
       <c r="E293" s="3" t="n">
-        <v>46230.83541666667</v>
+        <v>46229.91666666666</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>INVESTIGATE PERSON</t>
+          <t>ROBBERY</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr">
         <is>
-          <t>COLUMBUS SQ</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J293" t="n">
-        <v>42.34332879779392</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K293" t="n">
-        <v>-71.07788857963692</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L293" t="n">
-        <v>477.1</v>
+        <v>1123.7</v>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Investigate person on Jul 27, 2026, 477 m from Copley Place (COLUMBUS SQ). Case #262064822 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064432 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20329,11 +20329,11 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>262064697</t>
+          <t>262064822</t>
         </is>
       </c>
       <c r="E294" s="3" t="n">
-        <v>46230.70277777778</v>
+        <v>46230.83541666667</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -20348,21 +20348,21 @@
       <c r="H294" t="inlineStr"/>
       <c r="I294" t="inlineStr">
         <is>
-          <t>MASSACHUSETTS AVE</t>
+          <t>COLUMBUS SQ</t>
         </is>
       </c>
       <c r="J294" t="n">
-        <v>42.34867437636976</v>
+        <v>42.34332879779392</v>
       </c>
       <c r="K294" t="n">
-        <v>-71.08841866225799</v>
+        <v>-71.07788857963692</v>
       </c>
       <c r="L294" t="n">
-        <v>894.2</v>
+        <v>477.1</v>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Investigate person on Jul 27, 2026, 894 m from Copley Place (MASSACHUSETTS AVE). Case #262064697 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 27, 2026, 477 m from Copley Place (COLUMBUS SQ). Case #262064822 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20384,40 +20384,40 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>262064696</t>
+          <t>262064697</t>
         </is>
       </c>
       <c r="E295" s="3" t="n">
-        <v>46230.57777777778</v>
+        <v>46230.70277777778</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>LARCENY THEFT FROM BUILDING</t>
+          <t>INVESTIGATE PERSON</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr">
         <is>
-          <t>LINCOLN ST</t>
+          <t>MASSACHUSETTS AVE</t>
         </is>
       </c>
       <c r="J295" t="n">
-        <v>42.35043296884182</v>
+        <v>42.34867437636976</v>
       </c>
       <c r="K295" t="n">
-        <v>-71.05873157807835</v>
+        <v>-71.08841866225799</v>
       </c>
       <c r="L295" t="n">
-        <v>1584.6</v>
+        <v>894.2</v>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Larceny theft from building on Jul 27, 2026, 1585 m from Copley Place (LINCOLN ST). Case #262064696 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 27, 2026, 894 m from Copley Place (MASSACHUSETTS AVE). Case #262064697 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20439,15 +20439,15 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>262064796</t>
+          <t>262064696</t>
         </is>
       </c>
       <c r="E296" s="3" t="n">
-        <v>46230.75</v>
+        <v>46230.57777777778</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>PROPERTY - LOST/ MISSING</t>
+          <t>LARCENY THEFT FROM BUILDING</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -20458,21 +20458,21 @@
       <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>LINCOLN ST</t>
         </is>
       </c>
       <c r="J296" t="n">
-        <v>42.33954198983015</v>
+        <v>42.35043296884182</v>
       </c>
       <c r="K296" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.05873157807835</v>
       </c>
       <c r="L296" t="n">
-        <v>1123.7</v>
+        <v>1584.6</v>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Property - lost/ missing on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064796 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny theft from building on Jul 27, 2026, 1585 m from Copley Place (LINCOLN ST). Case #262064696 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20494,40 +20494,40 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>262064756</t>
+          <t>262064796</t>
         </is>
       </c>
       <c r="E297" s="3" t="n">
-        <v>46230.80347222222</v>
+        <v>46230.75</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>ASSAULT - SIMPLE</t>
+          <t>PROPERTY - LOST/ MISSING</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H297" t="inlineStr"/>
       <c r="I297" t="inlineStr">
         <is>
-          <t>MASSACHUSETTS AVE</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J297" t="n">
-        <v>42.34439568415441</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K297" t="n">
-        <v>-71.08632016344815</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L297" t="n">
-        <v>798.7</v>
+        <v>1123.7</v>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Assault - simple on Jul 27, 2026, 799 m from Copley Place (MASSACHUSETTS AVE). Case #262064756 (use for a records request — full narratives are not published in open data).</t>
+          <t>Property - lost/ missing on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064796 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20549,40 +20549,40 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>262064716</t>
+          <t>262064756</t>
         </is>
       </c>
       <c r="E298" s="3" t="n">
-        <v>46230.72638888889</v>
+        <v>46230.80347222222</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>LARCENY SHOPLIFTING</t>
+          <t>ASSAULT - SIMPLE</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H298" t="inlineStr"/>
       <c r="I298" t="inlineStr">
         <is>
-          <t>NEWBURY ST</t>
+          <t>MASSACHUSETTS AVE</t>
         </is>
       </c>
       <c r="J298" t="n">
-        <v>42.35059716982988</v>
+        <v>42.34439568415441</v>
       </c>
       <c r="K298" t="n">
-        <v>-71.07881030689927</v>
+        <v>-71.08632016344815</v>
       </c>
       <c r="L298" t="n">
-        <v>345.4</v>
+        <v>798.7</v>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Larceny shoplifting on Jul 27, 2026, 345 m from Copley Place (NEWBURY ST). Case #262064716 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - simple on Jul 27, 2026, 799 m from Copley Place (MASSACHUSETTS AVE). Case #262064756 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20604,40 +20604,40 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>262064587</t>
+          <t>262064716</t>
         </is>
       </c>
       <c r="E299" s="3" t="n">
-        <v>46230.5</v>
+        <v>46230.72638888889</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>ASSAULT - AGGRAVATED</t>
+          <t>LARCENY SHOPLIFTING</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H299" t="inlineStr"/>
       <c r="I299" t="inlineStr">
         <is>
-          <t>MASSACHUSETTS AVE</t>
+          <t>NEWBURY ST</t>
         </is>
       </c>
       <c r="J299" t="n">
-        <v>42.3342194178955</v>
+        <v>42.35059716982988</v>
       </c>
       <c r="K299" t="n">
-        <v>-71.07434615707857</v>
+        <v>-71.07881030689927</v>
       </c>
       <c r="L299" t="n">
-        <v>1513.9</v>
+        <v>345.4</v>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Assault - aggravated on Jul 27, 2026, 1514 m from Copley Place (MASSACHUSETTS AVE). Case #262064587 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny shoplifting on Jul 27, 2026, 345 m from Copley Place (NEWBURY ST). Case #262064716 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20659,40 +20659,40 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>262064392</t>
+          <t>262064587</t>
         </is>
       </c>
       <c r="E300" s="3" t="n">
-        <v>46229.82222222222</v>
+        <v>46230.5</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>M/V ACCIDENT - OTHER</t>
+          <t>ASSAULT - AGGRAVATED</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H300" t="inlineStr"/>
       <c r="I300" t="inlineStr">
         <is>
-          <t>TYLER ST</t>
+          <t>MASSACHUSETTS AVE</t>
         </is>
       </c>
       <c r="J300" t="n">
-        <v>42.3509005960865</v>
+        <v>42.3342194178955</v>
       </c>
       <c r="K300" t="n">
-        <v>-71.06068690177561</v>
+        <v>-71.07434615707857</v>
       </c>
       <c r="L300" t="n">
-        <v>1439.7</v>
+        <v>1513.9</v>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>M/v accident - other on Jul 26, 2026, 1440 m from Copley Place (TYLER ST). Case #262064392 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - aggravated on Jul 27, 2026, 1514 m from Copley Place (MASSACHUSETTS AVE). Case #262064587 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20714,15 +20714,15 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>262064350</t>
+          <t>262064392</t>
         </is>
       </c>
       <c r="E301" s="3" t="n">
-        <v>46229.70486111111</v>
+        <v>46229.82222222222</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>INVESTIGATE PERSON</t>
+          <t>M/V ACCIDENT - OTHER</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -20733,21 +20733,21 @@
       <c r="H301" t="inlineStr"/>
       <c r="I301" t="inlineStr">
         <is>
-          <t>HUNTINGTON AVE</t>
+          <t>TYLER ST</t>
         </is>
       </c>
       <c r="J301" t="n">
-        <v>42.3473097976345</v>
+        <v>42.3509005960865</v>
       </c>
       <c r="K301" t="n">
-        <v>-71.0791516658207</v>
+        <v>-71.06068690177561</v>
       </c>
       <c r="L301" t="n">
-        <v>129.3</v>
+        <v>1439.7</v>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Investigate person on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064350 (use for a records request — full narratives are not published in open data).</t>
+          <t>M/v accident - other on Jul 26, 2026, 1440 m from Copley Place (TYLER ST). Case #262064392 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20769,40 +20769,40 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>262064616</t>
+          <t>262064350</t>
         </is>
       </c>
       <c r="E302" s="3" t="n">
-        <v>46230.50347222222</v>
+        <v>46229.70486111111</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>DRUGS - POSSESSION/ SALE/ MANUFACTURING/ USE</t>
+          <t>INVESTIGATE PERSON</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr">
         <is>
-          <t>BOYLSTON SQ</t>
+          <t>HUNTINGTON AVE</t>
         </is>
       </c>
       <c r="J302" t="n">
-        <v>42.35197501205302</v>
+        <v>42.3473097976345</v>
       </c>
       <c r="K302" t="n">
-        <v>-71.06332910808086</v>
+        <v>-71.0791516658207</v>
       </c>
       <c r="L302" t="n">
-        <v>1271.5</v>
+        <v>129.3</v>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Drugs - possession/ sale/ manufacturing/ use on Jul 27, 2026, 1272 m from Copley Place (BOYLSTON SQ). Case #262064616 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064350 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20824,40 +20824,40 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>262064640</t>
+          <t>262064616</t>
         </is>
       </c>
       <c r="E303" s="3" t="n">
-        <v>46230.3125</v>
+        <v>46230.50347222222</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>INVESTIGATE PERSON</t>
+          <t>DRUGS - POSSESSION/ SALE/ MANUFACTURING/ USE</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
       <c r="H303" t="inlineStr"/>
       <c r="I303" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>BOYLSTON SQ</t>
         </is>
       </c>
       <c r="J303" t="n">
-        <v>42.33954198983015</v>
+        <v>42.35197501205302</v>
       </c>
       <c r="K303" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.06332910808086</v>
       </c>
       <c r="L303" t="n">
-        <v>1123.7</v>
+        <v>1271.5</v>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Investigate person on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064640 (use for a records request — full narratives are not published in open data).</t>
+          <t>Drugs - possession/ sale/ manufacturing/ use on Jul 27, 2026, 1272 m from Copley Place (BOYLSTON SQ). Case #262064616 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20879,40 +20879,40 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>262064573</t>
+          <t>262064640</t>
         </is>
       </c>
       <c r="E304" s="3" t="n">
-        <v>46230.45833333334</v>
+        <v>46230.3125</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>SICK ASSIST - DRUG RELATED ILLNESS</t>
+          <t>INVESTIGATE PERSON</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr">
         <is>
-          <t>ALBANY ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J304" t="n">
-        <v>42.33428840659414</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K304" t="n">
-        <v>-71.07239517543796</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L304" t="n">
-        <v>1543.1</v>
+        <v>1123.7</v>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Sick assist - drug related illness on Jul 27, 2026, 1543 m from Copley Place (ALBANY ST). Case #262064573 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064640 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20934,40 +20934,40 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>262064608</t>
+          <t>262064573</t>
         </is>
       </c>
       <c r="E305" s="3" t="n">
-        <v>46230</v>
+        <v>46230.45833333334</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>THREATS TO DO BODILY HARM</t>
+          <t>SICK ASSIST - DRUG RELATED ILLNESS</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
       <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>ALBANY ST</t>
         </is>
       </c>
       <c r="J305" t="n">
-        <v>42.33954198983015</v>
+        <v>42.33428840659414</v>
       </c>
       <c r="K305" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.07239517543796</v>
       </c>
       <c r="L305" t="n">
-        <v>1123.7</v>
+        <v>1543.1</v>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Threats to do bodily harm on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064608 (use for a records request — full narratives are not published in open data).</t>
+          <t>Sick assist - drug related illness on Jul 27, 2026, 1543 m from Copley Place (ALBANY ST). Case #262064573 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20989,40 +20989,40 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>262064378</t>
+          <t>262064608</t>
         </is>
       </c>
       <c r="E306" s="3" t="n">
-        <v>46229.79097222222</v>
+        <v>46230</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>LARCENY ALL OTHERS</t>
+          <t>THREATS TO DO BODILY HARM</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H306" t="inlineStr"/>
       <c r="I306" t="inlineStr">
         <is>
-          <t>W CONCORD ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J306" t="n">
-        <v>42.33961961800693</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K306" t="n">
-        <v>-71.07699236739417</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L306" t="n">
-        <v>890.6</v>
+        <v>1123.7</v>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Larceny all others on Jul 26, 2026, 891 m from Copley Place (W CONCORD ST). Case #262064378 (use for a records request — full narratives are not published in open data).</t>
+          <t>Threats to do bodily harm on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064608 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21044,40 +21044,40 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>262064152</t>
+          <t>262064378</t>
         </is>
       </c>
       <c r="E307" s="3" t="n">
-        <v>46229.01458333333</v>
+        <v>46229.79097222222</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>NOISY PARTY/RADIO-NO ARREST</t>
+          <t>LARCENY ALL OTHERS</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr">
         <is>
-          <t>PHILLIPS ST</t>
+          <t>W CONCORD ST</t>
         </is>
       </c>
       <c r="J307" t="n">
-        <v>42.36027809483424</v>
+        <v>42.33961961800693</v>
       </c>
       <c r="K307" t="n">
-        <v>-71.06899804851336</v>
+        <v>-71.07699236739417</v>
       </c>
       <c r="L307" t="n">
-        <v>1576.7</v>
+        <v>890.6</v>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Noisy party/radio-no arrest on Jul 26, 2026, 1577 m from Copley Place (PHILLIPS ST). Case #262064152 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny all others on Jul 26, 2026, 891 m from Copley Place (W CONCORD ST). Case #262064378 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21099,40 +21099,40 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>262064312</t>
+          <t>262064152</t>
         </is>
       </c>
       <c r="E308" s="3" t="n">
-        <v>46229.60625</v>
+        <v>46229.01458333333</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>SICK ASSIST - DRUG RELATED ILLNESS</t>
+          <t>NOISY PARTY/RADIO-NO ARREST</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H308" t="inlineStr"/>
       <c r="I308" t="inlineStr">
         <is>
-          <t>ALBANY ST</t>
+          <t>PHILLIPS ST</t>
         </is>
       </c>
       <c r="J308" t="n">
-        <v>42.33428840659414</v>
+        <v>42.36027809483424</v>
       </c>
       <c r="K308" t="n">
-        <v>-71.07239517543796</v>
+        <v>-71.06899804851336</v>
       </c>
       <c r="L308" t="n">
-        <v>1543.1</v>
+        <v>1576.7</v>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Sick assist - drug related illness on Jul 26, 2026, 1543 m from Copley Place (ALBANY ST). Case #262064312 (use for a records request — full narratives are not published in open data).</t>
+          <t>Noisy party/radio-no arrest on Jul 26, 2026, 1577 m from Copley Place (PHILLIPS ST). Case #262064152 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21154,40 +21154,40 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>262064770</t>
+          <t>262064312</t>
         </is>
       </c>
       <c r="E309" s="3" t="n">
-        <v>46230.52083333334</v>
+        <v>46229.60625</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>LARCENY THEFT FROM MV - NON-ACCESSORY</t>
+          <t>SICK ASSIST - DRUG RELATED ILLNESS</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
       <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>ALBANY ST</t>
         </is>
       </c>
       <c r="J309" t="n">
-        <v>42.33954198983015</v>
+        <v>42.33428840659414</v>
       </c>
       <c r="K309" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.07239517543796</v>
       </c>
       <c r="L309" t="n">
-        <v>1123.7</v>
+        <v>1543.1</v>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Larceny theft from mv - non-accessory on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064770 (use for a records request — full narratives are not published in open data).</t>
+          <t>Sick assist - drug related illness on Jul 26, 2026, 1543 m from Copley Place (ALBANY ST). Case #262064312 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21209,15 +21209,15 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>262064532</t>
+          <t>262064770</t>
         </is>
       </c>
       <c r="E310" s="3" t="n">
-        <v>46230.29166666666</v>
+        <v>46230.52083333334</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>PROPERTY - LOST/ MISSING</t>
+          <t>LARCENY THEFT FROM MV - NON-ACCESSORY</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -21242,7 +21242,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Property - lost/ missing on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064532 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny theft from mv - non-accessory on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064770 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21264,15 +21264,15 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>262064590</t>
+          <t>262064532</t>
         </is>
       </c>
       <c r="E311" s="3" t="n">
-        <v>46230.50625</v>
+        <v>46230.29166666666</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>LARCENY ALL OTHERS</t>
+          <t>PROPERTY - LOST/ MISSING</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -21283,21 +21283,21 @@
       <c r="H311" t="inlineStr"/>
       <c r="I311" t="inlineStr">
         <is>
-          <t>W BROOKLINE ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J311" t="n">
-        <v>42.34172590358821</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K311" t="n">
-        <v>-71.07501847816492</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L311" t="n">
-        <v>689.2</v>
+        <v>1123.7</v>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Larceny all others on Jul 27, 2026, 689 m from Copley Place (W BROOKLINE ST). Case #262064590 (use for a records request — full narratives are not published in open data).</t>
+          <t>Property - lost/ missing on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064532 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21319,15 +21319,15 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>262064674</t>
+          <t>262064590</t>
         </is>
       </c>
       <c r="E312" s="3" t="n">
-        <v>46229.33333333334</v>
+        <v>46230.50625</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>PROPERTY - LOST/ MISSING</t>
+          <t>LARCENY ALL OTHERS</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -21338,21 +21338,21 @@
       <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>W BROOKLINE ST</t>
         </is>
       </c>
       <c r="J312" t="n">
-        <v>42.33954198983015</v>
+        <v>42.34172590358821</v>
       </c>
       <c r="K312" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.07501847816492</v>
       </c>
       <c r="L312" t="n">
-        <v>1123.7</v>
+        <v>689.2</v>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Property - lost/ missing on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064674 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny all others on Jul 27, 2026, 689 m from Copley Place (W BROOKLINE ST). Case #262064590 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21374,40 +21374,40 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>262064591</t>
+          <t>262064674</t>
         </is>
       </c>
       <c r="E313" s="3" t="n">
-        <v>46229.77847222222</v>
+        <v>46229.33333333334</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>INVESTIGATE PERSON</t>
+          <t>PROPERTY - LOST/ MISSING</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H313" t="inlineStr"/>
       <c r="I313" t="inlineStr">
         <is>
-          <t>AVERY ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J313" t="n">
-        <v>42.35327560751949</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K313" t="n">
-        <v>-71.06345772204415</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L313" t="n">
-        <v>1324</v>
+        <v>1123.7</v>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Investigate person on Jul 26, 2026, 1324 m from Copley Place (AVERY ST). Case #262064591 (use for a records request — full narratives are not published in open data).</t>
+          <t>Property - lost/ missing on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064674 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21429,15 +21429,15 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>262064579</t>
+          <t>262064591</t>
         </is>
       </c>
       <c r="E314" s="3" t="n">
-        <v>46230.43402777778</v>
+        <v>46229.77847222222</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>SICK/INJURED/MEDICAL - PERSON</t>
+          <t>INVESTIGATE PERSON</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -21448,21 +21448,21 @@
       <c r="H314" t="inlineStr"/>
       <c r="I314" t="inlineStr">
         <is>
-          <t>NORTHAMPTON ST</t>
+          <t>AVERY ST</t>
         </is>
       </c>
       <c r="J314" t="n">
-        <v>42.33395124839377</v>
+        <v>42.35327560751949</v>
       </c>
       <c r="K314" t="n">
-        <v>-71.07538938822692</v>
+        <v>-71.06345772204415</v>
       </c>
       <c r="L314" t="n">
-        <v>1530.5</v>
+        <v>1324</v>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Sick/injured/medical - person on Jul 27, 2026, 1531 m from Copley Place (NORTHAMPTON ST). Case #262064579 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 26, 2026, 1324 m from Copley Place (AVERY ST). Case #262064591 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21484,40 +21484,40 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>262064357</t>
+          <t>262064579</t>
         </is>
       </c>
       <c r="E315" s="3" t="n">
-        <v>46229.72638888889</v>
+        <v>46230.43402777778</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>LARCENY SHOPLIFTING</t>
+          <t>SICK/INJURED/MEDICAL - PERSON</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H315" t="inlineStr"/>
       <c r="I315" t="inlineStr">
         <is>
-          <t>HUNTINGTON AVE</t>
+          <t>NORTHAMPTON ST</t>
         </is>
       </c>
       <c r="J315" t="n">
-        <v>42.3473097976345</v>
+        <v>42.33395124839377</v>
       </c>
       <c r="K315" t="n">
-        <v>-71.0791516658207</v>
+        <v>-71.07538938822692</v>
       </c>
       <c r="L315" t="n">
-        <v>129.3</v>
+        <v>1530.5</v>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Larceny shoplifting on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064357 (use for a records request — full narratives are not published in open data).</t>
+          <t>Sick/injured/medical - person on Jul 27, 2026, 1531 m from Copley Place (NORTHAMPTON ST). Case #262064579 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21539,15 +21539,15 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>262064198</t>
+          <t>262064802</t>
         </is>
       </c>
       <c r="E316" s="3" t="n">
-        <v>46229.16736111111</v>
+        <v>46230.89583333334</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>TOWED MOTOR VEHICLE</t>
+          <t>LARCENY SHOPLIFTING</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -21557,22 +21557,631 @@
       </c>
       <c r="H316" t="inlineStr"/>
       <c r="I316" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J316" t="n">
+        <v>42.34862381555496</v>
+      </c>
+      <c r="K316" t="n">
+        <v>-71.08277637086411</v>
+      </c>
+      <c r="L316" t="n">
+        <v>437.3</v>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 27, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064802 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>262064409</t>
+        </is>
+      </c>
+      <c r="E317" s="3" t="n">
+        <v>46229.85833333333</v>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>OXFORD ST</t>
+        </is>
+      </c>
+      <c r="J317" t="n">
+        <v>42.35193460488232</v>
+      </c>
+      <c r="K317" t="n">
+        <v>-71.06048592223925</v>
+      </c>
+      <c r="L317" t="n">
+        <v>1488.7</v>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 26, 2026, 1489 m from Copley Place (OXFORD ST). Case #262064409 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>262064318</t>
+        </is>
+      </c>
+      <c r="E318" s="3" t="n">
+        <v>46229.53958333333</v>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PERSON</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>SHAWMUT AVE</t>
+        </is>
+      </c>
+      <c r="J318" t="n">
+        <v>42.34319452771496</v>
+      </c>
+      <c r="K318" t="n">
+        <v>-71.06880536524001</v>
+      </c>
+      <c r="L318" t="n">
+        <v>876.3</v>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>Investigate person on Jul 26, 2026, 876 m from Copley Place (SHAWMUT AVE). Case #262064318 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>262064412</t>
+        </is>
+      </c>
+      <c r="E319" s="3" t="n">
+        <v>46229.87638888889</v>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>SICK/INJURED/MEDICAL - PERSON</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>TREMONT ST</t>
+        </is>
+      </c>
+      <c r="J319" t="n">
+        <v>42.35428377241487</v>
+      </c>
+      <c r="K319" t="n">
+        <v>-71.06380403747467</v>
+      </c>
+      <c r="L319" t="n">
+        <v>1356.9</v>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>Sick/injured/medical - person on Jul 26, 2026, 1357 m from Copley Place (TREMONT ST). Case #262064412 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>262064362</t>
+        </is>
+      </c>
+      <c r="E320" s="3" t="n">
+        <v>46229.64305555556</v>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>DARTMOUTH ST</t>
+        </is>
+      </c>
+      <c r="J320" t="n">
+        <v>42.35029374297969</v>
+      </c>
+      <c r="K320" t="n">
+        <v>-71.07744671381569</v>
+      </c>
+      <c r="L320" t="n">
+        <v>298.2</v>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 298 m from Copley Place (DARTMOUTH ST). Case #262064362 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>262064307</t>
+        </is>
+      </c>
+      <c r="E321" s="3" t="n">
+        <v>46229.59027777778</v>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>TREMONT ST &amp; TEMPLE PL
+BOSTON, MA 02111
+UNITED STA</t>
+        </is>
+      </c>
+      <c r="J321" t="n">
+        <v>42.35561100811422</v>
+      </c>
+      <c r="K321" t="n">
+        <v>-71.06289400004533</v>
+      </c>
+      <c r="L321" t="n">
+        <v>1502.5</v>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 26, 2026, 1502 m from Copley Place (TREMONT ST &amp; TEMPLE PL
+BOSTON, MA 02111
+UNITED STA). Case #262064307 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>262064419</t>
+        </is>
+      </c>
+      <c r="E322" s="3" t="n">
+        <v>46229.90138888889</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>HARASSMENT/ CRIMINAL HARASSMENT</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>NASSAU ST</t>
+        </is>
+      </c>
+      <c r="J322" t="n">
+        <v>42.34880604399623</v>
+      </c>
+      <c r="K322" t="n">
+        <v>-71.06285446968663</v>
+      </c>
+      <c r="L322" t="n">
+        <v>1221.7</v>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>Harassment/ criminal harassment on Jul 26, 2026, 1222 m from Copley Place (NASSAU ST). Case #262064419 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>262064339</t>
+        </is>
+      </c>
+      <c r="E323" s="3" t="n">
+        <v>46229.63333333333</v>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>ASSAULT - AGGRAVATED</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J323" t="n">
+        <v>42.33511903946613</v>
+      </c>
+      <c r="K323" t="n">
+        <v>-71.07491709613726</v>
+      </c>
+      <c r="L323" t="n">
+        <v>1407.3</v>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>Assault - aggravated on Jul 26, 2026, 1407 m from Copley Place (HARRISON AVE). Case #262064339 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>262064236</t>
+        </is>
+      </c>
+      <c r="E324" s="3" t="n">
+        <v>46229.37638888889</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>TREMONT ST</t>
+        </is>
+      </c>
+      <c r="J324" t="n">
+        <v>42.34470135794417</v>
+      </c>
+      <c r="K324" t="n">
+        <v>-71.0703760849388</v>
+      </c>
+      <c r="L324" t="n">
+        <v>678.7</v>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 26, 2026, 679 m from Copley Place (TREMONT ST). Case #262064236 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>262064234</t>
+        </is>
+      </c>
+      <c r="E325" s="3" t="n">
+        <v>46229.31944444445</v>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PERSON</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>SAINT JAMES AVE</t>
+        </is>
+      </c>
+      <c r="J325" t="n">
+        <v>42.34947585701249</v>
+      </c>
+      <c r="K325" t="n">
+        <v>-71.07640149637847</v>
+      </c>
+      <c r="L325" t="n">
+        <v>230.3</v>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>Investigate person on Jul 26, 2026, 230 m from Copley Place (SAINT JAMES AVE). Case #262064234 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>262064357</t>
+        </is>
+      </c>
+      <c r="E326" s="3" t="n">
+        <v>46229.72638888889</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>LARCENY SHOPLIFTING</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr"/>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>HUNTINGTON AVE</t>
+        </is>
+      </c>
+      <c r="J326" t="n">
+        <v>42.3473097976345</v>
+      </c>
+      <c r="K326" t="n">
+        <v>-71.0791516658207</v>
+      </c>
+      <c r="L326" t="n">
+        <v>129.3</v>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064357 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>262064198</t>
+        </is>
+      </c>
+      <c r="E327" s="3" t="n">
+        <v>46229.16736111111</v>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>TOWED MOTOR VEHICLE</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr">
         <is>
           <t>STUART ST &amp; CHARLES ST S
 BOSTON, MA 02116
 UNITED S</t>
         </is>
       </c>
-      <c r="J316" t="n">
+      <c r="J327" t="n">
         <v>42.35095701392956</v>
       </c>
-      <c r="K316" t="n">
+      <c r="K327" t="n">
         <v>-71.06685999332976</v>
       </c>
-      <c r="L316" t="n">
+      <c r="L327" t="n">
         <v>960.1</v>
       </c>
-      <c r="M316" t="inlineStr">
+      <c r="M327" t="inlineStr">
         <is>
           <t>Towed motor vehicle on Jul 26, 2026, 960 m from Copley Place (STUART ST &amp; CHARLES ST S
 BOSTON, MA 02116
@@ -21580,168 +22189,168 @@
         </is>
       </c>
     </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
+    <row r="328">
+      <c r="A328" t="inlineStr">
         <is>
           <t>COPLEY</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr">
+      <c r="B328" t="inlineStr">
         <is>
           <t>Copley Place</t>
         </is>
       </c>
-      <c r="C317" t="inlineStr">
+      <c r="C328" t="inlineStr">
         <is>
           <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr">
+      <c r="D328" t="inlineStr">
         <is>
           <t>262064309</t>
         </is>
       </c>
-      <c r="E317" s="3" t="n">
+      <c r="E328" s="3" t="n">
         <v>46229.39444444444</v>
       </c>
-      <c r="F317" t="inlineStr">
+      <c r="F328" t="inlineStr">
         <is>
           <t>INVESTIGATE PERSON</t>
         </is>
       </c>
-      <c r="G317" t="inlineStr">
+      <c r="G328" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H317" t="inlineStr"/>
-      <c r="I317" t="inlineStr">
+      <c r="H328" t="inlineStr"/>
+      <c r="I328" t="inlineStr">
         <is>
           <t>SAINT BOTOLPH ST</t>
         </is>
       </c>
-      <c r="J317" t="n">
+      <c r="J328" t="n">
         <v>42.34617475544754</v>
       </c>
-      <c r="K317" t="n">
+      <c r="K328" t="n">
         <v>-71.07925920373032</v>
       </c>
-      <c r="L317" t="n">
+      <c r="L328" t="n">
         <v>208.6</v>
       </c>
-      <c r="M317" t="inlineStr">
+      <c r="M328" t="inlineStr">
         <is>
           <t>Investigate person on Jul 26, 2026, 209 m from Copley Place (SAINT BOTOLPH ST). Case #262064309 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
+    <row r="329">
+      <c r="A329" t="inlineStr">
         <is>
           <t>COPLEY</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr">
+      <c r="B329" t="inlineStr">
         <is>
           <t>Copley Place</t>
         </is>
       </c>
-      <c r="C318" t="inlineStr">
+      <c r="C329" t="inlineStr">
         <is>
           <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr">
+      <c r="D329" t="inlineStr">
         <is>
           <t>262064283</t>
         </is>
       </c>
-      <c r="E318" s="3" t="n">
+      <c r="E329" s="3" t="n">
         <v>46229.51736111111</v>
       </c>
-      <c r="F318" t="inlineStr">
+      <c r="F329" t="inlineStr">
         <is>
           <t>LARCENY SHOPLIFTING</t>
         </is>
       </c>
-      <c r="G318" t="inlineStr">
+      <c r="G329" t="inlineStr">
         <is>
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr"/>
-      <c r="I318" t="inlineStr">
+      <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr">
         <is>
           <t>HUNTINGTON AVE</t>
         </is>
       </c>
-      <c r="J318" t="n">
+      <c r="J329" t="n">
         <v>42.3473097976345</v>
       </c>
-      <c r="K318" t="n">
+      <c r="K329" t="n">
         <v>-71.0791516658207</v>
       </c>
-      <c r="L318" t="n">
+      <c r="L329" t="n">
         <v>129.3</v>
       </c>
-      <c r="M318" t="inlineStr">
+      <c r="M329" t="inlineStr">
         <is>
           <t>Larceny shoplifting on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064283 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
+    <row r="330">
+      <c r="A330" t="inlineStr">
         <is>
           <t>COPLEY</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr">
+      <c r="B330" t="inlineStr">
         <is>
           <t>Copley Place</t>
         </is>
       </c>
-      <c r="C319" t="inlineStr">
+      <c r="C330" t="inlineStr">
         <is>
           <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr">
+      <c r="D330" t="inlineStr">
         <is>
           <t>262064226</t>
         </is>
       </c>
-      <c r="E319" s="3" t="n">
+      <c r="E330" s="3" t="n">
         <v>46229.375</v>
       </c>
-      <c r="F319" t="inlineStr">
+      <c r="F330" t="inlineStr">
         <is>
           <t>M/V ACCIDENT - PROPERTY DAMAGE</t>
         </is>
       </c>
-      <c r="G319" t="inlineStr">
+      <c r="G330" t="inlineStr">
         <is>
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H319" t="inlineStr"/>
-      <c r="I319" t="inlineStr">
+      <c r="H330" t="inlineStr"/>
+      <c r="I330" t="inlineStr">
         <is>
           <t>BERKELEY ST &amp; SAINT JAMES AVE
 BOSTON, MA 02116
 UNI</t>
         </is>
       </c>
-      <c r="J319" t="n">
+      <c r="J330" t="n">
         <v>42.3504290420294</v>
       </c>
-      <c r="K319" t="n">
+      <c r="K330" t="n">
         <v>-71.07264798093048</v>
       </c>
-      <c r="L319" t="n">
+      <c r="L330" t="n">
         <v>515.5</v>
       </c>
-      <c r="M319" t="inlineStr">
+      <c r="M330" t="inlineStr">
         <is>
           <t>M/v accident - property damage on Jul 26, 2026, 515 m from Copley Place (BERKELEY ST &amp; SAINT JAMES AVE
 BOSTON, MA 02116
@@ -21749,58 +22358,58 @@
         </is>
       </c>
     </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
+    <row r="331">
+      <c r="A331" t="inlineStr">
         <is>
           <t>COPLEY</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr">
+      <c r="B331" t="inlineStr">
         <is>
           <t>Copley Place</t>
         </is>
       </c>
-      <c r="C320" t="inlineStr">
+      <c r="C331" t="inlineStr">
         <is>
           <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr">
+      <c r="D331" t="inlineStr">
         <is>
           <t>262064268</t>
         </is>
       </c>
-      <c r="E320" s="3" t="n">
+      <c r="E331" s="3" t="n">
         <v>46229.48680555556</v>
       </c>
-      <c r="F320" t="inlineStr">
+      <c r="F331" t="inlineStr">
         <is>
           <t>LARCENY THEFT FROM BUILDING</t>
         </is>
       </c>
-      <c r="G320" t="inlineStr">
+      <c r="G331" t="inlineStr">
         <is>
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H320" t="inlineStr"/>
-      <c r="I320" t="inlineStr">
+      <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr">
         <is>
           <t>REED ST &amp; E LENOX ST
 ROXBURY, MA 02118
 UNITED STAT</t>
         </is>
       </c>
-      <c r="J320" t="n">
+      <c r="J331" t="n">
         <v>42.33406097367816</v>
       </c>
-      <c r="K320" t="n">
+      <c r="K331" t="n">
         <v>-71.07756301316894</v>
       </c>
-      <c r="L320" t="n">
+      <c r="L331" t="n">
         <v>1507.2</v>
       </c>
-      <c r="M320" t="inlineStr">
+      <c r="M331" t="inlineStr">
         <is>
           <t>Larceny theft from building on Jul 26, 2026, 1507 m from Copley Place (REED ST &amp; E LENOX ST
 ROXBURY, MA 02118
@@ -21808,58 +22417,58 @@
         </is>
       </c>
     </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
+    <row r="332">
+      <c r="A332" t="inlineStr">
         <is>
           <t>COPLEY</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr">
+      <c r="B332" t="inlineStr">
         <is>
           <t>Copley Place</t>
         </is>
       </c>
-      <c r="C321" t="inlineStr">
+      <c r="C332" t="inlineStr">
         <is>
           <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr">
+      <c r="D332" t="inlineStr">
         <is>
           <t>262064394</t>
         </is>
       </c>
-      <c r="E321" s="3" t="n">
+      <c r="E332" s="3" t="n">
         <v>46229.82152777778</v>
       </c>
-      <c r="F321" t="inlineStr">
+      <c r="F332" t="inlineStr">
         <is>
           <t>M/V ACCIDENT - OTHER</t>
         </is>
       </c>
-      <c r="G321" t="inlineStr">
+      <c r="G332" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H321" t="inlineStr"/>
-      <c r="I321" t="inlineStr">
+      <c r="H332" t="inlineStr"/>
+      <c r="I332" t="inlineStr">
         <is>
           <t>HARRISON AVE &amp; PLYMPTON ST
 BOSTON, MA 02118
 UNITED</t>
         </is>
       </c>
-      <c r="J321" t="n">
+      <c r="J332" t="n">
         <v>42.33973998780085</v>
       </c>
-      <c r="K321" t="n">
+      <c r="K332" t="n">
         <v>-71.0691099454142</v>
       </c>
-      <c r="L321" t="n">
+      <c r="L332" t="n">
         <v>1121.4</v>
       </c>
-      <c r="M321" t="inlineStr">
+      <c r="M332" t="inlineStr">
         <is>
           <t>M/v accident - other on Jul 26, 2026, 1121 m from Copley Place (HARRISON AVE &amp; PLYMPTON ST
 BOSTON, MA 02118
@@ -21867,611 +22476,6 @@
         </is>
       </c>
     </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>262064321</t>
-        </is>
-      </c>
-      <c r="E322" s="3" t="n">
-        <v>46229.59166666667</v>
-      </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>M/V - LEAVING SCENE - PROPERTY DAMAGE</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H322" t="inlineStr"/>
-      <c r="I322" t="inlineStr">
-        <is>
-          <t>HARRISON AVE</t>
-        </is>
-      </c>
-      <c r="J322" t="n">
-        <v>42.33954198983015</v>
-      </c>
-      <c r="K322" t="n">
-        <v>-71.06940876967543</v>
-      </c>
-      <c r="L322" t="n">
-        <v>1123.7</v>
-      </c>
-      <c r="M322" t="inlineStr">
-        <is>
-          <t>M/v - leaving scene - property damage on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064321 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>262064179</t>
-        </is>
-      </c>
-      <c r="E323" s="3" t="n">
-        <v>46229.07361111111</v>
-      </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>INVESTIGATE PROPERTY</t>
-        </is>
-      </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H323" t="inlineStr"/>
-      <c r="I323" t="inlineStr">
-        <is>
-          <t>BOYLSTON ST</t>
-        </is>
-      </c>
-      <c r="J323" t="n">
-        <v>42.35234109431519</v>
-      </c>
-      <c r="K323" t="n">
-        <v>-71.06432465046424</v>
-      </c>
-      <c r="L323" t="n">
-        <v>1213.3</v>
-      </c>
-      <c r="M323" t="inlineStr">
-        <is>
-          <t>Investigate property on Jul 26, 2026, 1213 m from Copley Place (BOYLSTON ST). Case #262064179 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>262064772</t>
-        </is>
-      </c>
-      <c r="E324" s="3" t="n">
-        <v>46230.82569444444</v>
-      </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>LARCENY SHOPLIFTING</t>
-        </is>
-      </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H324" t="inlineStr"/>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>BOYLSTON ST</t>
-        </is>
-      </c>
-      <c r="J324" t="n">
-        <v>42.34862381555496</v>
-      </c>
-      <c r="K324" t="n">
-        <v>-71.08277637086411</v>
-      </c>
-      <c r="L324" t="n">
-        <v>437.3</v>
-      </c>
-      <c r="M324" t="inlineStr">
-        <is>
-          <t>Larceny shoplifting on Jul 27, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064772 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>262064289</t>
-        </is>
-      </c>
-      <c r="E325" s="3" t="n">
-        <v>46229.54583333333</v>
-      </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>LARCENY SHOPLIFTING</t>
-        </is>
-      </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H325" t="inlineStr"/>
-      <c r="I325" t="inlineStr">
-        <is>
-          <t>BOYLSTON ST</t>
-        </is>
-      </c>
-      <c r="J325" t="n">
-        <v>42.35095908794595</v>
-      </c>
-      <c r="K325" t="n">
-        <v>-71.07412780075079</v>
-      </c>
-      <c r="L325" t="n">
-        <v>470.3</v>
-      </c>
-      <c r="M325" t="inlineStr">
-        <is>
-          <t>Larceny shoplifting on Jul 26, 2026, 470 m from Copley Place (BOYLSTON ST). Case #262064289 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>262064298</t>
-        </is>
-      </c>
-      <c r="E326" s="3" t="n">
-        <v>46229.08611111111</v>
-      </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>FIREARM/WEAPON - LOST</t>
-        </is>
-      </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H326" t="inlineStr"/>
-      <c r="I326" t="inlineStr">
-        <is>
-          <t>HARRISON AVE</t>
-        </is>
-      </c>
-      <c r="J326" t="n">
-        <v>42.33954198983015</v>
-      </c>
-      <c r="K326" t="n">
-        <v>-71.06940876967543</v>
-      </c>
-      <c r="L326" t="n">
-        <v>1123.7</v>
-      </c>
-      <c r="M326" t="inlineStr">
-        <is>
-          <t>Firearm/weapon - lost on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064298 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>262064416</t>
-        </is>
-      </c>
-      <c r="E327" s="3" t="n">
-        <v>46229.87569444445</v>
-      </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>ASSAULT - AGGRAVATED</t>
-        </is>
-      </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H327" t="inlineStr"/>
-      <c r="I327" t="inlineStr">
-        <is>
-          <t>HUNTINGTON AVE</t>
-        </is>
-      </c>
-      <c r="J327" t="n">
-        <v>42.34221543503831</v>
-      </c>
-      <c r="K327" t="n">
-        <v>-71.08577074656198</v>
-      </c>
-      <c r="L327" t="n">
-        <v>898.8</v>
-      </c>
-      <c r="M327" t="inlineStr">
-        <is>
-          <t>Assault - aggravated on Jul 26, 2026, 899 m from Copley Place (HUNTINGTON AVE). Case #262064416 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>262064700</t>
-        </is>
-      </c>
-      <c r="E328" s="3" t="n">
-        <v>46230.71458333333</v>
-      </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>BREAKING AND ENTERING (B&amp;E) MOTOR VEHICLE</t>
-        </is>
-      </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H328" t="inlineStr"/>
-      <c r="I328" t="inlineStr">
-        <is>
-          <t>HARRISON AVE</t>
-        </is>
-      </c>
-      <c r="J328" t="n">
-        <v>42.33954198983015</v>
-      </c>
-      <c r="K328" t="n">
-        <v>-71.06940876967543</v>
-      </c>
-      <c r="L328" t="n">
-        <v>1123.7</v>
-      </c>
-      <c r="M328" t="inlineStr">
-        <is>
-          <t>Breaking and entering (b&amp;e) motor vehicle on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064700 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>262064491</t>
-        </is>
-      </c>
-      <c r="E329" s="3" t="n">
-        <v>46230.22916666666</v>
-      </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>LARCENY ALL OTHERS</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H329" t="inlineStr"/>
-      <c r="I329" t="inlineStr">
-        <is>
-          <t>RUTLAND ST</t>
-        </is>
-      </c>
-      <c r="J329" t="n">
-        <v>42.34020387362647</v>
-      </c>
-      <c r="K329" t="n">
-        <v>-71.07645111113312</v>
-      </c>
-      <c r="L329" t="n">
-        <v>829.8</v>
-      </c>
-      <c r="M329" t="inlineStr">
-        <is>
-          <t>Larceny all others on Jul 27, 2026, 830 m from Copley Place (RUTLAND ST). Case #262064491 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>262064492</t>
-        </is>
-      </c>
-      <c r="E330" s="3" t="n">
-        <v>46230.10972222222</v>
-      </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>VANDALISM</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H330" t="inlineStr"/>
-      <c r="I330" t="inlineStr">
-        <is>
-          <t>NORTHAMPTON ST</t>
-        </is>
-      </c>
-      <c r="J330" t="n">
-        <v>42.33798932384219</v>
-      </c>
-      <c r="K330" t="n">
-        <v>-71.08003745874711</v>
-      </c>
-      <c r="L330" t="n">
-        <v>1088.4</v>
-      </c>
-      <c r="M330" t="inlineStr">
-        <is>
-          <t>Vandalism on Jul 27, 2026, 1088 m from Copley Place (NORTHAMPTON ST). Case #262064492 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>262064766</t>
-        </is>
-      </c>
-      <c r="E331" s="3" t="n">
-        <v>46230.75416666667</v>
-      </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>PROPERTY - LOST/ MISSING</t>
-        </is>
-      </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H331" t="inlineStr"/>
-      <c r="I331" t="inlineStr">
-        <is>
-          <t>COLUMBUS AVE</t>
-        </is>
-      </c>
-      <c r="J331" t="n">
-        <v>42.34294800069079</v>
-      </c>
-      <c r="K331" t="n">
-        <v>-71.07888700104606</v>
-      </c>
-      <c r="L331" t="n">
-        <v>529.1</v>
-      </c>
-      <c r="M331" t="inlineStr">
-        <is>
-          <t>Property - lost/ missing on Jul 27, 2026, 529 m from Copley Place (COLUMBUS AVE). Case #262064766 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>262064548</t>
-        </is>
-      </c>
-      <c r="E332" s="3" t="n">
-        <v>46230.44236111111</v>
-      </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>M/V - LEAVING SCENE - PROPERTY DAMAGE</t>
-        </is>
-      </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H332" t="inlineStr"/>
-      <c r="I332" t="inlineStr">
-        <is>
-          <t>HARRISON AVE</t>
-        </is>
-      </c>
-      <c r="J332" t="n">
-        <v>42.33954198983015</v>
-      </c>
-      <c r="K332" t="n">
-        <v>-71.06940876967543</v>
-      </c>
-      <c r="L332" t="n">
-        <v>1123.7</v>
-      </c>
-      <c r="M332" t="inlineStr">
-        <is>
-          <t>M/v - leaving scene - property damage on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064548 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
@@ -22490,15 +22494,15 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>262064504</t>
+          <t>262064321</t>
         </is>
       </c>
       <c r="E333" s="3" t="n">
-        <v>46230.34791666667</v>
+        <v>46229.59166666667</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>LARCENY SHOPLIFTING</t>
+          <t>M/V - LEAVING SCENE - PROPERTY DAMAGE</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -22509,21 +22513,21 @@
       <c r="H333" t="inlineStr"/>
       <c r="I333" t="inlineStr">
         <is>
-          <t>CHARLES ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J333" t="n">
-        <v>42.36064469554803</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K333" t="n">
-        <v>-71.07086192011141</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L333" t="n">
-        <v>1552</v>
+        <v>1123.7</v>
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Larceny shoplifting on Jul 27, 2026, 1552 m from Copley Place (CHARLES ST). Case #262064504 (use for a records request — full narratives are not published in open data).</t>
+          <t>M/v - leaving scene - property damage on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064321 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22545,20 +22549,20 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>262064506</t>
+          <t>262064772</t>
         </is>
       </c>
       <c r="E334" s="3" t="n">
-        <v>46230.34375</v>
+        <v>46230.82569444444</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>SICK ASSIST</t>
+          <t>LARCENY SHOPLIFTING</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H334" t="inlineStr"/>
@@ -22568,17 +22572,17 @@
         </is>
       </c>
       <c r="J334" t="n">
-        <v>42.35037869977646</v>
+        <v>42.34862381555496</v>
       </c>
       <c r="K334" t="n">
-        <v>-71.07626098382806</v>
+        <v>-71.08277637086411</v>
       </c>
       <c r="L334" t="n">
-        <v>327.3</v>
+        <v>437.3</v>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Sick assist on Jul 27, 2026, 327 m from Copley Place (BOYLSTON ST). Case #262064506 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny shoplifting on Jul 27, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064772 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22600,15 +22604,15 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>262064752</t>
+          <t>262064289</t>
         </is>
       </c>
       <c r="E335" s="3" t="n">
-        <v>46230.79166666666</v>
+        <v>46229.54583333333</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>STOLEN PROPERTY - BUYING / RECEIVING / POSSESSING</t>
+          <t>LARCENY SHOPLIFTING</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
@@ -22619,21 +22623,21 @@
       <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr">
         <is>
-          <t>HUDSON ST</t>
+          <t>BOYLSTON ST</t>
         </is>
       </c>
       <c r="J335" t="n">
-        <v>42.35074197291232</v>
+        <v>42.35095908794595</v>
       </c>
       <c r="K335" t="n">
-        <v>-71.06006134581432</v>
+        <v>-71.07412780075079</v>
       </c>
       <c r="L335" t="n">
-        <v>1485.3</v>
+        <v>470.3</v>
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Stolen property - buying / receiving / possessing on Jul 27, 2026, 1485 m from Copley Place (HUDSON ST). Case #262064752 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny shoplifting on Jul 26, 2026, 470 m from Copley Place (BOYLSTON ST). Case #262064289 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22655,40 +22659,590 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>262064383</t>
+          <t>262064298</t>
         </is>
       </c>
       <c r="E336" s="3" t="n">
-        <v>46229.79375</v>
+        <v>46229.08611111111</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
+          <t>FIREARM/WEAPON - LOST</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J336" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K336" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L336" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>Firearm/weapon - lost on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064298 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>262064416</t>
+        </is>
+      </c>
+      <c r="E337" s="3" t="n">
+        <v>46229.87569444445</v>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>ASSAULT - AGGRAVATED</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr"/>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>HUNTINGTON AVE</t>
+        </is>
+      </c>
+      <c r="J337" t="n">
+        <v>42.34221543503831</v>
+      </c>
+      <c r="K337" t="n">
+        <v>-71.08577074656198</v>
+      </c>
+      <c r="L337" t="n">
+        <v>898.8</v>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>Assault - aggravated on Jul 26, 2026, 899 m from Copley Place (HUNTINGTON AVE). Case #262064416 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>262064700</t>
+        </is>
+      </c>
+      <c r="E338" s="3" t="n">
+        <v>46230.71458333333</v>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>BREAKING AND ENTERING (B&amp;E) MOTOR VEHICLE</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr"/>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J338" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K338" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L338" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>Breaking and entering (b&amp;e) motor vehicle on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064700 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>262064491</t>
+        </is>
+      </c>
+      <c r="E339" s="3" t="n">
+        <v>46230.22916666666</v>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>LARCENY ALL OTHERS</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>RUTLAND ST</t>
+        </is>
+      </c>
+      <c r="J339" t="n">
+        <v>42.34020387362647</v>
+      </c>
+      <c r="K339" t="n">
+        <v>-71.07645111113312</v>
+      </c>
+      <c r="L339" t="n">
+        <v>829.8</v>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>Larceny all others on Jul 27, 2026, 830 m from Copley Place (RUTLAND ST). Case #262064491 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>262064492</t>
+        </is>
+      </c>
+      <c r="E340" s="3" t="n">
+        <v>46230.10972222222</v>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>VANDALISM</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr"/>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>NORTHAMPTON ST</t>
+        </is>
+      </c>
+      <c r="J340" t="n">
+        <v>42.33798932384219</v>
+      </c>
+      <c r="K340" t="n">
+        <v>-71.08003745874711</v>
+      </c>
+      <c r="L340" t="n">
+        <v>1088.4</v>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>Vandalism on Jul 27, 2026, 1088 m from Copley Place (NORTHAMPTON ST). Case #262064492 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>262064766</t>
+        </is>
+      </c>
+      <c r="E341" s="3" t="n">
+        <v>46230.75416666667</v>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>PROPERTY - LOST/ MISSING</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr"/>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>COLUMBUS AVE</t>
+        </is>
+      </c>
+      <c r="J341" t="n">
+        <v>42.34294800069079</v>
+      </c>
+      <c r="K341" t="n">
+        <v>-71.07888700104606</v>
+      </c>
+      <c r="L341" t="n">
+        <v>529.1</v>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>Property - lost/ missing on Jul 27, 2026, 529 m from Copley Place (COLUMBUS AVE). Case #262064766 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>262064548</t>
+        </is>
+      </c>
+      <c r="E342" s="3" t="n">
+        <v>46230.44236111111</v>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>M/V - LEAVING SCENE - PROPERTY DAMAGE</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr"/>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J342" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K342" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L342" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>M/v - leaving scene - property damage on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064548 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>262064504</t>
+        </is>
+      </c>
+      <c r="E343" s="3" t="n">
+        <v>46230.34791666667</v>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>LARCENY SHOPLIFTING</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr"/>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>CHARLES ST</t>
+        </is>
+      </c>
+      <c r="J343" t="n">
+        <v>42.36064469554803</v>
+      </c>
+      <c r="K343" t="n">
+        <v>-71.07086192011141</v>
+      </c>
+      <c r="L343" t="n">
+        <v>1552</v>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 27, 2026, 1552 m from Copley Place (CHARLES ST). Case #262064504 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>262064506</t>
+        </is>
+      </c>
+      <c r="E344" s="3" t="n">
+        <v>46230.34375</v>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J344" t="n">
+        <v>42.35037869977646</v>
+      </c>
+      <c r="K344" t="n">
+        <v>-71.07626098382806</v>
+      </c>
+      <c r="L344" t="n">
+        <v>327.3</v>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 27, 2026, 327 m from Copley Place (BOYLSTON ST). Case #262064506 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>262064752</t>
+        </is>
+      </c>
+      <c r="E345" s="3" t="n">
+        <v>46230.79166666666</v>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>STOLEN PROPERTY - BUYING / RECEIVING / POSSESSING</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr"/>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>HUDSON ST</t>
+        </is>
+      </c>
+      <c r="J345" t="n">
+        <v>42.35074197291232</v>
+      </c>
+      <c r="K345" t="n">
+        <v>-71.06006134581432</v>
+      </c>
+      <c r="L345" t="n">
+        <v>1485.3</v>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>Stolen property - buying / receiving / possessing on Jul 27, 2026, 1485 m from Copley Place (HUDSON ST). Case #262064752 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>262064383</t>
+        </is>
+      </c>
+      <c r="E346" s="3" t="n">
+        <v>46229.79375</v>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr"/>
+      <c r="I346" t="inlineStr">
         <is>
           <t>BOYLSTON ST &amp; DALTON ST
 BOSTON, MA 02115
 UNITED ST</t>
         </is>
       </c>
-      <c r="J336" t="n">
+      <c r="J346" t="n">
         <v>42.34787097987171</v>
       </c>
-      <c r="K336" t="n">
+      <c r="K346" t="n">
         <v>-71.08556796747074</v>
       </c>
-      <c r="L336" t="n">
+      <c r="L346" t="n">
         <v>652.7</v>
       </c>
-      <c r="M336" t="inlineStr">
+      <c r="M346" t="inlineStr">
         <is>
           <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 653 m from Copley Place (BOYLSTON ST &amp; DALTON ST
 BOSTON, MA 02115
@@ -22696,616 +23250,62 @@
         </is>
       </c>
     </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
+    <row r="347">
+      <c r="A347" t="inlineStr">
         <is>
           <t>COPLEY</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr">
+      <c r="B347" t="inlineStr">
         <is>
           <t>Copley Place</t>
         </is>
       </c>
-      <c r="C337" t="inlineStr">
+      <c r="C347" t="inlineStr">
         <is>
           <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr">
+      <c r="D347" t="inlineStr">
         <is>
           <t>262064391</t>
         </is>
       </c>
-      <c r="E337" s="3" t="n">
+      <c r="E347" s="3" t="n">
         <v>46229.83125</v>
       </c>
-      <c r="F337" t="inlineStr">
+      <c r="F347" t="inlineStr">
         <is>
           <t>DRUGS - POSSESSION/ SALE/ MANUFACTURING/ USE</t>
         </is>
       </c>
-      <c r="G337" t="inlineStr">
+      <c r="G347" t="inlineStr">
         <is>
           <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
-      <c r="H337" t="inlineStr"/>
-      <c r="I337" t="inlineStr">
+      <c r="H347" t="inlineStr"/>
+      <c r="I347" t="inlineStr">
         <is>
           <t xml:space="preserve">BOYLSTON ST &amp; BOYLSTON SQ
 BOSTON, MA 02111
 UNITED </t>
         </is>
       </c>
-      <c r="J337" t="n">
+      <c r="J347" t="n">
         <v>42.35231098936428</v>
       </c>
-      <c r="K337" t="n">
+      <c r="K347" t="n">
         <v>-71.06350996526169</v>
       </c>
-      <c r="L337" t="n">
+      <c r="L347" t="n">
         <v>1272.6</v>
       </c>
-      <c r="M337" t="inlineStr">
+      <c r="M347" t="inlineStr">
         <is>
           <t>Drugs - possession/ sale/ manufacturing/ use on Jul 26, 2026, 1273 m from Copley Place (BOYLSTON ST &amp; BOYLSTON SQ
 BOSTON, MA 02111
 UNITED ). Case #262064391 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>262064802</t>
-        </is>
-      </c>
-      <c r="E338" s="3" t="n">
-        <v>46230.89583333334</v>
-      </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>LARCENY SHOPLIFTING</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H338" t="inlineStr"/>
-      <c r="I338" t="inlineStr">
-        <is>
-          <t>BOYLSTON ST</t>
-        </is>
-      </c>
-      <c r="J338" t="n">
-        <v>42.34862381555496</v>
-      </c>
-      <c r="K338" t="n">
-        <v>-71.08277637086411</v>
-      </c>
-      <c r="L338" t="n">
-        <v>437.3</v>
-      </c>
-      <c r="M338" t="inlineStr">
-        <is>
-          <t>Larceny shoplifting on Jul 27, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064802 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>262064409</t>
-        </is>
-      </c>
-      <c r="E339" s="3" t="n">
-        <v>46229.85833333333</v>
-      </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>SICK ASSIST</t>
-        </is>
-      </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H339" t="inlineStr"/>
-      <c r="I339" t="inlineStr">
-        <is>
-          <t>OXFORD ST</t>
-        </is>
-      </c>
-      <c r="J339" t="n">
-        <v>42.35193460488232</v>
-      </c>
-      <c r="K339" t="n">
-        <v>-71.06048592223925</v>
-      </c>
-      <c r="L339" t="n">
-        <v>1488.7</v>
-      </c>
-      <c r="M339" t="inlineStr">
-        <is>
-          <t>Sick assist on Jul 26, 2026, 1489 m from Copley Place (OXFORD ST). Case #262064409 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>262064318</t>
-        </is>
-      </c>
-      <c r="E340" s="3" t="n">
-        <v>46229.53958333333</v>
-      </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>INVESTIGATE PERSON</t>
-        </is>
-      </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H340" t="inlineStr"/>
-      <c r="I340" t="inlineStr">
-        <is>
-          <t>SHAWMUT AVE</t>
-        </is>
-      </c>
-      <c r="J340" t="n">
-        <v>42.34319452771496</v>
-      </c>
-      <c r="K340" t="n">
-        <v>-71.06880536524001</v>
-      </c>
-      <c r="L340" t="n">
-        <v>876.3</v>
-      </c>
-      <c r="M340" t="inlineStr">
-        <is>
-          <t>Investigate person on Jul 26, 2026, 876 m from Copley Place (SHAWMUT AVE). Case #262064318 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>262064412</t>
-        </is>
-      </c>
-      <c r="E341" s="3" t="n">
-        <v>46229.87638888889</v>
-      </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>SICK/INJURED/MEDICAL - PERSON</t>
-        </is>
-      </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H341" t="inlineStr"/>
-      <c r="I341" t="inlineStr">
-        <is>
-          <t>TREMONT ST</t>
-        </is>
-      </c>
-      <c r="J341" t="n">
-        <v>42.35428377241487</v>
-      </c>
-      <c r="K341" t="n">
-        <v>-71.06380403747467</v>
-      </c>
-      <c r="L341" t="n">
-        <v>1356.9</v>
-      </c>
-      <c r="M341" t="inlineStr">
-        <is>
-          <t>Sick/injured/medical - person on Jul 26, 2026, 1357 m from Copley Place (TREMONT ST). Case #262064412 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>262064362</t>
-        </is>
-      </c>
-      <c r="E342" s="3" t="n">
-        <v>46229.64305555556</v>
-      </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
-        </is>
-      </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H342" t="inlineStr"/>
-      <c r="I342" t="inlineStr">
-        <is>
-          <t>DARTMOUTH ST</t>
-        </is>
-      </c>
-      <c r="J342" t="n">
-        <v>42.35029374297969</v>
-      </c>
-      <c r="K342" t="n">
-        <v>-71.07744671381569</v>
-      </c>
-      <c r="L342" t="n">
-        <v>298.2</v>
-      </c>
-      <c r="M342" t="inlineStr">
-        <is>
-          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 298 m from Copley Place (DARTMOUTH ST). Case #262064362 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>262064307</t>
-        </is>
-      </c>
-      <c r="E343" s="3" t="n">
-        <v>46229.59027777778</v>
-      </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>SICK ASSIST</t>
-        </is>
-      </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H343" t="inlineStr"/>
-      <c r="I343" t="inlineStr">
-        <is>
-          <t>TREMONT ST &amp; TEMPLE PL
-BOSTON, MA 02111
-UNITED STA</t>
-        </is>
-      </c>
-      <c r="J343" t="n">
-        <v>42.35561100811422</v>
-      </c>
-      <c r="K343" t="n">
-        <v>-71.06289400004533</v>
-      </c>
-      <c r="L343" t="n">
-        <v>1502.5</v>
-      </c>
-      <c r="M343" t="inlineStr">
-        <is>
-          <t>Sick assist on Jul 26, 2026, 1502 m from Copley Place (TREMONT ST &amp; TEMPLE PL
-BOSTON, MA 02111
-UNITED STA). Case #262064307 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>262064419</t>
-        </is>
-      </c>
-      <c r="E344" s="3" t="n">
-        <v>46229.90138888889</v>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>HARASSMENT/ CRIMINAL HARASSMENT</t>
-        </is>
-      </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H344" t="inlineStr"/>
-      <c r="I344" t="inlineStr">
-        <is>
-          <t>NASSAU ST</t>
-        </is>
-      </c>
-      <c r="J344" t="n">
-        <v>42.34880604399623</v>
-      </c>
-      <c r="K344" t="n">
-        <v>-71.06285446968663</v>
-      </c>
-      <c r="L344" t="n">
-        <v>1221.7</v>
-      </c>
-      <c r="M344" t="inlineStr">
-        <is>
-          <t>Harassment/ criminal harassment on Jul 26, 2026, 1222 m from Copley Place (NASSAU ST). Case #262064419 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>262064339</t>
-        </is>
-      </c>
-      <c r="E345" s="3" t="n">
-        <v>46229.63333333333</v>
-      </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>ASSAULT - AGGRAVATED</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H345" t="inlineStr"/>
-      <c r="I345" t="inlineStr">
-        <is>
-          <t>HARRISON AVE</t>
-        </is>
-      </c>
-      <c r="J345" t="n">
-        <v>42.33511903946613</v>
-      </c>
-      <c r="K345" t="n">
-        <v>-71.07491709613726</v>
-      </c>
-      <c r="L345" t="n">
-        <v>1407.3</v>
-      </c>
-      <c r="M345" t="inlineStr">
-        <is>
-          <t>Assault - aggravated on Jul 26, 2026, 1407 m from Copley Place (HARRISON AVE). Case #262064339 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>262064236</t>
-        </is>
-      </c>
-      <c r="E346" s="3" t="n">
-        <v>46229.37638888889</v>
-      </c>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>SICK ASSIST</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H346" t="inlineStr"/>
-      <c r="I346" t="inlineStr">
-        <is>
-          <t>TREMONT ST</t>
-        </is>
-      </c>
-      <c r="J346" t="n">
-        <v>42.34470135794417</v>
-      </c>
-      <c r="K346" t="n">
-        <v>-71.0703760849388</v>
-      </c>
-      <c r="L346" t="n">
-        <v>678.7</v>
-      </c>
-      <c r="M346" t="inlineStr">
-        <is>
-          <t>Sick assist on Jul 26, 2026, 679 m from Copley Place (TREMONT ST). Case #262064236 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>262064234</t>
-        </is>
-      </c>
-      <c r="E347" s="3" t="n">
-        <v>46229.31944444445</v>
-      </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>INVESTIGATE PERSON</t>
-        </is>
-      </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H347" t="inlineStr"/>
-      <c r="I347" t="inlineStr">
-        <is>
-          <t>SAINT JAMES AVE</t>
-        </is>
-      </c>
-      <c r="J347" t="n">
-        <v>42.34947585701249</v>
-      </c>
-      <c r="K347" t="n">
-        <v>-71.07640149637847</v>
-      </c>
-      <c r="L347" t="n">
-        <v>230.3</v>
-      </c>
-      <c r="M347" t="inlineStr">
-        <is>
-          <t>Investigate person on Jul 26, 2026, 230 m from Copley Place (SAINT JAMES AVE). Case #262064234 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -23513,7 +23513,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 05:00:58.075328+00:00</t>
+          <t>2026-08-01 05:06:16.167337+00:00</t>
         </is>
       </c>
     </row>
@@ -23545,7 +23545,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 05:00:58.075328+00:00</t>
+          <t>2026-07-25 05:06:16.167337+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/2026-08-01/blotter_report.xlsx
+++ b/reports/2026-08-01/blotter_report.xlsx
@@ -13,10 +13,10 @@
     <sheet name="Run Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$350</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$391</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1103,17 +1103,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INTLPLAZA</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>International Plaza</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
+          <t>2330 Kalakaua Avenue, Honolulu HI 96815</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1122,25 +1122,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
+        <v>41</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>1534.5</v>
+        <v>99.7</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>46232.16666666666</v>
+        <v>46233.78047453704</v>
       </c>
       <c r="L15" t="b">
         <v>0</v>
@@ -1149,32 +1149,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LENOX</t>
+          <t>INTLPLAZA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lenox Square</t>
+          <t>International Plaza</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1182,8 +1182,12 @@
       <c r="I16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>1534.5</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>46232.16666666666</v>
+      </c>
       <c r="L16" t="b">
         <v>0</v>
       </c>
@@ -1191,22 +1195,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MALLATMILLENIA</t>
+          <t>LENOX</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Mall at Millenia</t>
+          <t>Lenox Square</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4200 Conroy Road, Orlando, FL 32839</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1233,17 +1237,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NORFOLKPO</t>
+          <t>MALLATMILLENIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Norfolk Premium Outlets</t>
+          <t>The Mall at Millenia</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1600 Premium Outlets Boulevard Norfolk VA 23502</t>
+          <t>4200 Conroy Road, Orlando, FL 32839</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1252,7 +1256,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1264,14 +1268,10 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1118.9</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>46233</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="b">
         <v>0</v>
       </c>
@@ -1279,17 +1279,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>NORFOLKPO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Norfolk Premium Outlets</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>401 Northeast Northgate Way Seattle WA 98125</t>
+          <t>1600 Premium Outlets Boulevard Norfolk VA 23502</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1298,25 +1298,25 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>14</v>
-      </c>
-      <c r="F19" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
       <c r="G19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>145.2</v>
+        <v>1118.9</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>46233.28194444445</v>
+        <v>46233</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
@@ -1325,17 +1325,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>433 Opry Mills Drive Nashville TN 37214</t>
+          <t>401 Northeast Northgate Way Seattle WA 98125</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1344,22 +1344,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>46233.28194444445</v>
+      </c>
       <c r="L20" t="b">
         <v>0</v>
       </c>
@@ -1367,17 +1371,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4400 Sharon Road Charlotte NC 28211</t>
+          <t>433 Opry Mills Drive Nashville TN 37214</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1386,26 +1390,22 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>178.9</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>46232.16666666666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="b">
         <v>0</v>
       </c>
@@ -1413,17 +1413,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4502 South Steele Street Tacoma WA 98409</t>
+          <t>4400 Sharon Road Charlotte NC 28211</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1432,25 +1432,25 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>471.3</v>
+        <v>178.9</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>46233</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
@@ -1459,41 +1459,45 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>THEDOMAIN</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Domain</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11410 Century Oaks Terrace Austin TX 78758</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>4502 South Steele Street Tacoma WA 98409</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>471.3</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>46233</v>
+      </c>
       <c r="L23" t="b">
         <v>0</v>
       </c>
@@ -1501,45 +1505,41 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>THEDOMAIN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>The Domain</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>7700 East Kellogg Wichita KS 67207</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>11410 Century Oaks Terrace Austin TX 78758</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>33</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
-      </c>
-      <c r="J24" t="n">
-        <v>288.9</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>46233.7625</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="b">
         <v>0</v>
       </c>
@@ -1547,17 +1547,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UNIVPARKVILLAGE</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>University Park Village</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1612 South University Drive Fort Worth TX 76107</t>
+          <t>7700 East Kellogg Wichita KS 67207</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1566,28 +1566,116 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="J25" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>46233.7625</v>
+      </c>
       <c r="L25" t="b">
         <v>0</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>UNIVPARKVILLAGE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>University Park Village</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1612 South University Drive Fort Worth TX 76107</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>WAIKELE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Waikele Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>94-790 Lumiaina Street Waipahu HI 96797</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L25"/>
+  <autoFilter ref="A1:L27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1741,30 +1829,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
+          <t>INTLMARKET:vg88-5rn5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>094686126</t>
+          <t>260725-1158</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>46229</v>
+        <v>46228.70266203704</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Simple assault</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1774,26 +1862,26 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>13B</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5000-5099 WESTHEIMER RD</t>
+          <t>2300 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>29.74071090457959</v>
+        <v>21.27805648814</v>
       </c>
       <c r="K3" t="n">
-        <v>-95.46251430091121</v>
+        <v>-157.827664940544</v>
       </c>
       <c r="L3" t="n">
-        <v>217.1</v>
+        <v>99.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 26, 2026, 217 m from Houston Galleria (5000-5099 WESTHEIMER RD). Case #094686126 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 25, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260725-1158 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1903,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>094513626</t>
+          <t>094686126</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
@@ -1823,7 +1911,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>Simple assault</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1833,56 +1921,56 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>13A</t>
+          <t>13B</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5100-5199 HIDALGO ST</t>
+          <t>5000-5099 WESTHEIMER RD</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>29.73535149549964</v>
+        <v>29.74071090457959</v>
       </c>
       <c r="K4" t="n">
-        <v>-95.46474014804627</v>
+        <v>-95.46251430091121</v>
       </c>
       <c r="L4" t="n">
-        <v>447.9</v>
+        <v>217.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 26, 2026, 448 m from Houston Galleria (5100-5199 HIDALGO ST). Case #094513626 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 26, 2026, 217 m from Houston Galleria (5000-5099 WESTHEIMER RD). Case #094686126 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Property</t>
+          <t>INTLMARKET:vg88-5rn5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>095242126</t>
+          <t>260726-0222</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46230</v>
+        <v>46229.15130787037</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1892,56 +1980,56 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2700-2799 LOOP N</t>
+          <t>2200 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>29.7388306267185</v>
+        <v>21.280046658192</v>
       </c>
       <c r="K5" t="n">
-        <v>-95.45805588032616</v>
+        <v>-157.829687791355</v>
       </c>
       <c r="L5" t="n">
-        <v>588.1</v>
+        <v>384.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Robbery on Jul 27, 2026, 588 m from Houston Galleria (2700-2799 LOOP N). Case #095242126 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 26, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260726-0222 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CFS26-161839</t>
+          <t>094513626</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46231.00275462963</v>
+        <v>46229</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Assault P3</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1951,56 +2039,56 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>13A</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>W 47TH ST &amp; S WESTPORT AVE</t>
+          <t>5100-5199 HIDALGO ST</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>43.50940131405472</v>
+        <v>29.73535149549964</v>
       </c>
       <c r="K6" t="n">
-        <v>-96.76746570282992</v>
+        <v>-95.46474014804627</v>
       </c>
       <c r="L6" t="n">
-        <v>678.4</v>
+        <v>447.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Assault p3 on Jul 28, 2026, 678 m from Empire Mall (W 47TH ST &amp; S WESTPORT AVE). Case #CFS26-161839 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 26, 2026, 448 m from Houston Galleria (5100-5199 HIDALGO ST). Case #094513626 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>INTLMARKET:vg88-5rn5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DP2026411044131300</t>
+          <t>260729-0737</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46229.1125</v>
+        <v>46232.46952546296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>assault-simple</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2010,56 +2098,56 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>other-crimes-against-persons</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3200 BLOCK E CHERRY CREEK S DR</t>
+          <t>2500 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>39.71130989687384</v>
+        <v>21.273862837838</v>
       </c>
       <c r="K7" t="n">
-        <v>-104.9490029653731</v>
+        <v>-157.82387239543</v>
       </c>
       <c r="L7" t="n">
-        <v>696.3</v>
+        <v>544.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 29, 2026, 545 m from International Market Place (2500 BLOCK KALAKAUA AVE). Case #260729-0737 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COPLEY</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+          <t>INTLMARKET:vg88-5rn5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>262064756</t>
+          <t>260725-1627</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46230.80347222222</v>
+        <v>46228.93998842593</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASSAULT - SIMPLE</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2067,54 +2155,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MASSACHUSETTS AVE</t>
+          <t>200 BLOCK BEACH WALK</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>42.34439568415441</v>
+        <v>21.278930465176</v>
       </c>
       <c r="K8" t="n">
-        <v>-71.08632016344815</v>
+        <v>-157.832248174365</v>
       </c>
       <c r="L8" t="n">
-        <v>798.7</v>
+        <v>583.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Assault - simple on Jul 27, 2026, 799 m from Copley Place (MASSACHUSETTS AVE). Case #262064756 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 25, 2026, 584 m from International Market Place (200 BLOCK BEACH WALK). Case #260725-1627 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Property</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CFS26-161603</t>
+          <t>095242126</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46230.83325231481</v>
+        <v>46230</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2124,56 +2216,56 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>S WESTPORT AVE &amp; W 41ST ST</t>
+          <t>2700-2799 LOOP N</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>43.51485103457241</v>
+        <v>29.7388306267185</v>
       </c>
       <c r="K9" t="n">
-        <v>-96.76794119445807</v>
+        <v>-95.45805588032616</v>
       </c>
       <c r="L9" t="n">
-        <v>808.9</v>
+        <v>588.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Assault on Jul 27, 2026, 809 m from Empire Mall (S WESTPORT AVE &amp; W 41ST ST). Case #CFS26-161603 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 27, 2026, 588 m from Houston Galleria (2700-2799 LOOP N). Case #095242126 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20260729-1600-11</t>
+          <t>CFS26-161839</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46232.16666666666</v>
+        <v>46231.00275462963</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Simple Assault</t>
+          <t>Assault P3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2183,56 +2275,56 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>13B</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4700 PIEDMONT ROW DR</t>
+          <t>W 47TH ST &amp; S WESTPORT AVE</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>35.15196312662653</v>
+        <v>43.50940131405472</v>
       </c>
       <c r="K10" t="n">
-        <v>-80.83980651357408</v>
+        <v>-96.76746570282992</v>
       </c>
       <c r="L10" t="n">
-        <v>850.6</v>
+        <v>678.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 29, 2026, 851 m from Southpark (4700 PIEDMONT ROW DR). Status: Open. Case #20260729-1600-11 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault p3 on Jul 28, 2026, 678 m from Empire Mall (W 47TH ST &amp; S WESTPORT AVE). Case #CFS26-161839 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2620701835</t>
+          <t>DP2026411044131300</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46229</v>
+        <v>46229.1125</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>assault-simple</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2242,26 +2334,26 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>other-crimes-against-persons</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4000 S LAWRENCE ST</t>
+          <t>3200 BLOCK E CHERRY CREEK S DR</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>47.219421</v>
+        <v>39.71130989687384</v>
       </c>
       <c r="K11" t="n">
-        <v>-122.478428</v>
+        <v>-104.9490029653731</v>
       </c>
       <c r="L11" t="n">
-        <v>853.4</v>
+        <v>696.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 26, 2026, 853 m from Tacoma Mall (4000 S LAWRENCE ST). Case #2620701835 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2283,15 +2375,15 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>262064416</t>
+          <t>262064756</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46229.87569444445</v>
+        <v>46230.80347222222</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASSAULT - AGGRAVATED</t>
+          <t>ASSAULT - SIMPLE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2302,51 +2394,51 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>HUNTINGTON AVE</t>
+          <t>MASSACHUSETTS AVE</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>42.34221543503831</v>
+        <v>42.34439568415441</v>
       </c>
       <c r="K12" t="n">
-        <v>-71.08577074656198</v>
+        <v>-71.08632016344815</v>
       </c>
       <c r="L12" t="n">
-        <v>898.8</v>
+        <v>798.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Assault - aggravated on Jul 26, 2026, 899 m from Copley Place (HUNTINGTON AVE). Case #262064416 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - simple on Jul 27, 2026, 799 m from Copley Place (MASSACHUSETTS AVE). Case #262064756 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>71878728447</t>
+          <t>CFS26-161603</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46230.4375</v>
+        <v>46230.83325231481</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2356,56 +2448,56 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>16XX BLOCK OF N 105TH ST</t>
+          <t>S WESTPORT AVE &amp; W 41ST ST</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>47.70504225</v>
+        <v>43.51485103457241</v>
       </c>
       <c r="K13" t="n">
-        <v>-122.338094779232</v>
+        <v>-96.76794119445807</v>
       </c>
       <c r="L13" t="n">
-        <v>938.8</v>
+        <v>808.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 27, 2026, 809 m from Empire Mall (S WESTPORT AVE &amp; W 41ST ST). Case #CFS26-161603 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>INTLMARKET:vg88-5rn5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2621000152</t>
+          <t>260729-0943</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46232</v>
+        <v>46232.56469907407</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2415,56 +2507,56 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3500 S 45TH ST</t>
+          <t>2600 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>47.216421</v>
+        <v>21.271474893966</v>
       </c>
       <c r="K14" t="n">
-        <v>-122.482428</v>
+        <v>-157.82264961775</v>
       </c>
       <c r="L14" t="n">
-        <v>1074.3</v>
+        <v>837.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 29, 2026, 1074 m from Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 29, 2026, 837 m from International Market Place (2600 BLOCK KALAKAUA AVE). Case #260729-0943 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COPLEY</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>262064432</t>
+          <t>20260729-1600-11</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46229.91666666666</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ROBBERY</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2472,54 +2564,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>13B</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>4700 PIEDMONT ROW DR</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>42.33954198983015</v>
+        <v>35.15196312662653</v>
       </c>
       <c r="K15" t="n">
-        <v>-71.06940876967543</v>
+        <v>-80.83980651357408</v>
       </c>
       <c r="L15" t="n">
-        <v>1123.7</v>
+        <v>850.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Robbery on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064432 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 29, 2026, 851 m from Southpark (4700 PIEDMONT ROW DR). Status: Open. Case #20260729-1600-11 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COPLEY</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>262064298</t>
+          <t>2620701835</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46229.08611111111</v>
+        <v>46229</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FIREARM/WEAPON - LOST</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2527,54 +2623,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Assault Offenses</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>4000 S LAWRENCE ST</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>42.33954198983015</v>
+        <v>47.219421</v>
       </c>
       <c r="K16" t="n">
-        <v>-71.06940876967543</v>
+        <v>-122.478428</v>
       </c>
       <c r="L16" t="n">
-        <v>1123.7</v>
+        <v>853.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Firearm/weapon - lost on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064298 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 26, 2026, 853 m from Tacoma Mall (4000 S LAWRENCE ST). Case #2620701835 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>71894237115</t>
+          <t>262064416</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46231.20833333334</v>
+        <v>46229.87569444445</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>ASSAULT - AGGRAVATED</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2582,28 +2682,24 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>VIOLENT CRIME</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>HUNTINGTON AVE</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>47.70668788</v>
+        <v>42.34221543503831</v>
       </c>
       <c r="K17" t="n">
-        <v>-122.311189997702</v>
+        <v>-71.08577074656198</v>
       </c>
       <c r="L17" t="n">
-        <v>1145.7</v>
+        <v>898.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - aggravated on Jul 26, 2026, 899 m from Copley Place (HUNTINGTON AVE). Case #262064416 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2625,15 +2721,15 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>71889871382</t>
+          <t>71878728447</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46231.00625</v>
+        <v>46230.4375</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Simple Assault</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2643,56 +2739,56 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ALL OTHER</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>16XX BLOCK OF N 105TH ST</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>47.70668788</v>
+        <v>47.70504225</v>
       </c>
       <c r="K18" t="n">
-        <v>-122.311189997702</v>
+        <v>-122.338094779232</v>
       </c>
       <c r="L18" t="n">
-        <v>1145.7</v>
+        <v>938.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>26C142249</t>
+          <t>2621000152</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46230.75</v>
+        <v>46232</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BATTERY ABW</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2702,56 +2798,56 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>SIM_ASSAULT</t>
+          <t>Assault Offenses</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S MISSION RD</t>
+          <t>3500 S 45TH ST</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>37.6756469679485</v>
+        <v>47.216421</v>
       </c>
       <c r="K19" t="n">
-        <v>-97.25850032865422</v>
+        <v>-122.482428</v>
       </c>
       <c r="L19" t="n">
-        <v>1251.5</v>
+        <v>1074.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 29, 2026, 1074 m from Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CFS26-164521</t>
+          <t>262064432</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46234.03421296296</v>
+        <v>46229.91666666666</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>ROBBERY</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2759,58 +2855,54 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Assault</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>S MARION RD &amp; W 41ST ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>43.51481738299845</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K20" t="n">
-        <v>-96.79096028032072</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L20" t="n">
-        <v>1322.4</v>
+        <v>1123.7</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 31, 2026, 1322 m from Empire Mall (S MARION RD &amp; W 41ST ST). Case #CFS26-164521 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064432 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>096140526</t>
+          <t>262064298</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46232</v>
+        <v>46229.08611111111</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>FIREARM/WEAPON - LOST</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2818,58 +2910,54 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>13A</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1900-1999 POST OAK PARK DR</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>29.74712522681273</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K21" t="n">
-        <v>-95.45374747370188</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L21" t="n">
-        <v>1323.4</v>
+        <v>1123.7</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 29, 2026, 1323 m from Houston Galleria (1900-1999 POST OAK PARK DR). Case #096140526 (use for a records request — full narratives are not published in open data).</t>
+          <t>Firearm/weapon - lost on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064298 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ARZMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Arizona Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ARZMILLS:Tempe PD General Offenses</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE202675136         </t>
+          <t>71894237115</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46228.97847222222</v>
+        <v>46231.20833333334</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">[13B] ASSAULT                                                                   </t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2877,54 +2965,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>VIOLENT CRIME</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5XXX S HARDY DR</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>33.3757495513233</v>
+        <v>47.70668788</v>
       </c>
       <c r="K22" t="n">
-        <v>-111.9531832468173</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L22" t="n">
-        <v>1345.1</v>
+        <v>1145.7</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>[13b] assault on Jul 25, 2026, 1345 m from Arizona Mills (5XXX S HARDY DR). Case #TE202675136          (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>COPLEY</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>262064339</t>
+          <t>71889871382</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46229.63333333333</v>
+        <v>46231.00625</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ASSAULT - AGGRAVATED</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2932,54 +3024,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ALL OTHER</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>42.33511903946613</v>
+        <v>47.70668788</v>
       </c>
       <c r="K23" t="n">
-        <v>-71.07491709613726</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L23" t="n">
-        <v>1407.3</v>
+        <v>1145.7</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Assault - aggravated on Jul 26, 2026, 1407 m from Copley Place (HARRISON AVE). Case #262064339 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CFS26-164393</t>
+          <t>26C142249</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46233.93733796296</v>
+        <v>46230.75</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>BATTERY ABW</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2989,26 +3085,26 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>SIM_ASSAULT</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>S LARCH AVE &amp; W 43RD ST</t>
+          <t>700 BLOCK OF S MISSION RD</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>43.51319846254545</v>
+        <v>37.6756469679485</v>
       </c>
       <c r="K24" t="n">
-        <v>-96.79336119066248</v>
+        <v>-97.25850032865422</v>
       </c>
       <c r="L24" t="n">
-        <v>1453.4</v>
+        <v>1251.5</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Assault on Jul 30, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-164393 (use for a records request — full narratives are not published in open data).</t>
+          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -3030,15 +3126,15 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CFS26-159792</t>
+          <t>CFS26-164521</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46229.12712962963</v>
+        <v>46234.03421296296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Weapons Violations</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3048,56 +3144,56 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Weapons</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>S LARCH AVE &amp; W 43RD ST</t>
+          <t>S MARION RD &amp; W 41ST ST</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>43.51319846254545</v>
+        <v>43.51481738299845</v>
       </c>
       <c r="K25" t="n">
-        <v>-96.79336119066248</v>
+        <v>-96.79096028032072</v>
       </c>
       <c r="L25" t="n">
-        <v>1453.4</v>
+        <v>1322.4</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Weapons violations on Jul 26, 2026, 1453 m from Empire Mall (S LARCH AVE &amp; W 43RD ST). Case #CFS26-159792 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 31, 2026, 1322 m from Empire Mall (S MARION RD &amp; W 41ST ST). Case #CFS26-164521 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>COPLEY</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>262064587</t>
+          <t>096140526</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46230.5</v>
+        <v>46232</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ASSAULT - AGGRAVATED</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3105,24 +3201,28 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>13A</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MASSACHUSETTS AVE</t>
+          <t>1900-1999 POST OAK PARK DR</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>42.3342194178955</v>
+        <v>29.74712522681273</v>
       </c>
       <c r="K26" t="n">
-        <v>-71.07434615707857</v>
+        <v>-95.45374747370188</v>
       </c>
       <c r="L26" t="n">
-        <v>1513.9</v>
+        <v>1323.4</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Assault - aggravated on Jul 27, 2026, 1514 m from Copley Place (MASSACHUSETTS AVE). Case #262064587 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 29, 2026, 1323 m from Houston Galleria (1900-1999 POST OAK PARK DR). Case #096140526 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M350"/>
+  <dimension ref="A1:M391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19940,40 +20040,40 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>262064179</t>
+          <t>262064284</t>
         </is>
       </c>
       <c r="E287" s="3" t="n">
-        <v>46229.07361111111</v>
+        <v>46229.54305555556</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>INVESTIGATE PROPERTY</t>
+          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H287" t="inlineStr"/>
       <c r="I287" t="inlineStr">
         <is>
-          <t>BOYLSTON ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J287" t="n">
-        <v>42.35234109431519</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K287" t="n">
-        <v>-71.06432465046424</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L287" t="n">
-        <v>1213.3</v>
+        <v>1123.7</v>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Investigate property on Jul 26, 2026, 1213 m from Copley Place (BOYLSTON ST). Case #262064179 (use for a records request — full narratives are not published in open data).</t>
+          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064284 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -19995,15 +20095,15 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>262064284</t>
+          <t>262064275</t>
         </is>
       </c>
       <c r="E288" s="3" t="n">
-        <v>46229.54305555556</v>
+        <v>46229.51111111111</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
+          <t>FORGERY / COUNTERFEITING</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -20028,7 +20128,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064284 (use for a records request — full narratives are not published in open data).</t>
+          <t>Forgery / counterfeiting on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064275 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20050,15 +20150,15 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>262064275</t>
+          <t>262064650</t>
         </is>
       </c>
       <c r="E289" s="3" t="n">
-        <v>46229.51111111111</v>
+        <v>46230.61875</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>FORGERY / COUNTERFEITING</t>
+          <t>M/V ACCIDENT - INVOLVING BICYCLE - INJURY</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -20068,77 +20168,22 @@
       </c>
       <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr">
-        <is>
-          <t>HARRISON AVE</t>
-        </is>
-      </c>
-      <c r="J289" t="n">
-        <v>42.33954198983015</v>
-      </c>
-      <c r="K289" t="n">
-        <v>-71.06940876967543</v>
-      </c>
-      <c r="L289" t="n">
-        <v>1123.7</v>
-      </c>
-      <c r="M289" t="inlineStr">
-        <is>
-          <t>Forgery / counterfeiting on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064275 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>262064650</t>
-        </is>
-      </c>
-      <c r="E290" s="3" t="n">
-        <v>46230.61875</v>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>M/V ACCIDENT - INVOLVING BICYCLE - INJURY</t>
-        </is>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H290" t="inlineStr"/>
-      <c r="I290" t="inlineStr">
         <is>
           <t>MASSACHUSETTS AVE &amp; TREMONT ST
 BOSTON, MA 02118
 UN</t>
         </is>
       </c>
-      <c r="J290" t="n">
+      <c r="J289" t="n">
         <v>42.33929095757131</v>
       </c>
-      <c r="K290" t="n">
+      <c r="K289" t="n">
         <v>-71.08041395047391</v>
       </c>
-      <c r="L290" t="n">
+      <c r="L289" t="n">
         <v>953.4</v>
       </c>
-      <c r="M290" t="inlineStr">
+      <c r="M289" t="inlineStr">
         <is>
           <t>M/v accident - involving bicycle - injury on Jul 27, 2026, 953 m from Copley Place (MASSACHUSETTS AVE &amp; TREMONT ST
 BOSTON, MA 02118
@@ -20146,6 +20191,61 @@
         </is>
       </c>
     </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>262064295</t>
+        </is>
+      </c>
+      <c r="E290" s="3" t="n">
+        <v>46229.54791666667</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J290" t="n">
+        <v>42.34862381555496</v>
+      </c>
+      <c r="K290" t="n">
+        <v>-71.08277637086411</v>
+      </c>
+      <c r="L290" t="n">
+        <v>437.3</v>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 26, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064295 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
@@ -20164,15 +20264,15 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>262064295</t>
+          <t>262064382</t>
         </is>
       </c>
       <c r="E291" s="3" t="n">
-        <v>46229.54791666667</v>
+        <v>46229.78680555556</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>SICK ASSIST</t>
+          <t>VERBAL DISPUTE</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -20183,21 +20283,21 @@
       <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr">
         <is>
-          <t>BOYLSTON ST</t>
+          <t>HUDSON ST</t>
         </is>
       </c>
       <c r="J291" t="n">
-        <v>42.34862381555496</v>
+        <v>42.34976401607222</v>
       </c>
       <c r="K291" t="n">
-        <v>-71.08277637086411</v>
+        <v>-71.06045076420118</v>
       </c>
       <c r="L291" t="n">
-        <v>437.3</v>
+        <v>1432.1</v>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Sick assist on Jul 26, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064295 (use for a records request — full narratives are not published in open data).</t>
+          <t>Verbal dispute on Jul 26, 2026, 1432 m from Copley Place (HUDSON ST). Case #262064382 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20219,40 +20319,40 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>262064382</t>
+          <t>262064432</t>
         </is>
       </c>
       <c r="E292" s="3" t="n">
-        <v>46229.78680555556</v>
+        <v>46229.91666666666</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>VERBAL DISPUTE</t>
+          <t>ROBBERY</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr">
         <is>
-          <t>HUDSON ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J292" t="n">
-        <v>42.34976401607222</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K292" t="n">
-        <v>-71.06045076420118</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L292" t="n">
-        <v>1432.1</v>
+        <v>1123.7</v>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Verbal dispute on Jul 26, 2026, 1432 m from Copley Place (HUDSON ST). Case #262064382 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064432 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20274,40 +20374,40 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>262064432</t>
+          <t>262064822</t>
         </is>
       </c>
       <c r="E293" s="3" t="n">
-        <v>46229.91666666666</v>
+        <v>46230.83541666667</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>ROBBERY</t>
+          <t>INVESTIGATE PERSON</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>COLUMBUS SQ</t>
         </is>
       </c>
       <c r="J293" t="n">
-        <v>42.33954198983015</v>
+        <v>42.34332879779392</v>
       </c>
       <c r="K293" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.07788857963692</v>
       </c>
       <c r="L293" t="n">
-        <v>1123.7</v>
+        <v>477.1</v>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Robbery on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064432 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 27, 2026, 477 m from Copley Place (COLUMBUS SQ). Case #262064822 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20329,11 +20429,11 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>262064822</t>
+          <t>262064697</t>
         </is>
       </c>
       <c r="E294" s="3" t="n">
-        <v>46230.83541666667</v>
+        <v>46230.70277777778</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -20348,21 +20448,21 @@
       <c r="H294" t="inlineStr"/>
       <c r="I294" t="inlineStr">
         <is>
-          <t>COLUMBUS SQ</t>
+          <t>MASSACHUSETTS AVE</t>
         </is>
       </c>
       <c r="J294" t="n">
-        <v>42.34332879779392</v>
+        <v>42.34867437636976</v>
       </c>
       <c r="K294" t="n">
-        <v>-71.07788857963692</v>
+        <v>-71.08841866225799</v>
       </c>
       <c r="L294" t="n">
-        <v>477.1</v>
+        <v>894.2</v>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Investigate person on Jul 27, 2026, 477 m from Copley Place (COLUMBUS SQ). Case #262064822 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 27, 2026, 894 m from Copley Place (MASSACHUSETTS AVE). Case #262064697 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20384,40 +20484,40 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>262064697</t>
+          <t>262064696</t>
         </is>
       </c>
       <c r="E295" s="3" t="n">
-        <v>46230.70277777778</v>
+        <v>46230.57777777778</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>INVESTIGATE PERSON</t>
+          <t>LARCENY THEFT FROM BUILDING</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr">
         <is>
-          <t>MASSACHUSETTS AVE</t>
+          <t>LINCOLN ST</t>
         </is>
       </c>
       <c r="J295" t="n">
-        <v>42.34867437636976</v>
+        <v>42.35043296884182</v>
       </c>
       <c r="K295" t="n">
-        <v>-71.08841866225799</v>
+        <v>-71.05873157807835</v>
       </c>
       <c r="L295" t="n">
-        <v>894.2</v>
+        <v>1584.6</v>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Investigate person on Jul 27, 2026, 894 m from Copley Place (MASSACHUSETTS AVE). Case #262064697 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny theft from building on Jul 27, 2026, 1585 m from Copley Place (LINCOLN ST). Case #262064696 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20439,15 +20539,15 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>262064696</t>
+          <t>262064796</t>
         </is>
       </c>
       <c r="E296" s="3" t="n">
-        <v>46230.57777777778</v>
+        <v>46230.75</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>LARCENY THEFT FROM BUILDING</t>
+          <t>PROPERTY - LOST/ MISSING</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -20458,21 +20558,21 @@
       <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr">
         <is>
-          <t>LINCOLN ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J296" t="n">
-        <v>42.35043296884182</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K296" t="n">
-        <v>-71.05873157807835</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L296" t="n">
-        <v>1584.6</v>
+        <v>1123.7</v>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Larceny theft from building on Jul 27, 2026, 1585 m from Copley Place (LINCOLN ST). Case #262064696 (use for a records request — full narratives are not published in open data).</t>
+          <t>Property - lost/ missing on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064796 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20494,40 +20594,40 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>262064796</t>
+          <t>262064756</t>
         </is>
       </c>
       <c r="E297" s="3" t="n">
-        <v>46230.75</v>
+        <v>46230.80347222222</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>PROPERTY - LOST/ MISSING</t>
+          <t>ASSAULT - SIMPLE</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H297" t="inlineStr"/>
       <c r="I297" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>MASSACHUSETTS AVE</t>
         </is>
       </c>
       <c r="J297" t="n">
-        <v>42.33954198983015</v>
+        <v>42.34439568415441</v>
       </c>
       <c r="K297" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.08632016344815</v>
       </c>
       <c r="L297" t="n">
-        <v>1123.7</v>
+        <v>798.7</v>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Property - lost/ missing on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064796 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - simple on Jul 27, 2026, 799 m from Copley Place (MASSACHUSETTS AVE). Case #262064756 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20549,40 +20649,40 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>262064756</t>
+          <t>262064716</t>
         </is>
       </c>
       <c r="E298" s="3" t="n">
-        <v>46230.80347222222</v>
+        <v>46230.72638888889</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>ASSAULT - SIMPLE</t>
+          <t>LARCENY SHOPLIFTING</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H298" t="inlineStr"/>
       <c r="I298" t="inlineStr">
         <is>
-          <t>MASSACHUSETTS AVE</t>
+          <t>NEWBURY ST</t>
         </is>
       </c>
       <c r="J298" t="n">
-        <v>42.34439568415441</v>
+        <v>42.35059716982988</v>
       </c>
       <c r="K298" t="n">
-        <v>-71.08632016344815</v>
+        <v>-71.07881030689927</v>
       </c>
       <c r="L298" t="n">
-        <v>798.7</v>
+        <v>345.4</v>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Assault - simple on Jul 27, 2026, 799 m from Copley Place (MASSACHUSETTS AVE). Case #262064756 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny shoplifting on Jul 27, 2026, 345 m from Copley Place (NEWBURY ST). Case #262064716 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20604,40 +20704,40 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>262064716</t>
+          <t>262064587</t>
         </is>
       </c>
       <c r="E299" s="3" t="n">
-        <v>46230.72638888889</v>
+        <v>46230.5</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>LARCENY SHOPLIFTING</t>
+          <t>ASSAULT - AGGRAVATED</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H299" t="inlineStr"/>
       <c r="I299" t="inlineStr">
         <is>
-          <t>NEWBURY ST</t>
+          <t>MASSACHUSETTS AVE</t>
         </is>
       </c>
       <c r="J299" t="n">
-        <v>42.35059716982988</v>
+        <v>42.3342194178955</v>
       </c>
       <c r="K299" t="n">
-        <v>-71.07881030689927</v>
+        <v>-71.07434615707857</v>
       </c>
       <c r="L299" t="n">
-        <v>345.4</v>
+        <v>1513.9</v>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Larceny shoplifting on Jul 27, 2026, 345 m from Copley Place (NEWBURY ST). Case #262064716 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - aggravated on Jul 27, 2026, 1514 m from Copley Place (MASSACHUSETTS AVE). Case #262064587 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20659,40 +20759,40 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>262064587</t>
+          <t>262064392</t>
         </is>
       </c>
       <c r="E300" s="3" t="n">
-        <v>46230.5</v>
+        <v>46229.82222222222</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>ASSAULT - AGGRAVATED</t>
+          <t>M/V ACCIDENT - OTHER</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H300" t="inlineStr"/>
       <c r="I300" t="inlineStr">
         <is>
-          <t>MASSACHUSETTS AVE</t>
+          <t>TYLER ST</t>
         </is>
       </c>
       <c r="J300" t="n">
-        <v>42.3342194178955</v>
+        <v>42.3509005960865</v>
       </c>
       <c r="K300" t="n">
-        <v>-71.07434615707857</v>
+        <v>-71.06068690177561</v>
       </c>
       <c r="L300" t="n">
-        <v>1513.9</v>
+        <v>1439.7</v>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Assault - aggravated on Jul 27, 2026, 1514 m from Copley Place (MASSACHUSETTS AVE). Case #262064587 (use for a records request — full narratives are not published in open data).</t>
+          <t>M/v accident - other on Jul 26, 2026, 1440 m from Copley Place (TYLER ST). Case #262064392 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20714,15 +20814,15 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>262064392</t>
+          <t>262064350</t>
         </is>
       </c>
       <c r="E301" s="3" t="n">
-        <v>46229.82222222222</v>
+        <v>46229.70486111111</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>M/V ACCIDENT - OTHER</t>
+          <t>INVESTIGATE PERSON</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -20733,21 +20833,21 @@
       <c r="H301" t="inlineStr"/>
       <c r="I301" t="inlineStr">
         <is>
-          <t>TYLER ST</t>
+          <t>HUNTINGTON AVE</t>
         </is>
       </c>
       <c r="J301" t="n">
-        <v>42.3509005960865</v>
+        <v>42.3473097976345</v>
       </c>
       <c r="K301" t="n">
-        <v>-71.06068690177561</v>
+        <v>-71.0791516658207</v>
       </c>
       <c r="L301" t="n">
-        <v>1439.7</v>
+        <v>129.3</v>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>M/v accident - other on Jul 26, 2026, 1440 m from Copley Place (TYLER ST). Case #262064392 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064350 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20769,40 +20869,40 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>262064350</t>
+          <t>262064616</t>
         </is>
       </c>
       <c r="E302" s="3" t="n">
-        <v>46229.70486111111</v>
+        <v>46230.50347222222</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>INVESTIGATE PERSON</t>
+          <t>DRUGS - POSSESSION/ SALE/ MANUFACTURING/ USE</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
       <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr">
         <is>
-          <t>HUNTINGTON AVE</t>
+          <t>BOYLSTON SQ</t>
         </is>
       </c>
       <c r="J302" t="n">
-        <v>42.3473097976345</v>
+        <v>42.35197501205302</v>
       </c>
       <c r="K302" t="n">
-        <v>-71.0791516658207</v>
+        <v>-71.06332910808086</v>
       </c>
       <c r="L302" t="n">
-        <v>129.3</v>
+        <v>1271.5</v>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Investigate person on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064350 (use for a records request — full narratives are not published in open data).</t>
+          <t>Drugs - possession/ sale/ manufacturing/ use on Jul 27, 2026, 1272 m from Copley Place (BOYLSTON SQ). Case #262064616 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20824,40 +20924,40 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>262064616</t>
+          <t>262064640</t>
         </is>
       </c>
       <c r="E303" s="3" t="n">
-        <v>46230.50347222222</v>
+        <v>46230.3125</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>DRUGS - POSSESSION/ SALE/ MANUFACTURING/ USE</t>
+          <t>INVESTIGATE PERSON</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H303" t="inlineStr"/>
       <c r="I303" t="inlineStr">
         <is>
-          <t>BOYLSTON SQ</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J303" t="n">
-        <v>42.35197501205302</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K303" t="n">
-        <v>-71.06332910808086</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L303" t="n">
-        <v>1271.5</v>
+        <v>1123.7</v>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Drugs - possession/ sale/ manufacturing/ use on Jul 27, 2026, 1272 m from Copley Place (BOYLSTON SQ). Case #262064616 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064640 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20879,40 +20979,40 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>262064640</t>
+          <t>262064573</t>
         </is>
       </c>
       <c r="E304" s="3" t="n">
-        <v>46230.3125</v>
+        <v>46230.45833333334</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>INVESTIGATE PERSON</t>
+          <t>SICK ASSIST - DRUG RELATED ILLNESS</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
       <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>ALBANY ST</t>
         </is>
       </c>
       <c r="J304" t="n">
-        <v>42.33954198983015</v>
+        <v>42.33428840659414</v>
       </c>
       <c r="K304" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.07239517543796</v>
       </c>
       <c r="L304" t="n">
-        <v>1123.7</v>
+        <v>1543.1</v>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Investigate person on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064640 (use for a records request — full narratives are not published in open data).</t>
+          <t>Sick assist - drug related illness on Jul 27, 2026, 1543 m from Copley Place (ALBANY ST). Case #262064573 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20934,40 +21034,40 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>262064573</t>
+          <t>262064608</t>
         </is>
       </c>
       <c r="E305" s="3" t="n">
-        <v>46230.45833333334</v>
+        <v>46230</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>SICK ASSIST - DRUG RELATED ILLNESS</t>
+          <t>THREATS TO DO BODILY HARM</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr">
         <is>
-          <t>ALBANY ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J305" t="n">
-        <v>42.33428840659414</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K305" t="n">
-        <v>-71.07239517543796</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L305" t="n">
-        <v>1543.1</v>
+        <v>1123.7</v>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Sick assist - drug related illness on Jul 27, 2026, 1543 m from Copley Place (ALBANY ST). Case #262064573 (use for a records request — full narratives are not published in open data).</t>
+          <t>Threats to do bodily harm on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064608 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -20989,40 +21089,40 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>262064608</t>
+          <t>262064378</t>
         </is>
       </c>
       <c r="E306" s="3" t="n">
-        <v>46230</v>
+        <v>46229.79097222222</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>THREATS TO DO BODILY HARM</t>
+          <t>LARCENY ALL OTHERS</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H306" t="inlineStr"/>
       <c r="I306" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>W CONCORD ST</t>
         </is>
       </c>
       <c r="J306" t="n">
-        <v>42.33954198983015</v>
+        <v>42.33961961800693</v>
       </c>
       <c r="K306" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.07699236739417</v>
       </c>
       <c r="L306" t="n">
-        <v>1123.7</v>
+        <v>890.6</v>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Threats to do bodily harm on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064608 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny all others on Jul 26, 2026, 891 m from Copley Place (W CONCORD ST). Case #262064378 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21044,40 +21144,40 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>262064378</t>
+          <t>262064152</t>
         </is>
       </c>
       <c r="E307" s="3" t="n">
-        <v>46229.79097222222</v>
+        <v>46229.01458333333</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>LARCENY ALL OTHERS</t>
+          <t>NOISY PARTY/RADIO-NO ARREST</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr">
         <is>
-          <t>W CONCORD ST</t>
+          <t>PHILLIPS ST</t>
         </is>
       </c>
       <c r="J307" t="n">
-        <v>42.33961961800693</v>
+        <v>42.36027809483424</v>
       </c>
       <c r="K307" t="n">
-        <v>-71.07699236739417</v>
+        <v>-71.06899804851336</v>
       </c>
       <c r="L307" t="n">
-        <v>890.6</v>
+        <v>1576.7</v>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Larceny all others on Jul 26, 2026, 891 m from Copley Place (W CONCORD ST). Case #262064378 (use for a records request — full narratives are not published in open data).</t>
+          <t>Noisy party/radio-no arrest on Jul 26, 2026, 1577 m from Copley Place (PHILLIPS ST). Case #262064152 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21099,40 +21199,40 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>262064152</t>
+          <t>262064312</t>
         </is>
       </c>
       <c r="E308" s="3" t="n">
-        <v>46229.01458333333</v>
+        <v>46229.60625</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>NOISY PARTY/RADIO-NO ARREST</t>
+          <t>SICK ASSIST - DRUG RELATED ILLNESS</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
       <c r="H308" t="inlineStr"/>
       <c r="I308" t="inlineStr">
         <is>
-          <t>PHILLIPS ST</t>
+          <t>ALBANY ST</t>
         </is>
       </c>
       <c r="J308" t="n">
-        <v>42.36027809483424</v>
+        <v>42.33428840659414</v>
       </c>
       <c r="K308" t="n">
-        <v>-71.06899804851336</v>
+        <v>-71.07239517543796</v>
       </c>
       <c r="L308" t="n">
-        <v>1576.7</v>
+        <v>1543.1</v>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Noisy party/radio-no arrest on Jul 26, 2026, 1577 m from Copley Place (PHILLIPS ST). Case #262064152 (use for a records request — full narratives are not published in open data).</t>
+          <t>Sick assist - drug related illness on Jul 26, 2026, 1543 m from Copley Place (ALBANY ST). Case #262064312 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21154,40 +21254,40 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>262064312</t>
+          <t>262064770</t>
         </is>
       </c>
       <c r="E309" s="3" t="n">
-        <v>46229.60625</v>
+        <v>46230.52083333334</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>SICK ASSIST - DRUG RELATED ILLNESS</t>
+          <t>LARCENY THEFT FROM MV - NON-ACCESSORY</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr">
         <is>
-          <t>ALBANY ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J309" t="n">
-        <v>42.33428840659414</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K309" t="n">
-        <v>-71.07239517543796</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L309" t="n">
-        <v>1543.1</v>
+        <v>1123.7</v>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Sick assist - drug related illness on Jul 26, 2026, 1543 m from Copley Place (ALBANY ST). Case #262064312 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny theft from mv - non-accessory on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064770 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21209,15 +21309,15 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>262064770</t>
+          <t>262064532</t>
         </is>
       </c>
       <c r="E310" s="3" t="n">
-        <v>46230.52083333334</v>
+        <v>46230.29166666666</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>LARCENY THEFT FROM MV - NON-ACCESSORY</t>
+          <t>PROPERTY - LOST/ MISSING</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -21242,7 +21342,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Larceny theft from mv - non-accessory on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064770 (use for a records request — full narratives are not published in open data).</t>
+          <t>Property - lost/ missing on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064532 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21264,15 +21364,15 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>262064532</t>
+          <t>262064590</t>
         </is>
       </c>
       <c r="E311" s="3" t="n">
-        <v>46230.29166666666</v>
+        <v>46230.50625</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>PROPERTY - LOST/ MISSING</t>
+          <t>LARCENY ALL OTHERS</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -21283,21 +21383,21 @@
       <c r="H311" t="inlineStr"/>
       <c r="I311" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>W BROOKLINE ST</t>
         </is>
       </c>
       <c r="J311" t="n">
-        <v>42.33954198983015</v>
+        <v>42.34172590358821</v>
       </c>
       <c r="K311" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.07501847816492</v>
       </c>
       <c r="L311" t="n">
-        <v>1123.7</v>
+        <v>689.2</v>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Property - lost/ missing on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064532 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny all others on Jul 27, 2026, 689 m from Copley Place (W BROOKLINE ST). Case #262064590 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21319,15 +21419,15 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>262064590</t>
+          <t>262064674</t>
         </is>
       </c>
       <c r="E312" s="3" t="n">
-        <v>46230.50625</v>
+        <v>46229.33333333334</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>LARCENY ALL OTHERS</t>
+          <t>PROPERTY - LOST/ MISSING</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -21338,21 +21438,21 @@
       <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr">
         <is>
-          <t>W BROOKLINE ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J312" t="n">
-        <v>42.34172590358821</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K312" t="n">
-        <v>-71.07501847816492</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L312" t="n">
-        <v>689.2</v>
+        <v>1123.7</v>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Larceny all others on Jul 27, 2026, 689 m from Copley Place (W BROOKLINE ST). Case #262064590 (use for a records request — full narratives are not published in open data).</t>
+          <t>Property - lost/ missing on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064674 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21374,40 +21474,40 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>262064674</t>
+          <t>262064591</t>
         </is>
       </c>
       <c r="E313" s="3" t="n">
-        <v>46229.33333333334</v>
+        <v>46229.77847222222</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>PROPERTY - LOST/ MISSING</t>
+          <t>INVESTIGATE PERSON</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H313" t="inlineStr"/>
       <c r="I313" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>AVERY ST</t>
         </is>
       </c>
       <c r="J313" t="n">
-        <v>42.33954198983015</v>
+        <v>42.35327560751949</v>
       </c>
       <c r="K313" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.06345772204415</v>
       </c>
       <c r="L313" t="n">
-        <v>1123.7</v>
+        <v>1324</v>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Property - lost/ missing on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064674 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 26, 2026, 1324 m from Copley Place (AVERY ST). Case #262064591 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21429,15 +21529,15 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>262064591</t>
+          <t>262064579</t>
         </is>
       </c>
       <c r="E314" s="3" t="n">
-        <v>46229.77847222222</v>
+        <v>46230.43402777778</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>INVESTIGATE PERSON</t>
+          <t>SICK/INJURED/MEDICAL - PERSON</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -21448,21 +21548,21 @@
       <c r="H314" t="inlineStr"/>
       <c r="I314" t="inlineStr">
         <is>
-          <t>AVERY ST</t>
+          <t>NORTHAMPTON ST</t>
         </is>
       </c>
       <c r="J314" t="n">
-        <v>42.35327560751949</v>
+        <v>42.33395124839377</v>
       </c>
       <c r="K314" t="n">
-        <v>-71.06345772204415</v>
+        <v>-71.07538938822692</v>
       </c>
       <c r="L314" t="n">
-        <v>1324</v>
+        <v>1530.5</v>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Investigate person on Jul 26, 2026, 1324 m from Copley Place (AVERY ST). Case #262064591 (use for a records request — full narratives are not published in open data).</t>
+          <t>Sick/injured/medical - person on Jul 27, 2026, 1531 m from Copley Place (NORTHAMPTON ST). Case #262064579 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21484,40 +21584,40 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>262064579</t>
+          <t>262064357</t>
         </is>
       </c>
       <c r="E315" s="3" t="n">
-        <v>46230.43402777778</v>
+        <v>46229.72638888889</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>SICK/INJURED/MEDICAL - PERSON</t>
+          <t>LARCENY SHOPLIFTING</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H315" t="inlineStr"/>
       <c r="I315" t="inlineStr">
         <is>
-          <t>NORTHAMPTON ST</t>
+          <t>HUNTINGTON AVE</t>
         </is>
       </c>
       <c r="J315" t="n">
-        <v>42.33395124839377</v>
+        <v>42.3473097976345</v>
       </c>
       <c r="K315" t="n">
-        <v>-71.07538938822692</v>
+        <v>-71.0791516658207</v>
       </c>
       <c r="L315" t="n">
-        <v>1530.5</v>
+        <v>129.3</v>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Sick/injured/medical - person on Jul 27, 2026, 1531 m from Copley Place (NORTHAMPTON ST). Case #262064579 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny shoplifting on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064357 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21539,15 +21639,15 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>262064802</t>
+          <t>262064198</t>
         </is>
       </c>
       <c r="E316" s="3" t="n">
-        <v>46230.89583333334</v>
+        <v>46229.16736111111</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>LARCENY SHOPLIFTING</t>
+          <t>TOWED MOTOR VEHICLE</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -21558,21 +21658,25 @@
       <c r="H316" t="inlineStr"/>
       <c r="I316" t="inlineStr">
         <is>
-          <t>BOYLSTON ST</t>
+          <t>STUART ST &amp; CHARLES ST S
+BOSTON, MA 02116
+UNITED S</t>
         </is>
       </c>
       <c r="J316" t="n">
-        <v>42.34862381555496</v>
+        <v>42.35095701392956</v>
       </c>
       <c r="K316" t="n">
-        <v>-71.08277637086411</v>
+        <v>-71.06685999332976</v>
       </c>
       <c r="L316" t="n">
-        <v>437.3</v>
+        <v>960.1</v>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Larceny shoplifting on Jul 27, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064802 (use for a records request — full narratives are not published in open data).</t>
+          <t>Towed motor vehicle on Jul 26, 2026, 960 m from Copley Place (STUART ST &amp; CHARLES ST S
+BOSTON, MA 02116
+UNITED S). Case #262064198 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21594,15 +21698,15 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>262064409</t>
+          <t>262064309</t>
         </is>
       </c>
       <c r="E317" s="3" t="n">
-        <v>46229.85833333333</v>
+        <v>46229.39444444444</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>SICK ASSIST</t>
+          <t>INVESTIGATE PERSON</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -21613,21 +21717,21 @@
       <c r="H317" t="inlineStr"/>
       <c r="I317" t="inlineStr">
         <is>
-          <t>OXFORD ST</t>
+          <t>SAINT BOTOLPH ST</t>
         </is>
       </c>
       <c r="J317" t="n">
-        <v>42.35193460488232</v>
+        <v>42.34617475544754</v>
       </c>
       <c r="K317" t="n">
-        <v>-71.06048592223925</v>
+        <v>-71.07925920373032</v>
       </c>
       <c r="L317" t="n">
-        <v>1488.7</v>
+        <v>208.6</v>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Sick assist on Jul 26, 2026, 1489 m from Copley Place (OXFORD ST). Case #262064409 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 26, 2026, 209 m from Copley Place (SAINT BOTOLPH ST). Case #262064309 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21649,40 +21753,40 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>262064318</t>
+          <t>262064283</t>
         </is>
       </c>
       <c r="E318" s="3" t="n">
-        <v>46229.53958333333</v>
+        <v>46229.51736111111</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>INVESTIGATE PERSON</t>
+          <t>LARCENY SHOPLIFTING</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H318" t="inlineStr"/>
       <c r="I318" t="inlineStr">
         <is>
-          <t>SHAWMUT AVE</t>
+          <t>HUNTINGTON AVE</t>
         </is>
       </c>
       <c r="J318" t="n">
-        <v>42.34319452771496</v>
+        <v>42.3473097976345</v>
       </c>
       <c r="K318" t="n">
-        <v>-71.06880536524001</v>
+        <v>-71.0791516658207</v>
       </c>
       <c r="L318" t="n">
-        <v>876.3</v>
+        <v>129.3</v>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Investigate person on Jul 26, 2026, 876 m from Copley Place (SHAWMUT AVE). Case #262064318 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny shoplifting on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064283 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21704,40 +21808,44 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>262064412</t>
+          <t>262064226</t>
         </is>
       </c>
       <c r="E319" s="3" t="n">
-        <v>46229.87638888889</v>
+        <v>46229.375</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>SICK/INJURED/MEDICAL - PERSON</t>
+          <t>M/V ACCIDENT - PROPERTY DAMAGE</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H319" t="inlineStr"/>
       <c r="I319" t="inlineStr">
         <is>
-          <t>TREMONT ST</t>
+          <t>BERKELEY ST &amp; SAINT JAMES AVE
+BOSTON, MA 02116
+UNI</t>
         </is>
       </c>
       <c r="J319" t="n">
-        <v>42.35428377241487</v>
+        <v>42.3504290420294</v>
       </c>
       <c r="K319" t="n">
-        <v>-71.06380403747467</v>
+        <v>-71.07264798093048</v>
       </c>
       <c r="L319" t="n">
-        <v>1356.9</v>
+        <v>515.5</v>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Sick/injured/medical - person on Jul 26, 2026, 1357 m from Copley Place (TREMONT ST). Case #262064412 (use for a records request — full narratives are not published in open data).</t>
+          <t>M/v accident - property damage on Jul 26, 2026, 515 m from Copley Place (BERKELEY ST &amp; SAINT JAMES AVE
+BOSTON, MA 02116
+UNI). Case #262064226 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21759,40 +21867,44 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>262064362</t>
+          <t>262064268</t>
         </is>
       </c>
       <c r="E320" s="3" t="n">
-        <v>46229.64305555556</v>
+        <v>46229.48680555556</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
+          <t>LARCENY THEFT FROM BUILDING</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H320" t="inlineStr"/>
       <c r="I320" t="inlineStr">
         <is>
-          <t>DARTMOUTH ST</t>
+          <t>REED ST &amp; E LENOX ST
+ROXBURY, MA 02118
+UNITED STAT</t>
         </is>
       </c>
       <c r="J320" t="n">
-        <v>42.35029374297969</v>
+        <v>42.33406097367816</v>
       </c>
       <c r="K320" t="n">
-        <v>-71.07744671381569</v>
+        <v>-71.07756301316894</v>
       </c>
       <c r="L320" t="n">
-        <v>298.2</v>
+        <v>1507.2</v>
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 298 m from Copley Place (DARTMOUTH ST). Case #262064362 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny theft from building on Jul 26, 2026, 1507 m from Copley Place (REED ST &amp; E LENOX ST
+ROXBURY, MA 02118
+UNITED STAT). Case #262064268 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -21814,15 +21926,15 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>262064307</t>
+          <t>262064394</t>
         </is>
       </c>
       <c r="E321" s="3" t="n">
-        <v>46229.59027777778</v>
+        <v>46229.82152777778</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>SICK ASSIST</t>
+          <t>M/V ACCIDENT - OTHER</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -21832,22 +21944,466 @@
       </c>
       <c r="H321" t="inlineStr"/>
       <c r="I321" t="inlineStr">
+        <is>
+          <t>HARRISON AVE &amp; PLYMPTON ST
+BOSTON, MA 02118
+UNITED</t>
+        </is>
+      </c>
+      <c r="J321" t="n">
+        <v>42.33973998780085</v>
+      </c>
+      <c r="K321" t="n">
+        <v>-71.0691099454142</v>
+      </c>
+      <c r="L321" t="n">
+        <v>1121.4</v>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>M/v accident - other on Jul 26, 2026, 1121 m from Copley Place (HARRISON AVE &amp; PLYMPTON ST
+BOSTON, MA 02118
+UNITED). Case #262064394 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>262064321</t>
+        </is>
+      </c>
+      <c r="E322" s="3" t="n">
+        <v>46229.59166666667</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>M/V - LEAVING SCENE - PROPERTY DAMAGE</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J322" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K322" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L322" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>M/v - leaving scene - property damage on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064321 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>262064179</t>
+        </is>
+      </c>
+      <c r="E323" s="3" t="n">
+        <v>46229.07361111111</v>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PROPERTY</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J323" t="n">
+        <v>42.35234109431519</v>
+      </c>
+      <c r="K323" t="n">
+        <v>-71.06432465046424</v>
+      </c>
+      <c r="L323" t="n">
+        <v>1213.3</v>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>Investigate property on Jul 26, 2026, 1213 m from Copley Place (BOYLSTON ST). Case #262064179 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>262064802</t>
+        </is>
+      </c>
+      <c r="E324" s="3" t="n">
+        <v>46230.89583333334</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>LARCENY SHOPLIFTING</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J324" t="n">
+        <v>42.34862381555496</v>
+      </c>
+      <c r="K324" t="n">
+        <v>-71.08277637086411</v>
+      </c>
+      <c r="L324" t="n">
+        <v>437.3</v>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 27, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064802 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>262064409</t>
+        </is>
+      </c>
+      <c r="E325" s="3" t="n">
+        <v>46229.85833333333</v>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>OXFORD ST</t>
+        </is>
+      </c>
+      <c r="J325" t="n">
+        <v>42.35193460488232</v>
+      </c>
+      <c r="K325" t="n">
+        <v>-71.06048592223925</v>
+      </c>
+      <c r="L325" t="n">
+        <v>1488.7</v>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 26, 2026, 1489 m from Copley Place (OXFORD ST). Case #262064409 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>262064318</t>
+        </is>
+      </c>
+      <c r="E326" s="3" t="n">
+        <v>46229.53958333333</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PERSON</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr"/>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>SHAWMUT AVE</t>
+        </is>
+      </c>
+      <c r="J326" t="n">
+        <v>42.34319452771496</v>
+      </c>
+      <c r="K326" t="n">
+        <v>-71.06880536524001</v>
+      </c>
+      <c r="L326" t="n">
+        <v>876.3</v>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>Investigate person on Jul 26, 2026, 876 m from Copley Place (SHAWMUT AVE). Case #262064318 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>262064412</t>
+        </is>
+      </c>
+      <c r="E327" s="3" t="n">
+        <v>46229.87638888889</v>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>SICK/INJURED/MEDICAL - PERSON</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>TREMONT ST</t>
+        </is>
+      </c>
+      <c r="J327" t="n">
+        <v>42.35428377241487</v>
+      </c>
+      <c r="K327" t="n">
+        <v>-71.06380403747467</v>
+      </c>
+      <c r="L327" t="n">
+        <v>1356.9</v>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>Sick/injured/medical - person on Jul 26, 2026, 1357 m from Copley Place (TREMONT ST). Case #262064412 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>262064362</t>
+        </is>
+      </c>
+      <c r="E328" s="3" t="n">
+        <v>46229.64305555556</v>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr"/>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>DARTMOUTH ST</t>
+        </is>
+      </c>
+      <c r="J328" t="n">
+        <v>42.35029374297969</v>
+      </c>
+      <c r="K328" t="n">
+        <v>-71.07744671381569</v>
+      </c>
+      <c r="L328" t="n">
+        <v>298.2</v>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 298 m from Copley Place (DARTMOUTH ST). Case #262064362 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>262064307</t>
+        </is>
+      </c>
+      <c r="E329" s="3" t="n">
+        <v>46229.59027777778</v>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr">
         <is>
           <t>TREMONT ST &amp; TEMPLE PL
 BOSTON, MA 02111
 UNITED STA</t>
         </is>
       </c>
-      <c r="J321" t="n">
+      <c r="J329" t="n">
         <v>42.35561100811422</v>
       </c>
-      <c r="K321" t="n">
+      <c r="K329" t="n">
         <v>-71.06289400004533</v>
       </c>
-      <c r="L321" t="n">
+      <c r="L329" t="n">
         <v>1502.5</v>
       </c>
-      <c r="M321" t="inlineStr">
+      <c r="M329" t="inlineStr">
         <is>
           <t>Sick assist on Jul 26, 2026, 1502 m from Copley Place (TREMONT ST &amp; TEMPLE PL
 BOSTON, MA 02111
@@ -21855,450 +22411,6 @@
         </is>
       </c>
     </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>262064419</t>
-        </is>
-      </c>
-      <c r="E322" s="3" t="n">
-        <v>46229.90138888889</v>
-      </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>HARASSMENT/ CRIMINAL HARASSMENT</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H322" t="inlineStr"/>
-      <c r="I322" t="inlineStr">
-        <is>
-          <t>NASSAU ST</t>
-        </is>
-      </c>
-      <c r="J322" t="n">
-        <v>42.34880604399623</v>
-      </c>
-      <c r="K322" t="n">
-        <v>-71.06285446968663</v>
-      </c>
-      <c r="L322" t="n">
-        <v>1221.7</v>
-      </c>
-      <c r="M322" t="inlineStr">
-        <is>
-          <t>Harassment/ criminal harassment on Jul 26, 2026, 1222 m from Copley Place (NASSAU ST). Case #262064419 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>262064339</t>
-        </is>
-      </c>
-      <c r="E323" s="3" t="n">
-        <v>46229.63333333333</v>
-      </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>ASSAULT - AGGRAVATED</t>
-        </is>
-      </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H323" t="inlineStr"/>
-      <c r="I323" t="inlineStr">
-        <is>
-          <t>HARRISON AVE</t>
-        </is>
-      </c>
-      <c r="J323" t="n">
-        <v>42.33511903946613</v>
-      </c>
-      <c r="K323" t="n">
-        <v>-71.07491709613726</v>
-      </c>
-      <c r="L323" t="n">
-        <v>1407.3</v>
-      </c>
-      <c r="M323" t="inlineStr">
-        <is>
-          <t>Assault - aggravated on Jul 26, 2026, 1407 m from Copley Place (HARRISON AVE). Case #262064339 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>262064236</t>
-        </is>
-      </c>
-      <c r="E324" s="3" t="n">
-        <v>46229.37638888889</v>
-      </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>SICK ASSIST</t>
-        </is>
-      </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H324" t="inlineStr"/>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>TREMONT ST</t>
-        </is>
-      </c>
-      <c r="J324" t="n">
-        <v>42.34470135794417</v>
-      </c>
-      <c r="K324" t="n">
-        <v>-71.0703760849388</v>
-      </c>
-      <c r="L324" t="n">
-        <v>678.7</v>
-      </c>
-      <c r="M324" t="inlineStr">
-        <is>
-          <t>Sick assist on Jul 26, 2026, 679 m from Copley Place (TREMONT ST). Case #262064236 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>262064234</t>
-        </is>
-      </c>
-      <c r="E325" s="3" t="n">
-        <v>46229.31944444445</v>
-      </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>INVESTIGATE PERSON</t>
-        </is>
-      </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H325" t="inlineStr"/>
-      <c r="I325" t="inlineStr">
-        <is>
-          <t>SAINT JAMES AVE</t>
-        </is>
-      </c>
-      <c r="J325" t="n">
-        <v>42.34947585701249</v>
-      </c>
-      <c r="K325" t="n">
-        <v>-71.07640149637847</v>
-      </c>
-      <c r="L325" t="n">
-        <v>230.3</v>
-      </c>
-      <c r="M325" t="inlineStr">
-        <is>
-          <t>Investigate person on Jul 26, 2026, 230 m from Copley Place (SAINT JAMES AVE). Case #262064234 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>262064357</t>
-        </is>
-      </c>
-      <c r="E326" s="3" t="n">
-        <v>46229.72638888889</v>
-      </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>LARCENY SHOPLIFTING</t>
-        </is>
-      </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H326" t="inlineStr"/>
-      <c r="I326" t="inlineStr">
-        <is>
-          <t>HUNTINGTON AVE</t>
-        </is>
-      </c>
-      <c r="J326" t="n">
-        <v>42.3473097976345</v>
-      </c>
-      <c r="K326" t="n">
-        <v>-71.0791516658207</v>
-      </c>
-      <c r="L326" t="n">
-        <v>129.3</v>
-      </c>
-      <c r="M326" t="inlineStr">
-        <is>
-          <t>Larceny shoplifting on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064357 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>262064198</t>
-        </is>
-      </c>
-      <c r="E327" s="3" t="n">
-        <v>46229.16736111111</v>
-      </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>TOWED MOTOR VEHICLE</t>
-        </is>
-      </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H327" t="inlineStr"/>
-      <c r="I327" t="inlineStr">
-        <is>
-          <t>STUART ST &amp; CHARLES ST S
-BOSTON, MA 02116
-UNITED S</t>
-        </is>
-      </c>
-      <c r="J327" t="n">
-        <v>42.35095701392956</v>
-      </c>
-      <c r="K327" t="n">
-        <v>-71.06685999332976</v>
-      </c>
-      <c r="L327" t="n">
-        <v>960.1</v>
-      </c>
-      <c r="M327" t="inlineStr">
-        <is>
-          <t>Towed motor vehicle on Jul 26, 2026, 960 m from Copley Place (STUART ST &amp; CHARLES ST S
-BOSTON, MA 02116
-UNITED S). Case #262064198 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>262064309</t>
-        </is>
-      </c>
-      <c r="E328" s="3" t="n">
-        <v>46229.39444444444</v>
-      </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>INVESTIGATE PERSON</t>
-        </is>
-      </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H328" t="inlineStr"/>
-      <c r="I328" t="inlineStr">
-        <is>
-          <t>SAINT BOTOLPH ST</t>
-        </is>
-      </c>
-      <c r="J328" t="n">
-        <v>42.34617475544754</v>
-      </c>
-      <c r="K328" t="n">
-        <v>-71.07925920373032</v>
-      </c>
-      <c r="L328" t="n">
-        <v>208.6</v>
-      </c>
-      <c r="M328" t="inlineStr">
-        <is>
-          <t>Investigate person on Jul 26, 2026, 209 m from Copley Place (SAINT BOTOLPH ST). Case #262064309 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>262064283</t>
-        </is>
-      </c>
-      <c r="E329" s="3" t="n">
-        <v>46229.51736111111</v>
-      </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>LARCENY SHOPLIFTING</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H329" t="inlineStr"/>
-      <c r="I329" t="inlineStr">
-        <is>
-          <t>HUNTINGTON AVE</t>
-        </is>
-      </c>
-      <c r="J329" t="n">
-        <v>42.3473097976345</v>
-      </c>
-      <c r="K329" t="n">
-        <v>-71.0791516658207</v>
-      </c>
-      <c r="L329" t="n">
-        <v>129.3</v>
-      </c>
-      <c r="M329" t="inlineStr">
-        <is>
-          <t>Larceny shoplifting on Jul 26, 2026, 129 m from Copley Place (HUNTINGTON AVE). Case #262064283 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
@@ -22317,44 +22429,40 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>262064226</t>
+          <t>262064419</t>
         </is>
       </c>
       <c r="E330" s="3" t="n">
-        <v>46229.375</v>
+        <v>46229.90138888889</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>M/V ACCIDENT - PROPERTY DAMAGE</t>
+          <t>HARASSMENT/ CRIMINAL HARASSMENT</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H330" t="inlineStr"/>
       <c r="I330" t="inlineStr">
         <is>
-          <t>BERKELEY ST &amp; SAINT JAMES AVE
-BOSTON, MA 02116
-UNI</t>
+          <t>NASSAU ST</t>
         </is>
       </c>
       <c r="J330" t="n">
-        <v>42.3504290420294</v>
+        <v>42.34880604399623</v>
       </c>
       <c r="K330" t="n">
-        <v>-71.07264798093048</v>
+        <v>-71.06285446968663</v>
       </c>
       <c r="L330" t="n">
-        <v>515.5</v>
+        <v>1221.7</v>
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>M/v accident - property damage on Jul 26, 2026, 515 m from Copley Place (BERKELEY ST &amp; SAINT JAMES AVE
-BOSTON, MA 02116
-UNI). Case #262064226 (use for a records request — full narratives are not published in open data).</t>
+          <t>Harassment/ criminal harassment on Jul 26, 2026, 1222 m from Copley Place (NASSAU ST). Case #262064419 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22376,44 +22484,40 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>262064268</t>
+          <t>262064339</t>
         </is>
       </c>
       <c r="E331" s="3" t="n">
-        <v>46229.48680555556</v>
+        <v>46229.63333333333</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>LARCENY THEFT FROM BUILDING</t>
+          <t>ASSAULT - AGGRAVATED</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H331" t="inlineStr"/>
       <c r="I331" t="inlineStr">
         <is>
-          <t>REED ST &amp; E LENOX ST
-ROXBURY, MA 02118
-UNITED STAT</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J331" t="n">
-        <v>42.33406097367816</v>
+        <v>42.33511903946613</v>
       </c>
       <c r="K331" t="n">
-        <v>-71.07756301316894</v>
+        <v>-71.07491709613726</v>
       </c>
       <c r="L331" t="n">
-        <v>1507.2</v>
+        <v>1407.3</v>
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Larceny theft from building on Jul 26, 2026, 1507 m from Copley Place (REED ST &amp; E LENOX ST
-ROXBURY, MA 02118
-UNITED STAT). Case #262064268 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - aggravated on Jul 26, 2026, 1407 m from Copley Place (HARRISON AVE). Case #262064339 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22435,15 +22539,15 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>262064394</t>
+          <t>262064236</t>
         </is>
       </c>
       <c r="E332" s="3" t="n">
-        <v>46229.82152777778</v>
+        <v>46229.37638888889</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>M/V ACCIDENT - OTHER</t>
+          <t>SICK ASSIST</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -22454,25 +22558,21 @@
       <c r="H332" t="inlineStr"/>
       <c r="I332" t="inlineStr">
         <is>
-          <t>HARRISON AVE &amp; PLYMPTON ST
-BOSTON, MA 02118
-UNITED</t>
+          <t>TREMONT ST</t>
         </is>
       </c>
       <c r="J332" t="n">
-        <v>42.33973998780085</v>
+        <v>42.34470135794417</v>
       </c>
       <c r="K332" t="n">
-        <v>-71.0691099454142</v>
+        <v>-71.0703760849388</v>
       </c>
       <c r="L332" t="n">
-        <v>1121.4</v>
+        <v>678.7</v>
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>M/v accident - other on Jul 26, 2026, 1121 m from Copley Place (HARRISON AVE &amp; PLYMPTON ST
-BOSTON, MA 02118
-UNITED). Case #262064394 (use for a records request — full narratives are not published in open data).</t>
+          <t>Sick assist on Jul 26, 2026, 679 m from Copley Place (TREMONT ST). Case #262064236 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22494,40 +22594,40 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>262064321</t>
+          <t>262064234</t>
         </is>
       </c>
       <c r="E333" s="3" t="n">
-        <v>46229.59166666667</v>
+        <v>46229.31944444445</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>M/V - LEAVING SCENE - PROPERTY DAMAGE</t>
+          <t>INVESTIGATE PERSON</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H333" t="inlineStr"/>
       <c r="I333" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>SAINT JAMES AVE</t>
         </is>
       </c>
       <c r="J333" t="n">
-        <v>42.33954198983015</v>
+        <v>42.34947585701249</v>
       </c>
       <c r="K333" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.07640149637847</v>
       </c>
       <c r="L333" t="n">
-        <v>1123.7</v>
+        <v>230.3</v>
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>M/v - leaving scene - property damage on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064321 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 26, 2026, 230 m from Copley Place (SAINT JAMES AVE). Case #262064234 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -23474,8 +23574,2427 @@
         </is>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>260730-1542</t>
+        </is>
+      </c>
+      <c r="E351" s="3" t="n">
+        <v>46233.78047453704</v>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>DRUGS/ALCOHOL VIOLATIONS</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>2700 BLOCK MONSARRAT AVE</t>
+        </is>
+      </c>
+      <c r="J351" t="n">
+        <v>21.271072368884</v>
+      </c>
+      <c r="K351" t="n">
+        <v>-157.822447621636</v>
+      </c>
+      <c r="L351" t="n">
+        <v>886.5</v>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>Drugs/alcohol violations on Jul 30, 2026, 887 m from International Market Place (2700 BLOCK MONSARRAT AVE). Case #260730-1542 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>260730-1522</t>
+        </is>
+      </c>
+      <c r="E352" s="3" t="n">
+        <v>46233.76790509259</v>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>2400 BLOCK TUSITALA ST</t>
+        </is>
+      </c>
+      <c r="J352" t="n">
+        <v>21.278259926502</v>
+      </c>
+      <c r="K352" t="n">
+        <v>-157.822935782893</v>
+      </c>
+      <c r="L352" t="n">
+        <v>391.8</v>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 30, 2026, 392 m from International Market Place (2400 BLOCK TUSITALA ST). Case #260730-1522 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>260730-1520</t>
+        </is>
+      </c>
+      <c r="E353" s="3" t="n">
+        <v>46233.76768518519</v>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>2200 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J353" t="n">
+        <v>21.280046658192</v>
+      </c>
+      <c r="K353" t="n">
+        <v>-157.829687791355</v>
+      </c>
+      <c r="L353" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 30, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260730-1520 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>260730-1019</t>
+        </is>
+      </c>
+      <c r="E354" s="3" t="n">
+        <v>46233.56648148148</v>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>DRUGS/ALCOHOL VIOLATIONS</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>300 BLOCK KALAIMOKU ST</t>
+        </is>
+      </c>
+      <c r="J354" t="n">
+        <v>21.282350597517</v>
+      </c>
+      <c r="K354" t="n">
+        <v>-157.830982023446</v>
+      </c>
+      <c r="L354" t="n">
+        <v>657</v>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>Drugs/alcohol violations on Jul 30, 2026, 657 m from International Market Place (300 BLOCK KALAIMOKU ST). Case #260730-1019 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>260730-0815</t>
+        </is>
+      </c>
+      <c r="E355" s="3" t="n">
+        <v>46233.48552083333</v>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>800 BLOCK OLOKELE AVE</t>
+        </is>
+      </c>
+      <c r="J355" t="n">
+        <v>21.284576073594</v>
+      </c>
+      <c r="K355" t="n">
+        <v>-157.816508656221</v>
+      </c>
+      <c r="L355" t="n">
+        <v>1285.7</v>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 30, 2026, 1286 m from International Market Place (800 BLOCK OLOKELE AVE). Case #260730-0815 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>260730-0686</t>
+        </is>
+      </c>
+      <c r="E356" s="3" t="n">
+        <v>46233.43194444444</v>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>MOTOR VEHICLE THEFT</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>2000 BLOCK FERN ST</t>
+        </is>
+      </c>
+      <c r="J356" t="n">
+        <v>21.291077860315</v>
+      </c>
+      <c r="K356" t="n">
+        <v>-157.831592308337</v>
+      </c>
+      <c r="L356" t="n">
+        <v>1541.1</v>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 30, 2026, 1541 m from International Market Place (2000 BLOCK FERN ST). Case #260730-0686 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>260730-0665</t>
+        </is>
+      </c>
+      <c r="E357" s="3" t="n">
+        <v>46233.4228125</v>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>MOTOR VEHICLE THEFT</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>700 BLOCK MCCULLY ST</t>
+        </is>
+      </c>
+      <c r="J357" t="n">
+        <v>21.289543723588</v>
+      </c>
+      <c r="K357" t="n">
+        <v>-157.832336665095</v>
+      </c>
+      <c r="L357" t="n">
+        <v>1411.2</v>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 30, 2026, 1411 m from International Market Place (700 BLOCK MCCULLY ST). Case #260730-0665 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>260730-0644</t>
+        </is>
+      </c>
+      <c r="E358" s="3" t="n">
+        <v>46233.41398148148</v>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>MOTOR VEHICLE THEFT</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>2600 BLOCK PUALANI WAY</t>
+        </is>
+      </c>
+      <c r="J358" t="n">
+        <v>21.274324486506</v>
+      </c>
+      <c r="K358" t="n">
+        <v>-157.819632666016</v>
+      </c>
+      <c r="L358" t="n">
+        <v>838.5</v>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 30, 2026, 838 m from International Market Place (2600 BLOCK PUALANI WAY). Case #260730-0644 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>260730-0478</t>
+        </is>
+      </c>
+      <c r="E359" s="3" t="n">
+        <v>46233.34556712963</v>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>MOTOR VEHICLE THEFT</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>700 BLOCK MCCULLY ST</t>
+        </is>
+      </c>
+      <c r="J359" t="n">
+        <v>21.289543723588</v>
+      </c>
+      <c r="K359" t="n">
+        <v>-157.832336665095</v>
+      </c>
+      <c r="L359" t="n">
+        <v>1411.2</v>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 30, 2026, 1411 m from International Market Place (700 BLOCK MCCULLY ST). Case #260730-0478 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>260730-0471</t>
+        </is>
+      </c>
+      <c r="E360" s="3" t="n">
+        <v>46233.34482638889</v>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>VANDALISM</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>300 BLOCK OHUA AVE</t>
+        </is>
+      </c>
+      <c r="J360" t="n">
+        <v>21.275639514153</v>
+      </c>
+      <c r="K360" t="n">
+        <v>-157.820878627839</v>
+      </c>
+      <c r="L360" t="n">
+        <v>657.8</v>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>Vandalism on Jul 30, 2026, 658 m from International Market Place (300 BLOCK OHUA AVE). Case #260730-0471 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>260730-0103</t>
+        </is>
+      </c>
+      <c r="E361" s="3" t="n">
+        <v>46233.07450231481</v>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>DISTURBING THE PEACE</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>2300 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J361" t="n">
+        <v>21.27805648814</v>
+      </c>
+      <c r="K361" t="n">
+        <v>-157.827664940544</v>
+      </c>
+      <c r="L361" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>Disturbing the peace on Jul 30, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260730-0103 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>260729-1797</t>
+        </is>
+      </c>
+      <c r="E362" s="3" t="n">
+        <v>46232.92472222223</v>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>BURGLARY</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KUHIO AVE</t>
+        </is>
+      </c>
+      <c r="J362" t="n">
+        <v>21.277342437556</v>
+      </c>
+      <c r="K362" t="n">
+        <v>-157.824038253672</v>
+      </c>
+      <c r="L362" t="n">
+        <v>285.6</v>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>Burglary on Jul 29, 2026, 286 m from International Market Place (2400 BLOCK KUHIO AVE). Case #260729-1797 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>260729-1765</t>
+        </is>
+      </c>
+      <c r="E363" s="3" t="n">
+        <v>46232.91365740741</v>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J363" t="n">
+        <v>21.276010351182</v>
+      </c>
+      <c r="K363" t="n">
+        <v>-157.825469259274</v>
+      </c>
+      <c r="L363" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 29, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260729-1765 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>260729-1729</t>
+        </is>
+      </c>
+      <c r="E364" s="3" t="n">
+        <v>46232.89675925926</v>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>MOTOR VEHICLE THEFT</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>400 BLOCK LAUNIU ST</t>
+        </is>
+      </c>
+      <c r="J364" t="n">
+        <v>21.283477123129</v>
+      </c>
+      <c r="K364" t="n">
+        <v>-157.828862979048</v>
+      </c>
+      <c r="L364" t="n">
+        <v>650</v>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 29, 2026, 650 m from International Market Place (400 BLOCK LAUNIU ST). Case #260729-1729 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>260729-1717</t>
+        </is>
+      </c>
+      <c r="E365" s="3" t="n">
+        <v>46232.8941087963</v>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>VANDALISM</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>2300 BLOCK KUHIO AVE</t>
+        </is>
+      </c>
+      <c r="J365" t="n">
+        <v>21.279653508688</v>
+      </c>
+      <c r="K365" t="n">
+        <v>-157.826261195987</v>
+      </c>
+      <c r="L365" t="n">
+        <v>190.9</v>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>Vandalism on Jul 29, 2026, 191 m from International Market Place (2300 BLOCK KUHIO AVE). Case #260729-1717 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>260729-1602</t>
+        </is>
+      </c>
+      <c r="E366" s="3" t="n">
+        <v>46232.84670138889</v>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>200 BLOCK BEACH WALK</t>
+        </is>
+      </c>
+      <c r="J366" t="n">
+        <v>21.278930465176</v>
+      </c>
+      <c r="K366" t="n">
+        <v>-157.832248174365</v>
+      </c>
+      <c r="L366" t="n">
+        <v>583.7</v>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 29, 2026, 584 m from International Market Place (200 BLOCK BEACH WALK). Case #260729-1602 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>260729-1588</t>
+        </is>
+      </c>
+      <c r="E367" s="3" t="n">
+        <v>46232.84131944444</v>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>2100 BLOCK KALIA RD</t>
+        </is>
+      </c>
+      <c r="J367" t="n">
+        <v>21.278855725117</v>
+      </c>
+      <c r="K367" t="n">
+        <v>-157.832156390487</v>
+      </c>
+      <c r="L367" t="n">
+        <v>572.9</v>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 29, 2026, 573 m from International Market Place (2100 BLOCK KALIA RD). Case #260729-1588 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>260729-1549</t>
+        </is>
+      </c>
+      <c r="E368" s="3" t="n">
+        <v>46232.82087962963</v>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>2200 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J368" t="n">
+        <v>21.280046658192</v>
+      </c>
+      <c r="K368" t="n">
+        <v>-157.829687791355</v>
+      </c>
+      <c r="L368" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 29, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260729-1549 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>260729-1507</t>
+        </is>
+      </c>
+      <c r="E369" s="3" t="n">
+        <v>46232.8008912037</v>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>VANDALISM</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>2200 BLOCK KAPIOLANI BLVD</t>
+        </is>
+      </c>
+      <c r="J369" t="n">
+        <v>21.288755371647</v>
+      </c>
+      <c r="K369" t="n">
+        <v>-157.829913575344</v>
+      </c>
+      <c r="L369" t="n">
+        <v>1242.6</v>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>Vandalism on Jul 29, 2026, 1243 m from International Market Place (2200 BLOCK KAPIOLANI BLVD). Case #260729-1507 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>260729-1309</t>
+        </is>
+      </c>
+      <c r="E370" s="3" t="n">
+        <v>46232.72003472222</v>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J370" t="n">
+        <v>21.276010351182</v>
+      </c>
+      <c r="K370" t="n">
+        <v>-157.825469259274</v>
+      </c>
+      <c r="L370" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 29, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260729-1309 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>260729-0943</t>
+        </is>
+      </c>
+      <c r="E371" s="3" t="n">
+        <v>46232.56469907407</v>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>ASSAULT</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>2600 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J371" t="n">
+        <v>21.271474893966</v>
+      </c>
+      <c r="K371" t="n">
+        <v>-157.82264961775</v>
+      </c>
+      <c r="L371" t="n">
+        <v>837.3</v>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>Assault on Jul 29, 2026, 837 m from International Market Place (2600 BLOCK KALAKAUA AVE). Case #260729-0943 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>260729-0896</t>
+        </is>
+      </c>
+      <c r="E372" s="3" t="n">
+        <v>46232.54393518518</v>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>FRAUD</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>2500 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J372" t="n">
+        <v>21.273862837838</v>
+      </c>
+      <c r="K372" t="n">
+        <v>-157.82387239543</v>
+      </c>
+      <c r="L372" t="n">
+        <v>544.6</v>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>Fraud on Jul 29, 2026, 545 m from International Market Place (2500 BLOCK KALAKAUA AVE). Case #260729-0896 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>260729-0762</t>
+        </is>
+      </c>
+      <c r="E373" s="3" t="n">
+        <v>46232.47961805556</v>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>BURGLARY</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KUHIO AVE</t>
+        </is>
+      </c>
+      <c r="J373" t="n">
+        <v>21.277342437556</v>
+      </c>
+      <c r="K373" t="n">
+        <v>-157.824038253672</v>
+      </c>
+      <c r="L373" t="n">
+        <v>285.6</v>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>Burglary on Jul 29, 2026, 286 m from International Market Place (2400 BLOCK KUHIO AVE). Case #260729-0762 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>260729-0758</t>
+        </is>
+      </c>
+      <c r="E374" s="3" t="n">
+        <v>46232.47920138889</v>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>FRAUD</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>300 BLOCK HOBRON LN</t>
+        </is>
+      </c>
+      <c r="J374" t="n">
+        <v>21.286120798599</v>
+      </c>
+      <c r="K374" t="n">
+        <v>-157.838143867296</v>
+      </c>
+      <c r="L374" t="n">
+        <v>1490.8</v>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>Fraud on Jul 29, 2026, 1491 m from International Market Place (300 BLOCK HOBRON LN). Case #260729-0758 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>260729-0737</t>
+        </is>
+      </c>
+      <c r="E375" s="3" t="n">
+        <v>46232.46952546296</v>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>ASSAULT</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>2500 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J375" t="n">
+        <v>21.273862837838</v>
+      </c>
+      <c r="K375" t="n">
+        <v>-157.82387239543</v>
+      </c>
+      <c r="L375" t="n">
+        <v>544.6</v>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>Assault on Jul 29, 2026, 545 m from International Market Place (2500 BLOCK KALAKAUA AVE). Case #260729-0737 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>260728-1209</t>
+        </is>
+      </c>
+      <c r="E376" s="3" t="n">
+        <v>46231.68509259259</v>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>DRUGS/ALCOHOL VIOLATIONS</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KUHIO AVE</t>
+        </is>
+      </c>
+      <c r="J376" t="n">
+        <v>21.277342437556</v>
+      </c>
+      <c r="K376" t="n">
+        <v>-157.824038253672</v>
+      </c>
+      <c r="L376" t="n">
+        <v>285.6</v>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>Drugs/alcohol violations on Jul 28, 2026, 286 m from International Market Place (2400 BLOCK KUHIO AVE). Case #260728-1209 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>260728-1191</t>
+        </is>
+      </c>
+      <c r="E377" s="3" t="n">
+        <v>46231.67745370371</v>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>2300 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J377" t="n">
+        <v>21.27805648814</v>
+      </c>
+      <c r="K377" t="n">
+        <v>-157.827664940544</v>
+      </c>
+      <c r="L377" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 28, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260728-1191 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>260728-1126</t>
+        </is>
+      </c>
+      <c r="E378" s="3" t="n">
+        <v>46231.65560185185</v>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>2300 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J378" t="n">
+        <v>21.27805648814</v>
+      </c>
+      <c r="K378" t="n">
+        <v>-157.827664940544</v>
+      </c>
+      <c r="L378" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 28, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260728-1126 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>260727-1381</t>
+        </is>
+      </c>
+      <c r="E379" s="3" t="n">
+        <v>46230.75506944444</v>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>2200 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J379" t="n">
+        <v>21.280046658192</v>
+      </c>
+      <c r="K379" t="n">
+        <v>-157.829687791355</v>
+      </c>
+      <c r="L379" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 27, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260727-1381 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>260727-1302</t>
+        </is>
+      </c>
+      <c r="E380" s="3" t="n">
+        <v>46230.71513888889</v>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>300 BLOCK KALAIMOKU ST</t>
+        </is>
+      </c>
+      <c r="J380" t="n">
+        <v>21.282350597517</v>
+      </c>
+      <c r="K380" t="n">
+        <v>-157.830982023446</v>
+      </c>
+      <c r="L380" t="n">
+        <v>657</v>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 27, 2026, 657 m from International Market Place (300 BLOCK KALAIMOKU ST). Case #260727-1302 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>260727-0958</t>
+        </is>
+      </c>
+      <c r="E381" s="3" t="n">
+        <v>46230.57681712963</v>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>2200 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J381" t="n">
+        <v>21.280046658192</v>
+      </c>
+      <c r="K381" t="n">
+        <v>-157.829687791355</v>
+      </c>
+      <c r="L381" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 27, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260727-0958 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>260727-0160</t>
+        </is>
+      </c>
+      <c r="E382" s="3" t="n">
+        <v>46230.1952662037</v>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>VANDALISM</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J382" t="n">
+        <v>21.276010351182</v>
+      </c>
+      <c r="K382" t="n">
+        <v>-157.825469259274</v>
+      </c>
+      <c r="L382" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>Vandalism on Jul 27, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260727-0160 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>260726-0935</t>
+        </is>
+      </c>
+      <c r="E383" s="3" t="n">
+        <v>46229.61716435185</v>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J383" t="n">
+        <v>21.276010351182</v>
+      </c>
+      <c r="K383" t="n">
+        <v>-157.825469259274</v>
+      </c>
+      <c r="L383" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 26, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260726-0935 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>260726-0313</t>
+        </is>
+      </c>
+      <c r="E384" s="3" t="n">
+        <v>46229.25769675926</v>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>2500 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J384" t="n">
+        <v>21.273862837838</v>
+      </c>
+      <c r="K384" t="n">
+        <v>-157.82387239543</v>
+      </c>
+      <c r="L384" t="n">
+        <v>544.6</v>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 26, 2026, 545 m from International Market Place (2500 BLOCK KALAKAUA AVE). Case #260726-0313 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>260726-0222</t>
+        </is>
+      </c>
+      <c r="E385" s="3" t="n">
+        <v>46229.15130787037</v>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>ASSAULT</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>2200 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J385" t="n">
+        <v>21.280046658192</v>
+      </c>
+      <c r="K385" t="n">
+        <v>-157.829687791355</v>
+      </c>
+      <c r="L385" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>Assault on Jul 26, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260726-0222 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>260725-1627</t>
+        </is>
+      </c>
+      <c r="E386" s="3" t="n">
+        <v>46228.93998842593</v>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>ASSAULT</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>200 BLOCK BEACH WALK</t>
+        </is>
+      </c>
+      <c r="J386" t="n">
+        <v>21.278930465176</v>
+      </c>
+      <c r="K386" t="n">
+        <v>-157.832248174365</v>
+      </c>
+      <c r="L386" t="n">
+        <v>583.7</v>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>Assault on Jul 25, 2026, 584 m from International Market Place (200 BLOCK BEACH WALK). Case #260725-1627 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>260725-1228</t>
+        </is>
+      </c>
+      <c r="E387" s="3" t="n">
+        <v>46228.75162037037</v>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>2200 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J387" t="n">
+        <v>21.280046658192</v>
+      </c>
+      <c r="K387" t="n">
+        <v>-157.829687791355</v>
+      </c>
+      <c r="L387" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 25, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260725-1228 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>260725-1158</t>
+        </is>
+      </c>
+      <c r="E388" s="3" t="n">
+        <v>46228.70266203704</v>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>ASSAULT</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>2300 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J388" t="n">
+        <v>21.27805648814</v>
+      </c>
+      <c r="K388" t="n">
+        <v>-157.827664940544</v>
+      </c>
+      <c r="L388" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>Assault on Jul 25, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260725-1158 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>260725-0503</t>
+        </is>
+      </c>
+      <c r="E389" s="3" t="n">
+        <v>46228.35734953704</v>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>MOTOR VEHICLE THEFT</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J389" t="n">
+        <v>21.276010351182</v>
+      </c>
+      <c r="K389" t="n">
+        <v>-157.825469259274</v>
+      </c>
+      <c r="L389" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 25, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260725-0503 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>260725-0383</t>
+        </is>
+      </c>
+      <c r="E390" s="3" t="n">
+        <v>46228.28726851852</v>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>DISTURBING THE PEACE</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>2300 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J390" t="n">
+        <v>21.27805648814</v>
+      </c>
+      <c r="K390" t="n">
+        <v>-157.827664940544</v>
+      </c>
+      <c r="L390" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>Disturbing the peace on Jul 25, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260725-0383 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>260725-0324</t>
+        </is>
+      </c>
+      <c r="E391" s="3" t="n">
+        <v>46228.26383101852</v>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J391" t="n">
+        <v>21.276010351182</v>
+      </c>
+      <c r="K391" t="n">
+        <v>-157.825469259274</v>
+      </c>
+      <c r="L391" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 25, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260725-0324 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M350"/>
+  <autoFilter ref="A1:M391"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23486,7 +26005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -23513,7 +26032,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 05:06:16.167337+00:00</t>
+          <t>2026-08-01 05:08:21.498984+00:00</t>
         </is>
       </c>
     </row>
@@ -23545,7 +26064,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 05:06:16.167337+00:00</t>
+          <t>2026-07-25 05:08:21.498984+00:00</t>
         </is>
       </c>
     </row>
@@ -23556,7 +26075,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>349</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7">
@@ -23566,7 +26085,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -23869,8 +26388,32 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>source:INTLMARKET/Honolulu PD Crime Incidents</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>OK fetched=479 truncated=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>source:WAIKELE/Honolulu PD Crime Incidents</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>OK fetched=479 truncated=False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B32"/>
+  <autoFilter ref="A1:B34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/2026-08-01/blotter_report.xlsx
+++ b/reports/2026-08-01/blotter_report.xlsx
@@ -13,10 +13,10 @@
     <sheet name="Run Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$391</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$412</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1015,17 +1015,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>FASHIONVAL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Fashion Valley</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2126 Abbott Martin Road, Nashville, TN 37215</t>
+          <t>7007 Friars Road San Diego CA 92108</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1051,23 +1051,23 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>GREENHILLS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>The Mall at Green Hills</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5085 Westheimer Houston TX 77056</t>
+          <t>2126 Abbott Martin Road, Nashville, TN 37215</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1076,26 +1076,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>57</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>9</v>
-      </c>
-      <c r="J14" t="n">
-        <v>163.5</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>46233</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="b">
         <v>0</v>
       </c>
@@ -1103,17 +1099,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INTLMARKET</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>International Market Place</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2330 Kalakaua Avenue, Honolulu HI 96815</t>
+          <t>5085 Westheimer Houston TX 77056</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1122,25 +1118,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J15" t="n">
-        <v>99.7</v>
+        <v>163.5</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>46233.78047453704</v>
+        <v>46233</v>
       </c>
       <c r="L15" t="b">
         <v>0</v>
@@ -1149,17 +1145,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>INTLPLAZA</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>International Plaza</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
+          <t>2330 Kalakaua Avenue, Honolulu HI 96815</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1168,25 +1164,25 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
+        <v>62</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>1534.5</v>
+        <v>99.7</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>46232.16666666666</v>
+        <v>46233.78047453704</v>
       </c>
       <c r="L16" t="b">
         <v>0</v>
@@ -1195,32 +1191,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LENOX</t>
+          <t>INTLPLAZA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lenox Square</t>
+          <t>International Plaza</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1228,8 +1224,12 @@
       <c r="I17" t="n">
         <v>0</v>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>1534.5</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>46232.16666666666</v>
+      </c>
       <c r="L17" t="b">
         <v>0</v>
       </c>
@@ -1237,22 +1237,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MALLATMILLENIA</t>
+          <t>LENOX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Mall at Millenia</t>
+          <t>Lenox Square</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4200 Conroy Road, Orlando, FL 32839</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1279,17 +1279,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NORFOLKPO</t>
+          <t>MALLATMILLENIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Norfolk Premium Outlets</t>
+          <t>The Mall at Millenia</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1600 Premium Outlets Boulevard Norfolk VA 23502</t>
+          <t>4200 Conroy Road, Orlando, FL 32839</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1310,14 +1310,10 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1118.9</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>46233</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="b">
         <v>0</v>
       </c>
@@ -1325,17 +1321,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>NORFOLKPO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Norfolk Premium Outlets</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>401 Northeast Northgate Way Seattle WA 98125</t>
+          <t>1600 Premium Outlets Boulevard Norfolk VA 23502</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1344,25 +1340,25 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>14</v>
-      </c>
-      <c r="F20" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
       <c r="G20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>145.2</v>
+        <v>1118.9</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>46233.28194444445</v>
+        <v>46233</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
@@ -1371,17 +1367,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>433 Opry Mills Drive Nashville TN 37214</t>
+          <t>401 Northeast Northgate Way Seattle WA 98125</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1390,22 +1386,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>46233.28194444445</v>
+      </c>
       <c r="L21" t="b">
         <v>0</v>
       </c>
@@ -1413,17 +1413,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4400 Sharon Road Charlotte NC 28211</t>
+          <t>433 Opry Mills Drive Nashville TN 37214</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1432,26 +1432,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>7</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>178.9</v>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>46232.16666666666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="b">
         <v>0</v>
       </c>
@@ -1459,17 +1455,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4502 South Steele Street Tacoma WA 98409</t>
+          <t>4400 Sharon Road Charlotte NC 28211</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1478,25 +1474,25 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>471.3</v>
+        <v>178.9</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>46233</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
@@ -1505,41 +1501,45 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>THEDOMAIN</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Domain</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>11410 Century Oaks Terrace Austin TX 78758</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>4502 South Steele Street Tacoma WA 98409</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>471.3</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>46233</v>
+      </c>
       <c r="L24" t="b">
         <v>0</v>
       </c>
@@ -1547,45 +1547,41 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>THEDOMAIN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>The Domain</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>7700 East Kellogg Wichita KS 67207</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>11410 Century Oaks Terrace Austin TX 78758</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>33</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
-      </c>
-      <c r="J25" t="n">
-        <v>288.9</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>46233.7625</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="b">
         <v>0</v>
       </c>
@@ -1593,17 +1589,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>UNIVPARKVILLAGE</t>
+          <t>TOWNEEAST</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>University Park Village</t>
+          <t>Towne East Square</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1612 South University Drive Fort Worth TX 76107</t>
+          <t>7700 East Kellogg Wichita KS 67207</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1612,22 +1608,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="J26" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>46233.7625</v>
+      </c>
       <c r="L26" t="b">
         <v>0</v>
       </c>
@@ -1635,17 +1635,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WAIKELE</t>
+          <t>UNIVPARKVILLAGE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Waikele Premium Outlets</t>
+          <t>University Park Village</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>94-790 Lumiaina Street Waipahu HI 96797</t>
+          <t>1612 South University Drive Fort Worth TX 76107</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1674,8 +1674,50 @@
         <v>0</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>WAIKELE</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Waikele Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>94-790 Lumiaina Street Waipahu HI 96797</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L27"/>
+  <autoFilter ref="A1:L28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1962,11 +2004,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>260726-0222</t>
+          <t>260728-1185</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46229.15130787037</v>
+        <v>46231.67606481481</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1985,51 +2027,51 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2200 BLOCK KALAKAUA AVE</t>
+          <t>2200 BLOCK KUHIO AVE</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>21.280046658192</v>
+        <v>21.280829509204</v>
       </c>
       <c r="K5" t="n">
-        <v>-157.829687791355</v>
+        <v>-157.827642638381</v>
       </c>
       <c r="L5" t="n">
-        <v>384.6</v>
+        <v>330.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Assault on Jul 26, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260726-0222 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 28, 2026, 331 m from International Market Place (2200 BLOCK KUHIO AVE). Case #260728-1185 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
+          <t>INTLMARKET:vg88-5rn5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>094513626</t>
+          <t>260726-0222</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46229</v>
+        <v>46229.15130787037</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2039,26 +2081,26 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>13A</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5100-5199 HIDALGO ST</t>
+          <t>2200 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>29.73535149549964</v>
+        <v>21.280046658192</v>
       </c>
       <c r="K6" t="n">
-        <v>-95.46474014804627</v>
+        <v>-157.829687791355</v>
       </c>
       <c r="L6" t="n">
-        <v>447.9</v>
+        <v>384.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 26, 2026, 448 m from Houston Galleria (5100-5199 HIDALGO ST). Case #094513626 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 26, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260726-0222 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2080,11 +2122,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>260729-0737</t>
+          <t>260727-0609</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46232.46952546296</v>
+        <v>46230.42018518518</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2103,51 +2145,51 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2500 BLOCK KALAKAUA AVE</t>
+          <t>300 BLOCK LEWERS ST</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>21.273862837838</v>
+        <v>21.280145465259</v>
       </c>
       <c r="K7" t="n">
-        <v>-157.82387239543</v>
+        <v>-157.829777674689</v>
       </c>
       <c r="L7" t="n">
-        <v>544.6</v>
+        <v>398.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Assault on Jul 29, 2026, 545 m from International Market Place (2500 BLOCK KALAKAUA AVE). Case #260729-0737 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 27, 2026, 399 m from International Market Place (300 BLOCK LEWERS ST). Case #260727-0609 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INTLMARKET</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>International Market Place</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>INTLMARKET:vg88-5rn5</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>260725-1627</t>
+          <t>094513626</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46228.93998842593</v>
+        <v>46229</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASSAULT</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2157,56 +2199,56 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>13A</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>200 BLOCK BEACH WALK</t>
+          <t>5100-5199 HIDALGO ST</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>21.278930465176</v>
+        <v>29.73535149549964</v>
       </c>
       <c r="K8" t="n">
-        <v>-157.832248174365</v>
+        <v>-95.46474014804627</v>
       </c>
       <c r="L8" t="n">
-        <v>583.7</v>
+        <v>447.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Assault on Jul 25, 2026, 584 m from International Market Place (200 BLOCK BEACH WALK). Case #260725-1627 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 26, 2026, 448 m from Houston Galleria (5100-5199 HIDALGO ST). Case #094513626 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Property</t>
+          <t>INTLMARKET:vg88-5rn5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>095242126</t>
+          <t>260729-0737</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46230</v>
+        <v>46232.46952546296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2216,56 +2258,56 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2700-2799 LOOP N</t>
+          <t>2500 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>29.7388306267185</v>
+        <v>21.273862837838</v>
       </c>
       <c r="K9" t="n">
-        <v>-95.45805588032616</v>
+        <v>-157.82387239543</v>
       </c>
       <c r="L9" t="n">
-        <v>588.1</v>
+        <v>544.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Robbery on Jul 27, 2026, 588 m from Houston Galleria (2700-2799 LOOP N). Case #095242126 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 29, 2026, 545 m from International Market Place (2500 BLOCK KALAKAUA AVE). Case #260729-0737 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+          <t>INTLMARKET:vg88-5rn5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CFS26-161839</t>
+          <t>260725-1627</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46231.00275462963</v>
+        <v>46228.93998842593</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Assault P3</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2275,56 +2317,56 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>W 47TH ST &amp; S WESTPORT AVE</t>
+          <t>200 BLOCK BEACH WALK</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>43.50940131405472</v>
+        <v>21.278930465176</v>
       </c>
       <c r="K10" t="n">
-        <v>-96.76746570282992</v>
+        <v>-157.832248174365</v>
       </c>
       <c r="L10" t="n">
-        <v>678.4</v>
+        <v>583.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Assault p3 on Jul 28, 2026, 678 m from Empire Mall (W 47TH ST &amp; S WESTPORT AVE). Case #CFS26-161839 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 25, 2026, 584 m from International Market Place (200 BLOCK BEACH WALK). Case #260725-1627 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Property</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DP2026411044131300</t>
+          <t>095242126</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46229.1125</v>
+        <v>46230</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>assault-simple</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2334,56 +2376,56 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>other-crimes-against-persons</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3200 BLOCK E CHERRY CREEK S DR</t>
+          <t>2700-2799 LOOP N</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>39.71130989687384</v>
+        <v>29.7388306267185</v>
       </c>
       <c r="K11" t="n">
-        <v>-104.9490029653731</v>
+        <v>-95.45805588032616</v>
       </c>
       <c r="L11" t="n">
-        <v>696.3</v>
+        <v>588.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 27, 2026, 588 m from Houston Galleria (2700-2799 LOOP N). Case #095242126 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COPLEY</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>262064756</t>
+          <t>CFS26-161839</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46230.80347222222</v>
+        <v>46231.00275462963</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASSAULT - SIMPLE</t>
+          <t>Assault P3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2391,54 +2433,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Assault</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MASSACHUSETTS AVE</t>
+          <t>W 47TH ST &amp; S WESTPORT AVE</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>42.34439568415441</v>
+        <v>43.50940131405472</v>
       </c>
       <c r="K12" t="n">
-        <v>-71.08632016344815</v>
+        <v>-96.76746570282992</v>
       </c>
       <c r="L12" t="n">
-        <v>798.7</v>
+        <v>678.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Assault - simple on Jul 27, 2026, 799 m from Copley Place (MASSACHUSETTS AVE). Case #262064756 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault p3 on Jul 28, 2026, 678 m from Empire Mall (W 47TH ST &amp; S WESTPORT AVE). Case #CFS26-161839 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CFS26-161603</t>
+          <t>DP2026411044131300</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46230.83325231481</v>
+        <v>46229.1125</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>assault-simple</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2448,56 +2494,56 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>other-crimes-against-persons</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>S WESTPORT AVE &amp; W 41ST ST</t>
+          <t>3200 BLOCK E CHERRY CREEK S DR</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>43.51485103457241</v>
+        <v>39.71130989687384</v>
       </c>
       <c r="K13" t="n">
-        <v>-96.76794119445807</v>
+        <v>-104.9490029653731</v>
       </c>
       <c r="L13" t="n">
-        <v>808.9</v>
+        <v>696.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Assault on Jul 27, 2026, 809 m from Empire Mall (S WESTPORT AVE &amp; W 41ST ST). Case #CFS26-161603 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>INTLMARKET</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>International Market Place</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>INTLMARKET:vg88-5rn5</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>260729-0943</t>
+          <t>262064756</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46232.56469907407</v>
+        <v>46230.80347222222</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASSAULT</t>
+          <t>ASSAULT - SIMPLE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2505,58 +2551,54 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2600 BLOCK KALAKAUA AVE</t>
+          <t>MASSACHUSETTS AVE</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>21.271474893966</v>
+        <v>42.34439568415441</v>
       </c>
       <c r="K14" t="n">
-        <v>-157.82264961775</v>
+        <v>-71.08632016344815</v>
       </c>
       <c r="L14" t="n">
-        <v>837.3</v>
+        <v>798.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Assault on Jul 29, 2026, 837 m from International Market Place (2600 BLOCK KALAKAUA AVE). Case #260729-0943 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - simple on Jul 27, 2026, 799 m from Copley Place (MASSACHUSETTS AVE). Case #262064756 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20260729-1600-11</t>
+          <t>CFS26-161603</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46232.16666666666</v>
+        <v>46230.83325231481</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Simple Assault</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2566,56 +2608,56 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>13B</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4700 PIEDMONT ROW DR</t>
+          <t>S WESTPORT AVE &amp; W 41ST ST</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>35.15196312662653</v>
+        <v>43.51485103457241</v>
       </c>
       <c r="K15" t="n">
-        <v>-80.83980651357408</v>
+        <v>-96.76794119445807</v>
       </c>
       <c r="L15" t="n">
-        <v>850.6</v>
+        <v>808.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 29, 2026, 851 m from Southpark (4700 PIEDMONT ROW DR). Status: Open. Case #20260729-1600-11 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 27, 2026, 809 m from Empire Mall (S WESTPORT AVE &amp; W 41ST ST). Case #CFS26-161603 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>INTLMARKET:vg88-5rn5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2620701835</t>
+          <t>260729-0943</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46229</v>
+        <v>46232.56469907407</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2625,56 +2667,56 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4000 S LAWRENCE ST</t>
+          <t>2600 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>47.219421</v>
+        <v>21.271474893966</v>
       </c>
       <c r="K16" t="n">
-        <v>-122.478428</v>
+        <v>-157.82264961775</v>
       </c>
       <c r="L16" t="n">
-        <v>853.4</v>
+        <v>837.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 26, 2026, 853 m from Tacoma Mall (4000 S LAWRENCE ST). Case #2620701835 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 29, 2026, 837 m from International Market Place (2600 BLOCK KALAKAUA AVE). Case #260729-0943 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>COPLEY</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>262064416</t>
+          <t>20260729-1600-11</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46229.87569444445</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ASSAULT - AGGRAVATED</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2682,54 +2724,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>13B</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>HUNTINGTON AVE</t>
+          <t>4700 PIEDMONT ROW DR</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>42.34221543503831</v>
+        <v>35.15196312662653</v>
       </c>
       <c r="K17" t="n">
-        <v>-71.08577074656198</v>
+        <v>-80.83980651357408</v>
       </c>
       <c r="L17" t="n">
-        <v>898.8</v>
+        <v>850.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Assault - aggravated on Jul 26, 2026, 899 m from Copley Place (HUNTINGTON AVE). Case #262064416 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 29, 2026, 851 m from Southpark (4700 PIEDMONT ROW DR). Status: Open. Case #20260729-1600-11 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>71878728447</t>
+          <t>2620701835</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46230.4375</v>
+        <v>46229</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2739,56 +2785,56 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>Assault Offenses</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>16XX BLOCK OF N 105TH ST</t>
+          <t>4000 S LAWRENCE ST</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>47.70504225</v>
+        <v>47.219421</v>
       </c>
       <c r="K18" t="n">
-        <v>-122.338094779232</v>
+        <v>-122.478428</v>
       </c>
       <c r="L18" t="n">
-        <v>938.8</v>
+        <v>853.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 26, 2026, 853 m from Tacoma Mall (4000 S LAWRENCE ST). Case #2620701835 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2621000152</t>
+          <t>262064416</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46232</v>
+        <v>46229.87569444445</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>ASSAULT - AGGRAVATED</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2796,58 +2842,54 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Assault Offenses</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3500 S 45TH ST</t>
+          <t>HUNTINGTON AVE</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>47.216421</v>
+        <v>42.34221543503831</v>
       </c>
       <c r="K19" t="n">
-        <v>-122.482428</v>
+        <v>-71.08577074656198</v>
       </c>
       <c r="L19" t="n">
-        <v>1074.3</v>
+        <v>898.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 29, 2026, 1074 m from Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - aggravated on Jul 26, 2026, 899 m from Copley Place (HUNTINGTON AVE). Case #262064416 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>COPLEY</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>262064432</t>
+          <t>71878728447</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46229.91666666666</v>
+        <v>46230.4375</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ROBBERY</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2855,54 +2897,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>VIOLENT CRIME</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>16XX BLOCK OF N 105TH ST</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>42.33954198983015</v>
+        <v>47.70504225</v>
       </c>
       <c r="K20" t="n">
-        <v>-71.06940876967543</v>
+        <v>-122.338094779232</v>
       </c>
       <c r="L20" t="n">
-        <v>1123.7</v>
+        <v>938.8</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Robbery on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064432 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>COPLEY</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>262064298</t>
+          <t>2621000152</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46229.08611111111</v>
+        <v>46232</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FIREARM/WEAPON - LOST</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2910,54 +2956,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Assault Offenses</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>3500 S 45TH ST</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>42.33954198983015</v>
+        <v>47.216421</v>
       </c>
       <c r="K21" t="n">
-        <v>-71.06940876967543</v>
+        <v>-122.482428</v>
       </c>
       <c r="L21" t="n">
-        <v>1123.7</v>
+        <v>1074.3</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Firearm/weapon - lost on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064298 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 29, 2026, 1074 m from Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>INTLMARKET:vg88-5rn5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>71894237115</t>
+          <t>260727-1127</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46231.20833333334</v>
+        <v>46230.64813657408</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2967,56 +3017,56 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>1900 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>47.70668788</v>
+        <v>21.28609383604</v>
       </c>
       <c r="K22" t="n">
-        <v>-122.311189997702</v>
+        <v>-157.833074890083</v>
       </c>
       <c r="L22" t="n">
-        <v>1145.7</v>
+        <v>1117.1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 27, 2026, 1117 m from International Market Place (1900 BLOCK KALAKAUA AVE). Case #260727-1127 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>71889871382</t>
+          <t>262064432</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46231.00625</v>
+        <v>46229.91666666666</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Simple Assault</t>
+          <t>ROBBERY</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3024,58 +3074,54 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>ALL OTHER</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>47.70668788</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K23" t="n">
-        <v>-122.311189997702</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L23" t="n">
-        <v>1145.7</v>
+        <v>1123.7</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064432 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TOWNEEAST:Wichita PD Crimes (90d)</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>26C142249</t>
+          <t>262064298</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46230.75</v>
+        <v>46229.08611111111</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BATTERY ABW</t>
+          <t>FIREARM/WEAPON - LOST</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3083,54 +3129,50 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>SIM_ASSAULT</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>700 BLOCK OF S MISSION RD</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>37.6756469679485</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K24" t="n">
-        <v>-97.25850032865422</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L24" t="n">
-        <v>1251.5</v>
+        <v>1123.7</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Battery abw on Jul 27, 2026, 1251 m from Towne East Square (700 BLOCK OF S MISSION RD). Case #26C142249 (use for a records request — full narratives are not published in open data).</t>
+          <t>Firearm/weapon - lost on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064298 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CFS26-164521</t>
+          <t>71894237115</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46234.03421296296</v>
+        <v>46231.20833333334</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3144,56 +3186,56 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>VIOLENT CRIME</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>S MARION RD &amp; W 41ST ST</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>43.51481738299845</v>
+        <v>47.70668788</v>
       </c>
       <c r="K25" t="n">
-        <v>-96.79096028032072</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L25" t="n">
-        <v>1322.4</v>
+        <v>1145.7</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 31, 2026, 1322 m from Empire Mall (S MARION RD &amp; W 41ST ST). Case #CFS26-164521 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
+          <t>NORTHGATE:tazs-3rd5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>096140526</t>
+          <t>71889871382</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46232</v>
+        <v>46231.00625</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3203,26 +3245,26 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>13A</t>
+          <t>ALL OTHER</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1900-1999 POST OAK PARK DR</t>
+          <t>15XX BLOCK OF NE 107TH ST</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>29.74712522681273</v>
+        <v>47.70668788</v>
       </c>
       <c r="K26" t="n">
-        <v>-95.45374747370188</v>
+        <v>-122.311189997702</v>
       </c>
       <c r="L26" t="n">
-        <v>1323.4</v>
+        <v>1145.7</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 29, 2026, 1323 m from Houston Galleria (1900-1999 POST OAK PARK DR). Case #096140526 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M391"/>
+  <dimension ref="A1:M412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -25185,20 +25227,20 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>260728-1126</t>
+          <t>260728-1185</t>
         </is>
       </c>
       <c r="E378" s="3" t="n">
-        <v>46231.65560185185</v>
+        <v>46231.67606481481</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>THEFT/LARCENY</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -25208,21 +25250,21 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>2300 BLOCK KALAKAUA AVE</t>
+          <t>2200 BLOCK KUHIO AVE</t>
         </is>
       </c>
       <c r="J378" t="n">
-        <v>21.27805648814</v>
+        <v>21.280829509204</v>
       </c>
       <c r="K378" t="n">
-        <v>-157.827664940544</v>
+        <v>-157.827642638381</v>
       </c>
       <c r="L378" t="n">
-        <v>99.7</v>
+        <v>330.6</v>
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Theft/larceny on Jul 28, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260728-1126 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 28, 2026, 331 m from International Market Place (2200 BLOCK KUHIO AVE). Case #260728-1185 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25244,11 +25286,11 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>260727-1381</t>
+          <t>260728-1126</t>
         </is>
       </c>
       <c r="E379" s="3" t="n">
-        <v>46230.75506944444</v>
+        <v>46231.65560185185</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -25267,21 +25309,21 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>2200 BLOCK KALAKAUA AVE</t>
+          <t>2300 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J379" t="n">
-        <v>21.280046658192</v>
+        <v>21.27805648814</v>
       </c>
       <c r="K379" t="n">
-        <v>-157.829687791355</v>
+        <v>-157.827664940544</v>
       </c>
       <c r="L379" t="n">
-        <v>384.6</v>
+        <v>99.7</v>
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Theft/larceny on Jul 27, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260727-1381 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft/larceny on Jul 28, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260728-1126 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25303,15 +25345,15 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>260727-1302</t>
+          <t>260728-0991</t>
         </is>
       </c>
       <c r="E380" s="3" t="n">
-        <v>46230.71513888889</v>
+        <v>46231.59506944445</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>THEFT/LARCENY</t>
+          <t>BURGLARY</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
@@ -25326,21 +25368,21 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>300 BLOCK KALAIMOKU ST</t>
+          <t>2400 BLOCK DATE ST</t>
         </is>
       </c>
       <c r="J380" t="n">
-        <v>21.282350597517</v>
+        <v>21.289130371817</v>
       </c>
       <c r="K380" t="n">
-        <v>-157.830982023446</v>
+        <v>-157.825374685262</v>
       </c>
       <c r="L380" t="n">
-        <v>657</v>
+        <v>1246.7</v>
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Theft/larceny on Jul 27, 2026, 657 m from International Market Place (300 BLOCK KALAIMOKU ST). Case #260727-1302 (use for a records request — full narratives are not published in open data).</t>
+          <t>Burglary on Jul 28, 2026, 1247 m from International Market Place (2400 BLOCK DATE ST). Case #260728-0991 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25362,15 +25404,15 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>260727-0958</t>
+          <t>260728-0332</t>
         </is>
       </c>
       <c r="E381" s="3" t="n">
-        <v>46230.57681712963</v>
+        <v>46231.30905092593</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>THEFT/LARCENY</t>
+          <t>MOTOR VEHICLE THEFT</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
@@ -25385,21 +25427,21 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>2200 BLOCK KALAKAUA AVE</t>
+          <t>2500 BLOCK DATE ST</t>
         </is>
       </c>
       <c r="J381" t="n">
-        <v>21.280046658192</v>
+        <v>21.28755766535</v>
       </c>
       <c r="K381" t="n">
-        <v>-157.829687791355</v>
+        <v>-157.82360180606</v>
       </c>
       <c r="L381" t="n">
-        <v>384.6</v>
+        <v>1111.7</v>
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Theft/larceny on Jul 27, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260727-0958 (use for a records request — full narratives are not published in open data).</t>
+          <t>Motor vehicle theft on Jul 28, 2026, 1112 m from International Market Place (2500 BLOCK DATE ST). Case #260728-0332 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25421,15 +25463,15 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>260727-0160</t>
+          <t>260728-0204</t>
         </is>
       </c>
       <c r="E382" s="3" t="n">
-        <v>46230.1952662037</v>
+        <v>46231.24877314815</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>VANDALISM</t>
+          <t>MOTOR VEHICLE THEFT</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
@@ -25444,21 +25486,21 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>2400 BLOCK KALAKAUA AVE</t>
+          <t>400 BLOCK NAHUA ST</t>
         </is>
       </c>
       <c r="J382" t="n">
-        <v>21.276010351182</v>
+        <v>21.279119553163</v>
       </c>
       <c r="K382" t="n">
-        <v>-157.825469259274</v>
+        <v>-157.825676162889</v>
       </c>
       <c r="L382" t="n">
-        <v>254.5</v>
+        <v>165</v>
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Vandalism on Jul 27, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260727-0160 (use for a records request — full narratives are not published in open data).</t>
+          <t>Motor vehicle theft on Jul 28, 2026, 165 m from International Market Place (400 BLOCK NAHUA ST). Case #260728-0204 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25480,11 +25522,11 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>260726-0935</t>
+          <t>260728-0136</t>
         </is>
       </c>
       <c r="E383" s="3" t="n">
-        <v>46229.61716435185</v>
+        <v>46231.18006944445</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -25503,21 +25545,21 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>2400 BLOCK KALAKAUA AVE</t>
+          <t>3200 BLOCK HOOLULU ST</t>
         </is>
       </c>
       <c r="J383" t="n">
-        <v>21.276010351182</v>
+        <v>21.278479806365</v>
       </c>
       <c r="K383" t="n">
-        <v>-157.825469259274</v>
+        <v>-157.813873146982</v>
       </c>
       <c r="L383" t="n">
-        <v>254.5</v>
+        <v>1330.8</v>
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Theft/larceny on Jul 26, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260726-0935 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft/larceny on Jul 28, 2026, 1331 m from International Market Place (3200 BLOCK HOOLULU ST). Case #260728-0136 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25539,11 +25581,11 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>260726-0313</t>
+          <t>260728-0078</t>
         </is>
       </c>
       <c r="E384" s="3" t="n">
-        <v>46229.25769675926</v>
+        <v>46231.08966435185</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -25562,21 +25604,21 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>2500 BLOCK KALAKAUA AVE</t>
+          <t>1900 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J384" t="n">
-        <v>21.273862837838</v>
+        <v>21.28609383604</v>
       </c>
       <c r="K384" t="n">
-        <v>-157.82387239543</v>
+        <v>-157.833074890083</v>
       </c>
       <c r="L384" t="n">
-        <v>544.6</v>
+        <v>1117.1</v>
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Theft/larceny on Jul 26, 2026, 545 m from International Market Place (2500 BLOCK KALAKAUA AVE). Case #260726-0313 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft/larceny on Jul 28, 2026, 1117 m from International Market Place (1900 BLOCK KALAKAUA AVE). Case #260728-0078 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25598,20 +25640,20 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>260726-0222</t>
+          <t>260727-1787</t>
         </is>
       </c>
       <c r="E385" s="3" t="n">
-        <v>46229.15130787037</v>
+        <v>46230.9887037037</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>ASSAULT</t>
+          <t>THEFT/LARCENY</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -25621,21 +25663,21 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>2200 BLOCK KALAKAUA AVE</t>
+          <t>200 BLOCK LEWERS ST</t>
         </is>
       </c>
       <c r="J385" t="n">
-        <v>21.280046658192</v>
+        <v>21.278993587418</v>
       </c>
       <c r="K385" t="n">
-        <v>-157.829687791355</v>
+        <v>-157.83122782776</v>
       </c>
       <c r="L385" t="n">
-        <v>384.6</v>
+        <v>481.7</v>
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Assault on Jul 26, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260726-0222 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft/larceny on Jul 27, 2026, 482 m from International Market Place (200 BLOCK LEWERS ST). Case #260727-1787 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25657,20 +25699,20 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>260725-1627</t>
+          <t>260727-1586</t>
         </is>
       </c>
       <c r="E386" s="3" t="n">
-        <v>46228.93998842593</v>
+        <v>46230.86315972222</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>ASSAULT</t>
+          <t>VANDALISM</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -25680,21 +25722,21 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>200 BLOCK BEACH WALK</t>
+          <t>400 BLOCK NAMAHANA ST</t>
         </is>
       </c>
       <c r="J386" t="n">
-        <v>21.278930465176</v>
+        <v>21.283997526549</v>
       </c>
       <c r="K386" t="n">
-        <v>-157.832248174365</v>
+        <v>-157.831319892615</v>
       </c>
       <c r="L386" t="n">
-        <v>583.7</v>
+        <v>821.7</v>
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Assault on Jul 25, 2026, 584 m from International Market Place (200 BLOCK BEACH WALK). Case #260725-1627 (use for a records request — full narratives are not published in open data).</t>
+          <t>Vandalism on Jul 27, 2026, 822 m from International Market Place (400 BLOCK NAMAHANA ST). Case #260727-1586 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25716,11 +25758,11 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>260725-1228</t>
+          <t>260727-1381</t>
         </is>
       </c>
       <c r="E387" s="3" t="n">
-        <v>46228.75162037037</v>
+        <v>46230.75506944444</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -25753,7 +25795,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Theft/larceny on Jul 25, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260725-1228 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft/larceny on Jul 27, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260727-1381 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25775,20 +25817,20 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>260725-1158</t>
+          <t>260727-1340</t>
         </is>
       </c>
       <c r="E388" s="3" t="n">
-        <v>46228.70266203704</v>
+        <v>46230.73439814815</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>ASSAULT</t>
+          <t>THEFT/LARCENY</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -25798,21 +25840,21 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>2300 BLOCK KALAKAUA AVE</t>
+          <t>100 BLOCK PAOA PL</t>
         </is>
       </c>
       <c r="J388" t="n">
-        <v>21.27805648814</v>
+        <v>21.28152934735</v>
       </c>
       <c r="K388" t="n">
-        <v>-157.827664940544</v>
+        <v>-157.836992718528</v>
       </c>
       <c r="L388" t="n">
-        <v>99.7</v>
+        <v>1136.3</v>
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Assault on Jul 25, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260725-1158 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft/larceny on Jul 27, 2026, 1136 m from International Market Place (100 BLOCK PAOA PL). Case #260727-1340 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25834,15 +25876,15 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>260725-0503</t>
+          <t>260727-1304</t>
         </is>
       </c>
       <c r="E389" s="3" t="n">
-        <v>46228.35734953704</v>
+        <v>46230.71633101852</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>MOTOR VEHICLE THEFT</t>
+          <t>VANDALISM</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
@@ -25857,21 +25899,21 @@
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>2400 BLOCK KALAKAUA AVE</t>
+          <t>600 BLOCK HAUSTEN ST</t>
         </is>
       </c>
       <c r="J389" t="n">
-        <v>21.276010351182</v>
+        <v>21.287732337343</v>
       </c>
       <c r="K389" t="n">
-        <v>-157.825469259274</v>
+        <v>-157.82689064649</v>
       </c>
       <c r="L389" t="n">
-        <v>254.5</v>
+        <v>1083.7</v>
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Motor vehicle theft on Jul 25, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260725-0503 (use for a records request — full narratives are not published in open data).</t>
+          <t>Vandalism on Jul 27, 2026, 1084 m from International Market Place (600 BLOCK HAUSTEN ST). Case #260727-1304 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25893,20 +25935,20 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>260725-0383</t>
+          <t>260727-1302</t>
         </is>
       </c>
       <c r="E390" s="3" t="n">
-        <v>46228.28726851852</v>
+        <v>46230.71513888889</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>DISTURBING THE PEACE</t>
+          <t>THEFT/LARCENY</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -25916,21 +25958,21 @@
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>2300 BLOCK KALAKAUA AVE</t>
+          <t>300 BLOCK KALAIMOKU ST</t>
         </is>
       </c>
       <c r="J390" t="n">
-        <v>21.27805648814</v>
+        <v>21.282350597517</v>
       </c>
       <c r="K390" t="n">
-        <v>-157.827664940544</v>
+        <v>-157.830982023446</v>
       </c>
       <c r="L390" t="n">
-        <v>99.7</v>
+        <v>657</v>
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Disturbing the peace on Jul 25, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260725-0383 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft/larceny on Jul 27, 2026, 657 m from International Market Place (300 BLOCK KALAIMOKU ST). Case #260727-1302 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -25952,49 +25994,1288 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
+          <t>260727-1278</t>
+        </is>
+      </c>
+      <c r="E391" s="3" t="n">
+        <v>46230.70094907407</v>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>MOTOR VEHICLE THEFT</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>1800 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J391" t="n">
+        <v>21.288652807916</v>
+      </c>
+      <c r="K391" t="n">
+        <v>-157.834591426424</v>
+      </c>
+      <c r="L391" t="n">
+        <v>1440.1</v>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 27, 2026, 1440 m from International Market Place (1800 BLOCK KALAKAUA AVE). Case #260727-1278 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>260727-1127</t>
+        </is>
+      </c>
+      <c r="E392" s="3" t="n">
+        <v>46230.64813657408</v>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>ASSAULT</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>1900 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J392" t="n">
+        <v>21.28609383604</v>
+      </c>
+      <c r="K392" t="n">
+        <v>-157.833074890083</v>
+      </c>
+      <c r="L392" t="n">
+        <v>1117.1</v>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>Assault on Jul 27, 2026, 1117 m from International Market Place (1900 BLOCK KALAKAUA AVE). Case #260727-1127 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>260727-0958</t>
+        </is>
+      </c>
+      <c r="E393" s="3" t="n">
+        <v>46230.57681712963</v>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>2200 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J393" t="n">
+        <v>21.280046658192</v>
+      </c>
+      <c r="K393" t="n">
+        <v>-157.829687791355</v>
+      </c>
+      <c r="L393" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 27, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260727-0958 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>260727-0745</t>
+        </is>
+      </c>
+      <c r="E394" s="3" t="n">
+        <v>46230.48368055555</v>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>DRUGS/ALCOHOL VIOLATIONS</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>100 BLOCK KAIULANI AVE</t>
+        </is>
+      </c>
+      <c r="J394" t="n">
+        <v>21.277067198668</v>
+      </c>
+      <c r="K394" t="n">
+        <v>-157.82544391535</v>
+      </c>
+      <c r="L394" t="n">
+        <v>166.1</v>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>Drugs/alcohol violations on Jul 27, 2026, 166 m from International Market Place (100 BLOCK KAIULANI AVE). Case #260727-0745 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>260727-0609</t>
+        </is>
+      </c>
+      <c r="E395" s="3" t="n">
+        <v>46230.42018518518</v>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>ASSAULT</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>300 BLOCK LEWERS ST</t>
+        </is>
+      </c>
+      <c r="J395" t="n">
+        <v>21.280145465259</v>
+      </c>
+      <c r="K395" t="n">
+        <v>-157.829777674689</v>
+      </c>
+      <c r="L395" t="n">
+        <v>398.6</v>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>Assault on Jul 27, 2026, 399 m from International Market Place (300 BLOCK LEWERS ST). Case #260727-0609 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>260727-0604</t>
+        </is>
+      </c>
+      <c r="E396" s="3" t="n">
+        <v>46230.41591435186</v>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>800 BLOCK KAPAHULU AVE</t>
+        </is>
+      </c>
+      <c r="J396" t="n">
+        <v>21.281867877215</v>
+      </c>
+      <c r="K396" t="n">
+        <v>-157.814203084308</v>
+      </c>
+      <c r="L396" t="n">
+        <v>1365.4</v>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 27, 2026, 1365 m from International Market Place (800 BLOCK KAPAHULU AVE). Case #260727-0604 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>260727-0261</t>
+        </is>
+      </c>
+      <c r="E397" s="3" t="n">
+        <v>46230.27378472222</v>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>200 BLOCK LILIUOKALANI AVE</t>
+        </is>
+      </c>
+      <c r="J397" t="n">
+        <v>21.275580844298</v>
+      </c>
+      <c r="K397" t="n">
+        <v>-157.822410575513</v>
+      </c>
+      <c r="L397" t="n">
+        <v>519.3</v>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 27, 2026, 519 m from International Market Place (200 BLOCK LILIUOKALANI AVE). Case #260727-0261 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>260727-0160</t>
+        </is>
+      </c>
+      <c r="E398" s="3" t="n">
+        <v>46230.1952662037</v>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>VANDALISM</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J398" t="n">
+        <v>21.276010351182</v>
+      </c>
+      <c r="K398" t="n">
+        <v>-157.825469259274</v>
+      </c>
+      <c r="L398" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>Vandalism on Jul 27, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260727-0160 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>260726-1509</t>
+        </is>
+      </c>
+      <c r="E399" s="3" t="n">
+        <v>46229.94366898148</v>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>VANDALISM</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>100 BLOCK KAPAHULU AVE</t>
+        </is>
+      </c>
+      <c r="J399" t="n">
+        <v>21.271580290957</v>
+      </c>
+      <c r="K399" t="n">
+        <v>-157.822696449285</v>
+      </c>
+      <c r="L399" t="n">
+        <v>824.7</v>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>Vandalism on Jul 26, 2026, 825 m from International Market Place (100 BLOCK KAPAHULU AVE). Case #260726-1509 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>260726-1307</t>
+        </is>
+      </c>
+      <c r="E400" s="3" t="n">
+        <v>46229.82886574074</v>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>600 BLOCK KAPAHULU AVE</t>
+        </is>
+      </c>
+      <c r="J400" t="n">
+        <v>21.277595864317</v>
+      </c>
+      <c r="K400" t="n">
+        <v>-157.814205924306</v>
+      </c>
+      <c r="L400" t="n">
+        <v>1295.9</v>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 26, 2026, 1296 m from International Market Place (600 BLOCK KAPAHULU AVE). Case #260726-1307 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>260726-0935</t>
+        </is>
+      </c>
+      <c r="E401" s="3" t="n">
+        <v>46229.61716435185</v>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J401" t="n">
+        <v>21.276010351182</v>
+      </c>
+      <c r="K401" t="n">
+        <v>-157.825469259274</v>
+      </c>
+      <c r="L401" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 26, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260726-0935 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>260726-0313</t>
+        </is>
+      </c>
+      <c r="E402" s="3" t="n">
+        <v>46229.25769675926</v>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>2500 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J402" t="n">
+        <v>21.273862837838</v>
+      </c>
+      <c r="K402" t="n">
+        <v>-157.82387239543</v>
+      </c>
+      <c r="L402" t="n">
+        <v>544.6</v>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 26, 2026, 545 m from International Market Place (2500 BLOCK KALAKAUA AVE). Case #260726-0313 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>260726-0222</t>
+        </is>
+      </c>
+      <c r="E403" s="3" t="n">
+        <v>46229.15130787037</v>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>ASSAULT</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>2200 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J403" t="n">
+        <v>21.280046658192</v>
+      </c>
+      <c r="K403" t="n">
+        <v>-157.829687791355</v>
+      </c>
+      <c r="L403" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>Assault on Jul 26, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260726-0222 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>260725-1627</t>
+        </is>
+      </c>
+      <c r="E404" s="3" t="n">
+        <v>46228.93998842593</v>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>ASSAULT</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>200 BLOCK BEACH WALK</t>
+        </is>
+      </c>
+      <c r="J404" t="n">
+        <v>21.278930465176</v>
+      </c>
+      <c r="K404" t="n">
+        <v>-157.832248174365</v>
+      </c>
+      <c r="L404" t="n">
+        <v>583.7</v>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>Assault on Jul 25, 2026, 584 m from International Market Place (200 BLOCK BEACH WALK). Case #260725-1627 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>260725-1248</t>
+        </is>
+      </c>
+      <c r="E405" s="3" t="n">
+        <v>46228.76230324074</v>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>800 BLOCK KAPAHULU AVE</t>
+        </is>
+      </c>
+      <c r="J405" t="n">
+        <v>21.281867877215</v>
+      </c>
+      <c r="K405" t="n">
+        <v>-157.814203084308</v>
+      </c>
+      <c r="L405" t="n">
+        <v>1365.4</v>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 25, 2026, 1365 m from International Market Place (800 BLOCK KAPAHULU AVE). Case #260725-1248 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>260725-1228</t>
+        </is>
+      </c>
+      <c r="E406" s="3" t="n">
+        <v>46228.75162037037</v>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>2200 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J406" t="n">
+        <v>21.280046658192</v>
+      </c>
+      <c r="K406" t="n">
+        <v>-157.829687791355</v>
+      </c>
+      <c r="L406" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 25, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260725-1228 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>260725-1158</t>
+        </is>
+      </c>
+      <c r="E407" s="3" t="n">
+        <v>46228.70266203704</v>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>ASSAULT</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>2300 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J407" t="n">
+        <v>21.27805648814</v>
+      </c>
+      <c r="K407" t="n">
+        <v>-157.827664940544</v>
+      </c>
+      <c r="L407" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>Assault on Jul 25, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260725-1158 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>260725-0789</t>
+        </is>
+      </c>
+      <c r="E408" s="3" t="n">
+        <v>46228.50842592592</v>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>100 BLOCK PAOA PL</t>
+        </is>
+      </c>
+      <c r="J408" t="n">
+        <v>21.28152934735</v>
+      </c>
+      <c r="K408" t="n">
+        <v>-157.836992718528</v>
+      </c>
+      <c r="L408" t="n">
+        <v>1136.3</v>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 25, 2026, 1136 m from International Market Place (100 BLOCK PAOA PL). Case #260725-0789 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>260725-0503</t>
+        </is>
+      </c>
+      <c r="E409" s="3" t="n">
+        <v>46228.35734953704</v>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>MOTOR VEHICLE THEFT</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J409" t="n">
+        <v>21.276010351182</v>
+      </c>
+      <c r="K409" t="n">
+        <v>-157.825469259274</v>
+      </c>
+      <c r="L409" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 25, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260725-0503 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>260725-0383</t>
+        </is>
+      </c>
+      <c r="E410" s="3" t="n">
+        <v>46228.28726851852</v>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>DISTURBING THE PEACE</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>2300 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J410" t="n">
+        <v>21.27805648814</v>
+      </c>
+      <c r="K410" t="n">
+        <v>-157.827664940544</v>
+      </c>
+      <c r="L410" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>Disturbing the peace on Jul 25, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260725-0383 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
           <t>260725-0324</t>
         </is>
       </c>
-      <c r="E391" s="3" t="n">
+      <c r="E411" s="3" t="n">
         <v>46228.26383101852</v>
       </c>
-      <c r="F391" t="inlineStr">
+      <c r="F411" t="inlineStr">
         <is>
           <t>THEFT/LARCENY</t>
         </is>
       </c>
-      <c r="G391" t="inlineStr">
+      <c r="G411" t="inlineStr">
         <is>
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H391" t="inlineStr">
+      <c r="H411" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I391" t="inlineStr">
+      <c r="I411" t="inlineStr">
         <is>
           <t>2400 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
-      <c r="J391" t="n">
+      <c r="J411" t="n">
         <v>21.276010351182</v>
       </c>
-      <c r="K391" t="n">
+      <c r="K411" t="n">
         <v>-157.825469259274</v>
       </c>
-      <c r="L391" t="n">
+      <c r="L411" t="n">
         <v>254.5</v>
       </c>
-      <c r="M391" t="inlineStr">
+      <c r="M411" t="inlineStr">
         <is>
           <t>Theft/larceny on Jul 25, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260725-0324 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>260725-0300</t>
+        </is>
+      </c>
+      <c r="E412" s="3" t="n">
+        <v>46228.24635416667</v>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>1900 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J412" t="n">
+        <v>21.28609383604</v>
+      </c>
+      <c r="K412" t="n">
+        <v>-157.833074890083</v>
+      </c>
+      <c r="L412" t="n">
+        <v>1117.1</v>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 25, 2026, 1117 m from International Market Place (1900 BLOCK KALAKAUA AVE). Case #260725-0300 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M391"/>
+  <autoFilter ref="A1:M412"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -26005,7 +27286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -26032,7 +27313,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 05:08:21.498984+00:00</t>
+          <t>2026-08-01 05:17:38.206635+00:00</t>
         </is>
       </c>
     </row>
@@ -26064,7 +27345,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 05:08:21.498984+00:00</t>
+          <t>2026-07-25 05:17:38.206635+00:00</t>
         </is>
       </c>
     </row>
@@ -26075,7 +27356,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>390</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7">
@@ -26085,7 +27366,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
@@ -26396,7 +27677,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>OK fetched=479 truncated=False</t>
+          <t>OK fetched=478 truncated=False</t>
         </is>
       </c>
     </row>
@@ -26408,12 +27689,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>OK fetched=479 truncated=False</t>
+          <t>OK fetched=478 truncated=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>source:FASHIONVAL/San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>OK fetched=5000 truncated=True</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B34"/>
+  <autoFilter ref="A1:B35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/2026-08-01/blotter_report.xlsx
+++ b/reports/2026-08-01/blotter_report.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$412</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$531</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1046,12 +1046,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
+        <v>114</v>
+      </c>
+      <c r="J13" t="n">
+        <v>258.2</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>46233.87652777778</v>
+      </c>
+      <c r="L13" t="b">
         <v>0</v>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1164,19 +1168,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H16" t="n">
         <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
         <v>99.7</v>
@@ -3280,7 +3284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M412"/>
+  <dimension ref="A1:M531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -26643,15 +26647,15 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>260726-0313</t>
+          <t>260726-0446</t>
         </is>
       </c>
       <c r="E402" s="3" t="n">
-        <v>46229.25769675926</v>
+        <v>46229.33935185185</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>THEFT/LARCENY</t>
+          <t>MOTOR VEHICLE THEFT</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
@@ -26666,21 +26670,21 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>2500 BLOCK KALAKAUA AVE</t>
+          <t>400 BLOCK KALAIMOKU ST</t>
         </is>
       </c>
       <c r="J402" t="n">
-        <v>21.273862837838</v>
+        <v>21.283097590097</v>
       </c>
       <c r="K402" t="n">
-        <v>-157.82387239543</v>
+        <v>-157.830228693079</v>
       </c>
       <c r="L402" t="n">
-        <v>544.6</v>
+        <v>675.3</v>
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Theft/larceny on Jul 26, 2026, 545 m from International Market Place (2500 BLOCK KALAKAUA AVE). Case #260726-0313 (use for a records request — full narratives are not published in open data).</t>
+          <t>Motor vehicle theft on Jul 26, 2026, 675 m from International Market Place (400 BLOCK KALAIMOKU ST). Case #260726-0446 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -26702,20 +26706,20 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>260726-0222</t>
+          <t>260726-0313</t>
         </is>
       </c>
       <c r="E403" s="3" t="n">
-        <v>46229.15130787037</v>
+        <v>46229.25769675926</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>ASSAULT</t>
+          <t>THEFT/LARCENY</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -26725,21 +26729,21 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>2200 BLOCK KALAKAUA AVE</t>
+          <t>2500 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J403" t="n">
-        <v>21.280046658192</v>
+        <v>21.273862837838</v>
       </c>
       <c r="K403" t="n">
-        <v>-157.829687791355</v>
+        <v>-157.82387239543</v>
       </c>
       <c r="L403" t="n">
-        <v>384.6</v>
+        <v>544.6</v>
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Assault on Jul 26, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260726-0222 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft/larceny on Jul 26, 2026, 545 m from International Market Place (2500 BLOCK KALAKAUA AVE). Case #260726-0313 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -26761,11 +26765,11 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>260725-1627</t>
+          <t>260726-0222</t>
         </is>
       </c>
       <c r="E404" s="3" t="n">
-        <v>46228.93998842593</v>
+        <v>46229.15130787037</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -26784,21 +26788,21 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>200 BLOCK BEACH WALK</t>
+          <t>2200 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J404" t="n">
-        <v>21.278930465176</v>
+        <v>21.280046658192</v>
       </c>
       <c r="K404" t="n">
-        <v>-157.832248174365</v>
+        <v>-157.829687791355</v>
       </c>
       <c r="L404" t="n">
-        <v>583.7</v>
+        <v>384.6</v>
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Assault on Jul 25, 2026, 584 m from International Market Place (200 BLOCK BEACH WALK). Case #260725-1627 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 26, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260726-0222 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -26820,11 +26824,11 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>260725-1248</t>
+          <t>260725-1725</t>
         </is>
       </c>
       <c r="E405" s="3" t="n">
-        <v>46228.76230324074</v>
+        <v>46228.99921296296</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -26843,21 +26847,21 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>800 BLOCK KAPAHULU AVE</t>
+          <t>2400 BLOCK KAPIOLANI BLVD</t>
         </is>
       </c>
       <c r="J405" t="n">
-        <v>21.281867877215</v>
+        <v>21.287695571049</v>
       </c>
       <c r="K405" t="n">
-        <v>-157.814203084308</v>
+        <v>-157.8268105694</v>
       </c>
       <c r="L405" t="n">
-        <v>1365.4</v>
+        <v>1079.5</v>
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Theft/larceny on Jul 25, 2026, 1365 m from International Market Place (800 BLOCK KAPAHULU AVE). Case #260725-1248 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft/larceny on Jul 25, 2026, 1080 m from International Market Place (2400 BLOCK KAPIOLANI BLVD). Case #260725-1725 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -26879,20 +26883,20 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>260725-1228</t>
+          <t>260725-1627</t>
         </is>
       </c>
       <c r="E406" s="3" t="n">
-        <v>46228.75162037037</v>
+        <v>46228.93998842593</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>THEFT/LARCENY</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -26902,21 +26906,21 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>2200 BLOCK KALAKAUA AVE</t>
+          <t>200 BLOCK BEACH WALK</t>
         </is>
       </c>
       <c r="J406" t="n">
-        <v>21.280046658192</v>
+        <v>21.278930465176</v>
       </c>
       <c r="K406" t="n">
-        <v>-157.829687791355</v>
+        <v>-157.832248174365</v>
       </c>
       <c r="L406" t="n">
-        <v>384.6</v>
+        <v>583.7</v>
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Theft/larceny on Jul 25, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260725-1228 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 25, 2026, 584 m from International Market Place (200 BLOCK BEACH WALK). Case #260725-1627 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -26938,20 +26942,20 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>260725-1158</t>
+          <t>260725-1302</t>
         </is>
       </c>
       <c r="E407" s="3" t="n">
-        <v>46228.70266203704</v>
+        <v>46228.78915509259</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>ASSAULT</t>
+          <t>MOTOR VEHICLE THEFT</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -26961,21 +26965,21 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>2300 BLOCK KALAKAUA AVE</t>
+          <t>2800 BLOCK LEIALOHA AVE</t>
         </is>
       </c>
       <c r="J407" t="n">
-        <v>21.27805648814</v>
+        <v>21.285468829424</v>
       </c>
       <c r="K407" t="n">
-        <v>-157.827664940544</v>
+        <v>-157.815456755144</v>
       </c>
       <c r="L407" t="n">
-        <v>99.7</v>
+        <v>1432</v>
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Assault on Jul 25, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260725-1158 (use for a records request — full narratives are not published in open data).</t>
+          <t>Motor vehicle theft on Jul 25, 2026, 1432 m from International Market Place (2800 BLOCK LEIALOHA AVE). Case #260725-1302 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -26997,11 +27001,11 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>260725-0789</t>
+          <t>260725-1248</t>
         </is>
       </c>
       <c r="E408" s="3" t="n">
-        <v>46228.50842592592</v>
+        <v>46228.76230324074</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -27020,21 +27024,21 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>100 BLOCK PAOA PL</t>
+          <t>800 BLOCK KAPAHULU AVE</t>
         </is>
       </c>
       <c r="J408" t="n">
-        <v>21.28152934735</v>
+        <v>21.281867877215</v>
       </c>
       <c r="K408" t="n">
-        <v>-157.836992718528</v>
+        <v>-157.814203084308</v>
       </c>
       <c r="L408" t="n">
-        <v>1136.3</v>
+        <v>1365.4</v>
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Theft/larceny on Jul 25, 2026, 1136 m from International Market Place (100 BLOCK PAOA PL). Case #260725-0789 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft/larceny on Jul 25, 2026, 1365 m from International Market Place (800 BLOCK KAPAHULU AVE). Case #260725-1248 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -27056,15 +27060,15 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>260725-0503</t>
+          <t>260725-1228</t>
         </is>
       </c>
       <c r="E409" s="3" t="n">
-        <v>46228.35734953704</v>
+        <v>46228.75162037037</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>MOTOR VEHICLE THEFT</t>
+          <t>THEFT/LARCENY</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
@@ -27079,21 +27083,21 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>2400 BLOCK KALAKAUA AVE</t>
+          <t>2200 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J409" t="n">
-        <v>21.276010351182</v>
+        <v>21.280046658192</v>
       </c>
       <c r="K409" t="n">
-        <v>-157.825469259274</v>
+        <v>-157.829687791355</v>
       </c>
       <c r="L409" t="n">
-        <v>254.5</v>
+        <v>384.6</v>
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Motor vehicle theft on Jul 25, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260725-0503 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft/larceny on Jul 25, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260725-1228 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -27115,20 +27119,20 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>260725-0383</t>
+          <t>260725-1158</t>
         </is>
       </c>
       <c r="E410" s="3" t="n">
-        <v>46228.28726851852</v>
+        <v>46228.70266203704</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>DISTURBING THE PEACE</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -27152,7 +27156,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Disturbing the peace on Jul 25, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260725-0383 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 25, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260725-1158 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -27174,20 +27178,20 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>260725-0324</t>
+          <t>260725-0995</t>
         </is>
       </c>
       <c r="E411" s="3" t="n">
-        <v>46228.26383101852</v>
+        <v>46228.60679398148</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>THEFT/LARCENY</t>
+          <t>SEX CRIMES</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -27197,21 +27201,21 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>2400 BLOCK KALAKAUA AVE</t>
+          <t>2000 BLOCK KALIA RD</t>
         </is>
       </c>
       <c r="J411" t="n">
-        <v>21.276010351182</v>
+        <v>21.284854359111</v>
       </c>
       <c r="K411" t="n">
-        <v>-157.825469259274</v>
+        <v>-157.835622022577</v>
       </c>
       <c r="L411" t="n">
-        <v>254.5</v>
+        <v>1198.5</v>
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Theft/larceny on Jul 25, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260725-0324 (use for a records request — full narratives are not published in open data).</t>
+          <t>Sex crimes on Jul 25, 2026, 1199 m from International Market Place (2000 BLOCK KALIA RD). Case #260725-0995 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -27233,49 +27237,7070 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
+          <t>260725-0789</t>
+        </is>
+      </c>
+      <c r="E412" s="3" t="n">
+        <v>46228.50842592592</v>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>100 BLOCK PAOA PL</t>
+        </is>
+      </c>
+      <c r="J412" t="n">
+        <v>21.28152934735</v>
+      </c>
+      <c r="K412" t="n">
+        <v>-157.836992718528</v>
+      </c>
+      <c r="L412" t="n">
+        <v>1136.3</v>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 25, 2026, 1136 m from International Market Place (100 BLOCK PAOA PL). Case #260725-0789 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>260725-0503</t>
+        </is>
+      </c>
+      <c r="E413" s="3" t="n">
+        <v>46228.35734953704</v>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>MOTOR VEHICLE THEFT</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J413" t="n">
+        <v>21.276010351182</v>
+      </c>
+      <c r="K413" t="n">
+        <v>-157.825469259274</v>
+      </c>
+      <c r="L413" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 25, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260725-0503 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>260725-0464</t>
+        </is>
+      </c>
+      <c r="E414" s="3" t="n">
+        <v>46228.33700231482</v>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>500 BLOCK UNIVERSITY AVE</t>
+        </is>
+      </c>
+      <c r="J414" t="n">
+        <v>21.286039793998</v>
+      </c>
+      <c r="K414" t="n">
+        <v>-157.827429071873</v>
+      </c>
+      <c r="L414" t="n">
+        <v>898.5</v>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 25, 2026, 899 m from International Market Place (500 BLOCK UNIVERSITY AVE). Case #260725-0464 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>260725-0383</t>
+        </is>
+      </c>
+      <c r="E415" s="3" t="n">
+        <v>46228.28726851852</v>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>DISTURBING THE PEACE</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>2300 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J415" t="n">
+        <v>21.27805648814</v>
+      </c>
+      <c r="K415" t="n">
+        <v>-157.827664940544</v>
+      </c>
+      <c r="L415" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>Disturbing the peace on Jul 25, 2026, 100 m from International Market Place (2300 BLOCK KALAKAUA AVE). Case #260725-0383 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>260725-0324</t>
+        </is>
+      </c>
+      <c r="E416" s="3" t="n">
+        <v>46228.26383101852</v>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>THEFT/LARCENY</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>2400 BLOCK KALAKAUA AVE</t>
+        </is>
+      </c>
+      <c r="J416" t="n">
+        <v>21.276010351182</v>
+      </c>
+      <c r="K416" t="n">
+        <v>-157.825469259274</v>
+      </c>
+      <c r="L416" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>Theft/larceny on Jul 25, 2026, 254 m from International Market Place (2400 BLOCK KALAKAUA AVE). Case #260725-0324 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>INTLMARKET</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>International Market Place</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>INTLMARKET:vg88-5rn5</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
           <t>260725-0300</t>
         </is>
       </c>
-      <c r="E412" s="3" t="n">
+      <c r="E417" s="3" t="n">
         <v>46228.24635416667</v>
       </c>
-      <c r="F412" t="inlineStr">
+      <c r="F417" t="inlineStr">
         <is>
           <t>THEFT/LARCENY</t>
         </is>
       </c>
-      <c r="G412" t="inlineStr">
+      <c r="G417" t="inlineStr">
         <is>
           <t>PROPERTY</t>
         </is>
       </c>
-      <c r="H412" t="inlineStr">
+      <c r="H417" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I412" t="inlineStr">
+      <c r="I417" t="inlineStr">
         <is>
           <t>1900 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
-      <c r="J412" t="n">
+      <c r="J417" t="n">
         <v>21.28609383604</v>
       </c>
-      <c r="K412" t="n">
+      <c r="K417" t="n">
         <v>-157.833074890083</v>
       </c>
-      <c r="L412" t="n">
+      <c r="L417" t="n">
         <v>1117.1</v>
       </c>
-      <c r="M412" t="inlineStr">
+      <c r="M417" t="inlineStr">
         <is>
           <t>Theft/larceny on Jul 25, 2026, 1117 m from International Market Place (1900 BLOCK KALAKAUA AVE). Case #260725-0300 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>E26070037781</t>
+        </is>
+      </c>
+      <c r="E418" s="3" t="n">
+        <v>46229.7440625</v>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>594R</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>7000 FRIARS RD</t>
+        </is>
+      </c>
+      <c r="J418" t="n">
+        <v>32.769515710089</v>
+      </c>
+      <c r="K418" t="n">
+        <v>-117.169790033203</v>
+      </c>
+      <c r="L418" t="n">
+        <v>420.9</v>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>594r on Jul 26, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070037781 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>E26070041113</t>
+        </is>
+      </c>
+      <c r="E419" s="3" t="n">
+        <v>46231.94868055556</v>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>10851R</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>7500 HAZARD CENTER DR</t>
+        </is>
+      </c>
+      <c r="J419" t="n">
+        <v>32.769886247713</v>
+      </c>
+      <c r="K419" t="n">
+        <v>-117.159316836244</v>
+      </c>
+      <c r="L419" t="n">
+        <v>691.2</v>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>10851r on Jul 28, 2026, 691 m from Fashion Valley (7500 HAZARD CENTER DR). Case #E26070041113 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>E26070041890</t>
+        </is>
+      </c>
+      <c r="E420" s="3" t="n">
+        <v>46232.53804398148</v>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>AU23103</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>6900 FRIARS RD</t>
+        </is>
+      </c>
+      <c r="J420" t="n">
+        <v>32.768802058993</v>
+      </c>
+      <c r="K420" t="n">
+        <v>-117.171569461601</v>
+      </c>
+      <c r="L420" t="n">
+        <v>537.4</v>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>Au23103 on Jul 29, 2026, 537 m from Fashion Valley (6900 FRIARS RD). Case #E26070041890 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>E26070041760</t>
+        </is>
+      </c>
+      <c r="E421" s="3" t="n">
+        <v>46232.47642361111</v>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>10851RR</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>900 CAMINO DEL RIO SOUTH</t>
+        </is>
+      </c>
+      <c r="J421" t="n">
+        <v>32.764297296186</v>
+      </c>
+      <c r="K421" t="n">
+        <v>-117.154654014114</v>
+      </c>
+      <c r="L421" t="n">
+        <v>1121.7</v>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>10851rr on Jul 29, 2026, 1122 m from Fashion Valley (900 CAMINO DEL RIO SOUTH). Case #E26070041760 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>E26070040752</t>
+        </is>
+      </c>
+      <c r="E422" s="3" t="n">
+        <v>46231.73775462963</v>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>1100 CAMINO DE LA REINA</t>
+        </is>
+      </c>
+      <c r="J422" t="n">
+        <v>32.768503746841</v>
+      </c>
+      <c r="K422" t="n">
+        <v>-117.152853070724</v>
+      </c>
+      <c r="L422" t="n">
+        <v>1242.9</v>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>T on Jul 28, 2026, 1243 m from Fashion Valley (1100 CAMINO DE LA REINA). Case #E26070040752 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>E26070040776</t>
+        </is>
+      </c>
+      <c r="E423" s="3" t="n">
+        <v>46231.74665509259</v>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>1800 HOTEL CIRCLE SOUTH</t>
+        </is>
+      </c>
+      <c r="J423" t="n">
+        <v>32.759597128436</v>
+      </c>
+      <c r="K423" t="n">
+        <v>-117.177340012371</v>
+      </c>
+      <c r="L423" t="n">
+        <v>1362.6</v>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>415 on Jul 28, 2026, 1363 m from Fashion Valley (1800 HOTEL CIRCLE SOUTH). Case #E26070040776 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>E26070040789</t>
+        </is>
+      </c>
+      <c r="E424" s="3" t="n">
+        <v>46231.75309027778</v>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>7700 HAZARD CENTER DR</t>
+        </is>
+      </c>
+      <c r="J424" t="n">
+        <v>32.770935601241</v>
+      </c>
+      <c r="K424" t="n">
+        <v>-117.156166110813</v>
+      </c>
+      <c r="L424" t="n">
+        <v>1007.9</v>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>245 on Jul 28, 2026, 1008 m from Fashion Valley (7700 HAZARD CENTER DR). Case #E26070040789 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>E26070040831</t>
+        </is>
+      </c>
+      <c r="E425" s="3" t="n">
+        <v>46231.77418981482</v>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>800 HOTEL CIRCLE SOUTH</t>
+        </is>
+      </c>
+      <c r="J425" t="n">
+        <v>32.760837633784</v>
+      </c>
+      <c r="K425" t="n">
+        <v>-117.170557039813</v>
+      </c>
+      <c r="L425" t="n">
+        <v>838.8</v>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>911 on Jul 28, 2026, 839 m from Fashion Valley (800 HOTEL CIRCLE SOUTH). Case #E26070040831 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>E26070040857</t>
+        </is>
+      </c>
+      <c r="E426" s="3" t="n">
+        <v>46231.78961805555</v>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>1200 CAMINO DEL RIO NORTH</t>
+        </is>
+      </c>
+      <c r="J426" t="n">
+        <v>32.766861158912</v>
+      </c>
+      <c r="K426" t="n">
+        <v>-117.151286132201</v>
+      </c>
+      <c r="L426" t="n">
+        <v>1384.3</v>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>211 on Jul 28, 2026, 1384 m from Fashion Valley (1200 CAMINO DEL RIO NORTH). Case #E26070040857 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>E26070040991</t>
+        </is>
+      </c>
+      <c r="E427" s="3" t="n">
+        <v>46231.86539351852</v>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>1140OD</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>600 HOTEL CIRCLE SOUTH</t>
+        </is>
+      </c>
+      <c r="J427" t="n">
+        <v>32.761115185306</v>
+      </c>
+      <c r="K427" t="n">
+        <v>-117.169262923224</v>
+      </c>
+      <c r="L427" t="n">
+        <v>757</v>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>1140od on Jul 28, 2026, 757 m from Fashion Valley (600 HOTEL CIRCLE SOUTH). Case #E26070040991 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>E26070041000</t>
+        </is>
+      </c>
+      <c r="E428" s="3" t="n">
+        <v>46231.87225694444</v>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>459A</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>7000 FRIARS RD</t>
+        </is>
+      </c>
+      <c r="J428" t="n">
+        <v>32.769515710089</v>
+      </c>
+      <c r="K428" t="n">
+        <v>-117.169790033203</v>
+      </c>
+      <c r="L428" t="n">
+        <v>420.9</v>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>459a on Jul 28, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070041000 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>E26070039356</t>
+        </is>
+      </c>
+      <c r="E429" s="3" t="n">
+        <v>46230.81408564815</v>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>10851R</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>900 CAMINO DEL RIO SOUTH</t>
+        </is>
+      </c>
+      <c r="J429" t="n">
+        <v>32.764297296186</v>
+      </c>
+      <c r="K429" t="n">
+        <v>-117.154654014114</v>
+      </c>
+      <c r="L429" t="n">
+        <v>1121.7</v>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>10851r on Jul 27, 2026, 1122 m from Fashion Valley (900 CAMINO DEL RIO SOUTH). Case #E26070039356 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>E26070039761</t>
+        </is>
+      </c>
+      <c r="E430" s="3" t="n">
+        <v>46231.1196412037</v>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>10852C</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>300 CAMINO DE LA REINA</t>
+        </is>
+      </c>
+      <c r="J430" t="n">
+        <v>32.764468174789</v>
+      </c>
+      <c r="K430" t="n">
+        <v>-117.164515919347</v>
+      </c>
+      <c r="L430" t="n">
+        <v>354.6</v>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>10852c on Jul 28, 2026, 355 m from Fashion Valley (300 CAMINO DE LA REINA). Case #E26070039761 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>E26070041298</t>
+        </is>
+      </c>
+      <c r="E431" s="3" t="n">
+        <v>46232.13975694445</v>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>488R</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>7400 HAZARD CENTER DR</t>
+        </is>
+      </c>
+      <c r="J431" t="n">
+        <v>32.76831582062</v>
+      </c>
+      <c r="K431" t="n">
+        <v>-117.161380632533</v>
+      </c>
+      <c r="L431" t="n">
+        <v>451.6</v>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>488r on Jul 29, 2026, 452 m from Fashion Valley (7400 HAZARD CENTER DR). Case #E26070041298 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>E26070041301</t>
+        </is>
+      </c>
+      <c r="E432" s="3" t="n">
+        <v>46232.14467592593</v>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>AU1171</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>6800 FRIARS RD</t>
+        </is>
+      </c>
+      <c r="J432" t="n">
+        <v>32.768288067315</v>
+      </c>
+      <c r="K432" t="n">
+        <v>-117.172866645828</v>
+      </c>
+      <c r="L432" t="n">
+        <v>642.8</v>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>Au1171 on Jul 29, 2026, 643 m from Fashion Valley (6800 FRIARS RD). Case #E26070041301 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>E26070042450</t>
+        </is>
+      </c>
+      <c r="E433" s="3" t="n">
+        <v>46232.87263888889</v>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>1131</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>1800 HOTEL CIRCLE SOUTH</t>
+        </is>
+      </c>
+      <c r="J433" t="n">
+        <v>32.759597128436</v>
+      </c>
+      <c r="K433" t="n">
+        <v>-117.177340012371</v>
+      </c>
+      <c r="L433" t="n">
+        <v>1362.6</v>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>1131 on Jul 29, 2026, 1363 m from Fashion Valley (1800 HOTEL CIRCLE SOUTH). Case #E26070042450 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>E26070038579</t>
+        </is>
+      </c>
+      <c r="E434" s="3" t="n">
+        <v>46230.39099537037</v>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>7000 FRIARS RD</t>
+        </is>
+      </c>
+      <c r="J434" t="n">
+        <v>32.769515710089</v>
+      </c>
+      <c r="K434" t="n">
+        <v>-117.169790033203</v>
+      </c>
+      <c r="L434" t="n">
+        <v>420.9</v>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>T on Jul 27, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070038579 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>E26070038771</t>
+        </is>
+      </c>
+      <c r="E435" s="3" t="n">
+        <v>46230.48940972222</v>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>SELENF</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>400 HOTEL CIRCLE SOUTH</t>
+        </is>
+      </c>
+      <c r="J435" t="n">
+        <v>32.761426735043</v>
+      </c>
+      <c r="K435" t="n">
+        <v>-117.168017960012</v>
+      </c>
+      <c r="L435" t="n">
+        <v>685.7</v>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>Selenf on Jul 27, 2026, 686 m from Fashion Valley (400 HOTEL CIRCLE SOUTH). Case #E26070038771 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>E26070038652</t>
+        </is>
+      </c>
+      <c r="E436" s="3" t="n">
+        <v>46230.43452546297</v>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>2000 HOTEL CIRCLE SOUTH</t>
+        </is>
+      </c>
+      <c r="J436" t="n">
+        <v>32.7596759646</v>
+      </c>
+      <c r="K436" t="n">
+        <v>-117.18005631438</v>
+      </c>
+      <c r="L436" t="n">
+        <v>1562.4</v>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>242 on Jul 27, 2026, 1562 m from Fashion Valley (2000 HOTEL CIRCLE SOUTH). Case #E26070038652 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>E26070038798</t>
+        </is>
+      </c>
+      <c r="E437" s="3" t="n">
+        <v>46230.50460648148</v>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>1300 FRAZEE RD</t>
+        </is>
+      </c>
+      <c r="J437" t="n">
+        <v>32.770934576408</v>
+      </c>
+      <c r="K437" t="n">
+        <v>-117.156318032416</v>
+      </c>
+      <c r="L437" t="n">
+        <v>994.8</v>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>T on Jul 27, 2026, 995 m from Fashion Valley (1300 FRAZEE RD). Case #E26070038798 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>E26070038757</t>
+        </is>
+      </c>
+      <c r="E438" s="3" t="n">
+        <v>46230.48212962963</v>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>7700 HAZARD CENTER DR</t>
+        </is>
+      </c>
+      <c r="J438" t="n">
+        <v>32.770935601241</v>
+      </c>
+      <c r="K438" t="n">
+        <v>-117.156166110813</v>
+      </c>
+      <c r="L438" t="n">
+        <v>1007.9</v>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>415 on Jul 27, 2026, 1008 m from Fashion Valley (7700 HAZARD CENTER DR). Case #E26070038757 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>E26070038865</t>
+        </is>
+      </c>
+      <c r="E439" s="3" t="n">
+        <v>46230.54028935185</v>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>SELENF</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>400 HOTEL CIRCLE SOUTH</t>
+        </is>
+      </c>
+      <c r="J439" t="n">
+        <v>32.761426735043</v>
+      </c>
+      <c r="K439" t="n">
+        <v>-117.168017960012</v>
+      </c>
+      <c r="L439" t="n">
+        <v>685.7</v>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>Selenf on Jul 27, 2026, 686 m from Fashion Valley (400 HOTEL CIRCLE SOUTH). Case #E26070038865 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>E26070038534</t>
+        </is>
+      </c>
+      <c r="E440" s="3" t="n">
+        <v>46230.3720949074</v>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>5150</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>300 CAMINO DE LA REINA</t>
+        </is>
+      </c>
+      <c r="J440" t="n">
+        <v>32.764468174789</v>
+      </c>
+      <c r="K440" t="n">
+        <v>-117.164515919347</v>
+      </c>
+      <c r="L440" t="n">
+        <v>354.6</v>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>5150 on Jul 27, 2026, 355 m from Fashion Valley (300 CAMINO DE LA REINA). Case #E26070038534 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>E26070039075</t>
+        </is>
+      </c>
+      <c r="E441" s="3" t="n">
+        <v>46230.65422453704</v>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>5300 MISSION CENTER RD</t>
+        </is>
+      </c>
+      <c r="J441" t="n">
+        <v>32.770666615807</v>
+      </c>
+      <c r="K441" t="n">
+        <v>-117.154875071922</v>
+      </c>
+      <c r="L441" t="n">
+        <v>1109.6</v>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>415 on Jul 27, 2026, 1110 m from Fashion Valley (5300 MISSION CENTER RD). Case #E26070039075 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>E26070039194</t>
+        </is>
+      </c>
+      <c r="E442" s="3" t="n">
+        <v>46230.71634259259</v>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>SELENF</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>7500 HAZARD CENTER DR</t>
+        </is>
+      </c>
+      <c r="J442" t="n">
+        <v>32.769886247713</v>
+      </c>
+      <c r="K442" t="n">
+        <v>-117.159316836244</v>
+      </c>
+      <c r="L442" t="n">
+        <v>691.2</v>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>Selenf on Jul 27, 2026, 691 m from Fashion Valley (7500 HAZARD CENTER DR). Case #E26070039194 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>E26070039212</t>
+        </is>
+      </c>
+      <c r="E443" s="3" t="n">
+        <v>46230.72902777778</v>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>586H</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>1400 FRAZEE RD</t>
+        </is>
+      </c>
+      <c r="J443" t="n">
+        <v>32.77262848834</v>
+      </c>
+      <c r="K443" t="n">
+        <v>-117.157489907954</v>
+      </c>
+      <c r="L443" t="n">
+        <v>993.1</v>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>586h on Jul 27, 2026, 993 m from Fashion Valley (1400 FRAZEE RD). Case #E26070039212 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>E26070038744</t>
+        </is>
+      </c>
+      <c r="E444" s="3" t="n">
+        <v>46230.47576388889</v>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>5150</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>1000 CAMINO DEL RIO SOUTH</t>
+        </is>
+      </c>
+      <c r="J444" t="n">
+        <v>32.764600731806</v>
+      </c>
+      <c r="K444" t="n">
+        <v>-117.153654844752</v>
+      </c>
+      <c r="L444" t="n">
+        <v>1201.9</v>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>5150 on Jul 27, 2026, 1202 m from Fashion Valley (1000 CAMINO DEL RIO SOUTH). Case #E26070038744 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>E26070039143</t>
+        </is>
+      </c>
+      <c r="E445" s="3" t="n">
+        <v>46230.68831018519</v>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>7600 HAZARD CENTER DR</t>
+        </is>
+      </c>
+      <c r="J445" t="n">
+        <v>32.7706559026</v>
+      </c>
+      <c r="K445" t="n">
+        <v>-117.157920375467</v>
+      </c>
+      <c r="L445" t="n">
+        <v>845.6</v>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>242 on Jul 27, 2026, 846 m from Fashion Valley (7600 HAZARD CENTER DR). Case #E26070039143 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>E26070039518</t>
+        </is>
+      </c>
+      <c r="E446" s="3" t="n">
+        <v>46230.9037962963</v>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>FD</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>700 CAMINO DE LA REINA</t>
+        </is>
+      </c>
+      <c r="J446" t="n">
+        <v>32.766967409624</v>
+      </c>
+      <c r="K446" t="n">
+        <v>-117.158325543359</v>
+      </c>
+      <c r="L446" t="n">
+        <v>726.3</v>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>Fd on Jul 27, 2026, 726 m from Fashion Valley (700 CAMINO DE LA REINA). Case #E26070039518 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>E26070039611</t>
+        </is>
+      </c>
+      <c r="E447" s="3" t="n">
+        <v>46230.97168981482</v>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>1400 HOTEL CIRCLE NORTH</t>
+        </is>
+      </c>
+      <c r="J447" t="n">
+        <v>32.760567393859</v>
+      </c>
+      <c r="K447" t="n">
+        <v>-117.172083928832</v>
+      </c>
+      <c r="L447" t="n">
+        <v>942.4</v>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>T on Jul 27, 2026, 942 m from Fashion Valley (1400 HOTEL CIRCLE NORTH). Case #E26070039611 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>E26070040084</t>
+        </is>
+      </c>
+      <c r="E448" s="3" t="n">
+        <v>46231.38797453704</v>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>5600 MISSION CENTER RD</t>
+        </is>
+      </c>
+      <c r="J448" t="n">
+        <v>32.775588244581</v>
+      </c>
+      <c r="K448" t="n">
+        <v>-117.154010732639</v>
+      </c>
+      <c r="L448" t="n">
+        <v>1451.6</v>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>415 on Jul 28, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070040084 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>E26070040104</t>
+        </is>
+      </c>
+      <c r="E449" s="3" t="n">
+        <v>46231.40006944445</v>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>7900 MISSION CENTER CT</t>
+        </is>
+      </c>
+      <c r="J449" t="n">
+        <v>32.773605548078</v>
+      </c>
+      <c r="K449" t="n">
+        <v>-117.154100182722</v>
+      </c>
+      <c r="L449" t="n">
+        <v>1317</v>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>594 on Jul 28, 2026, 1317 m from Fashion Valley (7900 MISSION CENTER CT). Case #E26070040104 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>E26070042501</t>
+        </is>
+      </c>
+      <c r="E450" s="3" t="n">
+        <v>46232.90143518519</v>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>1400 CAMINO DEL RIO SOUTH</t>
+        </is>
+      </c>
+      <c r="J450" t="n">
+        <v>32.766220038347</v>
+      </c>
+      <c r="K450" t="n">
+        <v>-117.14952431001</v>
+      </c>
+      <c r="L450" t="n">
+        <v>1553.1</v>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>1130 on Jul 29, 2026, 1553 m from Fashion Valley (1400 CAMINO DEL RIO SOUTH). Case #E26070042501 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>E26070042328</t>
+        </is>
+      </c>
+      <c r="E451" s="3" t="n">
+        <v>46232.78821759259</v>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>1151</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>7600 HAZARD CENTER DR</t>
+        </is>
+      </c>
+      <c r="J451" t="n">
+        <v>32.7706559026</v>
+      </c>
+      <c r="K451" t="n">
+        <v>-117.157920375467</v>
+      </c>
+      <c r="L451" t="n">
+        <v>845.6</v>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>1151 on Jul 29, 2026, 846 m from Fashion Valley (7600 HAZARD CENTER DR). Case #E26070042328 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>E26070035630</t>
+        </is>
+      </c>
+      <c r="E452" s="3" t="n">
+        <v>46228.36368055556</v>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>415V</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>1400 HOTEL CIRCLE NORTH</t>
+        </is>
+      </c>
+      <c r="J452" t="n">
+        <v>32.760567393859</v>
+      </c>
+      <c r="K452" t="n">
+        <v>-117.172083928832</v>
+      </c>
+      <c r="L452" t="n">
+        <v>942.4</v>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>415v on Jul 25, 2026, 942 m from Fashion Valley (1400 HOTEL CIRCLE NORTH). Case #E26070035630 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>E26070035645</t>
+        </is>
+      </c>
+      <c r="E453" s="3" t="n">
+        <v>46228.37275462963</v>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>SELENF</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>400 CAMINO DE LA REINA</t>
+        </is>
+      </c>
+      <c r="J453" t="n">
+        <v>32.765970932873</v>
+      </c>
+      <c r="K453" t="n">
+        <v>-117.163878206505</v>
+      </c>
+      <c r="L453" t="n">
+        <v>258.2</v>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>Selenf on Jul 25, 2026, 258 m from Fashion Valley (400 CAMINO DE LA REINA). Case #E26070035645 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>E26070035690</t>
+        </is>
+      </c>
+      <c r="E454" s="3" t="n">
+        <v>46228.39959490741</v>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>1400 HOTEL CIRCLE NORTH</t>
+        </is>
+      </c>
+      <c r="J454" t="n">
+        <v>32.760567393859</v>
+      </c>
+      <c r="K454" t="n">
+        <v>-117.172083928832</v>
+      </c>
+      <c r="L454" t="n">
+        <v>942.4</v>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>Cc on Jul 25, 2026, 942 m from Fashion Valley (1400 HOTEL CIRCLE NORTH). Case #E26070035690 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>E26070035833</t>
+        </is>
+      </c>
+      <c r="E455" s="3" t="n">
+        <v>46228.48918981481</v>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>7000 FRIARS RD</t>
+        </is>
+      </c>
+      <c r="J455" t="n">
+        <v>32.769515710089</v>
+      </c>
+      <c r="K455" t="n">
+        <v>-117.169790033203</v>
+      </c>
+      <c r="L455" t="n">
+        <v>420.9</v>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>597 on Jul 25, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070035833 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>E26070035857</t>
+        </is>
+      </c>
+      <c r="E456" s="3" t="n">
+        <v>46228.50023148148</v>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>10852R</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>7000 FRIARS RD</t>
+        </is>
+      </c>
+      <c r="J456" t="n">
+        <v>32.769515710089</v>
+      </c>
+      <c r="K456" t="n">
+        <v>-117.169790033203</v>
+      </c>
+      <c r="L456" t="n">
+        <v>420.9</v>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>10852r on Jul 25, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070035857 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>E26070035881</t>
+        </is>
+      </c>
+      <c r="E457" s="3" t="n">
+        <v>46228.51431712963</v>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>1151</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>2000 ULRIC ST</t>
+        </is>
+      </c>
+      <c r="J457" t="n">
+        <v>32.781040367079</v>
+      </c>
+      <c r="K457" t="n">
+        <v>-117.169519983203</v>
+      </c>
+      <c r="L457" t="n">
+        <v>1553.3</v>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>1151 on Jul 25, 2026, 1553 m from Fashion Valley (2000 ULRIC ST). Case #E26070035881 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>E26070035912</t>
+        </is>
+      </c>
+      <c r="E458" s="3" t="n">
+        <v>46228.53122685185</v>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>SELENF</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>7600 HAZARD CENTER DR</t>
+        </is>
+      </c>
+      <c r="J458" t="n">
+        <v>32.7706559026</v>
+      </c>
+      <c r="K458" t="n">
+        <v>-117.157920375467</v>
+      </c>
+      <c r="L458" t="n">
+        <v>845.6</v>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>Selenf on Jul 25, 2026, 846 m from Fashion Valley (7600 HAZARD CENTER DR). Case #E26070035912 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>E26070036003</t>
+        </is>
+      </c>
+      <c r="E459" s="3" t="n">
+        <v>46228.58616898148</v>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>415V</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>600 CAMINO DE LA REINA</t>
+        </is>
+      </c>
+      <c r="J459" t="n">
+        <v>32.766630976251</v>
+      </c>
+      <c r="K459" t="n">
+        <v>-117.159547007833</v>
+      </c>
+      <c r="L459" t="n">
+        <v>616.3</v>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>415v on Jul 25, 2026, 616 m from Fashion Valley (600 CAMINO DE LA REINA). Case #E26070036003 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>E26070036121</t>
+        </is>
+      </c>
+      <c r="E460" s="3" t="n">
+        <v>46228.63888888889</v>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>500 HOTEL CIRCLE SOUTH</t>
+        </is>
+      </c>
+      <c r="J460" t="n">
+        <v>32.761281414433</v>
+      </c>
+      <c r="K460" t="n">
+        <v>-117.168573310454</v>
+      </c>
+      <c r="L460" t="n">
+        <v>716.5</v>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>T on Jul 25, 2026, 717 m from Fashion Valley (500 HOTEL CIRCLE SOUTH). Case #E26070036121 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>E26070036160</t>
+        </is>
+      </c>
+      <c r="E461" s="3" t="n">
+        <v>46228.6652662037</v>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>800 HOTEL CIRCLE SOUTH</t>
+        </is>
+      </c>
+      <c r="J461" t="n">
+        <v>32.760837633784</v>
+      </c>
+      <c r="K461" t="n">
+        <v>-117.170557039813</v>
+      </c>
+      <c r="L461" t="n">
+        <v>838.8</v>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>T on Jul 25, 2026, 839 m from Fashion Valley (800 HOTEL CIRCLE SOUTH). Case #E26070036160 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>E26070035887</t>
+        </is>
+      </c>
+      <c r="E462" s="3" t="n">
+        <v>46228.51732638889</v>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>5150</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>700 CAMINO DE LA REINA</t>
+        </is>
+      </c>
+      <c r="J462" t="n">
+        <v>32.766967409624</v>
+      </c>
+      <c r="K462" t="n">
+        <v>-117.158325543359</v>
+      </c>
+      <c r="L462" t="n">
+        <v>726.3</v>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>5150 on Jul 25, 2026, 726 m from Fashion Valley (700 CAMINO DE LA REINA). Case #E26070035887 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>E26070036201</t>
+        </is>
+      </c>
+      <c r="E463" s="3" t="n">
+        <v>46228.68618055555</v>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>AU1171</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>2000 HOTEL CIRCLE SOUTH</t>
+        </is>
+      </c>
+      <c r="J463" t="n">
+        <v>32.7596759646</v>
+      </c>
+      <c r="K463" t="n">
+        <v>-117.18005631438</v>
+      </c>
+      <c r="L463" t="n">
+        <v>1562.4</v>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>Au1171 on Jul 25, 2026, 1562 m from Fashion Valley (2000 HOTEL CIRCLE SOUTH). Case #E26070036201 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>E26070036255</t>
+        </is>
+      </c>
+      <c r="E464" s="3" t="n">
+        <v>46228.71361111111</v>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>1500 CAMINO DE LA REINA</t>
+        </is>
+      </c>
+      <c r="J464" t="n">
+        <v>32.769985467879</v>
+      </c>
+      <c r="K464" t="n">
+        <v>-117.149965439226</v>
+      </c>
+      <c r="L464" t="n">
+        <v>1534.3</v>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>415 on Jul 25, 2026, 1534 m from Fashion Valley (1500 CAMINO DE LA REINA). Case #E26070036255 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>E26070036348</t>
+        </is>
+      </c>
+      <c r="E465" s="3" t="n">
+        <v>46228.76747685186</v>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>1900 ULRIC ST</t>
+        </is>
+      </c>
+      <c r="J465" t="n">
+        <v>32.779900409244</v>
+      </c>
+      <c r="K465" t="n">
+        <v>-117.169180382822</v>
+      </c>
+      <c r="L465" t="n">
+        <v>1422.7</v>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>T on Jul 25, 2026, 1423 m from Fashion Valley (1900 ULRIC ST). Case #E26070036348 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>E26070036465</t>
+        </is>
+      </c>
+      <c r="E466" s="3" t="n">
+        <v>46228.84383101852</v>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>SLEEPER</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>5700 MISSION CENTER RD</t>
+        </is>
+      </c>
+      <c r="J466" t="n">
+        <v>32.77719888635</v>
+      </c>
+      <c r="K466" t="n">
+        <v>-117.15461034814</v>
+      </c>
+      <c r="L466" t="n">
+        <v>1530.7</v>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>Sleeper on Jul 25, 2026, 1531 m from Fashion Valley (5700 MISSION CENTER RD). Case #E26070036465 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>E26070036550</t>
+        </is>
+      </c>
+      <c r="E467" s="3" t="n">
+        <v>46228.88915509259</v>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>415V</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>1600 CAMINO DEL RIO NORTH</t>
+        </is>
+      </c>
+      <c r="J467" t="n">
+        <v>32.766861158912</v>
+      </c>
+      <c r="K467" t="n">
+        <v>-117.151286132201</v>
+      </c>
+      <c r="L467" t="n">
+        <v>1384.3</v>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>415v on Jul 25, 2026, 1384 m from Fashion Valley (1600 CAMINO DEL RIO NORTH). Case #E26070036550 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>E26070036590</t>
+        </is>
+      </c>
+      <c r="E468" s="3" t="n">
+        <v>46228.90773148148</v>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>NARC</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>1200 FASHION VALLEY RD</t>
+        </is>
+      </c>
+      <c r="J468" t="n">
+        <v>32.76745627379</v>
+      </c>
+      <c r="K468" t="n">
+        <v>-117.171245398889</v>
+      </c>
+      <c r="L468" t="n">
+        <v>483.2</v>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>Narc on Jul 25, 2026, 483 m from Fashion Valley (1200 FASHION VALLEY RD). Case #E26070036590 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>E26070036714</t>
+        </is>
+      </c>
+      <c r="E469" s="3" t="n">
+        <v>46228.96581018518</v>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>5150</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>1000 CAMINO DEL RIO NORTH</t>
+        </is>
+      </c>
+      <c r="J469" t="n">
+        <v>32.765761445049</v>
+      </c>
+      <c r="K469" t="n">
+        <v>-117.154646736046</v>
+      </c>
+      <c r="L469" t="n">
+        <v>1083.8</v>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>5150 on Jul 25, 2026, 1084 m from Fashion Valley (1000 CAMINO DEL RIO NORTH). Case #E26070036714 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>E26070040242</t>
+        </is>
+      </c>
+      <c r="E470" s="3" t="n">
+        <v>46231.46559027778</v>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>7000 FRIARS RD</t>
+        </is>
+      </c>
+      <c r="J470" t="n">
+        <v>32.769515710089</v>
+      </c>
+      <c r="K470" t="n">
+        <v>-117.169790033203</v>
+      </c>
+      <c r="L470" t="n">
+        <v>420.9</v>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>911 on Jul 28, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070040242 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>E26070040261</t>
+        </is>
+      </c>
+      <c r="E471" s="3" t="n">
+        <v>46231.47072916666</v>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>459A</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>400 CAMINO DEL RIO SOUTH</t>
+        </is>
+      </c>
+      <c r="J471" t="n">
+        <v>32.76100095804</v>
+      </c>
+      <c r="K471" t="n">
+        <v>-117.161321780527</v>
+      </c>
+      <c r="L471" t="n">
+        <v>836.7</v>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>459a on Jul 28, 2026, 837 m from Fashion Valley (400 CAMINO DEL RIO SOUTH). Case #E26070040261 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>E26070037102</t>
+        </is>
+      </c>
+      <c r="E472" s="3" t="n">
+        <v>46229.31866898148</v>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>700 HOTEL CIRCLE SOUTH</t>
+        </is>
+      </c>
+      <c r="J472" t="n">
+        <v>32.760967849672</v>
+      </c>
+      <c r="K472" t="n">
+        <v>-117.169908508074</v>
+      </c>
+      <c r="L472" t="n">
+        <v>797.3</v>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>T on Jul 26, 2026, 797 m from Fashion Valley (700 HOTEL CIRCLE SOUTH). Case #E26070037102 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>E26070037118</t>
+        </is>
+      </c>
+      <c r="E473" s="3" t="n">
+        <v>46229.33061342593</v>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>SELENF</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>7600 HAZARD CENTER DR</t>
+        </is>
+      </c>
+      <c r="J473" t="n">
+        <v>32.7706559026</v>
+      </c>
+      <c r="K473" t="n">
+        <v>-117.157920375467</v>
+      </c>
+      <c r="L473" t="n">
+        <v>845.6</v>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>Selenf on Jul 26, 2026, 846 m from Fashion Valley (7600 HAZARD CENTER DR). Case #E26070037118 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>E26070037124</t>
+        </is>
+      </c>
+      <c r="E474" s="3" t="n">
+        <v>46229.33637731482</v>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>5600 MISSION CENTER RD</t>
+        </is>
+      </c>
+      <c r="J474" t="n">
+        <v>32.775588244581</v>
+      </c>
+      <c r="K474" t="n">
+        <v>-117.154010732639</v>
+      </c>
+      <c r="L474" t="n">
+        <v>1451.6</v>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>415 on Jul 26, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070037124 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>E26070037123</t>
+        </is>
+      </c>
+      <c r="E475" s="3" t="n">
+        <v>46229.33495370371</v>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>1149</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>7800 MISSION CENTER CT</t>
+        </is>
+      </c>
+      <c r="J475" t="n">
+        <v>32.773261251159</v>
+      </c>
+      <c r="K475" t="n">
+        <v>-117.155811054338</v>
+      </c>
+      <c r="L475" t="n">
+        <v>1161.9</v>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>1149 on Jul 26, 2026, 1162 m from Fashion Valley (7800 MISSION CENTER CT). Case #E26070037123 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>E26070037211</t>
+        </is>
+      </c>
+      <c r="E476" s="3" t="n">
+        <v>46229.39908564815</v>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>1200 FASHION VALLEY RD</t>
+        </is>
+      </c>
+      <c r="J476" t="n">
+        <v>32.76745627379</v>
+      </c>
+      <c r="K476" t="n">
+        <v>-117.171245398889</v>
+      </c>
+      <c r="L476" t="n">
+        <v>483.2</v>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>T on Jul 26, 2026, 483 m from Fashion Valley (1200 FASHION VALLEY RD). Case #E26070037211 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>E26070037314</t>
+        </is>
+      </c>
+      <c r="E477" s="3" t="n">
+        <v>46229.46476851852</v>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>SELENF</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>800 CAMINO DEL RIO NORTH</t>
+        </is>
+      </c>
+      <c r="J477" t="n">
+        <v>32.765295418344</v>
+      </c>
+      <c r="K477" t="n">
+        <v>-117.15656006511</v>
+      </c>
+      <c r="L477" t="n">
+        <v>919.5</v>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>Selenf on Jul 26, 2026, 920 m from Fashion Valley (800 CAMINO DEL RIO NORTH). Case #E26070037314 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>E26070037620</t>
+        </is>
+      </c>
+      <c r="E478" s="3" t="n">
+        <v>46229.65253472222</v>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>1200 FASHION VALLEY RD</t>
+        </is>
+      </c>
+      <c r="J478" t="n">
+        <v>32.76745627379</v>
+      </c>
+      <c r="K478" t="n">
+        <v>-117.171245398889</v>
+      </c>
+      <c r="L478" t="n">
+        <v>483.2</v>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>T on Jul 26, 2026, 483 m from Fashion Valley (1200 FASHION VALLEY RD). Case #E26070037620 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>E26070037670</t>
+        </is>
+      </c>
+      <c r="E479" s="3" t="n">
+        <v>46229.6718287037</v>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>800 HOTEL CIRCLE SOUTH</t>
+        </is>
+      </c>
+      <c r="J479" t="n">
+        <v>32.760837633784</v>
+      </c>
+      <c r="K479" t="n">
+        <v>-117.170557039813</v>
+      </c>
+      <c r="L479" t="n">
+        <v>838.8</v>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>T on Jul 26, 2026, 839 m from Fashion Valley (800 HOTEL CIRCLE SOUTH). Case #E26070037670 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>E26070037681</t>
+        </is>
+      </c>
+      <c r="E480" s="3" t="n">
+        <v>46229.67883101852</v>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>300 CAMINO DE LA REINA</t>
+        </is>
+      </c>
+      <c r="J480" t="n">
+        <v>32.764468174789</v>
+      </c>
+      <c r="K480" t="n">
+        <v>-117.164515919347</v>
+      </c>
+      <c r="L480" t="n">
+        <v>354.6</v>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>415 on Jul 26, 2026, 355 m from Fashion Valley (300 CAMINO DE LA REINA). Case #E26070037681 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>E26070037731</t>
+        </is>
+      </c>
+      <c r="E481" s="3" t="n">
+        <v>46229.71314814815</v>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>415PP</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>5700 MISSION CENTER RD</t>
+        </is>
+      </c>
+      <c r="J481" t="n">
+        <v>32.77719888635</v>
+      </c>
+      <c r="K481" t="n">
+        <v>-117.15461034814</v>
+      </c>
+      <c r="L481" t="n">
+        <v>1530.7</v>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>415pp on Jul 26, 2026, 1531 m from Fashion Valley (5700 MISSION CENTER RD). Case #E26070037731 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>E26070037911</t>
+        </is>
+      </c>
+      <c r="E482" s="3" t="n">
+        <v>46229.82662037037</v>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>11-8</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>6800 FRIARS RD</t>
+        </is>
+      </c>
+      <c r="J482" t="n">
+        <v>32.768288067315</v>
+      </c>
+      <c r="K482" t="n">
+        <v>-117.172866645828</v>
+      </c>
+      <c r="L482" t="n">
+        <v>642.8</v>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>11-8 on Jul 26, 2026, 643 m from Fashion Valley (6800 FRIARS RD). Case #E26070037911 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>E26070037537</t>
+        </is>
+      </c>
+      <c r="E483" s="3" t="n">
+        <v>46229.60693287037</v>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>415V</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>6900 FRIARS RD</t>
+        </is>
+      </c>
+      <c r="J483" t="n">
+        <v>32.768802058993</v>
+      </c>
+      <c r="K483" t="n">
+        <v>-117.171569461601</v>
+      </c>
+      <c r="L483" t="n">
+        <v>537.4</v>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>415v on Jul 26, 2026, 537 m from Fashion Valley (6900 FRIARS RD). Case #E26070037537 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>E26070038020</t>
+        </is>
+      </c>
+      <c r="E484" s="3" t="n">
+        <v>46229.89195601852</v>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>AU2</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>1900 HOTEL CIRCLE NORTH</t>
+        </is>
+      </c>
+      <c r="J484" t="n">
+        <v>32.759628968658</v>
+      </c>
+      <c r="K484" t="n">
+        <v>-117.178696371386</v>
+      </c>
+      <c r="L484" t="n">
+        <v>1460.7</v>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>Au2 on Jul 26, 2026, 1461 m from Fashion Valley (1900 HOTEL CIRCLE NORTH). Case #E26070038020 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>E26070038144</t>
+        </is>
+      </c>
+      <c r="E485" s="3" t="n">
+        <v>46229.96445601852</v>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>1200 FASHION VALLEY RD</t>
+        </is>
+      </c>
+      <c r="J485" t="n">
+        <v>32.76745627379</v>
+      </c>
+      <c r="K485" t="n">
+        <v>-117.171245398889</v>
+      </c>
+      <c r="L485" t="n">
+        <v>483.2</v>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>594 on Jul 26, 2026, 483 m from Fashion Valley (1200 FASHION VALLEY RD). Case #E26070038144 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>E26070036804</t>
+        </is>
+      </c>
+      <c r="E486" s="3" t="n">
+        <v>46229.00714120371</v>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>415PP</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>1100 CAMINO DEL RIO NORTH</t>
+        </is>
+      </c>
+      <c r="J486" t="n">
+        <v>32.766249950757</v>
+      </c>
+      <c r="K486" t="n">
+        <v>-117.154010653111</v>
+      </c>
+      <c r="L486" t="n">
+        <v>1135.3</v>
+      </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>415pp on Jul 26, 2026, 1135 m from Fashion Valley (1100 CAMINO DEL RIO NORTH). Case #E26070036804 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>E26070036910</t>
+        </is>
+      </c>
+      <c r="E487" s="3" t="n">
+        <v>46229.07847222222</v>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>1151</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>5200 MISSION CENTER RD</t>
+        </is>
+      </c>
+      <c r="J487" t="n">
+        <v>32.770034888303</v>
+      </c>
+      <c r="K487" t="n">
+        <v>-117.154657341608</v>
+      </c>
+      <c r="L487" t="n">
+        <v>1108.1</v>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>1151 on Jul 26, 2026, 1108 m from Fashion Valley (5200 MISSION CENTER RD). Case #E26070036910 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>E26070041201</t>
+        </is>
+      </c>
+      <c r="E488" s="3" t="n">
+        <v>46232.01451388889</v>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>1087</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>5700 MISSION CENTER RD</t>
+        </is>
+      </c>
+      <c r="J488" t="n">
+        <v>32.77719888635</v>
+      </c>
+      <c r="K488" t="n">
+        <v>-117.15461034814</v>
+      </c>
+      <c r="L488" t="n">
+        <v>1530.7</v>
+      </c>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>1087 on Jul 29, 2026, 1531 m from Fashion Valley (5700 MISSION CENTER RD). Case #E26070041201 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>E26070037011</t>
+        </is>
+      </c>
+      <c r="E489" s="3" t="n">
+        <v>46229.18601851852</v>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>7700 HAZARD CENTER DR</t>
+        </is>
+      </c>
+      <c r="J489" t="n">
+        <v>32.770935601241</v>
+      </c>
+      <c r="K489" t="n">
+        <v>-117.156166110813</v>
+      </c>
+      <c r="L489" t="n">
+        <v>1007.9</v>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>211 on Jul 26, 2026, 1008 m from Fashion Valley (7700 HAZARD CENTER DR). Case #E26070037011 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>E26070037808</t>
+        </is>
+      </c>
+      <c r="E490" s="3" t="n">
+        <v>46229.76173611111</v>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>7700 HAZARD CENTER DR</t>
+        </is>
+      </c>
+      <c r="J490" t="n">
+        <v>32.770935601241</v>
+      </c>
+      <c r="K490" t="n">
+        <v>-117.156166110813</v>
+      </c>
+      <c r="L490" t="n">
+        <v>1007.9</v>
+      </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>415 on Jul 26, 2026, 1008 m from Fashion Valley (7700 HAZARD CENTER DR). Case #E26070037808 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>E26070038187</t>
+        </is>
+      </c>
+      <c r="E491" s="3" t="n">
+        <v>46230.00104166667</v>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>5300 MISSION CENTER RD</t>
+        </is>
+      </c>
+      <c r="J491" t="n">
+        <v>32.770666615807</v>
+      </c>
+      <c r="K491" t="n">
+        <v>-117.154875071922</v>
+      </c>
+      <c r="L491" t="n">
+        <v>1109.6</v>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>T on Jul 27, 2026, 1110 m from Fashion Valley (5300 MISSION CENTER RD). Case #E26070038187 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>E26070038210</t>
+        </is>
+      </c>
+      <c r="E492" s="3" t="n">
+        <v>46230.02491898148</v>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>459HP</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>7000 FRIARS RD</t>
+        </is>
+      </c>
+      <c r="J492" t="n">
+        <v>32.769515710089</v>
+      </c>
+      <c r="K492" t="n">
+        <v>-117.169790033203</v>
+      </c>
+      <c r="L492" t="n">
+        <v>420.9</v>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>459hp on Jul 27, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070038210 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>E26070041846</t>
+        </is>
+      </c>
+      <c r="E493" s="3" t="n">
+        <v>46232.51957175926</v>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>459R</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>7000 FRIARS RD</t>
+        </is>
+      </c>
+      <c r="J493" t="n">
+        <v>32.769515710089</v>
+      </c>
+      <c r="K493" t="n">
+        <v>-117.169790033203</v>
+      </c>
+      <c r="L493" t="n">
+        <v>420.9</v>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>459r on Jul 29, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070041846 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>E26070041405</t>
+        </is>
+      </c>
+      <c r="E494" s="3" t="n">
+        <v>46232.29825231482</v>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>1151</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>5600 MISSION CENTER RD</t>
+        </is>
+      </c>
+      <c r="J494" t="n">
+        <v>32.775588244581</v>
+      </c>
+      <c r="K494" t="n">
+        <v>-117.154010732639</v>
+      </c>
+      <c r="L494" t="n">
+        <v>1451.6</v>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>1151 on Jul 29, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070041405 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>E26070043326</t>
+        </is>
+      </c>
+      <c r="E495" s="3" t="n">
+        <v>46233.56378472222</v>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>1200 CAMINO DEL RIO NORTH</t>
+        </is>
+      </c>
+      <c r="J495" t="n">
+        <v>32.766861158912</v>
+      </c>
+      <c r="K495" t="n">
+        <v>-117.151286132201</v>
+      </c>
+      <c r="L495" t="n">
+        <v>1384.3</v>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>415 on Jul 30, 2026, 1384 m from Fashion Valley (1200 CAMINO DEL RIO NORTH). Case #E26070043326 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>E26070043437</t>
+        </is>
+      </c>
+      <c r="E496" s="3" t="n">
+        <v>46233.62685185186</v>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>211A</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>5600 MISSION CENTER RD</t>
+        </is>
+      </c>
+      <c r="J496" t="n">
+        <v>32.775588244581</v>
+      </c>
+      <c r="K496" t="n">
+        <v>-117.154010732639</v>
+      </c>
+      <c r="L496" t="n">
+        <v>1451.6</v>
+      </c>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>211a on Jul 30, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070043437 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>E26070043442</t>
+        </is>
+      </c>
+      <c r="E497" s="3" t="n">
+        <v>46233.63097222222</v>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>CW</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>7000 FRIARS RD</t>
+        </is>
+      </c>
+      <c r="J497" t="n">
+        <v>32.769515710089</v>
+      </c>
+      <c r="K497" t="n">
+        <v>-117.169790033203</v>
+      </c>
+      <c r="L497" t="n">
+        <v>420.9</v>
+      </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>Cw on Jul 30, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070043442 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>E26070043526</t>
+        </is>
+      </c>
+      <c r="E498" s="3" t="n">
+        <v>46233.67606481481</v>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>487R</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>6900 FRIARS RD</t>
+        </is>
+      </c>
+      <c r="J498" t="n">
+        <v>32.768802058993</v>
+      </c>
+      <c r="K498" t="n">
+        <v>-117.171569461601</v>
+      </c>
+      <c r="L498" t="n">
+        <v>537.4</v>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>487r on Jul 30, 2026, 537 m from Fashion Valley (6900 FRIARS RD). Case #E26070043526 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>E26070043551</t>
+        </is>
+      </c>
+      <c r="E499" s="3" t="n">
+        <v>46233.68956018519</v>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>10851R</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>600 HOTEL CIRCLE SOUTH</t>
+        </is>
+      </c>
+      <c r="J499" t="n">
+        <v>32.761115185306</v>
+      </c>
+      <c r="K499" t="n">
+        <v>-117.169262923224</v>
+      </c>
+      <c r="L499" t="n">
+        <v>757</v>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>10851r on Jul 30, 2026, 757 m from Fashion Valley (600 HOTEL CIRCLE SOUTH). Case #E26070043551 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>E26070043602</t>
+        </is>
+      </c>
+      <c r="E500" s="3" t="n">
+        <v>46233.71741898148</v>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>1200 CAMINO DEL RIO NORTH</t>
+        </is>
+      </c>
+      <c r="J500" t="n">
+        <v>32.766861158912</v>
+      </c>
+      <c r="K500" t="n">
+        <v>-117.151286132201</v>
+      </c>
+      <c r="L500" t="n">
+        <v>1384.3</v>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>488 on Jul 30, 2026, 1384 m from Fashion Valley (1200 CAMINO DEL RIO NORTH). Case #E26070043602 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>E26070043693</t>
+        </is>
+      </c>
+      <c r="E501" s="3" t="n">
+        <v>46233.77357638889</v>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>7000 FRIARS RD</t>
+        </is>
+      </c>
+      <c r="J501" t="n">
+        <v>32.769515710089</v>
+      </c>
+      <c r="K501" t="n">
+        <v>-117.169790033203</v>
+      </c>
+      <c r="L501" t="n">
+        <v>420.9</v>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>211 on Jul 30, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070043693 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>E26070043857</t>
+        </is>
+      </c>
+      <c r="E502" s="3" t="n">
+        <v>46233.87652777778</v>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>CW</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>7000 FRIARS RD</t>
+        </is>
+      </c>
+      <c r="J502" t="n">
+        <v>32.769515710089</v>
+      </c>
+      <c r="K502" t="n">
+        <v>-117.169790033203</v>
+      </c>
+      <c r="L502" t="n">
+        <v>420.9</v>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>Cw on Jul 30, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070043857 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>E26070042725</t>
+        </is>
+      </c>
+      <c r="E503" s="3" t="n">
+        <v>46233.12034722222</v>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>500 HOTEL CIRCLE SOUTH</t>
+        </is>
+      </c>
+      <c r="J503" t="n">
+        <v>32.761281414433</v>
+      </c>
+      <c r="K503" t="n">
+        <v>-117.168573310454</v>
+      </c>
+      <c r="L503" t="n">
+        <v>716.5</v>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>415 on Jul 30, 2026, 717 m from Fashion Valley (500 HOTEL CIRCLE SOUTH). Case #E26070042725 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>E26070036092</t>
+        </is>
+      </c>
+      <c r="E504" s="3" t="n">
+        <v>46228.62349537037</v>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>594R</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>6500 FRIARS RD</t>
+        </is>
+      </c>
+      <c r="J504" t="n">
+        <v>32.766853831795</v>
+      </c>
+      <c r="K504" t="n">
+        <v>-117.177313895974</v>
+      </c>
+      <c r="L504" t="n">
+        <v>1052.1</v>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>594r on Jul 25, 2026, 1052 m from Fashion Valley (6500 FRIARS RD). Case #E26070036092 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>E26070041720</t>
+        </is>
+      </c>
+      <c r="E505" s="3" t="n">
+        <v>46232.45722222222</v>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>TARASOFF</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>400 CAMINO DEL RIO SOUTH</t>
+        </is>
+      </c>
+      <c r="J505" t="n">
+        <v>32.76100095804</v>
+      </c>
+      <c r="K505" t="n">
+        <v>-117.161321780527</v>
+      </c>
+      <c r="L505" t="n">
+        <v>836.7</v>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>Tarasoff on Jul 29, 2026, 837 m from Fashion Valley (400 CAMINO DEL RIO SOUTH). Case #E26070041720 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>E26070042696</t>
+        </is>
+      </c>
+      <c r="E506" s="3" t="n">
+        <v>46233.08091435185</v>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>10851E</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>7000 FRIARS RD</t>
+        </is>
+      </c>
+      <c r="J506" t="n">
+        <v>32.769515710089</v>
+      </c>
+      <c r="K506" t="n">
+        <v>-117.169790033203</v>
+      </c>
+      <c r="L506" t="n">
+        <v>420.9</v>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>10851e on Jul 30, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070042696 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>E26070042700</t>
+        </is>
+      </c>
+      <c r="E507" s="3" t="n">
+        <v>46233.08909722222</v>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>459A</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>5600 MISSION CENTER RD</t>
+        </is>
+      </c>
+      <c r="J507" t="n">
+        <v>32.775588244581</v>
+      </c>
+      <c r="K507" t="n">
+        <v>-117.154010732639</v>
+      </c>
+      <c r="L507" t="n">
+        <v>1451.6</v>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>459a on Jul 30, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070042700 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>E26070042703</t>
+        </is>
+      </c>
+      <c r="E508" s="3" t="n">
+        <v>46233.09315972222</v>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>1131</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>400 HOTEL CIRCLE SOUTH</t>
+        </is>
+      </c>
+      <c r="J508" t="n">
+        <v>32.761426735043</v>
+      </c>
+      <c r="K508" t="n">
+        <v>-117.168017960012</v>
+      </c>
+      <c r="L508" t="n">
+        <v>685.7</v>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>1131 on Jul 30, 2026, 686 m from Fashion Valley (400 HOTEL CIRCLE SOUTH). Case #E26070042703 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>E26070042625</t>
+        </is>
+      </c>
+      <c r="E509" s="3" t="n">
+        <v>46233.00914351852</v>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>415V</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>600 CAMINO DEL RIO SOUTH</t>
+        </is>
+      </c>
+      <c r="J509" t="n">
+        <v>32.763192918349</v>
+      </c>
+      <c r="K509" t="n">
+        <v>-117.160257283461</v>
+      </c>
+      <c r="L509" t="n">
+        <v>715.8</v>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>415v on Jul 30, 2026, 716 m from Fashion Valley (600 CAMINO DEL RIO SOUTH). Case #E26070042625 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>E26070042662</t>
+        </is>
+      </c>
+      <c r="E510" s="3" t="n">
+        <v>46233.04231481482</v>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>459A</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>5100 MISSION CENTER RD</t>
+        </is>
+      </c>
+      <c r="J510" t="n">
+        <v>32.76820380818</v>
+      </c>
+      <c r="K510" t="n">
+        <v>-117.153929083437</v>
+      </c>
+      <c r="L510" t="n">
+        <v>1139.7</v>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>459a on Jul 30, 2026, 1140 m from Fashion Valley (5100 MISSION CENTER RD). Case #E26070042662 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>E26070042356</t>
+        </is>
+      </c>
+      <c r="E511" s="3" t="n">
+        <v>46232.80671296296</v>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>20002R</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>300 CAMINO DE LA REINA</t>
+        </is>
+      </c>
+      <c r="J511" t="n">
+        <v>32.764468174789</v>
+      </c>
+      <c r="K511" t="n">
+        <v>-117.164515919347</v>
+      </c>
+      <c r="L511" t="n">
+        <v>354.6</v>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>20002r on Jul 29, 2026, 355 m from Fashion Valley (300 CAMINO DE LA REINA). Case #E26070042356 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>E26070042371</t>
+        </is>
+      </c>
+      <c r="E512" s="3" t="n">
+        <v>46232.81894675926</v>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>10851R</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>600 HOTEL CIRCLE SOUTH</t>
+        </is>
+      </c>
+      <c r="J512" t="n">
+        <v>32.761115185306</v>
+      </c>
+      <c r="K512" t="n">
+        <v>-117.169262923224</v>
+      </c>
+      <c r="L512" t="n">
+        <v>757</v>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>10851r on Jul 29, 2026, 757 m from Fashion Valley (600 HOTEL CIRCLE SOUTH). Case #E26070042371 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>E26070040323</t>
+        </is>
+      </c>
+      <c r="E513" s="3" t="n">
+        <v>46231.49828703704</v>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>CW</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>500 HOTEL CIRCLE SOUTH</t>
+        </is>
+      </c>
+      <c r="J513" t="n">
+        <v>32.761281414433</v>
+      </c>
+      <c r="K513" t="n">
+        <v>-117.168573310454</v>
+      </c>
+      <c r="L513" t="n">
+        <v>716.5</v>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>Cw on Jul 28, 2026, 717 m from Fashion Valley (500 HOTEL CIRCLE SOUTH). Case #E26070040323 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>E26070040372</t>
+        </is>
+      </c>
+      <c r="E514" s="3" t="n">
+        <v>46231.52674768519</v>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>1186</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>1500 ULRIC ST</t>
+        </is>
+      </c>
+      <c r="J514" t="n">
+        <v>32.773883020934</v>
+      </c>
+      <c r="K514" t="n">
+        <v>-117.167950263495</v>
+      </c>
+      <c r="L514" t="n">
+        <v>744.6</v>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>1186 on Jul 28, 2026, 745 m from Fashion Valley (1500 ULRIC ST). Case #E26070040372 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>E26070040385</t>
+        </is>
+      </c>
+      <c r="E515" s="3" t="n">
+        <v>46231.5353587963</v>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>415V</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>7000 FRIARS RD</t>
+        </is>
+      </c>
+      <c r="J515" t="n">
+        <v>32.769515710089</v>
+      </c>
+      <c r="K515" t="n">
+        <v>-117.169790033203</v>
+      </c>
+      <c r="L515" t="n">
+        <v>420.9</v>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>415v on Jul 28, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070040385 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>E26070040431</t>
+        </is>
+      </c>
+      <c r="E516" s="3" t="n">
+        <v>46231.55746527778</v>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>500 HOTEL CIRCLE NORTH</t>
+        </is>
+      </c>
+      <c r="J516" t="n">
+        <v>32.761281414433</v>
+      </c>
+      <c r="K516" t="n">
+        <v>-117.168573310454</v>
+      </c>
+      <c r="L516" t="n">
+        <v>716.5</v>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>911 on Jul 28, 2026, 717 m from Fashion Valley (500 HOTEL CIRCLE NORTH). Case #E26070040431 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>E26070041203</t>
+        </is>
+      </c>
+      <c r="E517" s="3" t="n">
+        <v>46232.01657407408</v>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>1800 HOTEL CIRCLE SOUTH</t>
+        </is>
+      </c>
+      <c r="J517" t="n">
+        <v>32.759597128436</v>
+      </c>
+      <c r="K517" t="n">
+        <v>-117.177340012371</v>
+      </c>
+      <c r="L517" t="n">
+        <v>1362.6</v>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>415 on Jul 29, 2026, 1363 m from Fashion Valley (1800 HOTEL CIRCLE SOUTH). Case #E26070041203 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>E26070042324</t>
+        </is>
+      </c>
+      <c r="E518" s="3" t="n">
+        <v>46232.78690972222</v>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>415V</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>1900 HOTEL CIRCLE NORTH</t>
+        </is>
+      </c>
+      <c r="J518" t="n">
+        <v>32.759628968658</v>
+      </c>
+      <c r="K518" t="n">
+        <v>-117.178696371386</v>
+      </c>
+      <c r="L518" t="n">
+        <v>1460.7</v>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>415v on Jul 29, 2026, 1461 m from Fashion Valley (1900 HOTEL CIRCLE NORTH). Case #E26070042324 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>E26070041219</t>
+        </is>
+      </c>
+      <c r="E519" s="3" t="n">
+        <v>46232.03488425926</v>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>1800 HOTEL CIRCLE SOUTH</t>
+        </is>
+      </c>
+      <c r="J519" t="n">
+        <v>32.759597128436</v>
+      </c>
+      <c r="K519" t="n">
+        <v>-117.177340012371</v>
+      </c>
+      <c r="L519" t="n">
+        <v>1362.6</v>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>415 on Jul 29, 2026, 1363 m from Fashion Valley (1800 HOTEL CIRCLE SOUTH). Case #E26070041219 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>E26070041364</t>
+        </is>
+      </c>
+      <c r="E520" s="3" t="n">
+        <v>46232.27206018518</v>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>10851E</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>7000 FRIARS RD</t>
+        </is>
+      </c>
+      <c r="J520" t="n">
+        <v>32.769515710089</v>
+      </c>
+      <c r="K520" t="n">
+        <v>-117.169790033203</v>
+      </c>
+      <c r="L520" t="n">
+        <v>420.9</v>
+      </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>10851e on Jul 29, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070041364 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>E26070041775</t>
+        </is>
+      </c>
+      <c r="E521" s="3" t="n">
+        <v>46232.48231481481</v>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>5600 MISSION CENTER RD</t>
+        </is>
+      </c>
+      <c r="J521" t="n">
+        <v>32.775588244581</v>
+      </c>
+      <c r="K521" t="n">
+        <v>-117.154010732639</v>
+      </c>
+      <c r="L521" t="n">
+        <v>1451.6</v>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>415 on Jul 29, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070041775 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>E26070041499</t>
+        </is>
+      </c>
+      <c r="E522" s="3" t="n">
+        <v>46232.35490740741</v>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>1186</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>1400 ULRIC ST</t>
+        </is>
+      </c>
+      <c r="J522" t="n">
+        <v>32.771634475997</v>
+      </c>
+      <c r="K522" t="n">
+        <v>-117.163423466353</v>
+      </c>
+      <c r="L522" t="n">
+        <v>534.8</v>
+      </c>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>1186 on Jul 29, 2026, 535 m from Fashion Valley (1400 ULRIC ST). Case #E26070041499 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>E26070041500</t>
+        </is>
+      </c>
+      <c r="E523" s="3" t="n">
+        <v>46232.35491898148</v>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>5600 MISSION CENTER RD</t>
+        </is>
+      </c>
+      <c r="J523" t="n">
+        <v>32.775588244581</v>
+      </c>
+      <c r="K523" t="n">
+        <v>-117.154010732639</v>
+      </c>
+      <c r="L523" t="n">
+        <v>1451.6</v>
+      </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>415 on Jul 29, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070041500 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>E26070041029</t>
+        </is>
+      </c>
+      <c r="E524" s="3" t="n">
+        <v>46231.88591435185</v>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>CW</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>1200 CAMINO DEL RIO NORTH</t>
+        </is>
+      </c>
+      <c r="J524" t="n">
+        <v>32.766861158912</v>
+      </c>
+      <c r="K524" t="n">
+        <v>-117.151286132201</v>
+      </c>
+      <c r="L524" t="n">
+        <v>1384.3</v>
+      </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>Cw on Jul 28, 2026, 1384 m from Fashion Valley (1200 CAMINO DEL RIO NORTH). Case #E26070041029 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>E26070041447</t>
+        </is>
+      </c>
+      <c r="E525" s="3" t="n">
+        <v>46232.32430555556</v>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>1186</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>500 CAMINO DE LA REINA</t>
+        </is>
+      </c>
+      <c r="J525" t="n">
+        <v>32.766480146474</v>
+      </c>
+      <c r="K525" t="n">
+        <v>-117.160679937637</v>
+      </c>
+      <c r="L525" t="n">
+        <v>514.5</v>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>1186 on Jul 29, 2026, 514 m from Fashion Valley (500 CAMINO DE LA REINA). Case #E26070041447 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>E26070042989</t>
+        </is>
+      </c>
+      <c r="E526" s="3" t="n">
+        <v>46233.38532407407</v>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>AU2</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>7000 FRIARS RD</t>
+        </is>
+      </c>
+      <c r="J526" t="n">
+        <v>32.769515710089</v>
+      </c>
+      <c r="K526" t="n">
+        <v>-117.169790033203</v>
+      </c>
+      <c r="L526" t="n">
+        <v>420.9</v>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>Au2 on Jul 30, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070042989 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>E26070042991</t>
+        </is>
+      </c>
+      <c r="E527" s="3" t="n">
+        <v>46233.38563657407</v>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>CW</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>1800 HOTEL CIRCLE SOUTH</t>
+        </is>
+      </c>
+      <c r="J527" t="n">
+        <v>32.759597128436</v>
+      </c>
+      <c r="K527" t="n">
+        <v>-117.177340012371</v>
+      </c>
+      <c r="L527" t="n">
+        <v>1362.6</v>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>Cw on Jul 30, 2026, 1363 m from Fashion Valley (1800 HOTEL CIRCLE SOUTH). Case #E26070042991 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>E26070043131</t>
+        </is>
+      </c>
+      <c r="E528" s="3" t="n">
+        <v>46233.46133101852</v>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>5600 MISSION CENTER RD</t>
+        </is>
+      </c>
+      <c r="J528" t="n">
+        <v>32.775588244581</v>
+      </c>
+      <c r="K528" t="n">
+        <v>-117.154010732639</v>
+      </c>
+      <c r="L528" t="n">
+        <v>1451.6</v>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>911 on Jul 30, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070043131 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>E26070043263</t>
+        </is>
+      </c>
+      <c r="E529" s="3" t="n">
+        <v>46233.52984953704</v>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>AU2</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>7900 MISSION CENTER CT</t>
+        </is>
+      </c>
+      <c r="J529" t="n">
+        <v>32.773605548078</v>
+      </c>
+      <c r="K529" t="n">
+        <v>-117.154100182722</v>
+      </c>
+      <c r="L529" t="n">
+        <v>1317</v>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>Au2 on Jul 30, 2026, 1317 m from Fashion Valley (7900 MISSION CENTER CT). Case #E26070043263 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>E26070042098</t>
+        </is>
+      </c>
+      <c r="E530" s="3" t="n">
+        <v>46232.65872685185</v>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>CW</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>700 CAMINO DEL RIO NORTH</t>
+        </is>
+      </c>
+      <c r="J530" t="n">
+        <v>32.764930802223</v>
+      </c>
+      <c r="K530" t="n">
+        <v>-117.158054620315</v>
+      </c>
+      <c r="L530" t="n">
+        <v>797.9</v>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>Cw on Jul 29, 2026, 798 m from Fashion Valley (700 CAMINO DEL RIO NORTH). Case #E26070042098 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>E26070042229</t>
+        </is>
+      </c>
+      <c r="E531" s="3" t="n">
+        <v>46232.73496527778</v>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>AU2</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>5600 MISSION CENTER RD</t>
+        </is>
+      </c>
+      <c r="J531" t="n">
+        <v>32.775588244581</v>
+      </c>
+      <c r="K531" t="n">
+        <v>-117.154010732639</v>
+      </c>
+      <c r="L531" t="n">
+        <v>1451.6</v>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>Au2 on Jul 29, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070042229 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M412"/>
+  <autoFilter ref="A1:M531"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -27313,7 +34338,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 05:17:38.206635+00:00</t>
+          <t>2026-08-01 05:21:35.478529+00:00</t>
         </is>
       </c>
     </row>
@@ -27345,7 +34370,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 05:17:38.206635+00:00</t>
+          <t>2026-07-25 05:21:35.478529+00:00</t>
         </is>
       </c>
     </row>
@@ -27356,7 +34381,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>411</v>
+        <v>530</v>
       </c>
     </row>
     <row r="7">
@@ -27701,7 +34726,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>OK fetched=5000 truncated=True</t>
+          <t>OK fetched=239 truncated=False</t>
         </is>
       </c>
     </row>

--- a/reports/2026-08-01/blotter_report.xlsx
+++ b/reports/2026-08-01/blotter_report.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$526</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$530</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1700,22 +1700,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>1490.9</v>
+        <v>264.9</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>46231.75893518519</v>
@@ -3288,7 +3288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M526"/>
+  <dimension ref="A1:M530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22271,11 +22271,11 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>262064772</t>
+          <t>262064802</t>
         </is>
       </c>
       <c r="E326" s="3" t="n">
-        <v>46230.82569444444</v>
+        <v>46230.89583333334</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -22304,7 +22304,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Larceny shoplifting on Jul 27, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064772 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny shoplifting on Jul 27, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064802 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22326,40 +22326,40 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>262064289</t>
+          <t>262064409</t>
         </is>
       </c>
       <c r="E327" s="3" t="n">
-        <v>46229.54583333333</v>
+        <v>46229.85833333333</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>LARCENY SHOPLIFTING</t>
+          <t>SICK ASSIST</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H327" t="inlineStr"/>
       <c r="I327" t="inlineStr">
         <is>
-          <t>BOYLSTON ST</t>
+          <t>OXFORD ST</t>
         </is>
       </c>
       <c r="J327" t="n">
-        <v>42.35095908794595</v>
+        <v>42.35193460488232</v>
       </c>
       <c r="K327" t="n">
-        <v>-71.07412780075079</v>
+        <v>-71.06048592223925</v>
       </c>
       <c r="L327" t="n">
-        <v>470.3</v>
+        <v>1488.7</v>
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Larceny shoplifting on Jul 26, 2026, 470 m from Copley Place (BOYLSTON ST). Case #262064289 (use for a records request — full narratives are not published in open data).</t>
+          <t>Sick assist on Jul 26, 2026, 1489 m from Copley Place (OXFORD ST). Case #262064409 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22381,40 +22381,40 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>262064298</t>
+          <t>262064318</t>
         </is>
       </c>
       <c r="E328" s="3" t="n">
-        <v>46229.08611111111</v>
+        <v>46229.53958333333</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>FIREARM/WEAPON - LOST</t>
+          <t>INVESTIGATE PERSON</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H328" t="inlineStr"/>
       <c r="I328" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>SHAWMUT AVE</t>
         </is>
       </c>
       <c r="J328" t="n">
-        <v>42.33954198983015</v>
+        <v>42.34319452771496</v>
       </c>
       <c r="K328" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.06880536524001</v>
       </c>
       <c r="L328" t="n">
-        <v>1123.7</v>
+        <v>876.3</v>
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Firearm/weapon - lost on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064298 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 26, 2026, 876 m from Copley Place (SHAWMUT AVE). Case #262064318 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22436,40 +22436,40 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>262064416</t>
+          <t>262064412</t>
         </is>
       </c>
       <c r="E329" s="3" t="n">
-        <v>46229.87569444445</v>
+        <v>46229.87638888889</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>ASSAULT - AGGRAVATED</t>
+          <t>SICK/INJURED/MEDICAL - PERSON</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>VIOLENT</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H329" t="inlineStr"/>
       <c r="I329" t="inlineStr">
         <is>
-          <t>HUNTINGTON AVE</t>
+          <t>TREMONT ST</t>
         </is>
       </c>
       <c r="J329" t="n">
-        <v>42.34221543503831</v>
+        <v>42.35428377241487</v>
       </c>
       <c r="K329" t="n">
-        <v>-71.08577074656198</v>
+        <v>-71.06380403747467</v>
       </c>
       <c r="L329" t="n">
-        <v>898.8</v>
+        <v>1356.9</v>
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Assault - aggravated on Jul 26, 2026, 899 m from Copley Place (HUNTINGTON AVE). Case #262064416 (use for a records request — full narratives are not published in open data).</t>
+          <t>Sick/injured/medical - person on Jul 26, 2026, 1357 m from Copley Place (TREMONT ST). Case #262064412 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22491,40 +22491,40 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>262064700</t>
+          <t>262064362</t>
         </is>
       </c>
       <c r="E330" s="3" t="n">
-        <v>46230.71458333333</v>
+        <v>46229.64305555556</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>BREAKING AND ENTERING (B&amp;E) MOTOR VEHICLE</t>
+          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H330" t="inlineStr"/>
       <c r="I330" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>DARTMOUTH ST</t>
         </is>
       </c>
       <c r="J330" t="n">
-        <v>42.33954198983015</v>
+        <v>42.35029374297969</v>
       </c>
       <c r="K330" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.07744671381569</v>
       </c>
       <c r="L330" t="n">
-        <v>1123.7</v>
+        <v>298.2</v>
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Breaking and entering (b&amp;e) motor vehicle on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064700 (use for a records request — full narratives are not published in open data).</t>
+          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 298 m from Copley Place (DARTMOUTH ST). Case #262064362 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22546,40 +22546,44 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>262064491</t>
+          <t>262064307</t>
         </is>
       </c>
       <c r="E331" s="3" t="n">
-        <v>46230.22916666666</v>
+        <v>46229.59027777778</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>LARCENY ALL OTHERS</t>
+          <t>SICK ASSIST</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H331" t="inlineStr"/>
       <c r="I331" t="inlineStr">
         <is>
-          <t>RUTLAND ST</t>
+          <t>TREMONT ST &amp; TEMPLE PL
+BOSTON, MA 02111
+UNITED STA</t>
         </is>
       </c>
       <c r="J331" t="n">
-        <v>42.34020387362647</v>
+        <v>42.35561100811422</v>
       </c>
       <c r="K331" t="n">
-        <v>-71.07645111113312</v>
+        <v>-71.06289400004533</v>
       </c>
       <c r="L331" t="n">
-        <v>829.8</v>
+        <v>1502.5</v>
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Larceny all others on Jul 27, 2026, 830 m from Copley Place (RUTLAND ST). Case #262064491 (use for a records request — full narratives are not published in open data).</t>
+          <t>Sick assist on Jul 26, 2026, 1502 m from Copley Place (TREMONT ST &amp; TEMPLE PL
+BOSTON, MA 02111
+UNITED STA). Case #262064307 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22601,40 +22605,40 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>262064492</t>
+          <t>262064419</t>
         </is>
       </c>
       <c r="E332" s="3" t="n">
-        <v>46230.10972222222</v>
+        <v>46229.90138888889</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>VANDALISM</t>
+          <t>HARASSMENT/ CRIMINAL HARASSMENT</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H332" t="inlineStr"/>
       <c r="I332" t="inlineStr">
         <is>
-          <t>NORTHAMPTON ST</t>
+          <t>NASSAU ST</t>
         </is>
       </c>
       <c r="J332" t="n">
-        <v>42.33798932384219</v>
+        <v>42.34880604399623</v>
       </c>
       <c r="K332" t="n">
-        <v>-71.08003745874711</v>
+        <v>-71.06285446968663</v>
       </c>
       <c r="L332" t="n">
-        <v>1088.4</v>
+        <v>1221.7</v>
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Vandalism on Jul 27, 2026, 1088 m from Copley Place (NORTHAMPTON ST). Case #262064492 (use for a records request — full narratives are not published in open data).</t>
+          <t>Harassment/ criminal harassment on Jul 26, 2026, 1222 m from Copley Place (NASSAU ST). Case #262064419 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22656,40 +22660,40 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>262064766</t>
+          <t>262064339</t>
         </is>
       </c>
       <c r="E333" s="3" t="n">
-        <v>46230.75416666667</v>
+        <v>46229.63333333333</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>PROPERTY - LOST/ MISSING</t>
+          <t>ASSAULT - AGGRAVATED</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H333" t="inlineStr"/>
       <c r="I333" t="inlineStr">
         <is>
-          <t>COLUMBUS AVE</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J333" t="n">
-        <v>42.34294800069079</v>
+        <v>42.33511903946613</v>
       </c>
       <c r="K333" t="n">
-        <v>-71.07888700104606</v>
+        <v>-71.07491709613726</v>
       </c>
       <c r="L333" t="n">
-        <v>529.1</v>
+        <v>1407.3</v>
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Property - lost/ missing on Jul 27, 2026, 529 m from Copley Place (COLUMBUS AVE). Case #262064766 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - aggravated on Jul 26, 2026, 1407 m from Copley Place (HARRISON AVE). Case #262064339 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22711,40 +22715,40 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>262064548</t>
+          <t>262064236</t>
         </is>
       </c>
       <c r="E334" s="3" t="n">
-        <v>46230.44236111111</v>
+        <v>46229.37638888889</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>M/V - LEAVING SCENE - PROPERTY DAMAGE</t>
+          <t>SICK ASSIST</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H334" t="inlineStr"/>
       <c r="I334" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>TREMONT ST</t>
         </is>
       </c>
       <c r="J334" t="n">
-        <v>42.33954198983015</v>
+        <v>42.34470135794417</v>
       </c>
       <c r="K334" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.0703760849388</v>
       </c>
       <c r="L334" t="n">
-        <v>1123.7</v>
+        <v>678.7</v>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>M/v - leaving scene - property damage on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064548 (use for a records request — full narratives are not published in open data).</t>
+          <t>Sick assist on Jul 26, 2026, 679 m from Copley Place (TREMONT ST). Case #262064236 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22766,40 +22770,40 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>262064504</t>
+          <t>262064234</t>
         </is>
       </c>
       <c r="E335" s="3" t="n">
-        <v>46230.34791666667</v>
+        <v>46229.31944444445</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>LARCENY SHOPLIFTING</t>
+          <t>INVESTIGATE PERSON</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr">
         <is>
-          <t>CHARLES ST</t>
+          <t>SAINT JAMES AVE</t>
         </is>
       </c>
       <c r="J335" t="n">
-        <v>42.36064469554803</v>
+        <v>42.34947585701249</v>
       </c>
       <c r="K335" t="n">
-        <v>-71.07086192011141</v>
+        <v>-71.07640149637847</v>
       </c>
       <c r="L335" t="n">
-        <v>1552</v>
+        <v>230.3</v>
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Larceny shoplifting on Jul 27, 2026, 1552 m from Copley Place (CHARLES ST). Case #262064504 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 26, 2026, 230 m from Copley Place (SAINT JAMES AVE). Case #262064234 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22821,20 +22825,20 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>262064506</t>
+          <t>262064772</t>
         </is>
       </c>
       <c r="E336" s="3" t="n">
-        <v>46230.34375</v>
+        <v>46230.82569444444</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>SICK ASSIST</t>
+          <t>LARCENY SHOPLIFTING</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H336" t="inlineStr"/>
@@ -22844,17 +22848,17 @@
         </is>
       </c>
       <c r="J336" t="n">
-        <v>42.35037869977646</v>
+        <v>42.34862381555496</v>
       </c>
       <c r="K336" t="n">
-        <v>-71.07626098382806</v>
+        <v>-71.08277637086411</v>
       </c>
       <c r="L336" t="n">
-        <v>327.3</v>
+        <v>437.3</v>
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Sick assist on Jul 27, 2026, 327 m from Copley Place (BOYLSTON ST). Case #262064506 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny shoplifting on Jul 27, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064772 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22876,15 +22880,15 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>262064752</t>
+          <t>262064289</t>
         </is>
       </c>
       <c r="E337" s="3" t="n">
-        <v>46230.79166666666</v>
+        <v>46229.54583333333</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>STOLEN PROPERTY - BUYING / RECEIVING / POSSESSING</t>
+          <t>LARCENY SHOPLIFTING</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -22895,21 +22899,21 @@
       <c r="H337" t="inlineStr"/>
       <c r="I337" t="inlineStr">
         <is>
-          <t>HUDSON ST</t>
+          <t>BOYLSTON ST</t>
         </is>
       </c>
       <c r="J337" t="n">
-        <v>42.35074197291232</v>
+        <v>42.35095908794595</v>
       </c>
       <c r="K337" t="n">
-        <v>-71.06006134581432</v>
+        <v>-71.07412780075079</v>
       </c>
       <c r="L337" t="n">
-        <v>1485.3</v>
+        <v>470.3</v>
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Stolen property - buying / receiving / possessing on Jul 27, 2026, 1485 m from Copley Place (HUDSON ST). Case #262064752 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny shoplifting on Jul 26, 2026, 470 m from Copley Place (BOYLSTON ST). Case #262064289 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22931,40 +22935,590 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>262064383</t>
+          <t>262064298</t>
         </is>
       </c>
       <c r="E338" s="3" t="n">
-        <v>46229.79375</v>
+        <v>46229.08611111111</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
+          <t>FIREARM/WEAPON - LOST</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H338" t="inlineStr"/>
       <c r="I338" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J338" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K338" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L338" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>Firearm/weapon - lost on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064298 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>262064416</t>
+        </is>
+      </c>
+      <c r="E339" s="3" t="n">
+        <v>46229.87569444445</v>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>ASSAULT - AGGRAVATED</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>HUNTINGTON AVE</t>
+        </is>
+      </c>
+      <c r="J339" t="n">
+        <v>42.34221543503831</v>
+      </c>
+      <c r="K339" t="n">
+        <v>-71.08577074656198</v>
+      </c>
+      <c r="L339" t="n">
+        <v>898.8</v>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>Assault - aggravated on Jul 26, 2026, 899 m from Copley Place (HUNTINGTON AVE). Case #262064416 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>262064700</t>
+        </is>
+      </c>
+      <c r="E340" s="3" t="n">
+        <v>46230.71458333333</v>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>BREAKING AND ENTERING (B&amp;E) MOTOR VEHICLE</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr"/>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J340" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K340" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L340" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>Breaking and entering (b&amp;e) motor vehicle on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064700 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>262064491</t>
+        </is>
+      </c>
+      <c r="E341" s="3" t="n">
+        <v>46230.22916666666</v>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>LARCENY ALL OTHERS</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr"/>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>RUTLAND ST</t>
+        </is>
+      </c>
+      <c r="J341" t="n">
+        <v>42.34020387362647</v>
+      </c>
+      <c r="K341" t="n">
+        <v>-71.07645111113312</v>
+      </c>
+      <c r="L341" t="n">
+        <v>829.8</v>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>Larceny all others on Jul 27, 2026, 830 m from Copley Place (RUTLAND ST). Case #262064491 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>262064492</t>
+        </is>
+      </c>
+      <c r="E342" s="3" t="n">
+        <v>46230.10972222222</v>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>VANDALISM</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr"/>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>NORTHAMPTON ST</t>
+        </is>
+      </c>
+      <c r="J342" t="n">
+        <v>42.33798932384219</v>
+      </c>
+      <c r="K342" t="n">
+        <v>-71.08003745874711</v>
+      </c>
+      <c r="L342" t="n">
+        <v>1088.4</v>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>Vandalism on Jul 27, 2026, 1088 m from Copley Place (NORTHAMPTON ST). Case #262064492 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>262064766</t>
+        </is>
+      </c>
+      <c r="E343" s="3" t="n">
+        <v>46230.75416666667</v>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>PROPERTY - LOST/ MISSING</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr"/>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>COLUMBUS AVE</t>
+        </is>
+      </c>
+      <c r="J343" t="n">
+        <v>42.34294800069079</v>
+      </c>
+      <c r="K343" t="n">
+        <v>-71.07888700104606</v>
+      </c>
+      <c r="L343" t="n">
+        <v>529.1</v>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>Property - lost/ missing on Jul 27, 2026, 529 m from Copley Place (COLUMBUS AVE). Case #262064766 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>262064548</t>
+        </is>
+      </c>
+      <c r="E344" s="3" t="n">
+        <v>46230.44236111111</v>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>M/V - LEAVING SCENE - PROPERTY DAMAGE</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J344" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K344" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L344" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>M/v - leaving scene - property damage on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064548 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>262064504</t>
+        </is>
+      </c>
+      <c r="E345" s="3" t="n">
+        <v>46230.34791666667</v>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>LARCENY SHOPLIFTING</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr"/>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>CHARLES ST</t>
+        </is>
+      </c>
+      <c r="J345" t="n">
+        <v>42.36064469554803</v>
+      </c>
+      <c r="K345" t="n">
+        <v>-71.07086192011141</v>
+      </c>
+      <c r="L345" t="n">
+        <v>1552</v>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 27, 2026, 1552 m from Copley Place (CHARLES ST). Case #262064504 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>262064506</t>
+        </is>
+      </c>
+      <c r="E346" s="3" t="n">
+        <v>46230.34375</v>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr"/>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J346" t="n">
+        <v>42.35037869977646</v>
+      </c>
+      <c r="K346" t="n">
+        <v>-71.07626098382806</v>
+      </c>
+      <c r="L346" t="n">
+        <v>327.3</v>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 27, 2026, 327 m from Copley Place (BOYLSTON ST). Case #262064506 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>262064752</t>
+        </is>
+      </c>
+      <c r="E347" s="3" t="n">
+        <v>46230.79166666666</v>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>STOLEN PROPERTY - BUYING / RECEIVING / POSSESSING</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr"/>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>HUDSON ST</t>
+        </is>
+      </c>
+      <c r="J347" t="n">
+        <v>42.35074197291232</v>
+      </c>
+      <c r="K347" t="n">
+        <v>-71.06006134581432</v>
+      </c>
+      <c r="L347" t="n">
+        <v>1485.3</v>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>Stolen property - buying / receiving / possessing on Jul 27, 2026, 1485 m from Copley Place (HUDSON ST). Case #262064752 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>262064383</t>
+        </is>
+      </c>
+      <c r="E348" s="3" t="n">
+        <v>46229.79375</v>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr"/>
+      <c r="I348" t="inlineStr">
         <is>
           <t>BOYLSTON ST &amp; DALTON ST
 BOSTON, MA 02115
 UNITED ST</t>
         </is>
       </c>
-      <c r="J338" t="n">
+      <c r="J348" t="n">
         <v>42.34787097987171</v>
       </c>
-      <c r="K338" t="n">
+      <c r="K348" t="n">
         <v>-71.08556796747074</v>
       </c>
-      <c r="L338" t="n">
+      <c r="L348" t="n">
         <v>652.7</v>
       </c>
-      <c r="M338" t="inlineStr">
+      <c r="M348" t="inlineStr">
         <is>
           <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 653 m from Copley Place (BOYLSTON ST &amp; DALTON ST
 BOSTON, MA 02115
@@ -22972,58 +23526,58 @@
         </is>
       </c>
     </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
+    <row r="349">
+      <c r="A349" t="inlineStr">
         <is>
           <t>COPLEY</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr">
+      <c r="B349" t="inlineStr">
         <is>
           <t>Copley Place</t>
         </is>
       </c>
-      <c r="C339" t="inlineStr">
+      <c r="C349" t="inlineStr">
         <is>
           <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr">
+      <c r="D349" t="inlineStr">
         <is>
           <t>262064391</t>
         </is>
       </c>
-      <c r="E339" s="3" t="n">
+      <c r="E349" s="3" t="n">
         <v>46229.83125</v>
       </c>
-      <c r="F339" t="inlineStr">
+      <c r="F349" t="inlineStr">
         <is>
           <t>DRUGS - POSSESSION/ SALE/ MANUFACTURING/ USE</t>
         </is>
       </c>
-      <c r="G339" t="inlineStr">
+      <c r="G349" t="inlineStr">
         <is>
           <t>QUALITY_OF_LIFE</t>
         </is>
       </c>
-      <c r="H339" t="inlineStr"/>
-      <c r="I339" t="inlineStr">
+      <c r="H349" t="inlineStr"/>
+      <c r="I349" t="inlineStr">
         <is>
           <t xml:space="preserve">BOYLSTON ST &amp; BOYLSTON SQ
 BOSTON, MA 02111
 UNITED </t>
         </is>
       </c>
-      <c r="J339" t="n">
+      <c r="J349" t="n">
         <v>42.35231098936428</v>
       </c>
-      <c r="K339" t="n">
+      <c r="K349" t="n">
         <v>-71.06350996526169</v>
       </c>
-      <c r="L339" t="n">
+      <c r="L349" t="n">
         <v>1272.6</v>
       </c>
-      <c r="M339" t="inlineStr">
+      <c r="M349" t="inlineStr">
         <is>
           <t>Drugs - possession/ sale/ manufacturing/ use on Jul 26, 2026, 1273 m from Copley Place (BOYLSTON ST &amp; BOYLSTON SQ
 BOSTON, MA 02111
@@ -23031,560 +23585,6 @@
         </is>
       </c>
     </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>262064802</t>
-        </is>
-      </c>
-      <c r="E340" s="3" t="n">
-        <v>46230.89583333334</v>
-      </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>LARCENY SHOPLIFTING</t>
-        </is>
-      </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H340" t="inlineStr"/>
-      <c r="I340" t="inlineStr">
-        <is>
-          <t>BOYLSTON ST</t>
-        </is>
-      </c>
-      <c r="J340" t="n">
-        <v>42.34862381555496</v>
-      </c>
-      <c r="K340" t="n">
-        <v>-71.08277637086411</v>
-      </c>
-      <c r="L340" t="n">
-        <v>437.3</v>
-      </c>
-      <c r="M340" t="inlineStr">
-        <is>
-          <t>Larceny shoplifting on Jul 27, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064802 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>262064409</t>
-        </is>
-      </c>
-      <c r="E341" s="3" t="n">
-        <v>46229.85833333333</v>
-      </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>SICK ASSIST</t>
-        </is>
-      </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H341" t="inlineStr"/>
-      <c r="I341" t="inlineStr">
-        <is>
-          <t>OXFORD ST</t>
-        </is>
-      </c>
-      <c r="J341" t="n">
-        <v>42.35193460488232</v>
-      </c>
-      <c r="K341" t="n">
-        <v>-71.06048592223925</v>
-      </c>
-      <c r="L341" t="n">
-        <v>1488.7</v>
-      </c>
-      <c r="M341" t="inlineStr">
-        <is>
-          <t>Sick assist on Jul 26, 2026, 1489 m from Copley Place (OXFORD ST). Case #262064409 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>262064318</t>
-        </is>
-      </c>
-      <c r="E342" s="3" t="n">
-        <v>46229.53958333333</v>
-      </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>INVESTIGATE PERSON</t>
-        </is>
-      </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H342" t="inlineStr"/>
-      <c r="I342" t="inlineStr">
-        <is>
-          <t>SHAWMUT AVE</t>
-        </is>
-      </c>
-      <c r="J342" t="n">
-        <v>42.34319452771496</v>
-      </c>
-      <c r="K342" t="n">
-        <v>-71.06880536524001</v>
-      </c>
-      <c r="L342" t="n">
-        <v>876.3</v>
-      </c>
-      <c r="M342" t="inlineStr">
-        <is>
-          <t>Investigate person on Jul 26, 2026, 876 m from Copley Place (SHAWMUT AVE). Case #262064318 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>262064412</t>
-        </is>
-      </c>
-      <c r="E343" s="3" t="n">
-        <v>46229.87638888889</v>
-      </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>SICK/INJURED/MEDICAL - PERSON</t>
-        </is>
-      </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H343" t="inlineStr"/>
-      <c r="I343" t="inlineStr">
-        <is>
-          <t>TREMONT ST</t>
-        </is>
-      </c>
-      <c r="J343" t="n">
-        <v>42.35428377241487</v>
-      </c>
-      <c r="K343" t="n">
-        <v>-71.06380403747467</v>
-      </c>
-      <c r="L343" t="n">
-        <v>1356.9</v>
-      </c>
-      <c r="M343" t="inlineStr">
-        <is>
-          <t>Sick/injured/medical - person on Jul 26, 2026, 1357 m from Copley Place (TREMONT ST). Case #262064412 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>262064362</t>
-        </is>
-      </c>
-      <c r="E344" s="3" t="n">
-        <v>46229.64305555556</v>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
-        </is>
-      </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H344" t="inlineStr"/>
-      <c r="I344" t="inlineStr">
-        <is>
-          <t>DARTMOUTH ST</t>
-        </is>
-      </c>
-      <c r="J344" t="n">
-        <v>42.35029374297969</v>
-      </c>
-      <c r="K344" t="n">
-        <v>-71.07744671381569</v>
-      </c>
-      <c r="L344" t="n">
-        <v>298.2</v>
-      </c>
-      <c r="M344" t="inlineStr">
-        <is>
-          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 298 m from Copley Place (DARTMOUTH ST). Case #262064362 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>262064307</t>
-        </is>
-      </c>
-      <c r="E345" s="3" t="n">
-        <v>46229.59027777778</v>
-      </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>SICK ASSIST</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H345" t="inlineStr"/>
-      <c r="I345" t="inlineStr">
-        <is>
-          <t>TREMONT ST &amp; TEMPLE PL
-BOSTON, MA 02111
-UNITED STA</t>
-        </is>
-      </c>
-      <c r="J345" t="n">
-        <v>42.35561100811422</v>
-      </c>
-      <c r="K345" t="n">
-        <v>-71.06289400004533</v>
-      </c>
-      <c r="L345" t="n">
-        <v>1502.5</v>
-      </c>
-      <c r="M345" t="inlineStr">
-        <is>
-          <t>Sick assist on Jul 26, 2026, 1502 m from Copley Place (TREMONT ST &amp; TEMPLE PL
-BOSTON, MA 02111
-UNITED STA). Case #262064307 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>262064419</t>
-        </is>
-      </c>
-      <c r="E346" s="3" t="n">
-        <v>46229.90138888889</v>
-      </c>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>HARASSMENT/ CRIMINAL HARASSMENT</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H346" t="inlineStr"/>
-      <c r="I346" t="inlineStr">
-        <is>
-          <t>NASSAU ST</t>
-        </is>
-      </c>
-      <c r="J346" t="n">
-        <v>42.34880604399623</v>
-      </c>
-      <c r="K346" t="n">
-        <v>-71.06285446968663</v>
-      </c>
-      <c r="L346" t="n">
-        <v>1221.7</v>
-      </c>
-      <c r="M346" t="inlineStr">
-        <is>
-          <t>Harassment/ criminal harassment on Jul 26, 2026, 1222 m from Copley Place (NASSAU ST). Case #262064419 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>262064339</t>
-        </is>
-      </c>
-      <c r="E347" s="3" t="n">
-        <v>46229.63333333333</v>
-      </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>ASSAULT - AGGRAVATED</t>
-        </is>
-      </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H347" t="inlineStr"/>
-      <c r="I347" t="inlineStr">
-        <is>
-          <t>HARRISON AVE</t>
-        </is>
-      </c>
-      <c r="J347" t="n">
-        <v>42.33511903946613</v>
-      </c>
-      <c r="K347" t="n">
-        <v>-71.07491709613726</v>
-      </c>
-      <c r="L347" t="n">
-        <v>1407.3</v>
-      </c>
-      <c r="M347" t="inlineStr">
-        <is>
-          <t>Assault - aggravated on Jul 26, 2026, 1407 m from Copley Place (HARRISON AVE). Case #262064339 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>262064236</t>
-        </is>
-      </c>
-      <c r="E348" s="3" t="n">
-        <v>46229.37638888889</v>
-      </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>SICK ASSIST</t>
-        </is>
-      </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H348" t="inlineStr"/>
-      <c r="I348" t="inlineStr">
-        <is>
-          <t>TREMONT ST</t>
-        </is>
-      </c>
-      <c r="J348" t="n">
-        <v>42.34470135794417</v>
-      </c>
-      <c r="K348" t="n">
-        <v>-71.0703760849388</v>
-      </c>
-      <c r="L348" t="n">
-        <v>678.7</v>
-      </c>
-      <c r="M348" t="inlineStr">
-        <is>
-          <t>Sick assist on Jul 26, 2026, 679 m from Copley Place (TREMONT ST). Case #262064236 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>262064234</t>
-        </is>
-      </c>
-      <c r="E349" s="3" t="n">
-        <v>46229.31944444445</v>
-      </c>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>INVESTIGATE PERSON</t>
-        </is>
-      </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H349" t="inlineStr"/>
-      <c r="I349" t="inlineStr">
-        <is>
-          <t>SAINT JAMES AVE</t>
-        </is>
-      </c>
-      <c r="J349" t="n">
-        <v>42.34947585701249</v>
-      </c>
-      <c r="K349" t="n">
-        <v>-71.07640149637847</v>
-      </c>
-      <c r="L349" t="n">
-        <v>230.3</v>
-      </c>
-      <c r="M349" t="inlineStr">
-        <is>
-          <t>Investigate person on Jul 26, 2026, 230 m from Copley Place (SAINT JAMES AVE). Case #262064234 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
@@ -27470,89 +27470,89 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>FASHIONVAL</t>
+          <t>WAIKELE</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Fashion Valley</t>
+          <t>Waikele Premium Outlets</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+          <t>WAIKELE:vg88-5rn5</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>E26070037781</t>
+          <t>260726-0780</t>
         </is>
       </c>
       <c r="E416" s="3" t="n">
-        <v>46229.7440625</v>
+        <v>46229.53611111111</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>594R</t>
+          <t>THEFT/LARCENY</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>7000 FRIARS RD</t>
+          <t>940800 BLOCK LUMIAINA ST</t>
         </is>
       </c>
       <c r="J416" t="n">
-        <v>32.769515710089</v>
+        <v>21.400167140425</v>
       </c>
       <c r="K416" t="n">
-        <v>-117.169790033203</v>
+        <v>-158.005339738746</v>
       </c>
       <c r="L416" t="n">
-        <v>420.9</v>
+        <v>264.9</v>
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>594r on Jul 26, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070037781 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft/larceny on Jul 26, 2026, 265 m from Waikele Premium Outlets (940800 BLOCK LUMIAINA ST). Case #260726-0780 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>FASHIONVAL</t>
+          <t>WAIKELE</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Fashion Valley</t>
+          <t>Waikele Premium Outlets</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+          <t>WAIKELE:vg88-5rn5</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>E26070041113</t>
+          <t>260725-1681</t>
         </is>
       </c>
       <c r="E417" s="3" t="n">
-        <v>46231.94868055556</v>
+        <v>46228.97038194445</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>10851R</t>
+          <t>SEX CRIMES</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
@@ -27562,144 +27562,144 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>7500 HAZARD CENTER DR</t>
+          <t>940700 BLOCK LUMIAINA ST</t>
         </is>
       </c>
       <c r="J417" t="n">
-        <v>32.769886247713</v>
+        <v>21.401066137496</v>
       </c>
       <c r="K417" t="n">
-        <v>-117.159316836244</v>
+        <v>-158.009247892963</v>
       </c>
       <c r="L417" t="n">
-        <v>691.2</v>
+        <v>280.2</v>
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>10851r on Jul 28, 2026, 691 m from Fashion Valley (7500 HAZARD CENTER DR). Case #E26070041113 (use for a records request — full narratives are not published in open data).</t>
+          <t>Sex crimes on Jul 25, 2026, 280 m from Waikele Premium Outlets (940700 BLOCK LUMIAINA ST). Case #260725-1681 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>FASHIONVAL</t>
+          <t>WAIKELE</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Fashion Valley</t>
+          <t>Waikele Premium Outlets</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+          <t>WAIKELE:vg88-5rn5</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>E26070041890</t>
+          <t>260725-1382</t>
         </is>
       </c>
       <c r="E418" s="3" t="n">
-        <v>46232.53804398148</v>
+        <v>46228.8299537037</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>AU23103</t>
+          <t>THEFT/LARCENY</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>6900 FRIARS RD</t>
+          <t>940700 BLOCK LUMIAINA ST</t>
         </is>
       </c>
       <c r="J418" t="n">
-        <v>32.768802058993</v>
+        <v>21.401066137496</v>
       </c>
       <c r="K418" t="n">
-        <v>-117.171569461601</v>
+        <v>-158.009247892963</v>
       </c>
       <c r="L418" t="n">
-        <v>537.4</v>
+        <v>280.2</v>
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Au23103 on Jul 29, 2026, 537 m from Fashion Valley (6900 FRIARS RD). Case #E26070041890 (use for a records request — full narratives are not published in open data).</t>
+          <t>Theft/larceny on Jul 25, 2026, 280 m from Waikele Premium Outlets (940700 BLOCK LUMIAINA ST). Case #260725-1382 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>FASHIONVAL</t>
+          <t>WAIKELE</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Fashion Valley</t>
+          <t>Waikele Premium Outlets</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+          <t>WAIKELE:vg88-5rn5</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>E26070041760</t>
+          <t>260725-1296</t>
         </is>
       </c>
       <c r="E419" s="3" t="n">
-        <v>46232.47642361111</v>
+        <v>46228.78523148148</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>10851RR</t>
+          <t>VANDALISM</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>900 CAMINO DEL RIO SOUTH</t>
+          <t>940500 BLOCK LUMIAINA ST</t>
         </is>
       </c>
       <c r="J419" t="n">
-        <v>32.764297296186</v>
+        <v>21.394760337276</v>
       </c>
       <c r="K419" t="n">
-        <v>-117.154654014114</v>
+        <v>-158.014381845775</v>
       </c>
       <c r="L419" t="n">
-        <v>1121.7</v>
+        <v>1135.1</v>
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>10851rr on Jul 29, 2026, 1122 m from Fashion Valley (900 CAMINO DEL RIO SOUTH). Case #E26070041760 (use for a records request — full narratives are not published in open data).</t>
+          <t>Vandalism on Jul 25, 2026, 1135 m from Waikele Premium Outlets (940500 BLOCK LUMIAINA ST). Case #260725-1296 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -27721,15 +27721,15 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>E26070040752</t>
+          <t>E26070037781</t>
         </is>
       </c>
       <c r="E420" s="3" t="n">
-        <v>46231.73775462963</v>
+        <v>46229.7440625</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>594R</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
@@ -27739,26 +27739,26 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>K</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>1100 CAMINO DE LA REINA</t>
+          <t>7000 FRIARS RD</t>
         </is>
       </c>
       <c r="J420" t="n">
-        <v>32.768503746841</v>
+        <v>32.769515710089</v>
       </c>
       <c r="K420" t="n">
-        <v>-117.152853070724</v>
+        <v>-117.169790033203</v>
       </c>
       <c r="L420" t="n">
-        <v>1242.9</v>
+        <v>420.9</v>
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>T on Jul 28, 2026, 1243 m from Fashion Valley (1100 CAMINO DE LA REINA). Case #E26070040752 (use for a records request — full narratives are not published in open data).</t>
+          <t>594r on Jul 26, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070037781 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -27780,15 +27780,15 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>E26070040776</t>
+          <t>E26070041113</t>
         </is>
       </c>
       <c r="E421" s="3" t="n">
-        <v>46231.74665509259</v>
+        <v>46231.94868055556</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>10851R</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
@@ -27798,26 +27798,26 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>1800 HOTEL CIRCLE SOUTH</t>
+          <t>7500 HAZARD CENTER DR</t>
         </is>
       </c>
       <c r="J421" t="n">
-        <v>32.759597128436</v>
+        <v>32.769886247713</v>
       </c>
       <c r="K421" t="n">
-        <v>-117.177340012371</v>
+        <v>-117.159316836244</v>
       </c>
       <c r="L421" t="n">
-        <v>1362.6</v>
+        <v>691.2</v>
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>415 on Jul 28, 2026, 1363 m from Fashion Valley (1800 HOTEL CIRCLE SOUTH). Case #E26070040776 (use for a records request — full narratives are not published in open data).</t>
+          <t>10851r on Jul 28, 2026, 691 m from Fashion Valley (7500 HAZARD CENTER DR). Case #E26070041113 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -27839,15 +27839,15 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>E26070040789</t>
+          <t>E26070041890</t>
         </is>
       </c>
       <c r="E422" s="3" t="n">
-        <v>46231.75309027778</v>
+        <v>46232.53804398148</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>AU23103</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
@@ -27857,26 +27857,26 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>7700 HAZARD CENTER DR</t>
+          <t>6900 FRIARS RD</t>
         </is>
       </c>
       <c r="J422" t="n">
-        <v>32.770935601241</v>
+        <v>32.768802058993</v>
       </c>
       <c r="K422" t="n">
-        <v>-117.156166110813</v>
+        <v>-117.171569461601</v>
       </c>
       <c r="L422" t="n">
-        <v>1007.9</v>
+        <v>537.4</v>
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>245 on Jul 28, 2026, 1008 m from Fashion Valley (7700 HAZARD CENTER DR). Case #E26070040789 (use for a records request — full narratives are not published in open data).</t>
+          <t>Au23103 on Jul 29, 2026, 537 m from Fashion Valley (6900 FRIARS RD). Case #E26070041890 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -27898,15 +27898,15 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>E26070040831</t>
+          <t>E26070041760</t>
         </is>
       </c>
       <c r="E423" s="3" t="n">
-        <v>46231.77418981482</v>
+        <v>46232.47642361111</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>10851RR</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
@@ -27916,26 +27916,26 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>800 HOTEL CIRCLE SOUTH</t>
+          <t>900 CAMINO DEL RIO SOUTH</t>
         </is>
       </c>
       <c r="J423" t="n">
-        <v>32.760837633784</v>
+        <v>32.764297296186</v>
       </c>
       <c r="K423" t="n">
-        <v>-117.170557039813</v>
+        <v>-117.154654014114</v>
       </c>
       <c r="L423" t="n">
-        <v>838.8</v>
+        <v>1121.7</v>
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>911 on Jul 28, 2026, 839 m from Fashion Valley (800 HOTEL CIRCLE SOUTH). Case #E26070040831 (use for a records request — full narratives are not published in open data).</t>
+          <t>10851rr on Jul 29, 2026, 1122 m from Fashion Valley (900 CAMINO DEL RIO SOUTH). Case #E26070041760 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -27957,15 +27957,15 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>E26070040857</t>
+          <t>E26070040752</t>
         </is>
       </c>
       <c r="E424" s="3" t="n">
-        <v>46231.78961805555</v>
+        <v>46231.73775462963</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
@@ -27975,26 +27975,26 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>1200 CAMINO DEL RIO NORTH</t>
+          <t>1100 CAMINO DE LA REINA</t>
         </is>
       </c>
       <c r="J424" t="n">
-        <v>32.766861158912</v>
+        <v>32.768503746841</v>
       </c>
       <c r="K424" t="n">
-        <v>-117.151286132201</v>
+        <v>-117.152853070724</v>
       </c>
       <c r="L424" t="n">
-        <v>1384.3</v>
+        <v>1242.9</v>
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>211 on Jul 28, 2026, 1384 m from Fashion Valley (1200 CAMINO DEL RIO NORTH). Case #E26070040857 (use for a records request — full narratives are not published in open data).</t>
+          <t>T on Jul 28, 2026, 1243 m from Fashion Valley (1100 CAMINO DE LA REINA). Case #E26070040752 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -28016,15 +28016,15 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>E26070040991</t>
+          <t>E26070040776</t>
         </is>
       </c>
       <c r="E425" s="3" t="n">
-        <v>46231.86539351852</v>
+        <v>46231.74665509259</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>1140OD</t>
+          <t>415</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
@@ -28039,21 +28039,21 @@
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>600 HOTEL CIRCLE SOUTH</t>
+          <t>1800 HOTEL CIRCLE SOUTH</t>
         </is>
       </c>
       <c r="J425" t="n">
-        <v>32.761115185306</v>
+        <v>32.759597128436</v>
       </c>
       <c r="K425" t="n">
-        <v>-117.169262923224</v>
+        <v>-117.177340012371</v>
       </c>
       <c r="L425" t="n">
-        <v>757</v>
+        <v>1362.6</v>
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>1140od on Jul 28, 2026, 757 m from Fashion Valley (600 HOTEL CIRCLE SOUTH). Case #E26070040991 (use for a records request — full narratives are not published in open data).</t>
+          <t>415 on Jul 28, 2026, 1363 m from Fashion Valley (1800 HOTEL CIRCLE SOUTH). Case #E26070040776 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -28075,15 +28075,15 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>E26070041000</t>
+          <t>E26070040789</t>
         </is>
       </c>
       <c r="E426" s="3" t="n">
-        <v>46231.87225694444</v>
+        <v>46231.75309027778</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>459A</t>
+          <t>245</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
@@ -28093,26 +28093,26 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>7000 FRIARS RD</t>
+          <t>7700 HAZARD CENTER DR</t>
         </is>
       </c>
       <c r="J426" t="n">
-        <v>32.769515710089</v>
+        <v>32.770935601241</v>
       </c>
       <c r="K426" t="n">
-        <v>-117.169790033203</v>
+        <v>-117.156166110813</v>
       </c>
       <c r="L426" t="n">
-        <v>420.9</v>
+        <v>1007.9</v>
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>459a on Jul 28, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070041000 (use for a records request — full narratives are not published in open data).</t>
+          <t>245 on Jul 28, 2026, 1008 m from Fashion Valley (7700 HAZARD CENTER DR). Case #E26070040789 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -28134,15 +28134,15 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>E26070039356</t>
+          <t>E26070040831</t>
         </is>
       </c>
       <c r="E427" s="3" t="n">
-        <v>46230.81408564815</v>
+        <v>46231.77418981482</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>10851R</t>
+          <t>911</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
@@ -28152,26 +28152,26 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>900 CAMINO DEL RIO SOUTH</t>
+          <t>800 HOTEL CIRCLE SOUTH</t>
         </is>
       </c>
       <c r="J427" t="n">
-        <v>32.764297296186</v>
+        <v>32.760837633784</v>
       </c>
       <c r="K427" t="n">
-        <v>-117.154654014114</v>
+        <v>-117.170557039813</v>
       </c>
       <c r="L427" t="n">
-        <v>1121.7</v>
+        <v>838.8</v>
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>10851r on Jul 27, 2026, 1122 m from Fashion Valley (900 CAMINO DEL RIO SOUTH). Case #E26070039356 (use for a records request — full narratives are not published in open data).</t>
+          <t>911 on Jul 28, 2026, 839 m from Fashion Valley (800 HOTEL CIRCLE SOUTH). Case #E26070040831 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -28193,15 +28193,15 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>E26070039761</t>
+          <t>E26070040857</t>
         </is>
       </c>
       <c r="E428" s="3" t="n">
-        <v>46231.1196412037</v>
+        <v>46231.78961805555</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>10852C</t>
+          <t>211</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
@@ -28216,21 +28216,21 @@
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>300 CAMINO DE LA REINA</t>
+          <t>1200 CAMINO DEL RIO NORTH</t>
         </is>
       </c>
       <c r="J428" t="n">
-        <v>32.764468174789</v>
+        <v>32.766861158912</v>
       </c>
       <c r="K428" t="n">
-        <v>-117.164515919347</v>
+        <v>-117.151286132201</v>
       </c>
       <c r="L428" t="n">
-        <v>354.6</v>
+        <v>1384.3</v>
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>10852c on Jul 28, 2026, 355 m from Fashion Valley (300 CAMINO DE LA REINA). Case #E26070039761 (use for a records request — full narratives are not published in open data).</t>
+          <t>211 on Jul 28, 2026, 1384 m from Fashion Valley (1200 CAMINO DEL RIO NORTH). Case #E26070040857 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -28252,15 +28252,15 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>E26070041298</t>
+          <t>E26070040991</t>
         </is>
       </c>
       <c r="E429" s="3" t="n">
-        <v>46232.13975694445</v>
+        <v>46231.86539351852</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>488R</t>
+          <t>1140OD</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
@@ -28275,21 +28275,21 @@
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>7400 HAZARD CENTER DR</t>
+          <t>600 HOTEL CIRCLE SOUTH</t>
         </is>
       </c>
       <c r="J429" t="n">
-        <v>32.76831582062</v>
+        <v>32.761115185306</v>
       </c>
       <c r="K429" t="n">
-        <v>-117.161380632533</v>
+        <v>-117.169262923224</v>
       </c>
       <c r="L429" t="n">
-        <v>451.6</v>
+        <v>757</v>
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>488r on Jul 29, 2026, 452 m from Fashion Valley (7400 HAZARD CENTER DR). Case #E26070041298 (use for a records request — full narratives are not published in open data).</t>
+          <t>1140od on Jul 28, 2026, 757 m from Fashion Valley (600 HOTEL CIRCLE SOUTH). Case #E26070040991 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -28311,15 +28311,15 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>E26070041301</t>
+          <t>E26070041000</t>
         </is>
       </c>
       <c r="E430" s="3" t="n">
-        <v>46232.14467592593</v>
+        <v>46231.87225694444</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>AU1171</t>
+          <t>459A</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
@@ -28329,26 +28329,26 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>6800 FRIARS RD</t>
+          <t>7000 FRIARS RD</t>
         </is>
       </c>
       <c r="J430" t="n">
-        <v>32.768288067315</v>
+        <v>32.769515710089</v>
       </c>
       <c r="K430" t="n">
-        <v>-117.172866645828</v>
+        <v>-117.169790033203</v>
       </c>
       <c r="L430" t="n">
-        <v>642.8</v>
+        <v>420.9</v>
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Au1171 on Jul 29, 2026, 643 m from Fashion Valley (6800 FRIARS RD). Case #E26070041301 (use for a records request — full narratives are not published in open data).</t>
+          <t>459a on Jul 28, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070041000 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -28370,15 +28370,15 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>E26070042450</t>
+          <t>E26070039356</t>
         </is>
       </c>
       <c r="E431" s="3" t="n">
-        <v>46232.87263888889</v>
+        <v>46230.81408564815</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>10851R</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
@@ -28393,21 +28393,21 @@
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>1800 HOTEL CIRCLE SOUTH</t>
+          <t>900 CAMINO DEL RIO SOUTH</t>
         </is>
       </c>
       <c r="J431" t="n">
-        <v>32.759597128436</v>
+        <v>32.764297296186</v>
       </c>
       <c r="K431" t="n">
-        <v>-117.177340012371</v>
+        <v>-117.154654014114</v>
       </c>
       <c r="L431" t="n">
-        <v>1362.6</v>
+        <v>1121.7</v>
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>1131 on Jul 29, 2026, 1363 m from Fashion Valley (1800 HOTEL CIRCLE SOUTH). Case #E26070042450 (use for a records request — full narratives are not published in open data).</t>
+          <t>10851r on Jul 27, 2026, 1122 m from Fashion Valley (900 CAMINO DEL RIO SOUTH). Case #E26070039356 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -28429,15 +28429,15 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>E26070038579</t>
+          <t>E26070039761</t>
         </is>
       </c>
       <c r="E432" s="3" t="n">
-        <v>46230.39099537037</v>
+        <v>46231.1196412037</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>10852C</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
@@ -28452,21 +28452,21 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>7000 FRIARS RD</t>
+          <t>300 CAMINO DE LA REINA</t>
         </is>
       </c>
       <c r="J432" t="n">
-        <v>32.769515710089</v>
+        <v>32.764468174789</v>
       </c>
       <c r="K432" t="n">
-        <v>-117.169790033203</v>
+        <v>-117.164515919347</v>
       </c>
       <c r="L432" t="n">
-        <v>420.9</v>
+        <v>354.6</v>
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>T on Jul 27, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070038579 (use for a records request — full narratives are not published in open data).</t>
+          <t>10852c on Jul 28, 2026, 355 m from Fashion Valley (300 CAMINO DE LA REINA). Case #E26070039761 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -28488,15 +28488,15 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>E26070038771</t>
+          <t>E26070041298</t>
         </is>
       </c>
       <c r="E433" s="3" t="n">
-        <v>46230.48940972222</v>
+        <v>46232.13975694445</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>SELENF</t>
+          <t>488R</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
@@ -28511,21 +28511,21 @@
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>400 HOTEL CIRCLE SOUTH</t>
+          <t>7400 HAZARD CENTER DR</t>
         </is>
       </c>
       <c r="J433" t="n">
-        <v>32.761426735043</v>
+        <v>32.76831582062</v>
       </c>
       <c r="K433" t="n">
-        <v>-117.168017960012</v>
+        <v>-117.161380632533</v>
       </c>
       <c r="L433" t="n">
-        <v>685.7</v>
+        <v>451.6</v>
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Selenf on Jul 27, 2026, 686 m from Fashion Valley (400 HOTEL CIRCLE SOUTH). Case #E26070038771 (use for a records request — full narratives are not published in open data).</t>
+          <t>488r on Jul 29, 2026, 452 m from Fashion Valley (7400 HAZARD CENTER DR). Case #E26070041298 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -28547,15 +28547,15 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>E26070038652</t>
+          <t>E26070041301</t>
         </is>
       </c>
       <c r="E434" s="3" t="n">
-        <v>46230.43452546297</v>
+        <v>46232.14467592593</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>AU1171</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
@@ -28570,21 +28570,21 @@
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>2000 HOTEL CIRCLE SOUTH</t>
+          <t>6800 FRIARS RD</t>
         </is>
       </c>
       <c r="J434" t="n">
-        <v>32.7596759646</v>
+        <v>32.768288067315</v>
       </c>
       <c r="K434" t="n">
-        <v>-117.18005631438</v>
+        <v>-117.172866645828</v>
       </c>
       <c r="L434" t="n">
-        <v>1562.4</v>
+        <v>642.8</v>
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>242 on Jul 27, 2026, 1562 m from Fashion Valley (2000 HOTEL CIRCLE SOUTH). Case #E26070038652 (use for a records request — full narratives are not published in open data).</t>
+          <t>Au1171 on Jul 29, 2026, 643 m from Fashion Valley (6800 FRIARS RD). Case #E26070041301 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -28606,15 +28606,15 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>E26070038798</t>
+          <t>E26070042450</t>
         </is>
       </c>
       <c r="E435" s="3" t="n">
-        <v>46230.50460648148</v>
+        <v>46232.87263888889</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
@@ -28624,26 +28624,26 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>K</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>1300 FRAZEE RD</t>
+          <t>1800 HOTEL CIRCLE SOUTH</t>
         </is>
       </c>
       <c r="J435" t="n">
-        <v>32.770934576408</v>
+        <v>32.759597128436</v>
       </c>
       <c r="K435" t="n">
-        <v>-117.156318032416</v>
+        <v>-117.177340012371</v>
       </c>
       <c r="L435" t="n">
-        <v>994.8</v>
+        <v>1362.6</v>
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>T on Jul 27, 2026, 995 m from Fashion Valley (1300 FRAZEE RD). Case #E26070038798 (use for a records request — full narratives are not published in open data).</t>
+          <t>1131 on Jul 29, 2026, 1363 m from Fashion Valley (1800 HOTEL CIRCLE SOUTH). Case #E26070042450 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -28665,15 +28665,15 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>E26070038757</t>
+          <t>E26070038579</t>
         </is>
       </c>
       <c r="E436" s="3" t="n">
-        <v>46230.48212962963</v>
+        <v>46230.39099537037</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
@@ -28688,21 +28688,21 @@
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>7700 HAZARD CENTER DR</t>
+          <t>7000 FRIARS RD</t>
         </is>
       </c>
       <c r="J436" t="n">
-        <v>32.770935601241</v>
+        <v>32.769515710089</v>
       </c>
       <c r="K436" t="n">
-        <v>-117.156166110813</v>
+        <v>-117.169790033203</v>
       </c>
       <c r="L436" t="n">
-        <v>1007.9</v>
+        <v>420.9</v>
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>415 on Jul 27, 2026, 1008 m from Fashion Valley (7700 HAZARD CENTER DR). Case #E26070038757 (use for a records request — full narratives are not published in open data).</t>
+          <t>T on Jul 27, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070038579 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -28724,11 +28724,11 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>E26070038865</t>
+          <t>E26070038771</t>
         </is>
       </c>
       <c r="E437" s="3" t="n">
-        <v>46230.54028935185</v>
+        <v>46230.48940972222</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -28761,7 +28761,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Selenf on Jul 27, 2026, 686 m from Fashion Valley (400 HOTEL CIRCLE SOUTH). Case #E26070038865 (use for a records request — full narratives are not published in open data).</t>
+          <t>Selenf on Jul 27, 2026, 686 m from Fashion Valley (400 HOTEL CIRCLE SOUTH). Case #E26070038771 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -28783,15 +28783,15 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>E26070038534</t>
+          <t>E26070038652</t>
         </is>
       </c>
       <c r="E438" s="3" t="n">
-        <v>46230.3720949074</v>
+        <v>46230.43452546297</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
@@ -28801,26 +28801,26 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>K</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>300 CAMINO DE LA REINA</t>
+          <t>2000 HOTEL CIRCLE SOUTH</t>
         </is>
       </c>
       <c r="J438" t="n">
-        <v>32.764468174789</v>
+        <v>32.7596759646</v>
       </c>
       <c r="K438" t="n">
-        <v>-117.164515919347</v>
+        <v>-117.18005631438</v>
       </c>
       <c r="L438" t="n">
-        <v>354.6</v>
+        <v>1562.4</v>
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>5150 on Jul 27, 2026, 355 m from Fashion Valley (300 CAMINO DE LA REINA). Case #E26070038534 (use for a records request — full narratives are not published in open data).</t>
+          <t>242 on Jul 27, 2026, 1562 m from Fashion Valley (2000 HOTEL CIRCLE SOUTH). Case #E26070038652 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -28842,15 +28842,15 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>E26070039075</t>
+          <t>E26070038798</t>
         </is>
       </c>
       <c r="E439" s="3" t="n">
-        <v>46230.65422453704</v>
+        <v>46230.50460648148</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
@@ -28860,26 +28860,26 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>5300 MISSION CENTER RD</t>
+          <t>1300 FRAZEE RD</t>
         </is>
       </c>
       <c r="J439" t="n">
-        <v>32.770666615807</v>
+        <v>32.770934576408</v>
       </c>
       <c r="K439" t="n">
-        <v>-117.154875071922</v>
+        <v>-117.156318032416</v>
       </c>
       <c r="L439" t="n">
-        <v>1109.6</v>
+        <v>994.8</v>
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>415 on Jul 27, 2026, 1110 m from Fashion Valley (5300 MISSION CENTER RD). Case #E26070039075 (use for a records request — full narratives are not published in open data).</t>
+          <t>T on Jul 27, 2026, 995 m from Fashion Valley (1300 FRAZEE RD). Case #E26070038798 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -28901,15 +28901,15 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>E26070039194</t>
+          <t>E26070038757</t>
         </is>
       </c>
       <c r="E440" s="3" t="n">
-        <v>46230.71634259259</v>
+        <v>46230.48212962963</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>SELENF</t>
+          <t>415</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
@@ -28924,21 +28924,21 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>7500 HAZARD CENTER DR</t>
+          <t>7700 HAZARD CENTER DR</t>
         </is>
       </c>
       <c r="J440" t="n">
-        <v>32.769886247713</v>
+        <v>32.770935601241</v>
       </c>
       <c r="K440" t="n">
-        <v>-117.159316836244</v>
+        <v>-117.156166110813</v>
       </c>
       <c r="L440" t="n">
-        <v>691.2</v>
+        <v>1007.9</v>
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Selenf on Jul 27, 2026, 691 m from Fashion Valley (7500 HAZARD CENTER DR). Case #E26070039194 (use for a records request — full narratives are not published in open data).</t>
+          <t>415 on Jul 27, 2026, 1008 m from Fashion Valley (7700 HAZARD CENTER DR). Case #E26070038757 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -28960,15 +28960,15 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>E26070039212</t>
+          <t>E26070038865</t>
         </is>
       </c>
       <c r="E441" s="3" t="n">
-        <v>46230.72902777778</v>
+        <v>46230.54028935185</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>586H</t>
+          <t>SELENF</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
@@ -28978,26 +28978,26 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>K</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>1400 FRAZEE RD</t>
+          <t>400 HOTEL CIRCLE SOUTH</t>
         </is>
       </c>
       <c r="J441" t="n">
-        <v>32.77262848834</v>
+        <v>32.761426735043</v>
       </c>
       <c r="K441" t="n">
-        <v>-117.157489907954</v>
+        <v>-117.168017960012</v>
       </c>
       <c r="L441" t="n">
-        <v>993.1</v>
+        <v>685.7</v>
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>586h on Jul 27, 2026, 993 m from Fashion Valley (1400 FRAZEE RD). Case #E26070039212 (use for a records request — full narratives are not published in open data).</t>
+          <t>Selenf on Jul 27, 2026, 686 m from Fashion Valley (400 HOTEL CIRCLE SOUTH). Case #E26070038865 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -29019,11 +29019,11 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>E26070038744</t>
+          <t>E26070038534</t>
         </is>
       </c>
       <c r="E442" s="3" t="n">
-        <v>46230.47576388889</v>
+        <v>46230.3720949074</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -29037,26 +29037,26 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>1000 CAMINO DEL RIO SOUTH</t>
+          <t>300 CAMINO DE LA REINA</t>
         </is>
       </c>
       <c r="J442" t="n">
-        <v>32.764600731806</v>
+        <v>32.764468174789</v>
       </c>
       <c r="K442" t="n">
-        <v>-117.153654844752</v>
+        <v>-117.164515919347</v>
       </c>
       <c r="L442" t="n">
-        <v>1201.9</v>
+        <v>354.6</v>
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>5150 on Jul 27, 2026, 1202 m from Fashion Valley (1000 CAMINO DEL RIO SOUTH). Case #E26070038744 (use for a records request — full narratives are not published in open data).</t>
+          <t>5150 on Jul 27, 2026, 355 m from Fashion Valley (300 CAMINO DE LA REINA). Case #E26070038534 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -29078,15 +29078,15 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>E26070039143</t>
+          <t>E26070039075</t>
         </is>
       </c>
       <c r="E443" s="3" t="n">
-        <v>46230.68831018519</v>
+        <v>46230.65422453704</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>415</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
@@ -29096,26 +29096,26 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>K</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>7600 HAZARD CENTER DR</t>
+          <t>5300 MISSION CENTER RD</t>
         </is>
       </c>
       <c r="J443" t="n">
-        <v>32.7706559026</v>
+        <v>32.770666615807</v>
       </c>
       <c r="K443" t="n">
-        <v>-117.157920375467</v>
+        <v>-117.154875071922</v>
       </c>
       <c r="L443" t="n">
-        <v>845.6</v>
+        <v>1109.6</v>
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>242 on Jul 27, 2026, 846 m from Fashion Valley (7600 HAZARD CENTER DR). Case #E26070039143 (use for a records request — full narratives are not published in open data).</t>
+          <t>415 on Jul 27, 2026, 1110 m from Fashion Valley (5300 MISSION CENTER RD). Case #E26070039075 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -29137,15 +29137,15 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>E26070039518</t>
+          <t>E26070039194</t>
         </is>
       </c>
       <c r="E444" s="3" t="n">
-        <v>46230.9037962963</v>
+        <v>46230.71634259259</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>FD</t>
+          <t>SELENF</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
@@ -29160,21 +29160,21 @@
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>700 CAMINO DE LA REINA</t>
+          <t>7500 HAZARD CENTER DR</t>
         </is>
       </c>
       <c r="J444" t="n">
-        <v>32.766967409624</v>
+        <v>32.769886247713</v>
       </c>
       <c r="K444" t="n">
-        <v>-117.158325543359</v>
+        <v>-117.159316836244</v>
       </c>
       <c r="L444" t="n">
-        <v>726.3</v>
+        <v>691.2</v>
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Fd on Jul 27, 2026, 726 m from Fashion Valley (700 CAMINO DE LA REINA). Case #E26070039518 (use for a records request — full narratives are not published in open data).</t>
+          <t>Selenf on Jul 27, 2026, 691 m from Fashion Valley (7500 HAZARD CENTER DR). Case #E26070039194 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -29196,15 +29196,15 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>E26070039611</t>
+          <t>E26070039212</t>
         </is>
       </c>
       <c r="E445" s="3" t="n">
-        <v>46230.97168981482</v>
+        <v>46230.72902777778</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>586H</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
@@ -29214,26 +29214,26 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>1400 HOTEL CIRCLE NORTH</t>
+          <t>1400 FRAZEE RD</t>
         </is>
       </c>
       <c r="J445" t="n">
-        <v>32.760567393859</v>
+        <v>32.77262848834</v>
       </c>
       <c r="K445" t="n">
-        <v>-117.172083928832</v>
+        <v>-117.157489907954</v>
       </c>
       <c r="L445" t="n">
-        <v>942.4</v>
+        <v>993.1</v>
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>T on Jul 27, 2026, 942 m from Fashion Valley (1400 HOTEL CIRCLE NORTH). Case #E26070039611 (use for a records request — full narratives are not published in open data).</t>
+          <t>586h on Jul 27, 2026, 993 m from Fashion Valley (1400 FRAZEE RD). Case #E26070039212 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -29255,15 +29255,15 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>E26070040084</t>
+          <t>E26070038744</t>
         </is>
       </c>
       <c r="E446" s="3" t="n">
-        <v>46231.38797453704</v>
+        <v>46230.47576388889</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
@@ -29278,21 +29278,21 @@
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>5600 MISSION CENTER RD</t>
+          <t>1000 CAMINO DEL RIO SOUTH</t>
         </is>
       </c>
       <c r="J446" t="n">
-        <v>32.775588244581</v>
+        <v>32.764600731806</v>
       </c>
       <c r="K446" t="n">
-        <v>-117.154010732639</v>
+        <v>-117.153654844752</v>
       </c>
       <c r="L446" t="n">
-        <v>1451.6</v>
+        <v>1201.9</v>
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>415 on Jul 28, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070040084 (use for a records request — full narratives are not published in open data).</t>
+          <t>5150 on Jul 27, 2026, 1202 m from Fashion Valley (1000 CAMINO DEL RIO SOUTH). Case #E26070038744 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -29314,15 +29314,15 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>E26070040104</t>
+          <t>E26070039143</t>
         </is>
       </c>
       <c r="E447" s="3" t="n">
-        <v>46231.40006944445</v>
+        <v>46230.68831018519</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
@@ -29332,26 +29332,26 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>7900 MISSION CENTER CT</t>
+          <t>7600 HAZARD CENTER DR</t>
         </is>
       </c>
       <c r="J447" t="n">
-        <v>32.773605548078</v>
+        <v>32.7706559026</v>
       </c>
       <c r="K447" t="n">
-        <v>-117.154100182722</v>
+        <v>-117.157920375467</v>
       </c>
       <c r="L447" t="n">
-        <v>1317</v>
+        <v>845.6</v>
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>594 on Jul 28, 2026, 1317 m from Fashion Valley (7900 MISSION CENTER CT). Case #E26070040104 (use for a records request — full narratives are not published in open data).</t>
+          <t>242 on Jul 27, 2026, 846 m from Fashion Valley (7600 HAZARD CENTER DR). Case #E26070039143 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -29373,15 +29373,15 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>E26070042501</t>
+          <t>E26070039518</t>
         </is>
       </c>
       <c r="E448" s="3" t="n">
-        <v>46232.90143518519</v>
+        <v>46230.9037962963</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>FD</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
@@ -29396,21 +29396,21 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>1400 CAMINO DEL RIO SOUTH</t>
+          <t>700 CAMINO DE LA REINA</t>
         </is>
       </c>
       <c r="J448" t="n">
-        <v>32.766220038347</v>
+        <v>32.766967409624</v>
       </c>
       <c r="K448" t="n">
-        <v>-117.14952431001</v>
+        <v>-117.158325543359</v>
       </c>
       <c r="L448" t="n">
-        <v>1553.1</v>
+        <v>726.3</v>
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>1130 on Jul 29, 2026, 1553 m from Fashion Valley (1400 CAMINO DEL RIO SOUTH). Case #E26070042501 (use for a records request — full narratives are not published in open data).</t>
+          <t>Fd on Jul 27, 2026, 726 m from Fashion Valley (700 CAMINO DE LA REINA). Case #E26070039518 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -29432,15 +29432,15 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>E26070042328</t>
+          <t>E26070039611</t>
         </is>
       </c>
       <c r="E449" s="3" t="n">
-        <v>46232.78821759259</v>
+        <v>46230.97168981482</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
@@ -29450,26 +29450,26 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>K</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>7600 HAZARD CENTER DR</t>
+          <t>1400 HOTEL CIRCLE NORTH</t>
         </is>
       </c>
       <c r="J449" t="n">
-        <v>32.7706559026</v>
+        <v>32.760567393859</v>
       </c>
       <c r="K449" t="n">
-        <v>-117.157920375467</v>
+        <v>-117.172083928832</v>
       </c>
       <c r="L449" t="n">
-        <v>845.6</v>
+        <v>942.4</v>
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>1151 on Jul 29, 2026, 846 m from Fashion Valley (7600 HAZARD CENTER DR). Case #E26070042328 (use for a records request — full narratives are not published in open data).</t>
+          <t>T on Jul 27, 2026, 942 m from Fashion Valley (1400 HOTEL CIRCLE NORTH). Case #E26070039611 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -29491,15 +29491,15 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>E26070035833</t>
+          <t>E26070040084</t>
         </is>
       </c>
       <c r="E450" s="3" t="n">
-        <v>46228.48918981481</v>
+        <v>46231.38797453704</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>415</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
@@ -29514,21 +29514,21 @@
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>7000 FRIARS RD</t>
+          <t>5600 MISSION CENTER RD</t>
         </is>
       </c>
       <c r="J450" t="n">
-        <v>32.769515710089</v>
+        <v>32.775588244581</v>
       </c>
       <c r="K450" t="n">
-        <v>-117.169790033203</v>
+        <v>-117.154010732639</v>
       </c>
       <c r="L450" t="n">
-        <v>420.9</v>
+        <v>1451.6</v>
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>597 on Jul 25, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070035833 (use for a records request — full narratives are not published in open data).</t>
+          <t>415 on Jul 28, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070040084 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -29550,15 +29550,15 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>E26070035857</t>
+          <t>E26070040104</t>
         </is>
       </c>
       <c r="E451" s="3" t="n">
-        <v>46228.50023148148</v>
+        <v>46231.40006944445</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>10852R</t>
+          <t>594</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
@@ -29568,26 +29568,26 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>7000 FRIARS RD</t>
+          <t>7900 MISSION CENTER CT</t>
         </is>
       </c>
       <c r="J451" t="n">
-        <v>32.769515710089</v>
+        <v>32.773605548078</v>
       </c>
       <c r="K451" t="n">
-        <v>-117.169790033203</v>
+        <v>-117.154100182722</v>
       </c>
       <c r="L451" t="n">
-        <v>420.9</v>
+        <v>1317</v>
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>10852r on Jul 25, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070035857 (use for a records request — full narratives are not published in open data).</t>
+          <t>594 on Jul 28, 2026, 1317 m from Fashion Valley (7900 MISSION CENTER CT). Case #E26070040104 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -29609,15 +29609,15 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>E26070035881</t>
+          <t>E26070042501</t>
         </is>
       </c>
       <c r="E452" s="3" t="n">
-        <v>46228.51431712963</v>
+        <v>46232.90143518519</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
@@ -29632,21 +29632,21 @@
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>2000 ULRIC ST</t>
+          <t>1400 CAMINO DEL RIO SOUTH</t>
         </is>
       </c>
       <c r="J452" t="n">
-        <v>32.781040367079</v>
+        <v>32.766220038347</v>
       </c>
       <c r="K452" t="n">
-        <v>-117.169519983203</v>
+        <v>-117.14952431001</v>
       </c>
       <c r="L452" t="n">
-        <v>1553.3</v>
+        <v>1553.1</v>
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>1151 on Jul 25, 2026, 1553 m from Fashion Valley (2000 ULRIC ST). Case #E26070035881 (use for a records request — full narratives are not published in open data).</t>
+          <t>1130 on Jul 29, 2026, 1553 m from Fashion Valley (1400 CAMINO DEL RIO SOUTH). Case #E26070042501 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -29668,15 +29668,15 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>E26070035912</t>
+          <t>E26070042328</t>
         </is>
       </c>
       <c r="E453" s="3" t="n">
-        <v>46228.53122685185</v>
+        <v>46232.78821759259</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>SELENF</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
@@ -29686,7 +29686,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -29705,7 +29705,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Selenf on Jul 25, 2026, 846 m from Fashion Valley (7600 HAZARD CENTER DR). Case #E26070035912 (use for a records request — full narratives are not published in open data).</t>
+          <t>1151 on Jul 29, 2026, 846 m from Fashion Valley (7600 HAZARD CENTER DR). Case #E26070042328 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -29727,15 +29727,15 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>E26070036003</t>
+          <t>E26070035833</t>
         </is>
       </c>
       <c r="E454" s="3" t="n">
-        <v>46228.58616898148</v>
+        <v>46228.48918981481</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>415V</t>
+          <t>597</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
@@ -29750,21 +29750,21 @@
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>600 CAMINO DE LA REINA</t>
+          <t>7000 FRIARS RD</t>
         </is>
       </c>
       <c r="J454" t="n">
-        <v>32.766630976251</v>
+        <v>32.769515710089</v>
       </c>
       <c r="K454" t="n">
-        <v>-117.159547007833</v>
+        <v>-117.169790033203</v>
       </c>
       <c r="L454" t="n">
-        <v>616.3</v>
+        <v>420.9</v>
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>415v on Jul 25, 2026, 616 m from Fashion Valley (600 CAMINO DE LA REINA). Case #E26070036003 (use for a records request — full narratives are not published in open data).</t>
+          <t>597 on Jul 25, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070035833 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -29786,15 +29786,15 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>E26070036121</t>
+          <t>E26070035857</t>
         </is>
       </c>
       <c r="E455" s="3" t="n">
-        <v>46228.63888888889</v>
+        <v>46228.50023148148</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>10852R</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
@@ -29804,26 +29804,26 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>500 HOTEL CIRCLE SOUTH</t>
+          <t>7000 FRIARS RD</t>
         </is>
       </c>
       <c r="J455" t="n">
-        <v>32.761281414433</v>
+        <v>32.769515710089</v>
       </c>
       <c r="K455" t="n">
-        <v>-117.168573310454</v>
+        <v>-117.169790033203</v>
       </c>
       <c r="L455" t="n">
-        <v>716.5</v>
+        <v>420.9</v>
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>T on Jul 25, 2026, 717 m from Fashion Valley (500 HOTEL CIRCLE SOUTH). Case #E26070036121 (use for a records request — full narratives are not published in open data).</t>
+          <t>10852r on Jul 25, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070035857 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -29845,15 +29845,15 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>E26070036160</t>
+          <t>E26070035881</t>
         </is>
       </c>
       <c r="E456" s="3" t="n">
-        <v>46228.6652662037</v>
+        <v>46228.51431712963</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
@@ -29863,26 +29863,26 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>K</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>800 HOTEL CIRCLE SOUTH</t>
+          <t>2000 ULRIC ST</t>
         </is>
       </c>
       <c r="J456" t="n">
-        <v>32.760837633784</v>
+        <v>32.781040367079</v>
       </c>
       <c r="K456" t="n">
-        <v>-117.170557039813</v>
+        <v>-117.169519983203</v>
       </c>
       <c r="L456" t="n">
-        <v>838.8</v>
+        <v>1553.3</v>
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>T on Jul 25, 2026, 839 m from Fashion Valley (800 HOTEL CIRCLE SOUTH). Case #E26070036160 (use for a records request — full narratives are not published in open data).</t>
+          <t>1151 on Jul 25, 2026, 1553 m from Fashion Valley (2000 ULRIC ST). Case #E26070035881 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -29904,15 +29904,15 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>E26070035887</t>
+          <t>E26070035912</t>
         </is>
       </c>
       <c r="E457" s="3" t="n">
-        <v>46228.51732638889</v>
+        <v>46228.53122685185</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>SELENF</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
@@ -29927,21 +29927,21 @@
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>700 CAMINO DE LA REINA</t>
+          <t>7600 HAZARD CENTER DR</t>
         </is>
       </c>
       <c r="J457" t="n">
-        <v>32.766967409624</v>
+        <v>32.7706559026</v>
       </c>
       <c r="K457" t="n">
-        <v>-117.158325543359</v>
+        <v>-117.157920375467</v>
       </c>
       <c r="L457" t="n">
-        <v>726.3</v>
+        <v>845.6</v>
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>5150 on Jul 25, 2026, 726 m from Fashion Valley (700 CAMINO DE LA REINA). Case #E26070035887 (use for a records request — full narratives are not published in open data).</t>
+          <t>Selenf on Jul 25, 2026, 846 m from Fashion Valley (7600 HAZARD CENTER DR). Case #E26070035912 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -29963,15 +29963,15 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>E26070036201</t>
+          <t>E26070036003</t>
         </is>
       </c>
       <c r="E458" s="3" t="n">
-        <v>46228.68618055555</v>
+        <v>46228.58616898148</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>AU1171</t>
+          <t>415V</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
@@ -29981,26 +29981,26 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>K</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>2000 HOTEL CIRCLE SOUTH</t>
+          <t>600 CAMINO DE LA REINA</t>
         </is>
       </c>
       <c r="J458" t="n">
-        <v>32.7596759646</v>
+        <v>32.766630976251</v>
       </c>
       <c r="K458" t="n">
-        <v>-117.18005631438</v>
+        <v>-117.159547007833</v>
       </c>
       <c r="L458" t="n">
-        <v>1562.4</v>
+        <v>616.3</v>
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Au1171 on Jul 25, 2026, 1562 m from Fashion Valley (2000 HOTEL CIRCLE SOUTH). Case #E26070036201 (use for a records request — full narratives are not published in open data).</t>
+          <t>415v on Jul 25, 2026, 616 m from Fashion Valley (600 CAMINO DE LA REINA). Case #E26070036003 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -30022,15 +30022,15 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>E26070036255</t>
+          <t>E26070036121</t>
         </is>
       </c>
       <c r="E459" s="3" t="n">
-        <v>46228.71361111111</v>
+        <v>46228.63888888889</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
@@ -30045,21 +30045,21 @@
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>1500 CAMINO DE LA REINA</t>
+          <t>500 HOTEL CIRCLE SOUTH</t>
         </is>
       </c>
       <c r="J459" t="n">
-        <v>32.769985467879</v>
+        <v>32.761281414433</v>
       </c>
       <c r="K459" t="n">
-        <v>-117.149965439226</v>
+        <v>-117.168573310454</v>
       </c>
       <c r="L459" t="n">
-        <v>1534.3</v>
+        <v>716.5</v>
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>415 on Jul 25, 2026, 1534 m from Fashion Valley (1500 CAMINO DE LA REINA). Case #E26070036255 (use for a records request — full narratives are not published in open data).</t>
+          <t>T on Jul 25, 2026, 717 m from Fashion Valley (500 HOTEL CIRCLE SOUTH). Case #E26070036121 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -30081,11 +30081,11 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>E26070036348</t>
+          <t>E26070036160</t>
         </is>
       </c>
       <c r="E460" s="3" t="n">
-        <v>46228.76747685186</v>
+        <v>46228.6652662037</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -30099,26 +30099,26 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>1900 ULRIC ST</t>
+          <t>800 HOTEL CIRCLE SOUTH</t>
         </is>
       </c>
       <c r="J460" t="n">
-        <v>32.779900409244</v>
+        <v>32.760837633784</v>
       </c>
       <c r="K460" t="n">
-        <v>-117.169180382822</v>
+        <v>-117.170557039813</v>
       </c>
       <c r="L460" t="n">
-        <v>1422.7</v>
+        <v>838.8</v>
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>T on Jul 25, 2026, 1423 m from Fashion Valley (1900 ULRIC ST). Case #E26070036348 (use for a records request — full narratives are not published in open data).</t>
+          <t>T on Jul 25, 2026, 839 m from Fashion Valley (800 HOTEL CIRCLE SOUTH). Case #E26070036160 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -30140,15 +30140,15 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>E26070036465</t>
+          <t>E26070035887</t>
         </is>
       </c>
       <c r="E461" s="3" t="n">
-        <v>46228.84383101852</v>
+        <v>46228.51732638889</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>SLEEPER</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
@@ -30158,26 +30158,26 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>5700 MISSION CENTER RD</t>
+          <t>700 CAMINO DE LA REINA</t>
         </is>
       </c>
       <c r="J461" t="n">
-        <v>32.77719888635</v>
+        <v>32.766967409624</v>
       </c>
       <c r="K461" t="n">
-        <v>-117.15461034814</v>
+        <v>-117.158325543359</v>
       </c>
       <c r="L461" t="n">
-        <v>1530.7</v>
+        <v>726.3</v>
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Sleeper on Jul 25, 2026, 1531 m from Fashion Valley (5700 MISSION CENTER RD). Case #E26070036465 (use for a records request — full narratives are not published in open data).</t>
+          <t>5150 on Jul 25, 2026, 726 m from Fashion Valley (700 CAMINO DE LA REINA). Case #E26070035887 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -30199,15 +30199,15 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>E26070036550</t>
+          <t>E26070036201</t>
         </is>
       </c>
       <c r="E462" s="3" t="n">
-        <v>46228.88915509259</v>
+        <v>46228.68618055555</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>415V</t>
+          <t>AU1171</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
@@ -30217,26 +30217,26 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>1600 CAMINO DEL RIO NORTH</t>
+          <t>2000 HOTEL CIRCLE SOUTH</t>
         </is>
       </c>
       <c r="J462" t="n">
-        <v>32.766861158912</v>
+        <v>32.7596759646</v>
       </c>
       <c r="K462" t="n">
-        <v>-117.151286132201</v>
+        <v>-117.18005631438</v>
       </c>
       <c r="L462" t="n">
-        <v>1384.3</v>
+        <v>1562.4</v>
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>415v on Jul 25, 2026, 1384 m from Fashion Valley (1600 CAMINO DEL RIO NORTH). Case #E26070036550 (use for a records request — full narratives are not published in open data).</t>
+          <t>Au1171 on Jul 25, 2026, 1562 m from Fashion Valley (2000 HOTEL CIRCLE SOUTH). Case #E26070036201 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -30258,15 +30258,15 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>E26070036590</t>
+          <t>E26070036255</t>
         </is>
       </c>
       <c r="E463" s="3" t="n">
-        <v>46228.90773148148</v>
+        <v>46228.71361111111</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>NARC</t>
+          <t>415</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
@@ -30281,21 +30281,21 @@
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t>1200 FASHION VALLEY RD</t>
+          <t>1500 CAMINO DE LA REINA</t>
         </is>
       </c>
       <c r="J463" t="n">
-        <v>32.76745627379</v>
+        <v>32.769985467879</v>
       </c>
       <c r="K463" t="n">
-        <v>-117.171245398889</v>
+        <v>-117.149965439226</v>
       </c>
       <c r="L463" t="n">
-        <v>483.2</v>
+        <v>1534.3</v>
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Narc on Jul 25, 2026, 483 m from Fashion Valley (1200 FASHION VALLEY RD). Case #E26070036590 (use for a records request — full narratives are not published in open data).</t>
+          <t>415 on Jul 25, 2026, 1534 m from Fashion Valley (1500 CAMINO DE LA REINA). Case #E26070036255 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -30317,15 +30317,15 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>E26070036714</t>
+          <t>E26070036348</t>
         </is>
       </c>
       <c r="E464" s="3" t="n">
-        <v>46228.96581018518</v>
+        <v>46228.76747685186</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
@@ -30335,26 +30335,26 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>K</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>1000 CAMINO DEL RIO NORTH</t>
+          <t>1900 ULRIC ST</t>
         </is>
       </c>
       <c r="J464" t="n">
-        <v>32.765761445049</v>
+        <v>32.779900409244</v>
       </c>
       <c r="K464" t="n">
-        <v>-117.154646736046</v>
+        <v>-117.169180382822</v>
       </c>
       <c r="L464" t="n">
-        <v>1083.8</v>
+        <v>1422.7</v>
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>5150 on Jul 25, 2026, 1084 m from Fashion Valley (1000 CAMINO DEL RIO NORTH). Case #E26070036714 (use for a records request — full narratives are not published in open data).</t>
+          <t>T on Jul 25, 2026, 1423 m from Fashion Valley (1900 ULRIC ST). Case #E26070036348 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -30376,15 +30376,15 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>E26070040242</t>
+          <t>E26070036465</t>
         </is>
       </c>
       <c r="E465" s="3" t="n">
-        <v>46231.46559027778</v>
+        <v>46228.84383101852</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>SLEEPER</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
@@ -30394,26 +30394,26 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>K</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>7000 FRIARS RD</t>
+          <t>5700 MISSION CENTER RD</t>
         </is>
       </c>
       <c r="J465" t="n">
-        <v>32.769515710089</v>
+        <v>32.77719888635</v>
       </c>
       <c r="K465" t="n">
-        <v>-117.169790033203</v>
+        <v>-117.15461034814</v>
       </c>
       <c r="L465" t="n">
-        <v>420.9</v>
+        <v>1530.7</v>
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>911 on Jul 28, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070040242 (use for a records request — full narratives are not published in open data).</t>
+          <t>Sleeper on Jul 25, 2026, 1531 m from Fashion Valley (5700 MISSION CENTER RD). Case #E26070036465 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -30435,15 +30435,15 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>E26070040261</t>
+          <t>E26070036550</t>
         </is>
       </c>
       <c r="E466" s="3" t="n">
-        <v>46231.47072916666</v>
+        <v>46228.88915509259</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>459A</t>
+          <t>415V</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
@@ -30453,26 +30453,26 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>K</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>400 CAMINO DEL RIO SOUTH</t>
+          <t>1600 CAMINO DEL RIO NORTH</t>
         </is>
       </c>
       <c r="J466" t="n">
-        <v>32.76100095804</v>
+        <v>32.766861158912</v>
       </c>
       <c r="K466" t="n">
-        <v>-117.161321780527</v>
+        <v>-117.151286132201</v>
       </c>
       <c r="L466" t="n">
-        <v>836.7</v>
+        <v>1384.3</v>
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>459a on Jul 28, 2026, 837 m from Fashion Valley (400 CAMINO DEL RIO SOUTH). Case #E26070040261 (use for a records request — full narratives are not published in open data).</t>
+          <t>415v on Jul 25, 2026, 1384 m from Fashion Valley (1600 CAMINO DEL RIO NORTH). Case #E26070036550 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -30494,15 +30494,15 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>E26070037102</t>
+          <t>E26070036590</t>
         </is>
       </c>
       <c r="E467" s="3" t="n">
-        <v>46229.31866898148</v>
+        <v>46228.90773148148</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>NARC</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
@@ -30517,21 +30517,21 @@
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>700 HOTEL CIRCLE SOUTH</t>
+          <t>1200 FASHION VALLEY RD</t>
         </is>
       </c>
       <c r="J467" t="n">
-        <v>32.760967849672</v>
+        <v>32.76745627379</v>
       </c>
       <c r="K467" t="n">
-        <v>-117.169908508074</v>
+        <v>-117.171245398889</v>
       </c>
       <c r="L467" t="n">
-        <v>797.3</v>
+        <v>483.2</v>
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>T on Jul 26, 2026, 797 m from Fashion Valley (700 HOTEL CIRCLE SOUTH). Case #E26070037102 (use for a records request — full narratives are not published in open data).</t>
+          <t>Narc on Jul 25, 2026, 483 m from Fashion Valley (1200 FASHION VALLEY RD). Case #E26070036590 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -30553,15 +30553,15 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>E26070037118</t>
+          <t>E26070036714</t>
         </is>
       </c>
       <c r="E468" s="3" t="n">
-        <v>46229.33061342593</v>
+        <v>46228.96581018518</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>SELENF</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
@@ -30571,26 +30571,26 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>7600 HAZARD CENTER DR</t>
+          <t>1000 CAMINO DEL RIO NORTH</t>
         </is>
       </c>
       <c r="J468" t="n">
-        <v>32.7706559026</v>
+        <v>32.765761445049</v>
       </c>
       <c r="K468" t="n">
-        <v>-117.157920375467</v>
+        <v>-117.154646736046</v>
       </c>
       <c r="L468" t="n">
-        <v>845.6</v>
+        <v>1083.8</v>
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Selenf on Jul 26, 2026, 846 m from Fashion Valley (7600 HAZARD CENTER DR). Case #E26070037118 (use for a records request — full narratives are not published in open data).</t>
+          <t>5150 on Jul 25, 2026, 1084 m from Fashion Valley (1000 CAMINO DEL RIO NORTH). Case #E26070036714 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -30612,15 +30612,15 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>E26070037124</t>
+          <t>E26070040242</t>
         </is>
       </c>
       <c r="E469" s="3" t="n">
-        <v>46229.33637731482</v>
+        <v>46231.46559027778</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>911</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
@@ -30635,21 +30635,21 @@
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>5600 MISSION CENTER RD</t>
+          <t>7000 FRIARS RD</t>
         </is>
       </c>
       <c r="J469" t="n">
-        <v>32.775588244581</v>
+        <v>32.769515710089</v>
       </c>
       <c r="K469" t="n">
-        <v>-117.154010732639</v>
+        <v>-117.169790033203</v>
       </c>
       <c r="L469" t="n">
-        <v>1451.6</v>
+        <v>420.9</v>
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>415 on Jul 26, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070037124 (use for a records request — full narratives are not published in open data).</t>
+          <t>911 on Jul 28, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070040242 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -30671,15 +30671,15 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>E26070037123</t>
+          <t>E26070040261</t>
         </is>
       </c>
       <c r="E470" s="3" t="n">
-        <v>46229.33495370371</v>
+        <v>46231.47072916666</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>459A</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
@@ -30689,26 +30689,26 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>7800 MISSION CENTER CT</t>
+          <t>400 CAMINO DEL RIO SOUTH</t>
         </is>
       </c>
       <c r="J470" t="n">
-        <v>32.773261251159</v>
+        <v>32.76100095804</v>
       </c>
       <c r="K470" t="n">
-        <v>-117.155811054338</v>
+        <v>-117.161321780527</v>
       </c>
       <c r="L470" t="n">
-        <v>1161.9</v>
+        <v>836.7</v>
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>1149 on Jul 26, 2026, 1162 m from Fashion Valley (7800 MISSION CENTER CT). Case #E26070037123 (use for a records request — full narratives are not published in open data).</t>
+          <t>459a on Jul 28, 2026, 837 m from Fashion Valley (400 CAMINO DEL RIO SOUTH). Case #E26070040261 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -30730,11 +30730,11 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>E26070037211</t>
+          <t>E26070037102</t>
         </is>
       </c>
       <c r="E471" s="3" t="n">
-        <v>46229.39908564815</v>
+        <v>46229.31866898148</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -30753,21 +30753,21 @@
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>1200 FASHION VALLEY RD</t>
+          <t>700 HOTEL CIRCLE SOUTH</t>
         </is>
       </c>
       <c r="J471" t="n">
-        <v>32.76745627379</v>
+        <v>32.760967849672</v>
       </c>
       <c r="K471" t="n">
-        <v>-117.171245398889</v>
+        <v>-117.169908508074</v>
       </c>
       <c r="L471" t="n">
-        <v>483.2</v>
+        <v>797.3</v>
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>T on Jul 26, 2026, 483 m from Fashion Valley (1200 FASHION VALLEY RD). Case #E26070037211 (use for a records request — full narratives are not published in open data).</t>
+          <t>T on Jul 26, 2026, 797 m from Fashion Valley (700 HOTEL CIRCLE SOUTH). Case #E26070037102 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -30789,11 +30789,11 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>E26070037314</t>
+          <t>E26070037118</t>
         </is>
       </c>
       <c r="E472" s="3" t="n">
-        <v>46229.46476851852</v>
+        <v>46229.33061342593</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -30812,21 +30812,21 @@
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>800 CAMINO DEL RIO NORTH</t>
+          <t>7600 HAZARD CENTER DR</t>
         </is>
       </c>
       <c r="J472" t="n">
-        <v>32.765295418344</v>
+        <v>32.7706559026</v>
       </c>
       <c r="K472" t="n">
-        <v>-117.15656006511</v>
+        <v>-117.157920375467</v>
       </c>
       <c r="L472" t="n">
-        <v>919.5</v>
+        <v>845.6</v>
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Selenf on Jul 26, 2026, 920 m from Fashion Valley (800 CAMINO DEL RIO NORTH). Case #E26070037314 (use for a records request — full narratives are not published in open data).</t>
+          <t>Selenf on Jul 26, 2026, 846 m from Fashion Valley (7600 HAZARD CENTER DR). Case #E26070037118 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -30848,15 +30848,15 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>E26070037620</t>
+          <t>E26070037124</t>
         </is>
       </c>
       <c r="E473" s="3" t="n">
-        <v>46229.65253472222</v>
+        <v>46229.33637731482</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>415</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
@@ -30866,26 +30866,26 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>1200 FASHION VALLEY RD</t>
+          <t>5600 MISSION CENTER RD</t>
         </is>
       </c>
       <c r="J473" t="n">
-        <v>32.76745627379</v>
+        <v>32.775588244581</v>
       </c>
       <c r="K473" t="n">
-        <v>-117.171245398889</v>
+        <v>-117.154010732639</v>
       </c>
       <c r="L473" t="n">
-        <v>483.2</v>
+        <v>1451.6</v>
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>T on Jul 26, 2026, 483 m from Fashion Valley (1200 FASHION VALLEY RD). Case #E26070037620 (use for a records request — full narratives are not published in open data).</t>
+          <t>415 on Jul 26, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070037124 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -30907,15 +30907,15 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>E26070037670</t>
+          <t>E26070037123</t>
         </is>
       </c>
       <c r="E474" s="3" t="n">
-        <v>46229.6718287037</v>
+        <v>46229.33495370371</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
@@ -30930,21 +30930,21 @@
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>800 HOTEL CIRCLE SOUTH</t>
+          <t>7800 MISSION CENTER CT</t>
         </is>
       </c>
       <c r="J474" t="n">
-        <v>32.760837633784</v>
+        <v>32.773261251159</v>
       </c>
       <c r="K474" t="n">
-        <v>-117.170557039813</v>
+        <v>-117.155811054338</v>
       </c>
       <c r="L474" t="n">
-        <v>838.8</v>
+        <v>1161.9</v>
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>T on Jul 26, 2026, 839 m from Fashion Valley (800 HOTEL CIRCLE SOUTH). Case #E26070037670 (use for a records request — full narratives are not published in open data).</t>
+          <t>1149 on Jul 26, 2026, 1162 m from Fashion Valley (7800 MISSION CENTER CT). Case #E26070037123 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -30966,15 +30966,15 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>E26070037681</t>
+          <t>E26070037211</t>
         </is>
       </c>
       <c r="E475" s="3" t="n">
-        <v>46229.67883101852</v>
+        <v>46229.39908564815</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
@@ -30989,21 +30989,21 @@
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>300 CAMINO DE LA REINA</t>
+          <t>1200 FASHION VALLEY RD</t>
         </is>
       </c>
       <c r="J475" t="n">
-        <v>32.764468174789</v>
+        <v>32.76745627379</v>
       </c>
       <c r="K475" t="n">
-        <v>-117.164515919347</v>
+        <v>-117.171245398889</v>
       </c>
       <c r="L475" t="n">
-        <v>354.6</v>
+        <v>483.2</v>
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>415 on Jul 26, 2026, 355 m from Fashion Valley (300 CAMINO DE LA REINA). Case #E26070037681 (use for a records request — full narratives are not published in open data).</t>
+          <t>T on Jul 26, 2026, 483 m from Fashion Valley (1200 FASHION VALLEY RD). Case #E26070037211 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -31025,15 +31025,15 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>E26070037731</t>
+          <t>E26070037314</t>
         </is>
       </c>
       <c r="E476" s="3" t="n">
-        <v>46229.71314814815</v>
+        <v>46229.46476851852</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>415PP</t>
+          <t>SELENF</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
@@ -31048,21 +31048,21 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>5700 MISSION CENTER RD</t>
+          <t>800 CAMINO DEL RIO NORTH</t>
         </is>
       </c>
       <c r="J476" t="n">
-        <v>32.77719888635</v>
+        <v>32.765295418344</v>
       </c>
       <c r="K476" t="n">
-        <v>-117.15461034814</v>
+        <v>-117.15656006511</v>
       </c>
       <c r="L476" t="n">
-        <v>1530.7</v>
+        <v>919.5</v>
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>415pp on Jul 26, 2026, 1531 m from Fashion Valley (5700 MISSION CENTER RD). Case #E26070037731 (use for a records request — full narratives are not published in open data).</t>
+          <t>Selenf on Jul 26, 2026, 920 m from Fashion Valley (800 CAMINO DEL RIO NORTH). Case #E26070037314 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -31084,15 +31084,15 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>E26070037911</t>
+          <t>E26070037620</t>
         </is>
       </c>
       <c r="E477" s="3" t="n">
-        <v>46229.82662037037</v>
+        <v>46229.65253472222</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>11-8</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
@@ -31102,26 +31102,26 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t>6800 FRIARS RD</t>
+          <t>1200 FASHION VALLEY RD</t>
         </is>
       </c>
       <c r="J477" t="n">
-        <v>32.768288067315</v>
+        <v>32.76745627379</v>
       </c>
       <c r="K477" t="n">
-        <v>-117.172866645828</v>
+        <v>-117.171245398889</v>
       </c>
       <c r="L477" t="n">
-        <v>642.8</v>
+        <v>483.2</v>
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>11-8 on Jul 26, 2026, 643 m from Fashion Valley (6800 FRIARS RD). Case #E26070037911 (use for a records request — full narratives are not published in open data).</t>
+          <t>T on Jul 26, 2026, 483 m from Fashion Valley (1200 FASHION VALLEY RD). Case #E26070037620 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -31143,15 +31143,15 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>E26070037537</t>
+          <t>E26070037670</t>
         </is>
       </c>
       <c r="E478" s="3" t="n">
-        <v>46229.60693287037</v>
+        <v>46229.6718287037</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>415V</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
@@ -31161,26 +31161,26 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>6900 FRIARS RD</t>
+          <t>800 HOTEL CIRCLE SOUTH</t>
         </is>
       </c>
       <c r="J478" t="n">
-        <v>32.768802058993</v>
+        <v>32.760837633784</v>
       </c>
       <c r="K478" t="n">
-        <v>-117.171569461601</v>
+        <v>-117.170557039813</v>
       </c>
       <c r="L478" t="n">
-        <v>537.4</v>
+        <v>838.8</v>
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>415v on Jul 26, 2026, 537 m from Fashion Valley (6900 FRIARS RD). Case #E26070037537 (use for a records request — full narratives are not published in open data).</t>
+          <t>T on Jul 26, 2026, 839 m from Fashion Valley (800 HOTEL CIRCLE SOUTH). Case #E26070037670 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -31202,15 +31202,15 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>E26070038020</t>
+          <t>E26070037681</t>
         </is>
       </c>
       <c r="E479" s="3" t="n">
-        <v>46229.89195601852</v>
+        <v>46229.67883101852</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>AU2</t>
+          <t>415</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
@@ -31220,26 +31220,26 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>K</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>1900 HOTEL CIRCLE NORTH</t>
+          <t>300 CAMINO DE LA REINA</t>
         </is>
       </c>
       <c r="J479" t="n">
-        <v>32.759628968658</v>
+        <v>32.764468174789</v>
       </c>
       <c r="K479" t="n">
-        <v>-117.178696371386</v>
+        <v>-117.164515919347</v>
       </c>
       <c r="L479" t="n">
-        <v>1460.7</v>
+        <v>354.6</v>
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Au2 on Jul 26, 2026, 1461 m from Fashion Valley (1900 HOTEL CIRCLE NORTH). Case #E26070038020 (use for a records request — full narratives are not published in open data).</t>
+          <t>415 on Jul 26, 2026, 355 m from Fashion Valley (300 CAMINO DE LA REINA). Case #E26070037681 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -31261,15 +31261,15 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>E26070038144</t>
+          <t>E26070037731</t>
         </is>
       </c>
       <c r="E480" s="3" t="n">
-        <v>46229.96445601852</v>
+        <v>46229.71314814815</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>415PP</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
@@ -31279,26 +31279,26 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>K</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>1200 FASHION VALLEY RD</t>
+          <t>5700 MISSION CENTER RD</t>
         </is>
       </c>
       <c r="J480" t="n">
-        <v>32.76745627379</v>
+        <v>32.77719888635</v>
       </c>
       <c r="K480" t="n">
-        <v>-117.171245398889</v>
+        <v>-117.15461034814</v>
       </c>
       <c r="L480" t="n">
-        <v>483.2</v>
+        <v>1530.7</v>
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>594 on Jul 26, 2026, 483 m from Fashion Valley (1200 FASHION VALLEY RD). Case #E26070038144 (use for a records request — full narratives are not published in open data).</t>
+          <t>415pp on Jul 26, 2026, 1531 m from Fashion Valley (5700 MISSION CENTER RD). Case #E26070037731 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -31320,15 +31320,15 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>E26070036804</t>
+          <t>E26070037911</t>
         </is>
       </c>
       <c r="E481" s="3" t="n">
-        <v>46229.00714120371</v>
+        <v>46229.82662037037</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>415PP</t>
+          <t>11-8</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
@@ -31343,21 +31343,21 @@
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>1100 CAMINO DEL RIO NORTH</t>
+          <t>6800 FRIARS RD</t>
         </is>
       </c>
       <c r="J481" t="n">
-        <v>32.766249950757</v>
+        <v>32.768288067315</v>
       </c>
       <c r="K481" t="n">
-        <v>-117.154010653111</v>
+        <v>-117.172866645828</v>
       </c>
       <c r="L481" t="n">
-        <v>1135.3</v>
+        <v>642.8</v>
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>415pp on Jul 26, 2026, 1135 m from Fashion Valley (1100 CAMINO DEL RIO NORTH). Case #E26070036804 (use for a records request — full narratives are not published in open data).</t>
+          <t>11-8 on Jul 26, 2026, 643 m from Fashion Valley (6800 FRIARS RD). Case #E26070037911 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -31379,15 +31379,15 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>E26070036910</t>
+          <t>E26070037537</t>
         </is>
       </c>
       <c r="E482" s="3" t="n">
-        <v>46229.07847222222</v>
+        <v>46229.60693287037</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>415V</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
@@ -31397,26 +31397,26 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t>5200 MISSION CENTER RD</t>
+          <t>6900 FRIARS RD</t>
         </is>
       </c>
       <c r="J482" t="n">
-        <v>32.770034888303</v>
+        <v>32.768802058993</v>
       </c>
       <c r="K482" t="n">
-        <v>-117.154657341608</v>
+        <v>-117.171569461601</v>
       </c>
       <c r="L482" t="n">
-        <v>1108.1</v>
+        <v>537.4</v>
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>1151 on Jul 26, 2026, 1108 m from Fashion Valley (5200 MISSION CENTER RD). Case #E26070036910 (use for a records request — full narratives are not published in open data).</t>
+          <t>415v on Jul 26, 2026, 537 m from Fashion Valley (6900 FRIARS RD). Case #E26070037537 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -31438,15 +31438,15 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>E26070041201</t>
+          <t>E26070038020</t>
         </is>
       </c>
       <c r="E483" s="3" t="n">
-        <v>46232.01451388889</v>
+        <v>46229.89195601852</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>AU2</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
@@ -31456,26 +31456,26 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>5700 MISSION CENTER RD</t>
+          <t>1900 HOTEL CIRCLE NORTH</t>
         </is>
       </c>
       <c r="J483" t="n">
-        <v>32.77719888635</v>
+        <v>32.759628968658</v>
       </c>
       <c r="K483" t="n">
-        <v>-117.15461034814</v>
+        <v>-117.178696371386</v>
       </c>
       <c r="L483" t="n">
-        <v>1530.7</v>
+        <v>1460.7</v>
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>1087 on Jul 29, 2026, 1531 m from Fashion Valley (5700 MISSION CENTER RD). Case #E26070041201 (use for a records request — full narratives are not published in open data).</t>
+          <t>Au2 on Jul 26, 2026, 1461 m from Fashion Valley (1900 HOTEL CIRCLE NORTH). Case #E26070038020 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -31497,15 +31497,15 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>E26070037011</t>
+          <t>E26070038144</t>
         </is>
       </c>
       <c r="E484" s="3" t="n">
-        <v>46229.18601851852</v>
+        <v>46229.96445601852</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>594</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
@@ -31515,26 +31515,26 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>7700 HAZARD CENTER DR</t>
+          <t>1200 FASHION VALLEY RD</t>
         </is>
       </c>
       <c r="J484" t="n">
-        <v>32.770935601241</v>
+        <v>32.76745627379</v>
       </c>
       <c r="K484" t="n">
-        <v>-117.156166110813</v>
+        <v>-117.171245398889</v>
       </c>
       <c r="L484" t="n">
-        <v>1007.9</v>
+        <v>483.2</v>
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>211 on Jul 26, 2026, 1008 m from Fashion Valley (7700 HAZARD CENTER DR). Case #E26070037011 (use for a records request — full narratives are not published in open data).</t>
+          <t>594 on Jul 26, 2026, 483 m from Fashion Valley (1200 FASHION VALLEY RD). Case #E26070038144 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -31556,15 +31556,15 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>E26070037808</t>
+          <t>E26070036804</t>
         </is>
       </c>
       <c r="E485" s="3" t="n">
-        <v>46229.76173611111</v>
+        <v>46229.00714120371</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>415PP</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
@@ -31579,21 +31579,21 @@
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>7700 HAZARD CENTER DR</t>
+          <t>1100 CAMINO DEL RIO NORTH</t>
         </is>
       </c>
       <c r="J485" t="n">
-        <v>32.770935601241</v>
+        <v>32.766249950757</v>
       </c>
       <c r="K485" t="n">
-        <v>-117.156166110813</v>
+        <v>-117.154010653111</v>
       </c>
       <c r="L485" t="n">
-        <v>1007.9</v>
+        <v>1135.3</v>
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>415 on Jul 26, 2026, 1008 m from Fashion Valley (7700 HAZARD CENTER DR). Case #E26070037808 (use for a records request — full narratives are not published in open data).</t>
+          <t>415pp on Jul 26, 2026, 1135 m from Fashion Valley (1100 CAMINO DEL RIO NORTH). Case #E26070036804 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -31615,15 +31615,15 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>E26070038187</t>
+          <t>E26070036910</t>
         </is>
       </c>
       <c r="E486" s="3" t="n">
-        <v>46230.00104166667</v>
+        <v>46229.07847222222</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
@@ -31638,21 +31638,21 @@
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>5300 MISSION CENTER RD</t>
+          <t>5200 MISSION CENTER RD</t>
         </is>
       </c>
       <c r="J486" t="n">
-        <v>32.770666615807</v>
+        <v>32.770034888303</v>
       </c>
       <c r="K486" t="n">
-        <v>-117.154875071922</v>
+        <v>-117.154657341608</v>
       </c>
       <c r="L486" t="n">
-        <v>1109.6</v>
+        <v>1108.1</v>
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>T on Jul 27, 2026, 1110 m from Fashion Valley (5300 MISSION CENTER RD). Case #E26070038187 (use for a records request — full narratives are not published in open data).</t>
+          <t>1151 on Jul 26, 2026, 1108 m from Fashion Valley (5200 MISSION CENTER RD). Case #E26070036910 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -31674,15 +31674,15 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>E26070038210</t>
+          <t>E26070041201</t>
         </is>
       </c>
       <c r="E487" s="3" t="n">
-        <v>46230.02491898148</v>
+        <v>46232.01451388889</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>459HP</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
@@ -31697,21 +31697,21 @@
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>7000 FRIARS RD</t>
+          <t>5700 MISSION CENTER RD</t>
         </is>
       </c>
       <c r="J487" t="n">
-        <v>32.769515710089</v>
+        <v>32.77719888635</v>
       </c>
       <c r="K487" t="n">
-        <v>-117.169790033203</v>
+        <v>-117.15461034814</v>
       </c>
       <c r="L487" t="n">
-        <v>420.9</v>
+        <v>1530.7</v>
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>459hp on Jul 27, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070038210 (use for a records request — full narratives are not published in open data).</t>
+          <t>1087 on Jul 29, 2026, 1531 m from Fashion Valley (5700 MISSION CENTER RD). Case #E26070041201 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -31733,15 +31733,15 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>E26070041846</t>
+          <t>E26070037011</t>
         </is>
       </c>
       <c r="E488" s="3" t="n">
-        <v>46232.51957175926</v>
+        <v>46229.18601851852</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>459R</t>
+          <t>211</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
@@ -31756,21 +31756,21 @@
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>7000 FRIARS RD</t>
+          <t>7700 HAZARD CENTER DR</t>
         </is>
       </c>
       <c r="J488" t="n">
-        <v>32.769515710089</v>
+        <v>32.770935601241</v>
       </c>
       <c r="K488" t="n">
-        <v>-117.169790033203</v>
+        <v>-117.156166110813</v>
       </c>
       <c r="L488" t="n">
-        <v>420.9</v>
+        <v>1007.9</v>
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>459r on Jul 29, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070041846 (use for a records request — full narratives are not published in open data).</t>
+          <t>211 on Jul 26, 2026, 1008 m from Fashion Valley (7700 HAZARD CENTER DR). Case #E26070037011 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -31792,15 +31792,15 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>E26070041405</t>
+          <t>E26070037808</t>
         </is>
       </c>
       <c r="E489" s="3" t="n">
-        <v>46232.29825231482</v>
+        <v>46229.76173611111</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>415</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
@@ -31810,26 +31810,26 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>K</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>5600 MISSION CENTER RD</t>
+          <t>7700 HAZARD CENTER DR</t>
         </is>
       </c>
       <c r="J489" t="n">
-        <v>32.775588244581</v>
+        <v>32.770935601241</v>
       </c>
       <c r="K489" t="n">
-        <v>-117.154010732639</v>
+        <v>-117.156166110813</v>
       </c>
       <c r="L489" t="n">
-        <v>1451.6</v>
+        <v>1007.9</v>
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>1151 on Jul 29, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070041405 (use for a records request — full narratives are not published in open data).</t>
+          <t>415 on Jul 26, 2026, 1008 m from Fashion Valley (7700 HAZARD CENTER DR). Case #E26070037808 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -31851,15 +31851,15 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>E26070043326</t>
+          <t>E26070038187</t>
         </is>
       </c>
       <c r="E490" s="3" t="n">
-        <v>46233.56378472222</v>
+        <v>46230.00104166667</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
@@ -31874,21 +31874,21 @@
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>1200 CAMINO DEL RIO NORTH</t>
+          <t>5300 MISSION CENTER RD</t>
         </is>
       </c>
       <c r="J490" t="n">
-        <v>32.766861158912</v>
+        <v>32.770666615807</v>
       </c>
       <c r="K490" t="n">
-        <v>-117.151286132201</v>
+        <v>-117.154875071922</v>
       </c>
       <c r="L490" t="n">
-        <v>1384.3</v>
+        <v>1109.6</v>
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>415 on Jul 30, 2026, 1384 m from Fashion Valley (1200 CAMINO DEL RIO NORTH). Case #E26070043326 (use for a records request — full narratives are not published in open data).</t>
+          <t>T on Jul 27, 2026, 1110 m from Fashion Valley (5300 MISSION CENTER RD). Case #E26070038187 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -31910,15 +31910,15 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>E26070043437</t>
+          <t>E26070038210</t>
         </is>
       </c>
       <c r="E491" s="3" t="n">
-        <v>46233.62685185186</v>
+        <v>46230.02491898148</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>211A</t>
+          <t>459HP</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
@@ -31933,21 +31933,21 @@
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>5600 MISSION CENTER RD</t>
+          <t>7000 FRIARS RD</t>
         </is>
       </c>
       <c r="J491" t="n">
-        <v>32.775588244581</v>
+        <v>32.769515710089</v>
       </c>
       <c r="K491" t="n">
-        <v>-117.154010732639</v>
+        <v>-117.169790033203</v>
       </c>
       <c r="L491" t="n">
-        <v>1451.6</v>
+        <v>420.9</v>
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>211a on Jul 30, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070043437 (use for a records request — full narratives are not published in open data).</t>
+          <t>459hp on Jul 27, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070038210 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -31969,15 +31969,15 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>E26070043442</t>
+          <t>E26070041846</t>
         </is>
       </c>
       <c r="E492" s="3" t="n">
-        <v>46233.63097222222</v>
+        <v>46232.51957175926</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>CW</t>
+          <t>459R</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
@@ -32006,7 +32006,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Cw on Jul 30, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070043442 (use for a records request — full narratives are not published in open data).</t>
+          <t>459r on Jul 29, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070041846 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -32028,15 +32028,15 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>E26070043526</t>
+          <t>E26070041405</t>
         </is>
       </c>
       <c r="E493" s="3" t="n">
-        <v>46233.67606481481</v>
+        <v>46232.29825231482</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>487R</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
@@ -32046,26 +32046,26 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>6900 FRIARS RD</t>
+          <t>5600 MISSION CENTER RD</t>
         </is>
       </c>
       <c r="J493" t="n">
-        <v>32.768802058993</v>
+        <v>32.775588244581</v>
       </c>
       <c r="K493" t="n">
-        <v>-117.171569461601</v>
+        <v>-117.154010732639</v>
       </c>
       <c r="L493" t="n">
-        <v>537.4</v>
+        <v>1451.6</v>
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>487r on Jul 30, 2026, 537 m from Fashion Valley (6900 FRIARS RD). Case #E26070043526 (use for a records request — full narratives are not published in open data).</t>
+          <t>1151 on Jul 29, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070041405 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -32087,15 +32087,15 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>E26070043551</t>
+          <t>E26070043326</t>
         </is>
       </c>
       <c r="E494" s="3" t="n">
-        <v>46233.68956018519</v>
+        <v>46233.56378472222</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>10851R</t>
+          <t>415</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
@@ -32105,26 +32105,26 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>K</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>600 HOTEL CIRCLE SOUTH</t>
+          <t>1200 CAMINO DEL RIO NORTH</t>
         </is>
       </c>
       <c r="J494" t="n">
-        <v>32.761115185306</v>
+        <v>32.766861158912</v>
       </c>
       <c r="K494" t="n">
-        <v>-117.169262923224</v>
+        <v>-117.151286132201</v>
       </c>
       <c r="L494" t="n">
-        <v>757</v>
+        <v>1384.3</v>
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>10851r on Jul 30, 2026, 757 m from Fashion Valley (600 HOTEL CIRCLE SOUTH). Case #E26070043551 (use for a records request — full narratives are not published in open data).</t>
+          <t>415 on Jul 30, 2026, 1384 m from Fashion Valley (1200 CAMINO DEL RIO NORTH). Case #E26070043326 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -32146,15 +32146,15 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>E26070043602</t>
+          <t>E26070043437</t>
         </is>
       </c>
       <c r="E495" s="3" t="n">
-        <v>46233.71741898148</v>
+        <v>46233.62685185186</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>211A</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
@@ -32169,21 +32169,21 @@
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t>1200 CAMINO DEL RIO NORTH</t>
+          <t>5600 MISSION CENTER RD</t>
         </is>
       </c>
       <c r="J495" t="n">
-        <v>32.766861158912</v>
+        <v>32.775588244581</v>
       </c>
       <c r="K495" t="n">
-        <v>-117.151286132201</v>
+        <v>-117.154010732639</v>
       </c>
       <c r="L495" t="n">
-        <v>1384.3</v>
+        <v>1451.6</v>
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>488 on Jul 30, 2026, 1384 m from Fashion Valley (1200 CAMINO DEL RIO NORTH). Case #E26070043602 (use for a records request — full narratives are not published in open data).</t>
+          <t>211a on Jul 30, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070043437 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -32205,15 +32205,15 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>E26070043693</t>
+          <t>E26070043442</t>
         </is>
       </c>
       <c r="E496" s="3" t="n">
-        <v>46233.77357638889</v>
+        <v>46233.63097222222</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>CW</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
@@ -32223,7 +32223,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>K</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -32242,7 +32242,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>211 on Jul 30, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070043693 (use for a records request — full narratives are not published in open data).</t>
+          <t>Cw on Jul 30, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070043442 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -32264,15 +32264,15 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>E26070043857</t>
+          <t>E26070043526</t>
         </is>
       </c>
       <c r="E497" s="3" t="n">
-        <v>46233.87652777778</v>
+        <v>46233.67606481481</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>CW</t>
+          <t>487R</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
@@ -32282,26 +32282,26 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>7000 FRIARS RD</t>
+          <t>6900 FRIARS RD</t>
         </is>
       </c>
       <c r="J497" t="n">
-        <v>32.769515710089</v>
+        <v>32.768802058993</v>
       </c>
       <c r="K497" t="n">
-        <v>-117.169790033203</v>
+        <v>-117.171569461601</v>
       </c>
       <c r="L497" t="n">
-        <v>420.9</v>
+        <v>537.4</v>
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Cw on Jul 30, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070043857 (use for a records request — full narratives are not published in open data).</t>
+          <t>487r on Jul 30, 2026, 537 m from Fashion Valley (6900 FRIARS RD). Case #E26070043526 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -32323,15 +32323,15 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>E26070042725</t>
+          <t>E26070043551</t>
         </is>
       </c>
       <c r="E498" s="3" t="n">
-        <v>46233.12034722222</v>
+        <v>46233.68956018519</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>10851R</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
@@ -32341,26 +32341,26 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>500 HOTEL CIRCLE SOUTH</t>
+          <t>600 HOTEL CIRCLE SOUTH</t>
         </is>
       </c>
       <c r="J498" t="n">
-        <v>32.761281414433</v>
+        <v>32.761115185306</v>
       </c>
       <c r="K498" t="n">
-        <v>-117.168573310454</v>
+        <v>-117.169262923224</v>
       </c>
       <c r="L498" t="n">
-        <v>716.5</v>
+        <v>757</v>
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>415 on Jul 30, 2026, 717 m from Fashion Valley (500 HOTEL CIRCLE SOUTH). Case #E26070042725 (use for a records request — full narratives are not published in open data).</t>
+          <t>10851r on Jul 30, 2026, 757 m from Fashion Valley (600 HOTEL CIRCLE SOUTH). Case #E26070043551 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -32382,15 +32382,15 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>E26070036092</t>
+          <t>E26070043602</t>
         </is>
       </c>
       <c r="E499" s="3" t="n">
-        <v>46228.62349537037</v>
+        <v>46233.71741898148</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>594R</t>
+          <t>488</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
@@ -32405,21 +32405,21 @@
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>6500 FRIARS RD</t>
+          <t>1200 CAMINO DEL RIO NORTH</t>
         </is>
       </c>
       <c r="J499" t="n">
-        <v>32.766853831795</v>
+        <v>32.766861158912</v>
       </c>
       <c r="K499" t="n">
-        <v>-117.177313895974</v>
+        <v>-117.151286132201</v>
       </c>
       <c r="L499" t="n">
-        <v>1052.1</v>
+        <v>1384.3</v>
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>594r on Jul 25, 2026, 1052 m from Fashion Valley (6500 FRIARS RD). Case #E26070036092 (use for a records request — full narratives are not published in open data).</t>
+          <t>488 on Jul 30, 2026, 1384 m from Fashion Valley (1200 CAMINO DEL RIO NORTH). Case #E26070043602 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -32441,15 +32441,15 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>E26070041720</t>
+          <t>E26070043693</t>
         </is>
       </c>
       <c r="E500" s="3" t="n">
-        <v>46232.45722222222</v>
+        <v>46233.77357638889</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>TARASOFF</t>
+          <t>211</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
@@ -32459,26 +32459,26 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>400 CAMINO DEL RIO SOUTH</t>
+          <t>7000 FRIARS RD</t>
         </is>
       </c>
       <c r="J500" t="n">
-        <v>32.76100095804</v>
+        <v>32.769515710089</v>
       </c>
       <c r="K500" t="n">
-        <v>-117.161321780527</v>
+        <v>-117.169790033203</v>
       </c>
       <c r="L500" t="n">
-        <v>836.7</v>
+        <v>420.9</v>
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Tarasoff on Jul 29, 2026, 837 m from Fashion Valley (400 CAMINO DEL RIO SOUTH). Case #E26070041720 (use for a records request — full narratives are not published in open data).</t>
+          <t>211 on Jul 30, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070043693 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -32500,15 +32500,15 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>E26070042696</t>
+          <t>E26070043857</t>
         </is>
       </c>
       <c r="E501" s="3" t="n">
-        <v>46233.08091435185</v>
+        <v>46233.87652777778</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>10851E</t>
+          <t>CW</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
@@ -32537,7 +32537,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>10851e on Jul 30, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070042696 (use for a records request — full narratives are not published in open data).</t>
+          <t>Cw on Jul 30, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070043857 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -32559,15 +32559,15 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>E26070042700</t>
+          <t>E26070042725</t>
         </is>
       </c>
       <c r="E502" s="3" t="n">
-        <v>46233.08909722222</v>
+        <v>46233.12034722222</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>459A</t>
+          <t>415</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
@@ -32582,21 +32582,21 @@
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>5600 MISSION CENTER RD</t>
+          <t>500 HOTEL CIRCLE SOUTH</t>
         </is>
       </c>
       <c r="J502" t="n">
-        <v>32.775588244581</v>
+        <v>32.761281414433</v>
       </c>
       <c r="K502" t="n">
-        <v>-117.154010732639</v>
+        <v>-117.168573310454</v>
       </c>
       <c r="L502" t="n">
-        <v>1451.6</v>
+        <v>716.5</v>
       </c>
       <c r="M502" t="inlineStr">
         <is>
-          <t>459a on Jul 30, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070042700 (use for a records request — full narratives are not published in open data).</t>
+          <t>415 on Jul 30, 2026, 717 m from Fashion Valley (500 HOTEL CIRCLE SOUTH). Case #E26070042725 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -32618,15 +32618,15 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>E26070042703</t>
+          <t>E26070036092</t>
         </is>
       </c>
       <c r="E503" s="3" t="n">
-        <v>46233.09315972222</v>
+        <v>46228.62349537037</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>594R</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
@@ -32641,21 +32641,21 @@
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>400 HOTEL CIRCLE SOUTH</t>
+          <t>6500 FRIARS RD</t>
         </is>
       </c>
       <c r="J503" t="n">
-        <v>32.761426735043</v>
+        <v>32.766853831795</v>
       </c>
       <c r="K503" t="n">
-        <v>-117.168017960012</v>
+        <v>-117.177313895974</v>
       </c>
       <c r="L503" t="n">
-        <v>685.7</v>
+        <v>1052.1</v>
       </c>
       <c r="M503" t="inlineStr">
         <is>
-          <t>1131 on Jul 30, 2026, 686 m from Fashion Valley (400 HOTEL CIRCLE SOUTH). Case #E26070042703 (use for a records request — full narratives are not published in open data).</t>
+          <t>594r on Jul 25, 2026, 1052 m from Fashion Valley (6500 FRIARS RD). Case #E26070036092 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -32677,15 +32677,15 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>E26070042625</t>
+          <t>E26070041720</t>
         </is>
       </c>
       <c r="E504" s="3" t="n">
-        <v>46233.00914351852</v>
+        <v>46232.45722222222</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>415V</t>
+          <t>TARASOFF</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
@@ -32700,21 +32700,21 @@
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>600 CAMINO DEL RIO SOUTH</t>
+          <t>400 CAMINO DEL RIO SOUTH</t>
         </is>
       </c>
       <c r="J504" t="n">
-        <v>32.763192918349</v>
+        <v>32.76100095804</v>
       </c>
       <c r="K504" t="n">
-        <v>-117.160257283461</v>
+        <v>-117.161321780527</v>
       </c>
       <c r="L504" t="n">
-        <v>715.8</v>
+        <v>836.7</v>
       </c>
       <c r="M504" t="inlineStr">
         <is>
-          <t>415v on Jul 30, 2026, 716 m from Fashion Valley (600 CAMINO DEL RIO SOUTH). Case #E26070042625 (use for a records request — full narratives are not published in open data).</t>
+          <t>Tarasoff on Jul 29, 2026, 837 m from Fashion Valley (400 CAMINO DEL RIO SOUTH). Case #E26070041720 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -32736,15 +32736,15 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>E26070042662</t>
+          <t>E26070042696</t>
         </is>
       </c>
       <c r="E505" s="3" t="n">
-        <v>46233.04231481482</v>
+        <v>46233.08091435185</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>459A</t>
+          <t>10851E</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
@@ -32759,21 +32759,21 @@
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>5100 MISSION CENTER RD</t>
+          <t>7000 FRIARS RD</t>
         </is>
       </c>
       <c r="J505" t="n">
-        <v>32.76820380818</v>
+        <v>32.769515710089</v>
       </c>
       <c r="K505" t="n">
-        <v>-117.153929083437</v>
+        <v>-117.169790033203</v>
       </c>
       <c r="L505" t="n">
-        <v>1139.7</v>
+        <v>420.9</v>
       </c>
       <c r="M505" t="inlineStr">
         <is>
-          <t>459a on Jul 30, 2026, 1140 m from Fashion Valley (5100 MISSION CENTER RD). Case #E26070042662 (use for a records request — full narratives are not published in open data).</t>
+          <t>10851e on Jul 30, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070042696 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -32795,15 +32795,15 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>E26070042356</t>
+          <t>E26070042700</t>
         </is>
       </c>
       <c r="E506" s="3" t="n">
-        <v>46232.80671296296</v>
+        <v>46233.08909722222</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>20002R</t>
+          <t>459A</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
@@ -32818,21 +32818,21 @@
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>300 CAMINO DE LA REINA</t>
+          <t>5600 MISSION CENTER RD</t>
         </is>
       </c>
       <c r="J506" t="n">
-        <v>32.764468174789</v>
+        <v>32.775588244581</v>
       </c>
       <c r="K506" t="n">
-        <v>-117.164515919347</v>
+        <v>-117.154010732639</v>
       </c>
       <c r="L506" t="n">
-        <v>354.6</v>
+        <v>1451.6</v>
       </c>
       <c r="M506" t="inlineStr">
         <is>
-          <t>20002r on Jul 29, 2026, 355 m from Fashion Valley (300 CAMINO DE LA REINA). Case #E26070042356 (use for a records request — full narratives are not published in open data).</t>
+          <t>459a on Jul 30, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070042700 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -32854,15 +32854,15 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>E26070042371</t>
+          <t>E26070042703</t>
         </is>
       </c>
       <c r="E507" s="3" t="n">
-        <v>46232.81894675926</v>
+        <v>46233.09315972222</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>10851R</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
@@ -32872,26 +32872,26 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>K</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>600 HOTEL CIRCLE SOUTH</t>
+          <t>400 HOTEL CIRCLE SOUTH</t>
         </is>
       </c>
       <c r="J507" t="n">
-        <v>32.761115185306</v>
+        <v>32.761426735043</v>
       </c>
       <c r="K507" t="n">
-        <v>-117.169262923224</v>
+        <v>-117.168017960012</v>
       </c>
       <c r="L507" t="n">
-        <v>757</v>
+        <v>685.7</v>
       </c>
       <c r="M507" t="inlineStr">
         <is>
-          <t>10851r on Jul 29, 2026, 757 m from Fashion Valley (600 HOTEL CIRCLE SOUTH). Case #E26070042371 (use for a records request — full narratives are not published in open data).</t>
+          <t>1131 on Jul 30, 2026, 686 m from Fashion Valley (400 HOTEL CIRCLE SOUTH). Case #E26070042703 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -32913,15 +32913,15 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>E26070040323</t>
+          <t>E26070042625</t>
         </is>
       </c>
       <c r="E508" s="3" t="n">
-        <v>46231.49828703704</v>
+        <v>46233.00914351852</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>CW</t>
+          <t>415V</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
@@ -32936,21 +32936,21 @@
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>500 HOTEL CIRCLE SOUTH</t>
+          <t>600 CAMINO DEL RIO SOUTH</t>
         </is>
       </c>
       <c r="J508" t="n">
-        <v>32.761281414433</v>
+        <v>32.763192918349</v>
       </c>
       <c r="K508" t="n">
-        <v>-117.168573310454</v>
+        <v>-117.160257283461</v>
       </c>
       <c r="L508" t="n">
-        <v>716.5</v>
+        <v>715.8</v>
       </c>
       <c r="M508" t="inlineStr">
         <is>
-          <t>Cw on Jul 28, 2026, 717 m from Fashion Valley (500 HOTEL CIRCLE SOUTH). Case #E26070040323 (use for a records request — full narratives are not published in open data).</t>
+          <t>415v on Jul 30, 2026, 716 m from Fashion Valley (600 CAMINO DEL RIO SOUTH). Case #E26070042625 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -32972,15 +32972,15 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>E26070040372</t>
+          <t>E26070042662</t>
         </is>
       </c>
       <c r="E509" s="3" t="n">
-        <v>46231.52674768519</v>
+        <v>46233.04231481482</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>459A</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
@@ -32995,21 +32995,21 @@
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>1500 ULRIC ST</t>
+          <t>5100 MISSION CENTER RD</t>
         </is>
       </c>
       <c r="J509" t="n">
-        <v>32.773883020934</v>
+        <v>32.76820380818</v>
       </c>
       <c r="K509" t="n">
-        <v>-117.167950263495</v>
+        <v>-117.153929083437</v>
       </c>
       <c r="L509" t="n">
-        <v>744.6</v>
+        <v>1139.7</v>
       </c>
       <c r="M509" t="inlineStr">
         <is>
-          <t>1186 on Jul 28, 2026, 745 m from Fashion Valley (1500 ULRIC ST). Case #E26070040372 (use for a records request — full narratives are not published in open data).</t>
+          <t>459a on Jul 30, 2026, 1140 m from Fashion Valley (5100 MISSION CENTER RD). Case #E26070042662 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -33031,15 +33031,15 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>E26070040385</t>
+          <t>E26070042356</t>
         </is>
       </c>
       <c r="E510" s="3" t="n">
-        <v>46231.5353587963</v>
+        <v>46232.80671296296</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>415V</t>
+          <t>20002R</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
@@ -33054,21 +33054,21 @@
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>7000 FRIARS RD</t>
+          <t>300 CAMINO DE LA REINA</t>
         </is>
       </c>
       <c r="J510" t="n">
-        <v>32.769515710089</v>
+        <v>32.764468174789</v>
       </c>
       <c r="K510" t="n">
-        <v>-117.169790033203</v>
+        <v>-117.164515919347</v>
       </c>
       <c r="L510" t="n">
-        <v>420.9</v>
+        <v>354.6</v>
       </c>
       <c r="M510" t="inlineStr">
         <is>
-          <t>415v on Jul 28, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070040385 (use for a records request — full narratives are not published in open data).</t>
+          <t>20002r on Jul 29, 2026, 355 m from Fashion Valley (300 CAMINO DE LA REINA). Case #E26070042356 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -33090,15 +33090,15 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>E26070040431</t>
+          <t>E26070042371</t>
         </is>
       </c>
       <c r="E511" s="3" t="n">
-        <v>46231.55746527778</v>
+        <v>46232.81894675926</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>10851R</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
@@ -33108,26 +33108,26 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>500 HOTEL CIRCLE NORTH</t>
+          <t>600 HOTEL CIRCLE SOUTH</t>
         </is>
       </c>
       <c r="J511" t="n">
-        <v>32.761281414433</v>
+        <v>32.761115185306</v>
       </c>
       <c r="K511" t="n">
-        <v>-117.168573310454</v>
+        <v>-117.169262923224</v>
       </c>
       <c r="L511" t="n">
-        <v>716.5</v>
+        <v>757</v>
       </c>
       <c r="M511" t="inlineStr">
         <is>
-          <t>911 on Jul 28, 2026, 717 m from Fashion Valley (500 HOTEL CIRCLE NORTH). Case #E26070040431 (use for a records request — full narratives are not published in open data).</t>
+          <t>10851r on Jul 29, 2026, 757 m from Fashion Valley (600 HOTEL CIRCLE SOUTH). Case #E26070042371 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -33149,15 +33149,15 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>E26070041203</t>
+          <t>E26070040323</t>
         </is>
       </c>
       <c r="E512" s="3" t="n">
-        <v>46232.01657407408</v>
+        <v>46231.49828703704</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>CW</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
@@ -33172,21 +33172,21 @@
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>1800 HOTEL CIRCLE SOUTH</t>
+          <t>500 HOTEL CIRCLE SOUTH</t>
         </is>
       </c>
       <c r="J512" t="n">
-        <v>32.759597128436</v>
+        <v>32.761281414433</v>
       </c>
       <c r="K512" t="n">
-        <v>-117.177340012371</v>
+        <v>-117.168573310454</v>
       </c>
       <c r="L512" t="n">
-        <v>1362.6</v>
+        <v>716.5</v>
       </c>
       <c r="M512" t="inlineStr">
         <is>
-          <t>415 on Jul 29, 2026, 1363 m from Fashion Valley (1800 HOTEL CIRCLE SOUTH). Case #E26070041203 (use for a records request — full narratives are not published in open data).</t>
+          <t>Cw on Jul 28, 2026, 717 m from Fashion Valley (500 HOTEL CIRCLE SOUTH). Case #E26070040323 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -33208,15 +33208,15 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>E26070042324</t>
+          <t>E26070040372</t>
         </is>
       </c>
       <c r="E513" s="3" t="n">
-        <v>46232.78690972222</v>
+        <v>46231.52674768519</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>415V</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
@@ -33226,26 +33226,26 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>K</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>1900 HOTEL CIRCLE NORTH</t>
+          <t>1500 ULRIC ST</t>
         </is>
       </c>
       <c r="J513" t="n">
-        <v>32.759628968658</v>
+        <v>32.773883020934</v>
       </c>
       <c r="K513" t="n">
-        <v>-117.178696371386</v>
+        <v>-117.167950263495</v>
       </c>
       <c r="L513" t="n">
-        <v>1460.7</v>
+        <v>744.6</v>
       </c>
       <c r="M513" t="inlineStr">
         <is>
-          <t>415v on Jul 29, 2026, 1461 m from Fashion Valley (1900 HOTEL CIRCLE NORTH). Case #E26070042324 (use for a records request — full narratives are not published in open data).</t>
+          <t>1186 on Jul 28, 2026, 745 m from Fashion Valley (1500 ULRIC ST). Case #E26070040372 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -33267,15 +33267,15 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>E26070041219</t>
+          <t>E26070040385</t>
         </is>
       </c>
       <c r="E514" s="3" t="n">
-        <v>46232.03488425926</v>
+        <v>46231.5353587963</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>415V</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
@@ -33290,21 +33290,21 @@
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>1800 HOTEL CIRCLE SOUTH</t>
+          <t>7000 FRIARS RD</t>
         </is>
       </c>
       <c r="J514" t="n">
-        <v>32.759597128436</v>
+        <v>32.769515710089</v>
       </c>
       <c r="K514" t="n">
-        <v>-117.177340012371</v>
+        <v>-117.169790033203</v>
       </c>
       <c r="L514" t="n">
-        <v>1362.6</v>
+        <v>420.9</v>
       </c>
       <c r="M514" t="inlineStr">
         <is>
-          <t>415 on Jul 29, 2026, 1363 m from Fashion Valley (1800 HOTEL CIRCLE SOUTH). Case #E26070041219 (use for a records request — full narratives are not published in open data).</t>
+          <t>415v on Jul 28, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070040385 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -33326,15 +33326,15 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>E26070041364</t>
+          <t>E26070040431</t>
         </is>
       </c>
       <c r="E515" s="3" t="n">
-        <v>46232.27206018518</v>
+        <v>46231.55746527778</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>10851E</t>
+          <t>911</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
@@ -33344,26 +33344,26 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>7000 FRIARS RD</t>
+          <t>500 HOTEL CIRCLE NORTH</t>
         </is>
       </c>
       <c r="J515" t="n">
-        <v>32.769515710089</v>
+        <v>32.761281414433</v>
       </c>
       <c r="K515" t="n">
-        <v>-117.169790033203</v>
+        <v>-117.168573310454</v>
       </c>
       <c r="L515" t="n">
-        <v>420.9</v>
+        <v>716.5</v>
       </c>
       <c r="M515" t="inlineStr">
         <is>
-          <t>10851e on Jul 29, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070041364 (use for a records request — full narratives are not published in open data).</t>
+          <t>911 on Jul 28, 2026, 717 m from Fashion Valley (500 HOTEL CIRCLE NORTH). Case #E26070040431 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -33385,11 +33385,11 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>E26070041775</t>
+          <t>E26070041203</t>
         </is>
       </c>
       <c r="E516" s="3" t="n">
-        <v>46232.48231481481</v>
+        <v>46232.01657407408</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -33408,21 +33408,21 @@
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>5600 MISSION CENTER RD</t>
+          <t>1800 HOTEL CIRCLE SOUTH</t>
         </is>
       </c>
       <c r="J516" t="n">
-        <v>32.775588244581</v>
+        <v>32.759597128436</v>
       </c>
       <c r="K516" t="n">
-        <v>-117.154010732639</v>
+        <v>-117.177340012371</v>
       </c>
       <c r="L516" t="n">
-        <v>1451.6</v>
+        <v>1362.6</v>
       </c>
       <c r="M516" t="inlineStr">
         <is>
-          <t>415 on Jul 29, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070041775 (use for a records request — full narratives are not published in open data).</t>
+          <t>415 on Jul 29, 2026, 1363 m from Fashion Valley (1800 HOTEL CIRCLE SOUTH). Case #E26070041203 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -33444,15 +33444,15 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>E26070041499</t>
+          <t>E26070042324</t>
         </is>
       </c>
       <c r="E517" s="3" t="n">
-        <v>46232.35490740741</v>
+        <v>46232.78690972222</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>415V</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
@@ -33462,26 +33462,26 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t>1400 ULRIC ST</t>
+          <t>1900 HOTEL CIRCLE NORTH</t>
         </is>
       </c>
       <c r="J517" t="n">
-        <v>32.771634475997</v>
+        <v>32.759628968658</v>
       </c>
       <c r="K517" t="n">
-        <v>-117.163423466353</v>
+        <v>-117.178696371386</v>
       </c>
       <c r="L517" t="n">
-        <v>534.8</v>
+        <v>1460.7</v>
       </c>
       <c r="M517" t="inlineStr">
         <is>
-          <t>1186 on Jul 29, 2026, 535 m from Fashion Valley (1400 ULRIC ST). Case #E26070041499 (use for a records request — full narratives are not published in open data).</t>
+          <t>415v on Jul 29, 2026, 1461 m from Fashion Valley (1900 HOTEL CIRCLE NORTH). Case #E26070042324 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -33503,11 +33503,11 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>E26070041500</t>
+          <t>E26070041219</t>
         </is>
       </c>
       <c r="E518" s="3" t="n">
-        <v>46232.35491898148</v>
+        <v>46232.03488425926</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -33526,21 +33526,21 @@
       </c>
       <c r="I518" t="inlineStr">
         <is>
-          <t>5600 MISSION CENTER RD</t>
+          <t>1800 HOTEL CIRCLE SOUTH</t>
         </is>
       </c>
       <c r="J518" t="n">
-        <v>32.775588244581</v>
+        <v>32.759597128436</v>
       </c>
       <c r="K518" t="n">
-        <v>-117.154010732639</v>
+        <v>-117.177340012371</v>
       </c>
       <c r="L518" t="n">
-        <v>1451.6</v>
+        <v>1362.6</v>
       </c>
       <c r="M518" t="inlineStr">
         <is>
-          <t>415 on Jul 29, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070041500 (use for a records request — full narratives are not published in open data).</t>
+          <t>415 on Jul 29, 2026, 1363 m from Fashion Valley (1800 HOTEL CIRCLE SOUTH). Case #E26070041219 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -33562,15 +33562,15 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>E26070041029</t>
+          <t>E26070041364</t>
         </is>
       </c>
       <c r="E519" s="3" t="n">
-        <v>46231.88591435185</v>
+        <v>46232.27206018518</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>CW</t>
+          <t>10851E</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
@@ -33580,26 +33580,26 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>K</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>1200 CAMINO DEL RIO NORTH</t>
+          <t>7000 FRIARS RD</t>
         </is>
       </c>
       <c r="J519" t="n">
-        <v>32.766861158912</v>
+        <v>32.769515710089</v>
       </c>
       <c r="K519" t="n">
-        <v>-117.151286132201</v>
+        <v>-117.169790033203</v>
       </c>
       <c r="L519" t="n">
-        <v>1384.3</v>
+        <v>420.9</v>
       </c>
       <c r="M519" t="inlineStr">
         <is>
-          <t>Cw on Jul 28, 2026, 1384 m from Fashion Valley (1200 CAMINO DEL RIO NORTH). Case #E26070041029 (use for a records request — full narratives are not published in open data).</t>
+          <t>10851e on Jul 29, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070041364 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -33621,15 +33621,15 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>E26070041447</t>
+          <t>E26070041775</t>
         </is>
       </c>
       <c r="E520" s="3" t="n">
-        <v>46232.32430555556</v>
+        <v>46232.48231481481</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>415</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
@@ -33644,21 +33644,21 @@
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>500 CAMINO DE LA REINA</t>
+          <t>5600 MISSION CENTER RD</t>
         </is>
       </c>
       <c r="J520" t="n">
-        <v>32.766480146474</v>
+        <v>32.775588244581</v>
       </c>
       <c r="K520" t="n">
-        <v>-117.160679937637</v>
+        <v>-117.154010732639</v>
       </c>
       <c r="L520" t="n">
-        <v>514.5</v>
+        <v>1451.6</v>
       </c>
       <c r="M520" t="inlineStr">
         <is>
-          <t>1186 on Jul 29, 2026, 514 m from Fashion Valley (500 CAMINO DE LA REINA). Case #E26070041447 (use for a records request — full narratives are not published in open data).</t>
+          <t>415 on Jul 29, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070041775 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -33680,15 +33680,15 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>E26070042989</t>
+          <t>E26070041499</t>
         </is>
       </c>
       <c r="E521" s="3" t="n">
-        <v>46233.38532407407</v>
+        <v>46232.35490740741</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>AU2</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
@@ -33698,26 +33698,26 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>K</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>7000 FRIARS RD</t>
+          <t>1400 ULRIC ST</t>
         </is>
       </c>
       <c r="J521" t="n">
-        <v>32.769515710089</v>
+        <v>32.771634475997</v>
       </c>
       <c r="K521" t="n">
-        <v>-117.169790033203</v>
+        <v>-117.163423466353</v>
       </c>
       <c r="L521" t="n">
-        <v>420.9</v>
+        <v>534.8</v>
       </c>
       <c r="M521" t="inlineStr">
         <is>
-          <t>Au2 on Jul 30, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070042989 (use for a records request — full narratives are not published in open data).</t>
+          <t>1186 on Jul 29, 2026, 535 m from Fashion Valley (1400 ULRIC ST). Case #E26070041499 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -33739,15 +33739,15 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>E26070042991</t>
+          <t>E26070041500</t>
         </is>
       </c>
       <c r="E522" s="3" t="n">
-        <v>46233.38563657407</v>
+        <v>46232.35491898148</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>CW</t>
+          <t>415</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
@@ -33757,26 +33757,26 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>K</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>1800 HOTEL CIRCLE SOUTH</t>
+          <t>5600 MISSION CENTER RD</t>
         </is>
       </c>
       <c r="J522" t="n">
-        <v>32.759597128436</v>
+        <v>32.775588244581</v>
       </c>
       <c r="K522" t="n">
-        <v>-117.177340012371</v>
+        <v>-117.154010732639</v>
       </c>
       <c r="L522" t="n">
-        <v>1362.6</v>
+        <v>1451.6</v>
       </c>
       <c r="M522" t="inlineStr">
         <is>
-          <t>Cw on Jul 30, 2026, 1363 m from Fashion Valley (1800 HOTEL CIRCLE SOUTH). Case #E26070042991 (use for a records request — full narratives are not published in open data).</t>
+          <t>415 on Jul 29, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070041500 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -33798,15 +33798,15 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>E26070043131</t>
+          <t>E26070041029</t>
         </is>
       </c>
       <c r="E523" s="3" t="n">
-        <v>46233.46133101852</v>
+        <v>46231.88591435185</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>CW</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
@@ -33816,26 +33816,26 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>5600 MISSION CENTER RD</t>
+          <t>1200 CAMINO DEL RIO NORTH</t>
         </is>
       </c>
       <c r="J523" t="n">
-        <v>32.775588244581</v>
+        <v>32.766861158912</v>
       </c>
       <c r="K523" t="n">
-        <v>-117.154010732639</v>
+        <v>-117.151286132201</v>
       </c>
       <c r="L523" t="n">
-        <v>1451.6</v>
+        <v>1384.3</v>
       </c>
       <c r="M523" t="inlineStr">
         <is>
-          <t>911 on Jul 30, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070043131 (use for a records request — full narratives are not published in open data).</t>
+          <t>Cw on Jul 28, 2026, 1384 m from Fashion Valley (1200 CAMINO DEL RIO NORTH). Case #E26070041029 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -33857,15 +33857,15 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>E26070043263</t>
+          <t>E26070041447</t>
         </is>
       </c>
       <c r="E524" s="3" t="n">
-        <v>46233.52984953704</v>
+        <v>46232.32430555556</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>AU2</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
@@ -33875,26 +33875,26 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>K</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>7900 MISSION CENTER CT</t>
+          <t>500 CAMINO DE LA REINA</t>
         </is>
       </c>
       <c r="J524" t="n">
-        <v>32.773605548078</v>
+        <v>32.766480146474</v>
       </c>
       <c r="K524" t="n">
-        <v>-117.154100182722</v>
+        <v>-117.160679937637</v>
       </c>
       <c r="L524" t="n">
-        <v>1317</v>
+        <v>514.5</v>
       </c>
       <c r="M524" t="inlineStr">
         <is>
-          <t>Au2 on Jul 30, 2026, 1317 m from Fashion Valley (7900 MISSION CENTER CT). Case #E26070043263 (use for a records request — full narratives are not published in open data).</t>
+          <t>1186 on Jul 29, 2026, 514 m from Fashion Valley (500 CAMINO DE LA REINA). Case #E26070041447 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -33916,15 +33916,15 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>E26070042098</t>
+          <t>E26070042989</t>
         </is>
       </c>
       <c r="E525" s="3" t="n">
-        <v>46232.65872685185</v>
+        <v>46233.38532407407</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>CW</t>
+          <t>AU2</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
@@ -33934,26 +33934,26 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>700 CAMINO DEL RIO NORTH</t>
+          <t>7000 FRIARS RD</t>
         </is>
       </c>
       <c r="J525" t="n">
-        <v>32.764930802223</v>
+        <v>32.769515710089</v>
       </c>
       <c r="K525" t="n">
-        <v>-117.158054620315</v>
+        <v>-117.169790033203</v>
       </c>
       <c r="L525" t="n">
-        <v>797.9</v>
+        <v>420.9</v>
       </c>
       <c r="M525" t="inlineStr">
         <is>
-          <t>Cw on Jul 29, 2026, 798 m from Fashion Valley (700 CAMINO DEL RIO NORTH). Case #E26070042098 (use for a records request — full narratives are not published in open data).</t>
+          <t>Au2 on Jul 30, 2026, 421 m from Fashion Valley (7000 FRIARS RD). Case #E26070042989 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -33975,49 +33975,285 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
+          <t>E26070042991</t>
+        </is>
+      </c>
+      <c r="E526" s="3" t="n">
+        <v>46233.38563657407</v>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>CW</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>1800 HOTEL CIRCLE SOUTH</t>
+        </is>
+      </c>
+      <c r="J526" t="n">
+        <v>32.759597128436</v>
+      </c>
+      <c r="K526" t="n">
+        <v>-117.177340012371</v>
+      </c>
+      <c r="L526" t="n">
+        <v>1362.6</v>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>Cw on Jul 30, 2026, 1363 m from Fashion Valley (1800 HOTEL CIRCLE SOUTH). Case #E26070042991 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>E26070043131</t>
+        </is>
+      </c>
+      <c r="E527" s="3" t="n">
+        <v>46233.46133101852</v>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>5600 MISSION CENTER RD</t>
+        </is>
+      </c>
+      <c r="J527" t="n">
+        <v>32.775588244581</v>
+      </c>
+      <c r="K527" t="n">
+        <v>-117.154010732639</v>
+      </c>
+      <c r="L527" t="n">
+        <v>1451.6</v>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>911 on Jul 30, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070043131 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>E26070043263</t>
+        </is>
+      </c>
+      <c r="E528" s="3" t="n">
+        <v>46233.52984953704</v>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>AU2</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>7900 MISSION CENTER CT</t>
+        </is>
+      </c>
+      <c r="J528" t="n">
+        <v>32.773605548078</v>
+      </c>
+      <c r="K528" t="n">
+        <v>-117.154100182722</v>
+      </c>
+      <c r="L528" t="n">
+        <v>1317</v>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>Au2 on Jul 30, 2026, 1317 m from Fashion Valley (7900 MISSION CENTER CT). Case #E26070043263 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>E26070042098</t>
+        </is>
+      </c>
+      <c r="E529" s="3" t="n">
+        <v>46232.65872685185</v>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>CW</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>700 CAMINO DEL RIO NORTH</t>
+        </is>
+      </c>
+      <c r="J529" t="n">
+        <v>32.764930802223</v>
+      </c>
+      <c r="K529" t="n">
+        <v>-117.158054620315</v>
+      </c>
+      <c r="L529" t="n">
+        <v>797.9</v>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>Cw on Jul 29, 2026, 798 m from Fashion Valley (700 CAMINO DEL RIO NORTH). Case #E26070042098 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>FASHIONVAL</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Fashion Valley</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>FASHIONVAL:San Diego PD Calls for Service</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
           <t>E26070042229</t>
         </is>
       </c>
-      <c r="E526" s="3" t="n">
+      <c r="E530" s="3" t="n">
         <v>46232.73496527778</v>
       </c>
-      <c r="F526" t="inlineStr">
+      <c r="F530" t="inlineStr">
         <is>
           <t>AU2</t>
         </is>
       </c>
-      <c r="G526" t="inlineStr">
+      <c r="G530" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
       </c>
-      <c r="H526" t="inlineStr">
+      <c r="H530" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I526" t="inlineStr">
+      <c r="I530" t="inlineStr">
         <is>
           <t>5600 MISSION CENTER RD</t>
         </is>
       </c>
-      <c r="J526" t="n">
+      <c r="J530" t="n">
         <v>32.775588244581</v>
       </c>
-      <c r="K526" t="n">
+      <c r="K530" t="n">
         <v>-117.154010732639</v>
       </c>
-      <c r="L526" t="n">
+      <c r="L530" t="n">
         <v>1451.6</v>
       </c>
-      <c r="M526" t="inlineStr">
+      <c r="M530" t="inlineStr">
         <is>
           <t>Au2 on Jul 29, 2026, 1452 m from Fashion Valley (5600 MISSION CENTER RD). Case #E26070042229 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M526"/>
+  <autoFilter ref="A1:M530"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -34055,7 +34291,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:48.034583+00:00</t>
+          <t>2026-08-01 09:49:29.028322+00:00</t>
         </is>
       </c>
     </row>
@@ -34087,7 +34323,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 09:46:48.034583+00:00</t>
+          <t>2026-07-25 09:49:29.028322+00:00</t>
         </is>
       </c>
     </row>
@@ -34098,7 +34334,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="7">

--- a/reports/2026-08-01/blotter_report.xlsx
+++ b/reports/2026-08-01/blotter_report.xlsx
@@ -13,10 +13,10 @@
     <sheet name="Run Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$L$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$530</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$608</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,11 +443,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="57" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
@@ -456,7 +456,7 @@
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -923,45 +923,41 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COPLEY</t>
+          <t>COLLEGE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>College Mall</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2 Copley Place Boston MA 02116</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>2894 East Third Street Bloomington IN 47401</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>61</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>26</v>
-      </c>
-      <c r="J11" t="n">
-        <v>129.3</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>46230.89583333334</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="b">
         <v>0</v>
       </c>
@@ -969,17 +965,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5000 Empire Mall Sioux Falls SD 57106</t>
+          <t>2 Copley Place Boston MA 02116</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -988,25 +984,25 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>119</v>
+        <v>61</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
         <v>26</v>
       </c>
-      <c r="I12" t="n">
-        <v>76</v>
-      </c>
       <c r="J12" t="n">
-        <v>315.5</v>
+        <v>129.3</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>46234.24527777778</v>
+        <v>46230.89583333334</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
@@ -1015,17 +1011,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FASHIONVAL</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fashion Valley</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7007 Friars Road San Diego CA 92108</t>
+          <t>5000 Empire Mall Sioux Falls SD 57106</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1034,25 +1030,25 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>111</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
+        <v>119</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I13" t="n">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="J13" t="n">
-        <v>354.6</v>
+        <v>315.5</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>46233.87652777778</v>
+        <v>46234.24527777778</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
@@ -1061,17 +1057,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GREENHILLS</t>
+          <t>ENCOREWYNNVEGAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Mall at Green Hills</t>
+          <t>Encore at Wynn Las Vegas</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2126 Abbott Martin Road, Nashville, TN 37215</t>
+          <t>3121 S Las Vegas Blvd Las Vegas NV 89109, USA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1080,22 +1076,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>46229.51539351852</v>
+      </c>
       <c r="L14" t="b">
         <v>0</v>
       </c>
@@ -1103,17 +1103,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>FASHIONVAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>Fashion Valley</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5085 Westheimer Houston TX 77056</t>
+          <t>7007 Friars Road San Diego CA 92108</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1122,25 +1122,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>57</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>4</v>
+        <v>111</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>9</v>
+        <v>111</v>
       </c>
       <c r="J15" t="n">
-        <v>163.5</v>
+        <v>354.6</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>46233</v>
+        <v>46233.87652777778</v>
       </c>
       <c r="L15" t="b">
         <v>0</v>
@@ -1149,17 +1149,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>INTLMARKET</t>
+          <t>GREENHILLS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>International Market Place</t>
+          <t>The Mall at Green Hills</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2330 Kalakaua Avenue, Honolulu HI 96815</t>
+          <t>2126 Abbott Martin Road, Nashville, TN 37215</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1168,26 +1168,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>62</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>46233.78047453704</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="b">
         <v>0</v>
       </c>
@@ -1195,17 +1191,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>INTLPLAZA</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>International Plaza</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
+          <t>5085 Westheimer Houston TX 77056</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1214,25 +1210,25 @@
         </is>
       </c>
       <c r="E17" t="n">
+        <v>57</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" t="n">
+        <v>43</v>
+      </c>
+      <c r="H17" t="n">
         <v>1</v>
       </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J17" t="n">
-        <v>1534.5</v>
+        <v>163.5</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>46232.16666666666</v>
+        <v>46233</v>
       </c>
       <c r="L17" t="b">
         <v>0</v>
@@ -1241,41 +1237,45 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LENOX</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lenox Square</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>2330 Kalakaua Avenue, Honolulu HI 96815</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
+        <v>62</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>46233.78047453704</v>
+      </c>
       <c r="L18" t="b">
         <v>0</v>
       </c>
@@ -1283,17 +1283,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MALLATMILLENIA</t>
+          <t>INTLPLAZA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Mall at Millenia</t>
+          <t>International Plaza</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4200 Conroy Road, Orlando, FL 32839</t>
+          <t>2223 North West Shore Boulevard Tampa FL 33607</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1302,13 +1302,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1316,8 +1316,12 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>1534.5</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>46232.16666666666</v>
+      </c>
       <c r="L19" t="b">
         <v>0</v>
       </c>
@@ -1325,26 +1329,26 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NORFOLKPO</t>
+          <t>LENOX</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Norfolk Premium Outlets</t>
+          <t>Lenox Square</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1600 Premium Outlets Boulevard Norfolk VA 23502</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>3393 Peachtree Road Northeast Atlanta GA 30326</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1356,14 +1360,10 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1118.9</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>46233</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="b">
         <v>0</v>
       </c>
@@ -1371,17 +1371,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>MALLATMILLENIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>The Mall at Millenia</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>401 Northeast Northgate Way Seattle WA 98125</t>
+          <t>4200 Conroy Road, Orlando, FL 32839</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1390,26 +1390,22 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>14</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>145.2</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>46233.28194444445</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="b">
         <v>0</v>
       </c>
@@ -1417,17 +1413,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OPRYMILLS</t>
+          <t>NORFOLKPO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Opry Mills</t>
+          <t>Norfolk Premium Outlets</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>433 Opry Mills Drive Nashville TN 37214</t>
+          <t>1600 Premium Outlets Boulevard Norfolk VA 23502</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1436,7 +1432,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1448,10 +1444,14 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1118.9</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>46233</v>
+      </c>
       <c r="L22" t="b">
         <v>0</v>
       </c>
@@ -1459,17 +1459,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4400 Sharon Road Charlotte NC 28211</t>
+          <t>401 Northeast Northgate Way Seattle WA 98125</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1478,13 +1478,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1493,10 +1493,10 @@
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>178.9</v>
+        <v>145.2</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>46232.16666666666</v>
+        <v>46233.28194444445</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
@@ -1505,17 +1505,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>OPRYMILLS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Opry Mills</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>4502 South Steele Street Tacoma WA 98409</t>
+          <t>433 Opry Mills Drive Nashville TN 37214</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1524,26 +1524,22 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>9</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
-      </c>
-      <c r="J24" t="n">
-        <v>471.3</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>46233</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="b">
         <v>0</v>
       </c>
@@ -1551,41 +1547,45 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>THEDOMAIN</t>
+          <t>SHOPSATCAESARS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Domain</t>
+          <t>The Forum Shops at Caesars</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>11410 Century Oaks Terrace Austin TX 78758</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>NO COVERAGE</t>
+          <t>3500 Las Vegas Boulevard S Las Vegas NV 89109</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>158.3</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>46229.4527658912</v>
+      </c>
       <c r="L25" t="b">
         <v>0</v>
       </c>
@@ -1593,17 +1593,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TOWNEEAST</t>
+          <t>SHOPSCRYSTALS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Towne East Square</t>
+          <t>The Shops at Crystals</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>7700 East Kellogg Wichita KS 67207</t>
+          <t>3720 South Las Vegas Boulevard Las Vegas NV 89158</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1612,25 +1612,25 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="F26" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" t="n">
+        <v>16</v>
+      </c>
+      <c r="H26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" t="n">
-        <v>9</v>
-      </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>4</v>
       </c>
-      <c r="I26" t="n">
-        <v>27</v>
-      </c>
       <c r="J26" t="n">
-        <v>288.9</v>
+        <v>103.8</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>46234.92013888889</v>
+        <v>46229.49368055556</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
@@ -1639,17 +1639,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>UNIVPARKVILLAGE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>University Park Village</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1612 South University Drive Fort Worth TX 76107</t>
+          <t>4400 Sharon Road Charlotte NC 28211</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1658,22 +1658,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>46232.16666666666</v>
+      </c>
       <c r="L27" t="b">
         <v>0</v>
       </c>
@@ -1681,17 +1685,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>WAIKELE</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Waikele Premium Outlets</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>94-790 Lumiaina Street Waipahu HI 96797</t>
+          <t>4502 South Steele Street Tacoma WA 98409</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1700,10 +1704,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
         <v>3</v>
@@ -1712,20 +1716,334 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
-        <v>264.9</v>
+        <v>471.3</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>46231.75893518519</v>
+        <v>46233</v>
       </c>
       <c r="L28" t="b">
         <v>0</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>THEDOMAIN</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>The Domain</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>11410 Century Oaks Terrace Austin TX 78758</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>NO COVERAGE</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TOWNEEAST</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Towne East Square</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>7700 East Kellogg Wichita KS 67207</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>41</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>9</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4</v>
+      </c>
+      <c r="I30" t="n">
+        <v>27</v>
+      </c>
+      <c r="J30" t="n">
+        <v>288.9</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>46234.92013888889</v>
+      </c>
+      <c r="L30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>UNIVPARKVILLAGE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>University Park Village</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1612 South University Drive Fort Worth TX 76107</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Las Vegas Convention Center</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>3150 Paradise Rd Las Vegas NV 89109, USA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>14</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>880.5</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>46229.48666423611</v>
+      </c>
+      <c r="L32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>VEGASNORTHPO</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Las Vegas North Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>875 South Grand Central Parkway Las Vegas NV 89106</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>970.8</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>46229.32986111111</v>
+      </c>
+      <c r="L33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>VEGASSOUTHPO</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Las Vegas South Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>7400 Las Vegas Boulevard South Las Vegas NV 89123</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>445.3</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>46229.3967684375</v>
+      </c>
+      <c r="L34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>WAIKELE</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Waikele Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>94-790 Lumiaina Street Waipahu HI 96797</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>264.9</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>46231.75893518519</v>
+      </c>
+      <c r="L35" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L28"/>
+  <autoFilter ref="A1:L35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1739,11 +2057,11 @@
   <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
@@ -1938,30 +2256,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>SHOPSCRYSTALS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>The Shops at Crystals</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>094686126</t>
+          <t>LLV260700102332</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>46229</v>
+        <v>46229.26111111111</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Simple assault</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1971,56 +2289,56 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>13B</t>
+          <t>ASSAULT OFFENSES</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5000-5099 WESTHEIMER RD</t>
+          <t>LAS VEGAS BLVD &amp; W HARMON AVE</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>29.74071090457959</v>
+        <v>36.10856523975185</v>
       </c>
       <c r="K4" t="n">
-        <v>-95.46251430091121</v>
+        <v>-115.1729787498052</v>
       </c>
       <c r="L4" t="n">
-        <v>217.1</v>
+        <v>103.8</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 26, 2026, 217 m from Houston Galleria (5000-5099 WESTHEIMER RD). Case #094686126 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 26, 2026, 104 m from The Shops at Crystals (LAS VEGAS BLVD &amp; W HARMON AVE). Case #LLV260700102332 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INTLMARKET</t>
+          <t>SHOPSATCAESARS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>International Market Place</t>
+          <t>The Forum Shops at Caesars</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>INTLMARKET:vg88-5rn5</t>
+          <t>SHOPSATCAESARS:LVMPD Reported NIBRS Crimes</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>260728-1185</t>
+          <t>LLV260700102987</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46231.67606481481</v>
+        <v>46229.42507789352</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ASSAULT</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2030,56 +2348,56 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>ASSAULT OFFENSES</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2200 BLOCK KUHIO AVE</t>
+          <t>3500 S LAS VEGAS BLVD</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>21.280829509204</v>
+        <v>36.11731907946647</v>
       </c>
       <c r="K5" t="n">
-        <v>-157.827642638381</v>
+        <v>-115.1747388395123</v>
       </c>
       <c r="L5" t="n">
-        <v>330.6</v>
+        <v>175.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Assault on Jul 28, 2026, 331 m from International Market Place (2200 BLOCK KUHIO AVE). Case #260728-1185 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 26, 2026, 176 m from The Forum Shops at Caesars (3500 S LAS VEGAS BLVD). Case #LLV260700102987 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>INTLMARKET</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>International Market Place</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>INTLMARKET:vg88-5rn5</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>260726-0222</t>
+          <t>094686126</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46229.15130787037</v>
+        <v>46229</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ASSAULT</t>
+          <t>Simple assault</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2089,26 +2407,26 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>13B</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2200 BLOCK KALAKAUA AVE</t>
+          <t>5000-5099 WESTHEIMER RD</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>21.280046658192</v>
+        <v>29.74071090457959</v>
       </c>
       <c r="K6" t="n">
-        <v>-157.829687791355</v>
+        <v>-95.46251430091121</v>
       </c>
       <c r="L6" t="n">
-        <v>384.6</v>
+        <v>217.1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Assault on Jul 26, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260726-0222 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 26, 2026, 217 m from Houston Galleria (5000-5099 WESTHEIMER RD). Case #094686126 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2130,11 +2448,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>260727-0609</t>
+          <t>260728-1185</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46230.42018518518</v>
+        <v>46231.67606481481</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2153,51 +2471,51 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>300 BLOCK LEWERS ST</t>
+          <t>2200 BLOCK KUHIO AVE</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>21.280145465259</v>
+        <v>21.280829509204</v>
       </c>
       <c r="K7" t="n">
-        <v>-157.829777674689</v>
+        <v>-157.827642638381</v>
       </c>
       <c r="L7" t="n">
-        <v>398.6</v>
+        <v>330.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Assault on Jul 27, 2026, 399 m from International Market Place (300 BLOCK LEWERS ST). Case #260727-0609 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 28, 2026, 331 m from International Market Place (2200 BLOCK KUHIO AVE). Case #260728-1185 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HOUSTONGAL</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Houston Galleria</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
+          <t>INTLMARKET:vg88-5rn5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>094513626</t>
+          <t>260726-0222</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46229</v>
+        <v>46229.15130787037</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2207,26 +2525,26 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>13A</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5100-5199 HIDALGO ST</t>
+          <t>2200 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>29.73535149549964</v>
+        <v>21.280046658192</v>
       </c>
       <c r="K8" t="n">
-        <v>-95.46474014804627</v>
+        <v>-157.829687791355</v>
       </c>
       <c r="L8" t="n">
-        <v>447.9</v>
+        <v>384.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 26, 2026, 448 m from Houston Galleria (5100-5199 HIDALGO ST). Case #094513626 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 26, 2026, 385 m from International Market Place (2200 BLOCK KALAKAUA AVE). Case #260726-0222 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2248,11 +2566,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>260729-0737</t>
+          <t>260727-0609</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46232.46952546296</v>
+        <v>46230.42018518518</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2271,51 +2589,51 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2500 BLOCK KALAKAUA AVE</t>
+          <t>300 BLOCK LEWERS ST</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>21.273862837838</v>
+        <v>21.280145465259</v>
       </c>
       <c r="K9" t="n">
-        <v>-157.82387239543</v>
+        <v>-157.829777674689</v>
       </c>
       <c r="L9" t="n">
-        <v>544.6</v>
+        <v>398.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Assault on Jul 29, 2026, 545 m from International Market Place (2500 BLOCK KALAKAUA AVE). Case #260729-0737 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 27, 2026, 399 m from International Market Place (300 BLOCK LEWERS ST). Case #260727-0609 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INTLMARKET</t>
+          <t>VEGASSOUTHPO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>International Market Place</t>
+          <t>Las Vegas South Premium Outlets</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>INTLMARKET:vg88-5rn5</t>
+          <t>VEGASSOUTHPO:LVMPD Reported NIBRS Crimes</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>260725-1627</t>
+          <t>LLV260700102919</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46228.93998842593</v>
+        <v>46229.3967684375</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ASSAULT</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2325,26 +2643,26 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>ASSAULT OFFENSES</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>200 BLOCK BEACH WALK</t>
+          <t>7200 S LAS VEGAS BLVD</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>21.278930465176</v>
+        <v>36.05858458939953</v>
       </c>
       <c r="K10" t="n">
-        <v>-157.832248174365</v>
+        <v>-115.1702279073654</v>
       </c>
       <c r="L10" t="n">
-        <v>583.7</v>
+        <v>445.3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Assault on Jul 25, 2026, 584 m from International Market Place (200 BLOCK BEACH WALK). Case #260725-1627 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 26, 2026, 445 m from Las Vegas South Premium Outlets (7200 S LAS VEGAS BLVD). Case #LLV260700102919 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2361,20 +2679,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HOUSTONGAL:Houston PD NIBRS — Property</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Person</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>095242126</t>
+          <t>094513626</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Aggravated Assault</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2384,56 +2702,56 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>13A</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2700-2799 LOOP N</t>
+          <t>5100-5199 HIDALGO ST</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>29.7388306267185</v>
+        <v>29.73535149549964</v>
       </c>
       <c r="K11" t="n">
-        <v>-95.45805588032616</v>
+        <v>-95.46474014804627</v>
       </c>
       <c r="L11" t="n">
-        <v>588.1</v>
+        <v>447.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Robbery on Jul 27, 2026, 588 m from Houston Galleria (2700-2799 LOOP N). Case #095242126 (use for a records request — full narratives are not published in open data).</t>
+          <t>Aggravated assault on Jul 26, 2026, 448 m from Houston Galleria (5100-5199 HIDALGO ST). Case #094513626 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Empire Mall</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
+          <t>INTLMARKET:vg88-5rn5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CFS26-161839</t>
+          <t>260729-0737</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46231.00275462963</v>
+        <v>46232.46952546296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Assault P3</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2443,56 +2761,56 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>W 47TH ST &amp; S WESTPORT AVE</t>
+          <t>2500 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>43.50940131405472</v>
+        <v>21.273862837838</v>
       </c>
       <c r="K12" t="n">
-        <v>-96.76746570282992</v>
+        <v>-157.82387239543</v>
       </c>
       <c r="L12" t="n">
-        <v>678.4</v>
+        <v>544.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Assault p3 on Jul 28, 2026, 678 m from Empire Mall (W 47TH ST &amp; S WESTPORT AVE). Case #CFS26-161839 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 29, 2026, 545 m from International Market Place (2500 BLOCK KALAKAUA AVE). Case #260729-0737 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CHERRYCREEK</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CHERRYCREEK:Denver PD Crime</t>
+          <t>INTLMARKET:vg88-5rn5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DP2026411044131300</t>
+          <t>260725-1627</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46229.1125</v>
+        <v>46228.93998842593</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>assault-simple</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2502,56 +2820,56 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>other-crimes-against-persons</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3200 BLOCK E CHERRY CREEK S DR</t>
+          <t>200 BLOCK BEACH WALK</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>39.71130989687384</v>
+        <v>21.278930465176</v>
       </c>
       <c r="K13" t="n">
-        <v>-104.9490029653731</v>
+        <v>-157.832248174365</v>
       </c>
       <c r="L13" t="n">
-        <v>696.3</v>
+        <v>583.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 25, 2026, 584 m from International Market Place (200 BLOCK BEACH WALK). Case #260725-1627 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COPLEY</t>
+          <t>HOUSTONGAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>Houston Galleria</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+          <t>HOUSTONGAL:Houston PD NIBRS — Property</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>262064756</t>
+          <t>095242126</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46230.80347222222</v>
+        <v>46230</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASSAULT - SIMPLE</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2559,24 +2877,28 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MASSACHUSETTS AVE</t>
+          <t>2700-2799 LOOP N</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>42.34439568415441</v>
+        <v>29.7388306267185</v>
       </c>
       <c r="K14" t="n">
-        <v>-71.08632016344815</v>
+        <v>-95.45805588032616</v>
       </c>
       <c r="L14" t="n">
-        <v>798.7</v>
+        <v>588.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Assault - simple on Jul 27, 2026, 799 m from Copley Place (MASSACHUSETTS AVE). Case #262064756 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 27, 2026, 588 m from Houston Galleria (2700-2799 LOOP N). Case #095242126 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -2598,74 +2920,74 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CFS26-161603</t>
+          <t>CFS26-161839</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46230.83325231481</v>
+        <v>46231.00275462963</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>Assault P3</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>Assault</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Assault</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>S WESTPORT AVE &amp; W 41ST ST</t>
+          <t>W 47TH ST &amp; S WESTPORT AVE</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>43.51485103457241</v>
+        <v>43.50940131405472</v>
       </c>
       <c r="K15" t="n">
-        <v>-96.76794119445807</v>
+        <v>-96.76746570282992</v>
       </c>
       <c r="L15" t="n">
-        <v>808.9</v>
+        <v>678.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Assault on Jul 27, 2026, 809 m from Empire Mall (S WESTPORT AVE &amp; W 41ST ST). Case #CFS26-161603 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault p3 on Jul 28, 2026, 678 m from Empire Mall (W 47TH ST &amp; S WESTPORT AVE). Case #CFS26-161839 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>INTLMARKET</t>
+          <t>CHERRYCREEK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>International Market Place</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>INTLMARKET:vg88-5rn5</t>
+          <t>CHERRYCREEK:Denver PD Crime</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>260729-0943</t>
+          <t>DP2026411044131300</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46232.56469907407</v>
+        <v>46229.1125</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ASSAULT</t>
+          <t>assault-simple</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2675,56 +2997,56 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>other-crimes-against-persons</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2600 BLOCK KALAKAUA AVE</t>
+          <t>3200 BLOCK E CHERRY CREEK S DR</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>21.271474893966</v>
+        <v>39.71130989687384</v>
       </c>
       <c r="K16" t="n">
-        <v>-157.82264961775</v>
+        <v>-104.9490029653731</v>
       </c>
       <c r="L16" t="n">
-        <v>837.3</v>
+        <v>696.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Assault on Jul 29, 2026, 837 m from International Market Place (2600 BLOCK KALAKAUA AVE). Case #260729-0943 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault-simple on Jul 26, 2026, 696 m from Cherry Creek Shopping Center (3200 BLOCK E CHERRY CREEK S DR). Victims: 1. Case #DP2026411044 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>COPLEY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SOUTHPARK:CMPD Incidents</t>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20260729-1600-11</t>
+          <t>262064756</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46232.16666666666</v>
+        <v>46230.80347222222</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Simple Assault</t>
+          <t>ASSAULT - SIMPLE</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2732,58 +3054,54 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>13B</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4700 PIEDMONT ROW DR</t>
+          <t>MASSACHUSETTS AVE</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>35.15196312662653</v>
+        <v>42.34439568415441</v>
       </c>
       <c r="K17" t="n">
-        <v>-80.83980651357408</v>
+        <v>-71.08632016344815</v>
       </c>
       <c r="L17" t="n">
-        <v>850.6</v>
+        <v>798.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 29, 2026, 851 m from Southpark (4700 PIEDMONT ROW DR). Status: Open. Case #20260729-1600-11 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - simple on Jul 27, 2026, 799 m from Copley Place (MASSACHUSETTS AVE). Case #262064756 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Empire Mall</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>EMPIRE:Sioux Falls PD Calls for Service</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2620701835</t>
+          <t>CFS26-161603</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46229</v>
+        <v>46230.83325231481</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2793,56 +3111,56 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4000 S LAWRENCE ST</t>
+          <t>S WESTPORT AVE &amp; W 41ST ST</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>47.219421</v>
+        <v>43.51485103457241</v>
       </c>
       <c r="K18" t="n">
-        <v>-122.478428</v>
+        <v>-96.76794119445807</v>
       </c>
       <c r="L18" t="n">
-        <v>853.4</v>
+        <v>808.9</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 26, 2026, 853 m from Tacoma Mall (4000 S LAWRENCE ST). Case #2620701835 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 27, 2026, 809 m from Empire Mall (S WESTPORT AVE &amp; W 41ST ST). Case #CFS26-161603 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>COPLEY</t>
+          <t>SHOPSATCAESARS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>The Forum Shops at Caesars</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+          <t>SHOPSATCAESARS:LVMPD Reported NIBRS Crimes</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>262064416</t>
+          <t>LLV260700102948</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46229.87569444445</v>
+        <v>46229.40803371528</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ASSAULT - AGGRAVATED</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2850,54 +3168,58 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ASSAULT OFFENSES</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>HUNTINGTON AVE</t>
+          <t>3700 S LAS VEGAS BLVD</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>42.34221543503831</v>
+        <v>36.11009780070533</v>
       </c>
       <c r="K19" t="n">
-        <v>-71.08577074656198</v>
+        <v>-115.1756791808693</v>
       </c>
       <c r="L19" t="n">
-        <v>898.8</v>
+        <v>822.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Assault - aggravated on Jul 26, 2026, 899 m from Copley Place (HUNTINGTON AVE). Case #262064416 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 26, 2026, 823 m from The Forum Shops at Caesars (3700 S LAS VEGAS BLVD). Case #LLV260700102948 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>INTLMARKET</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>INTLMARKET:vg88-5rn5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>71878728447</t>
+          <t>260729-0943</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46230.4375</v>
+        <v>46232.56469907407</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>ASSAULT</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2907,56 +3229,56 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>VIOLENT CRIME</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16XX BLOCK OF N 105TH ST</t>
+          <t>2600 BLOCK KALAKAUA AVE</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>47.70504225</v>
+        <v>21.271474893966</v>
       </c>
       <c r="K20" t="n">
-        <v>-122.338094779232</v>
+        <v>-157.82264961775</v>
       </c>
       <c r="L20" t="n">
-        <v>938.8</v>
+        <v>837.3</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault on Jul 29, 2026, 837 m from International Market Place (2600 BLOCK KALAKAUA AVE). Case #260729-0943 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TACOMAMALL</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
+          <t>SOUTHPARK:CMPD Incidents</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2621000152</t>
+          <t>20260729-1600-11</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46232</v>
+        <v>46232.16666666666</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Assault Simple</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2966,56 +3288,56 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Assault Offenses</t>
+          <t>13B</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3500 S 45TH ST</t>
+          <t>4700 PIEDMONT ROW DR</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>47.216421</v>
+        <v>35.15196312662653</v>
       </c>
       <c r="K21" t="n">
-        <v>-122.482428</v>
+        <v>-80.83980651357408</v>
       </c>
       <c r="L21" t="n">
-        <v>1074.3</v>
+        <v>850.6</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Assault simple on Jul 29, 2026, 1074 m from Tacoma Mall (3500 S 45TH ST). Case #2621000152 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 29, 2026, 851 m from Southpark (4700 PIEDMONT ROW DR). Status: Open. Case #20260729-1600-11 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>INTLMARKET</t>
+          <t>TACOMAMALL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>International Market Place</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>INTLMARKET:vg88-5rn5</t>
+          <t>TACOMAMALL:Tacoma PD Reported Crime</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>260727-1127</t>
+          <t>2620701835</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46230.64813657408</v>
+        <v>46229</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ASSAULT</t>
+          <t>Assault Simple</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3025,56 +3347,56 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Assault Offenses</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1900 BLOCK KALAKAUA AVE</t>
+          <t>4000 S LAWRENCE ST</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>21.28609383604</v>
+        <v>47.219421</v>
       </c>
       <c r="K22" t="n">
-        <v>-157.833074890083</v>
+        <v>-122.478428</v>
       </c>
       <c r="L22" t="n">
-        <v>1117.1</v>
+        <v>853.4</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Assault on Jul 27, 2026, 1117 m from International Market Place (1900 BLOCK KALAKAUA AVE). Case #260727-1127 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault simple on Jul 26, 2026, 853 m from Tacoma Mall (4000 S LAWRENCE ST). Case #2620701835 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>COPLEY</t>
+          <t>VEGASCONVENTION</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>Las Vegas Convention Center</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+          <t>VEGASCONVENTION:LVMPD Reported NIBRS Crimes</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>262064432</t>
+          <t>LLV260700101084</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46229.91666666666</v>
+        <v>46229.03793769676</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ROBBERY</t>
+          <t>Simple Assault</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3082,24 +3404,28 @@
           <t>VIOLENT</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ASSAULT OFFENSES</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>2700 S LAS VEGAS BLVD</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>42.33954198983015</v>
+        <v>36.13758804215176</v>
       </c>
       <c r="K23" t="n">
-        <v>-71.06940876967543</v>
+        <v>-115.1590244775813</v>
       </c>
       <c r="L23" t="n">
-        <v>1123.7</v>
+        <v>880.5</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Robbery on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064432 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 26, 2026, 880 m from Las Vegas Convention Center (2700 S LAS VEGAS BLVD). Case #LLV260700101084 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -3121,15 +3447,15 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>262064298</t>
+          <t>262064416</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46229.08611111111</v>
+        <v>46229.87569444445</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FIREARM/WEAPON - LOST</t>
+          <t>ASSAULT - AGGRAVATED</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3140,21 +3466,21 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>HARRISON AVE</t>
+          <t>HUNTINGTON AVE</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>42.33954198983015</v>
+        <v>42.34221543503831</v>
       </c>
       <c r="K24" t="n">
-        <v>-71.06940876967543</v>
+        <v>-71.08577074656198</v>
       </c>
       <c r="L24" t="n">
-        <v>1123.7</v>
+        <v>898.8</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Firearm/weapon - lost on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064298 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - aggravated on Jul 26, 2026, 899 m from Copley Place (HUNTINGTON AVE). Case #262064416 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -3176,15 +3502,15 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>71894237115</t>
+          <t>71878728447</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46231.20833333334</v>
+        <v>46230.4375</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aggravated Assault</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3199,47 +3525,47 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>16XX BLOCK OF N 105TH ST</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>47.70668788</v>
+        <v>47.70504225</v>
       </c>
       <c r="K25" t="n">
-        <v>-122.311189997702</v>
+        <v>-122.338094779232</v>
       </c>
       <c r="L25" t="n">
-        <v>1145.7</v>
+        <v>938.8</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Aggravated assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-221056 (use for a records request — full narratives are not published in open data).</t>
+          <t>Robbery on Jul 27, 2026, 939 m from Northgate Station (16XX BLOCK OF N 105TH ST). Case #2026-220064 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SHOPSCRYSTALS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>The Shops at Crystals</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NORTHGATE:tazs-3rd5</t>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>71889871382</t>
+          <t>LLV260700102987</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46231.00625</v>
+        <v>46229.42507789352</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3253,26 +3579,26 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>ALL OTHER</t>
+          <t>ASSAULT OFFENSES</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15XX BLOCK OF NE 107TH ST</t>
+          <t>3500 S LAS VEGAS BLVD</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>47.70668788</v>
+        <v>36.11731907946647</v>
       </c>
       <c r="K26" t="n">
-        <v>-122.311189997702</v>
+        <v>-115.1747388395123</v>
       </c>
       <c r="L26" t="n">
-        <v>1145.7</v>
+        <v>1003</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Simple assault on Jul 28, 2026, 1146 m from Northgate Station (15XX BLOCK OF NE 107TH ST). Case #2026-220636 (use for a records request — full narratives are not published in open data).</t>
+          <t>Simple assault on Jul 26, 2026, 1003 m from The Shops at Crystals (3500 S LAS VEGAS BLVD). Case #LLV260700102987 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -3288,14 +3614,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M530"/>
+  <dimension ref="A1:M608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
@@ -22271,11 +22597,11 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>262064802</t>
+          <t>262064772</t>
         </is>
       </c>
       <c r="E326" s="3" t="n">
-        <v>46230.89583333334</v>
+        <v>46230.82569444444</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -22304,7 +22630,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Larceny shoplifting on Jul 27, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064802 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny shoplifting on Jul 27, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064772 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22326,40 +22652,40 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>262064409</t>
+          <t>262064289</t>
         </is>
       </c>
       <c r="E327" s="3" t="n">
-        <v>46229.85833333333</v>
+        <v>46229.54583333333</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>SICK ASSIST</t>
+          <t>LARCENY SHOPLIFTING</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H327" t="inlineStr"/>
       <c r="I327" t="inlineStr">
         <is>
-          <t>OXFORD ST</t>
+          <t>BOYLSTON ST</t>
         </is>
       </c>
       <c r="J327" t="n">
-        <v>42.35193460488232</v>
+        <v>42.35095908794595</v>
       </c>
       <c r="K327" t="n">
-        <v>-71.06048592223925</v>
+        <v>-71.07412780075079</v>
       </c>
       <c r="L327" t="n">
-        <v>1488.7</v>
+        <v>470.3</v>
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Sick assist on Jul 26, 2026, 1489 m from Copley Place (OXFORD ST). Case #262064409 (use for a records request — full narratives are not published in open data).</t>
+          <t>Larceny shoplifting on Jul 26, 2026, 470 m from Copley Place (BOYLSTON ST). Case #262064289 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22381,40 +22707,40 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>262064318</t>
+          <t>262064298</t>
         </is>
       </c>
       <c r="E328" s="3" t="n">
-        <v>46229.53958333333</v>
+        <v>46229.08611111111</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>INVESTIGATE PERSON</t>
+          <t>FIREARM/WEAPON - LOST</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H328" t="inlineStr"/>
       <c r="I328" t="inlineStr">
         <is>
-          <t>SHAWMUT AVE</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J328" t="n">
-        <v>42.34319452771496</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K328" t="n">
-        <v>-71.06880536524001</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L328" t="n">
-        <v>876.3</v>
+        <v>1123.7</v>
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Investigate person on Jul 26, 2026, 876 m from Copley Place (SHAWMUT AVE). Case #262064318 (use for a records request — full narratives are not published in open data).</t>
+          <t>Firearm/weapon - lost on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064298 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22436,40 +22762,40 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>262064412</t>
+          <t>262064416</t>
         </is>
       </c>
       <c r="E329" s="3" t="n">
-        <v>46229.87638888889</v>
+        <v>46229.87569444445</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>SICK/INJURED/MEDICAL - PERSON</t>
+          <t>ASSAULT - AGGRAVATED</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H329" t="inlineStr"/>
       <c r="I329" t="inlineStr">
         <is>
-          <t>TREMONT ST</t>
+          <t>HUNTINGTON AVE</t>
         </is>
       </c>
       <c r="J329" t="n">
-        <v>42.35428377241487</v>
+        <v>42.34221543503831</v>
       </c>
       <c r="K329" t="n">
-        <v>-71.06380403747467</v>
+        <v>-71.08577074656198</v>
       </c>
       <c r="L329" t="n">
-        <v>1356.9</v>
+        <v>898.8</v>
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Sick/injured/medical - person on Jul 26, 2026, 1357 m from Copley Place (TREMONT ST). Case #262064412 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - aggravated on Jul 26, 2026, 899 m from Copley Place (HUNTINGTON AVE). Case #262064416 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22491,40 +22817,40 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>262064362</t>
+          <t>262064700</t>
         </is>
       </c>
       <c r="E330" s="3" t="n">
-        <v>46229.64305555556</v>
+        <v>46230.71458333333</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
+          <t>BREAKING AND ENTERING (B&amp;E) MOTOR VEHICLE</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H330" t="inlineStr"/>
       <c r="I330" t="inlineStr">
         <is>
-          <t>DARTMOUTH ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J330" t="n">
-        <v>42.35029374297969</v>
+        <v>42.33954198983015</v>
       </c>
       <c r="K330" t="n">
-        <v>-71.07744671381569</v>
+        <v>-71.06940876967543</v>
       </c>
       <c r="L330" t="n">
-        <v>298.2</v>
+        <v>1123.7</v>
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 298 m from Copley Place (DARTMOUTH ST). Case #262064362 (use for a records request — full narratives are not published in open data).</t>
+          <t>Breaking and entering (b&amp;e) motor vehicle on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064700 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -22546,40 +22872,818 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>262064307</t>
+          <t>262064491</t>
         </is>
       </c>
       <c r="E331" s="3" t="n">
-        <v>46229.59027777778</v>
+        <v>46230.22916666666</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>SICK ASSIST</t>
+          <t>LARCENY ALL OTHERS</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PROPERTY</t>
         </is>
       </c>
       <c r="H331" t="inlineStr"/>
       <c r="I331" t="inlineStr">
+        <is>
+          <t>RUTLAND ST</t>
+        </is>
+      </c>
+      <c r="J331" t="n">
+        <v>42.34020387362647</v>
+      </c>
+      <c r="K331" t="n">
+        <v>-71.07645111113312</v>
+      </c>
+      <c r="L331" t="n">
+        <v>829.8</v>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>Larceny all others on Jul 27, 2026, 830 m from Copley Place (RUTLAND ST). Case #262064491 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>262064492</t>
+        </is>
+      </c>
+      <c r="E332" s="3" t="n">
+        <v>46230.10972222222</v>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>VANDALISM</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr"/>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>NORTHAMPTON ST</t>
+        </is>
+      </c>
+      <c r="J332" t="n">
+        <v>42.33798932384219</v>
+      </c>
+      <c r="K332" t="n">
+        <v>-71.08003745874711</v>
+      </c>
+      <c r="L332" t="n">
+        <v>1088.4</v>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>Vandalism on Jul 27, 2026, 1088 m from Copley Place (NORTHAMPTON ST). Case #262064492 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>262064766</t>
+        </is>
+      </c>
+      <c r="E333" s="3" t="n">
+        <v>46230.75416666667</v>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>PROPERTY - LOST/ MISSING</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr"/>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>COLUMBUS AVE</t>
+        </is>
+      </c>
+      <c r="J333" t="n">
+        <v>42.34294800069079</v>
+      </c>
+      <c r="K333" t="n">
+        <v>-71.07888700104606</v>
+      </c>
+      <c r="L333" t="n">
+        <v>529.1</v>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>Property - lost/ missing on Jul 27, 2026, 529 m from Copley Place (COLUMBUS AVE). Case #262064766 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>262064548</t>
+        </is>
+      </c>
+      <c r="E334" s="3" t="n">
+        <v>46230.44236111111</v>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>M/V - LEAVING SCENE - PROPERTY DAMAGE</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr"/>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>HARRISON AVE</t>
+        </is>
+      </c>
+      <c r="J334" t="n">
+        <v>42.33954198983015</v>
+      </c>
+      <c r="K334" t="n">
+        <v>-71.06940876967543</v>
+      </c>
+      <c r="L334" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>M/v - leaving scene - property damage on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064548 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>262064504</t>
+        </is>
+      </c>
+      <c r="E335" s="3" t="n">
+        <v>46230.34791666667</v>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>LARCENY SHOPLIFTING</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr"/>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>CHARLES ST</t>
+        </is>
+      </c>
+      <c r="J335" t="n">
+        <v>42.36064469554803</v>
+      </c>
+      <c r="K335" t="n">
+        <v>-71.07086192011141</v>
+      </c>
+      <c r="L335" t="n">
+        <v>1552</v>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 27, 2026, 1552 m from Copley Place (CHARLES ST). Case #262064504 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>262064506</t>
+        </is>
+      </c>
+      <c r="E336" s="3" t="n">
+        <v>46230.34375</v>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr"/>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J336" t="n">
+        <v>42.35037869977646</v>
+      </c>
+      <c r="K336" t="n">
+        <v>-71.07626098382806</v>
+      </c>
+      <c r="L336" t="n">
+        <v>327.3</v>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 27, 2026, 327 m from Copley Place (BOYLSTON ST). Case #262064506 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>262064752</t>
+        </is>
+      </c>
+      <c r="E337" s="3" t="n">
+        <v>46230.79166666666</v>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>STOLEN PROPERTY - BUYING / RECEIVING / POSSESSING</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr"/>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>HUDSON ST</t>
+        </is>
+      </c>
+      <c r="J337" t="n">
+        <v>42.35074197291232</v>
+      </c>
+      <c r="K337" t="n">
+        <v>-71.06006134581432</v>
+      </c>
+      <c r="L337" t="n">
+        <v>1485.3</v>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>Stolen property - buying / receiving / possessing on Jul 27, 2026, 1485 m from Copley Place (HUDSON ST). Case #262064752 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>262064383</t>
+        </is>
+      </c>
+      <c r="E338" s="3" t="n">
+        <v>46229.79375</v>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr"/>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST &amp; DALTON ST
+BOSTON, MA 02115
+UNITED ST</t>
+        </is>
+      </c>
+      <c r="J338" t="n">
+        <v>42.34787097987171</v>
+      </c>
+      <c r="K338" t="n">
+        <v>-71.08556796747074</v>
+      </c>
+      <c r="L338" t="n">
+        <v>652.7</v>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 653 m from Copley Place (BOYLSTON ST &amp; DALTON ST
+BOSTON, MA 02115
+UNITED ST). Case #262064383 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>262064391</t>
+        </is>
+      </c>
+      <c r="E339" s="3" t="n">
+        <v>46229.83125</v>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>DRUGS - POSSESSION/ SALE/ MANUFACTURING/ USE</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOYLSTON ST &amp; BOYLSTON SQ
+BOSTON, MA 02111
+UNITED </t>
+        </is>
+      </c>
+      <c r="J339" t="n">
+        <v>42.35231098936428</v>
+      </c>
+      <c r="K339" t="n">
+        <v>-71.06350996526169</v>
+      </c>
+      <c r="L339" t="n">
+        <v>1272.6</v>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>Drugs - possession/ sale/ manufacturing/ use on Jul 26, 2026, 1273 m from Copley Place (BOYLSTON ST &amp; BOYLSTON SQ
+BOSTON, MA 02111
+UNITED ). Case #262064391 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>262064802</t>
+        </is>
+      </c>
+      <c r="E340" s="3" t="n">
+        <v>46230.89583333334</v>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>LARCENY SHOPLIFTING</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr"/>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>BOYLSTON ST</t>
+        </is>
+      </c>
+      <c r="J340" t="n">
+        <v>42.34862381555496</v>
+      </c>
+      <c r="K340" t="n">
+        <v>-71.08277637086411</v>
+      </c>
+      <c r="L340" t="n">
+        <v>437.3</v>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>Larceny shoplifting on Jul 27, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064802 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>262064409</t>
+        </is>
+      </c>
+      <c r="E341" s="3" t="n">
+        <v>46229.85833333333</v>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr"/>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>OXFORD ST</t>
+        </is>
+      </c>
+      <c r="J341" t="n">
+        <v>42.35193460488232</v>
+      </c>
+      <c r="K341" t="n">
+        <v>-71.06048592223925</v>
+      </c>
+      <c r="L341" t="n">
+        <v>1488.7</v>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>Sick assist on Jul 26, 2026, 1489 m from Copley Place (OXFORD ST). Case #262064409 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>262064318</t>
+        </is>
+      </c>
+      <c r="E342" s="3" t="n">
+        <v>46229.53958333333</v>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>INVESTIGATE PERSON</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr"/>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>SHAWMUT AVE</t>
+        </is>
+      </c>
+      <c r="J342" t="n">
+        <v>42.34319452771496</v>
+      </c>
+      <c r="K342" t="n">
+        <v>-71.06880536524001</v>
+      </c>
+      <c r="L342" t="n">
+        <v>876.3</v>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>Investigate person on Jul 26, 2026, 876 m from Copley Place (SHAWMUT AVE). Case #262064318 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>262064412</t>
+        </is>
+      </c>
+      <c r="E343" s="3" t="n">
+        <v>46229.87638888889</v>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>SICK/INJURED/MEDICAL - PERSON</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr"/>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>TREMONT ST</t>
+        </is>
+      </c>
+      <c r="J343" t="n">
+        <v>42.35428377241487</v>
+      </c>
+      <c r="K343" t="n">
+        <v>-71.06380403747467</v>
+      </c>
+      <c r="L343" t="n">
+        <v>1356.9</v>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>Sick/injured/medical - person on Jul 26, 2026, 1357 m from Copley Place (TREMONT ST). Case #262064412 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>262064362</t>
+        </is>
+      </c>
+      <c r="E344" s="3" t="n">
+        <v>46229.64305555556</v>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>DARTMOUTH ST</t>
+        </is>
+      </c>
+      <c r="J344" t="n">
+        <v>42.35029374297969</v>
+      </c>
+      <c r="K344" t="n">
+        <v>-71.07744671381569</v>
+      </c>
+      <c r="L344" t="n">
+        <v>298.2</v>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 298 m from Copley Place (DARTMOUTH ST). Case #262064362 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>COPLEY</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Copley Place</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>262064307</t>
+        </is>
+      </c>
+      <c r="E345" s="3" t="n">
+        <v>46229.59027777778</v>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>SICK ASSIST</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr"/>
+      <c r="I345" t="inlineStr">
         <is>
           <t>TREMONT ST &amp; TEMPLE PL
 BOSTON, MA 02111
 UNITED STA</t>
         </is>
       </c>
-      <c r="J331" t="n">
+      <c r="J345" t="n">
         <v>42.35561100811422</v>
       </c>
-      <c r="K331" t="n">
+      <c r="K345" t="n">
         <v>-71.06289400004533</v>
       </c>
-      <c r="L331" t="n">
+      <c r="L345" t="n">
         <v>1502.5</v>
       </c>
-      <c r="M331" t="inlineStr">
+      <c r="M345" t="inlineStr">
         <is>
           <t>Sick assist on Jul 26, 2026, 1502 m from Copley Place (TREMONT ST &amp; TEMPLE PL
 BOSTON, MA 02111
@@ -22587,776 +23691,6 @@
         </is>
       </c>
     </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>262064419</t>
-        </is>
-      </c>
-      <c r="E332" s="3" t="n">
-        <v>46229.90138888889</v>
-      </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>HARASSMENT/ CRIMINAL HARASSMENT</t>
-        </is>
-      </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H332" t="inlineStr"/>
-      <c r="I332" t="inlineStr">
-        <is>
-          <t>NASSAU ST</t>
-        </is>
-      </c>
-      <c r="J332" t="n">
-        <v>42.34880604399623</v>
-      </c>
-      <c r="K332" t="n">
-        <v>-71.06285446968663</v>
-      </c>
-      <c r="L332" t="n">
-        <v>1221.7</v>
-      </c>
-      <c r="M332" t="inlineStr">
-        <is>
-          <t>Harassment/ criminal harassment on Jul 26, 2026, 1222 m from Copley Place (NASSAU ST). Case #262064419 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>262064339</t>
-        </is>
-      </c>
-      <c r="E333" s="3" t="n">
-        <v>46229.63333333333</v>
-      </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>ASSAULT - AGGRAVATED</t>
-        </is>
-      </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H333" t="inlineStr"/>
-      <c r="I333" t="inlineStr">
-        <is>
-          <t>HARRISON AVE</t>
-        </is>
-      </c>
-      <c r="J333" t="n">
-        <v>42.33511903946613</v>
-      </c>
-      <c r="K333" t="n">
-        <v>-71.07491709613726</v>
-      </c>
-      <c r="L333" t="n">
-        <v>1407.3</v>
-      </c>
-      <c r="M333" t="inlineStr">
-        <is>
-          <t>Assault - aggravated on Jul 26, 2026, 1407 m from Copley Place (HARRISON AVE). Case #262064339 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>262064236</t>
-        </is>
-      </c>
-      <c r="E334" s="3" t="n">
-        <v>46229.37638888889</v>
-      </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>SICK ASSIST</t>
-        </is>
-      </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H334" t="inlineStr"/>
-      <c r="I334" t="inlineStr">
-        <is>
-          <t>TREMONT ST</t>
-        </is>
-      </c>
-      <c r="J334" t="n">
-        <v>42.34470135794417</v>
-      </c>
-      <c r="K334" t="n">
-        <v>-71.0703760849388</v>
-      </c>
-      <c r="L334" t="n">
-        <v>678.7</v>
-      </c>
-      <c r="M334" t="inlineStr">
-        <is>
-          <t>Sick assist on Jul 26, 2026, 679 m from Copley Place (TREMONT ST). Case #262064236 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>262064234</t>
-        </is>
-      </c>
-      <c r="E335" s="3" t="n">
-        <v>46229.31944444445</v>
-      </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>INVESTIGATE PERSON</t>
-        </is>
-      </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="H335" t="inlineStr"/>
-      <c r="I335" t="inlineStr">
-        <is>
-          <t>SAINT JAMES AVE</t>
-        </is>
-      </c>
-      <c r="J335" t="n">
-        <v>42.34947585701249</v>
-      </c>
-      <c r="K335" t="n">
-        <v>-71.07640149637847</v>
-      </c>
-      <c r="L335" t="n">
-        <v>230.3</v>
-      </c>
-      <c r="M335" t="inlineStr">
-        <is>
-          <t>Investigate person on Jul 26, 2026, 230 m from Copley Place (SAINT JAMES AVE). Case #262064234 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>262064772</t>
-        </is>
-      </c>
-      <c r="E336" s="3" t="n">
-        <v>46230.82569444444</v>
-      </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>LARCENY SHOPLIFTING</t>
-        </is>
-      </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H336" t="inlineStr"/>
-      <c r="I336" t="inlineStr">
-        <is>
-          <t>BOYLSTON ST</t>
-        </is>
-      </c>
-      <c r="J336" t="n">
-        <v>42.34862381555496</v>
-      </c>
-      <c r="K336" t="n">
-        <v>-71.08277637086411</v>
-      </c>
-      <c r="L336" t="n">
-        <v>437.3</v>
-      </c>
-      <c r="M336" t="inlineStr">
-        <is>
-          <t>Larceny shoplifting on Jul 27, 2026, 437 m from Copley Place (BOYLSTON ST). Case #262064772 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>262064289</t>
-        </is>
-      </c>
-      <c r="E337" s="3" t="n">
-        <v>46229.54583333333</v>
-      </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>LARCENY SHOPLIFTING</t>
-        </is>
-      </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H337" t="inlineStr"/>
-      <c r="I337" t="inlineStr">
-        <is>
-          <t>BOYLSTON ST</t>
-        </is>
-      </c>
-      <c r="J337" t="n">
-        <v>42.35095908794595</v>
-      </c>
-      <c r="K337" t="n">
-        <v>-71.07412780075079</v>
-      </c>
-      <c r="L337" t="n">
-        <v>470.3</v>
-      </c>
-      <c r="M337" t="inlineStr">
-        <is>
-          <t>Larceny shoplifting on Jul 26, 2026, 470 m from Copley Place (BOYLSTON ST). Case #262064289 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>262064298</t>
-        </is>
-      </c>
-      <c r="E338" s="3" t="n">
-        <v>46229.08611111111</v>
-      </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>FIREARM/WEAPON - LOST</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H338" t="inlineStr"/>
-      <c r="I338" t="inlineStr">
-        <is>
-          <t>HARRISON AVE</t>
-        </is>
-      </c>
-      <c r="J338" t="n">
-        <v>42.33954198983015</v>
-      </c>
-      <c r="K338" t="n">
-        <v>-71.06940876967543</v>
-      </c>
-      <c r="L338" t="n">
-        <v>1123.7</v>
-      </c>
-      <c r="M338" t="inlineStr">
-        <is>
-          <t>Firearm/weapon - lost on Jul 26, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064298 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>262064416</t>
-        </is>
-      </c>
-      <c r="E339" s="3" t="n">
-        <v>46229.87569444445</v>
-      </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>ASSAULT - AGGRAVATED</t>
-        </is>
-      </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>VIOLENT</t>
-        </is>
-      </c>
-      <c r="H339" t="inlineStr"/>
-      <c r="I339" t="inlineStr">
-        <is>
-          <t>HUNTINGTON AVE</t>
-        </is>
-      </c>
-      <c r="J339" t="n">
-        <v>42.34221543503831</v>
-      </c>
-      <c r="K339" t="n">
-        <v>-71.08577074656198</v>
-      </c>
-      <c r="L339" t="n">
-        <v>898.8</v>
-      </c>
-      <c r="M339" t="inlineStr">
-        <is>
-          <t>Assault - aggravated on Jul 26, 2026, 899 m from Copley Place (HUNTINGTON AVE). Case #262064416 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>262064700</t>
-        </is>
-      </c>
-      <c r="E340" s="3" t="n">
-        <v>46230.71458333333</v>
-      </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>BREAKING AND ENTERING (B&amp;E) MOTOR VEHICLE</t>
-        </is>
-      </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H340" t="inlineStr"/>
-      <c r="I340" t="inlineStr">
-        <is>
-          <t>HARRISON AVE</t>
-        </is>
-      </c>
-      <c r="J340" t="n">
-        <v>42.33954198983015</v>
-      </c>
-      <c r="K340" t="n">
-        <v>-71.06940876967543</v>
-      </c>
-      <c r="L340" t="n">
-        <v>1123.7</v>
-      </c>
-      <c r="M340" t="inlineStr">
-        <is>
-          <t>Breaking and entering (b&amp;e) motor vehicle on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064700 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>262064491</t>
-        </is>
-      </c>
-      <c r="E341" s="3" t="n">
-        <v>46230.22916666666</v>
-      </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>LARCENY ALL OTHERS</t>
-        </is>
-      </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H341" t="inlineStr"/>
-      <c r="I341" t="inlineStr">
-        <is>
-          <t>RUTLAND ST</t>
-        </is>
-      </c>
-      <c r="J341" t="n">
-        <v>42.34020387362647</v>
-      </c>
-      <c r="K341" t="n">
-        <v>-71.07645111113312</v>
-      </c>
-      <c r="L341" t="n">
-        <v>829.8</v>
-      </c>
-      <c r="M341" t="inlineStr">
-        <is>
-          <t>Larceny all others on Jul 27, 2026, 830 m from Copley Place (RUTLAND ST). Case #262064491 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>262064492</t>
-        </is>
-      </c>
-      <c r="E342" s="3" t="n">
-        <v>46230.10972222222</v>
-      </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>VANDALISM</t>
-        </is>
-      </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H342" t="inlineStr"/>
-      <c r="I342" t="inlineStr">
-        <is>
-          <t>NORTHAMPTON ST</t>
-        </is>
-      </c>
-      <c r="J342" t="n">
-        <v>42.33798932384219</v>
-      </c>
-      <c r="K342" t="n">
-        <v>-71.08003745874711</v>
-      </c>
-      <c r="L342" t="n">
-        <v>1088.4</v>
-      </c>
-      <c r="M342" t="inlineStr">
-        <is>
-          <t>Vandalism on Jul 27, 2026, 1088 m from Copley Place (NORTHAMPTON ST). Case #262064492 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>262064766</t>
-        </is>
-      </c>
-      <c r="E343" s="3" t="n">
-        <v>46230.75416666667</v>
-      </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>PROPERTY - LOST/ MISSING</t>
-        </is>
-      </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H343" t="inlineStr"/>
-      <c r="I343" t="inlineStr">
-        <is>
-          <t>COLUMBUS AVE</t>
-        </is>
-      </c>
-      <c r="J343" t="n">
-        <v>42.34294800069079</v>
-      </c>
-      <c r="K343" t="n">
-        <v>-71.07888700104606</v>
-      </c>
-      <c r="L343" t="n">
-        <v>529.1</v>
-      </c>
-      <c r="M343" t="inlineStr">
-        <is>
-          <t>Property - lost/ missing on Jul 27, 2026, 529 m from Copley Place (COLUMBUS AVE). Case #262064766 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>262064548</t>
-        </is>
-      </c>
-      <c r="E344" s="3" t="n">
-        <v>46230.44236111111</v>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>M/V - LEAVING SCENE - PROPERTY DAMAGE</t>
-        </is>
-      </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H344" t="inlineStr"/>
-      <c r="I344" t="inlineStr">
-        <is>
-          <t>HARRISON AVE</t>
-        </is>
-      </c>
-      <c r="J344" t="n">
-        <v>42.33954198983015</v>
-      </c>
-      <c r="K344" t="n">
-        <v>-71.06940876967543</v>
-      </c>
-      <c r="L344" t="n">
-        <v>1123.7</v>
-      </c>
-      <c r="M344" t="inlineStr">
-        <is>
-          <t>M/v - leaving scene - property damage on Jul 27, 2026, 1124 m from Copley Place (HARRISON AVE). Case #262064548 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>COPLEY</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>Copley Place</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>COPLEY:b973d8cb-eeb2-4e7e-99da-c92938efc9c0</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>262064504</t>
-        </is>
-      </c>
-      <c r="E345" s="3" t="n">
-        <v>46230.34791666667</v>
-      </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>LARCENY SHOPLIFTING</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>PROPERTY</t>
-        </is>
-      </c>
-      <c r="H345" t="inlineStr"/>
-      <c r="I345" t="inlineStr">
-        <is>
-          <t>CHARLES ST</t>
-        </is>
-      </c>
-      <c r="J345" t="n">
-        <v>42.36064469554803</v>
-      </c>
-      <c r="K345" t="n">
-        <v>-71.07086192011141</v>
-      </c>
-      <c r="L345" t="n">
-        <v>1552</v>
-      </c>
-      <c r="M345" t="inlineStr">
-        <is>
-          <t>Larceny shoplifting on Jul 27, 2026, 1552 m from Copley Place (CHARLES ST). Case #262064504 (use for a records request — full narratives are not published in open data).</t>
-        </is>
-      </c>
-    </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
@@ -23375,15 +23709,15 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>262064506</t>
+          <t>262064419</t>
         </is>
       </c>
       <c r="E346" s="3" t="n">
-        <v>46230.34375</v>
+        <v>46229.90138888889</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>SICK ASSIST</t>
+          <t>HARASSMENT/ CRIMINAL HARASSMENT</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -23394,21 +23728,21 @@
       <c r="H346" t="inlineStr"/>
       <c r="I346" t="inlineStr">
         <is>
-          <t>BOYLSTON ST</t>
+          <t>NASSAU ST</t>
         </is>
       </c>
       <c r="J346" t="n">
-        <v>42.35037869977646</v>
+        <v>42.34880604399623</v>
       </c>
       <c r="K346" t="n">
-        <v>-71.07626098382806</v>
+        <v>-71.06285446968663</v>
       </c>
       <c r="L346" t="n">
-        <v>327.3</v>
+        <v>1221.7</v>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Sick assist on Jul 27, 2026, 327 m from Copley Place (BOYLSTON ST). Case #262064506 (use for a records request — full narratives are not published in open data).</t>
+          <t>Harassment/ criminal harassment on Jul 26, 2026, 1222 m from Copley Place (NASSAU ST). Case #262064419 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -23430,40 +23764,40 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>262064752</t>
+          <t>262064339</t>
         </is>
       </c>
       <c r="E347" s="3" t="n">
-        <v>46230.79166666666</v>
+        <v>46229.63333333333</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>STOLEN PROPERTY - BUYING / RECEIVING / POSSESSING</t>
+          <t>ASSAULT - AGGRAVATED</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>PROPERTY</t>
+          <t>VIOLENT</t>
         </is>
       </c>
       <c r="H347" t="inlineStr"/>
       <c r="I347" t="inlineStr">
         <is>
-          <t>HUDSON ST</t>
+          <t>HARRISON AVE</t>
         </is>
       </c>
       <c r="J347" t="n">
-        <v>42.35074197291232</v>
+        <v>42.33511903946613</v>
       </c>
       <c r="K347" t="n">
-        <v>-71.06006134581432</v>
+        <v>-71.07491709613726</v>
       </c>
       <c r="L347" t="n">
-        <v>1485.3</v>
+        <v>1407.3</v>
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Stolen property - buying / receiving / possessing on Jul 27, 2026, 1485 m from Copley Place (HUDSON ST). Case #262064752 (use for a records request — full narratives are not published in open data).</t>
+          <t>Assault - aggravated on Jul 26, 2026, 1407 m from Copley Place (HARRISON AVE). Case #262064339 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -23485,15 +23819,15 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>262064383</t>
+          <t>262064236</t>
         </is>
       </c>
       <c r="E348" s="3" t="n">
-        <v>46229.79375</v>
+        <v>46229.37638888889</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>M/V ACCIDENT - INVOLVING PEDESTRIAN - INJURY</t>
+          <t>SICK ASSIST</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -23504,25 +23838,21 @@
       <c r="H348" t="inlineStr"/>
       <c r="I348" t="inlineStr">
         <is>
-          <t>BOYLSTON ST &amp; DALTON ST
-BOSTON, MA 02115
-UNITED ST</t>
+          <t>TREMONT ST</t>
         </is>
       </c>
       <c r="J348" t="n">
-        <v>42.34787097987171</v>
+        <v>42.34470135794417</v>
       </c>
       <c r="K348" t="n">
-        <v>-71.08556796747074</v>
+        <v>-71.0703760849388</v>
       </c>
       <c r="L348" t="n">
-        <v>652.7</v>
+        <v>678.7</v>
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>M/v accident - involving pedestrian - injury on Jul 26, 2026, 653 m from Copley Place (BOYLSTON ST &amp; DALTON ST
-BOSTON, MA 02115
-UNITED ST). Case #262064383 (use for a records request — full narratives are not published in open data).</t>
+          <t>Sick assist on Jul 26, 2026, 679 m from Copley Place (TREMONT ST). Case #262064236 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -23544,44 +23874,40 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>262064391</t>
+          <t>262064234</t>
         </is>
       </c>
       <c r="E349" s="3" t="n">
-        <v>46229.83125</v>
+        <v>46229.31944444445</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>DRUGS - POSSESSION/ SALE/ MANUFACTURING/ USE</t>
+          <t>INVESTIGATE PERSON</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>QUALITY_OF_LIFE</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="H349" t="inlineStr"/>
       <c r="I349" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOYLSTON ST &amp; BOYLSTON SQ
-BOSTON, MA 02111
-UNITED </t>
+          <t>SAINT JAMES AVE</t>
         </is>
       </c>
       <c r="J349" t="n">
-        <v>42.35231098936428</v>
+        <v>42.34947585701249</v>
       </c>
       <c r="K349" t="n">
-        <v>-71.06350996526169</v>
+        <v>-71.07640149637847</v>
       </c>
       <c r="L349" t="n">
-        <v>1272.6</v>
+        <v>230.3</v>
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Drugs - possession/ sale/ manufacturing/ use on Jul 26, 2026, 1273 m from Copley Place (BOYLSTON ST &amp; BOYLSTON SQ
-BOSTON, MA 02111
-UNITED ). Case #262064391 (use for a records request — full narratives are not published in open data).</t>
+          <t>Investigate person on Jul 26, 2026, 230 m from Copley Place (SAINT JAMES AVE). Case #262064234 (use for a records request — full narratives are not published in open data).</t>
         </is>
       </c>
     </row>
@@ -34252,8 +34578,4610 @@
         </is>
       </c>
     </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>VEGASNORTHPO</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Las Vegas North Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>VEGASNORTHPO:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>LLV260700102710</t>
+        </is>
+      </c>
+      <c r="E531" s="3" t="n">
+        <v>46229.32986111111</v>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>Driving Under the Influence</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>S Casino Center Blvd &amp; E Bonneville Ave</t>
+        </is>
+      </c>
+      <c r="J531" t="n">
+        <v>36.16531783480884</v>
+      </c>
+      <c r="K531" t="n">
+        <v>-115.1482734035375</v>
+      </c>
+      <c r="L531" t="n">
+        <v>970.8</v>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>Driving under the influence on Jul 26, 2026, 971 m from Las Vegas North Premium Outlets (S Casino Center Blvd &amp; E Bonneville Ave). Case #LLV260700102710 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>VEGASNORTHPO</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Las Vegas North Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>VEGASNORTHPO:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>LLV260700098894</t>
+        </is>
+      </c>
+      <c r="E532" s="3" t="n">
+        <v>46228.43263888889</v>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>Driving Under the Influence</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>S MAIN ST &amp; E CARSON AVE</t>
+        </is>
+      </c>
+      <c r="J532" t="n">
+        <v>36.17074916380269</v>
+      </c>
+      <c r="K532" t="n">
+        <v>-115.1472467525323</v>
+      </c>
+      <c r="L532" t="n">
+        <v>1331.5</v>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>Driving under the influence on Jul 25, 2026, 1331 m from Las Vegas North Premium Outlets (S MAIN ST &amp; E CARSON AVE). Case #LLV260700098894 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>VEGASSOUTHPO</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Las Vegas South Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>VEGASSOUTHPO:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>LLV260700102919</t>
+        </is>
+      </c>
+      <c r="E533" s="3" t="n">
+        <v>46229.3967684375</v>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>Simple Assault</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>ASSAULT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>7200 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J533" t="n">
+        <v>36.05858458939953</v>
+      </c>
+      <c r="K533" t="n">
+        <v>-115.1702279073654</v>
+      </c>
+      <c r="L533" t="n">
+        <v>445.3</v>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 26, 2026, 445 m from Las Vegas South Premium Outlets (7200 S LAS VEGAS BLVD). Case #LLV260700102919 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>VEGASSOUTHPO</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Las Vegas South Premium Outlets</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>VEGASSOUTHPO:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>LLV260700100652</t>
+        </is>
+      </c>
+      <c r="E534" s="3" t="n">
+        <v>46228.9468440162</v>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>All Other Larceny</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>LARCENY/THEFT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>7600 S Las Vegas Blvd</t>
+        </is>
+      </c>
+      <c r="J534" t="n">
+        <v>36.04976008022761</v>
+      </c>
+      <c r="K534" t="n">
+        <v>-115.1730445784763</v>
+      </c>
+      <c r="L534" t="n">
+        <v>622</v>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>All other larceny on Jul 25, 2026, 622 m from Las Vegas South Premium Outlets (7600 S Las Vegas Blvd). Case #LLV260700100652 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>The Forum Shops at Caesars</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>LLV260700099335</t>
+        </is>
+      </c>
+      <c r="E535" s="3" t="n">
+        <v>46228.48560748842</v>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>All Other Larceny</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>LARCENY/THEFT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>3500 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J535" t="n">
+        <v>36.11687308181964</v>
+      </c>
+      <c r="K535" t="n">
+        <v>-115.1750785479665</v>
+      </c>
+      <c r="L535" t="n">
+        <v>158.3</v>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>All other larceny on Jul 25, 2026, 158 m from The Forum Shops at Caesars (3500 S LAS VEGAS BLVD). Case #LLV260700099335 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>The Forum Shops at Caesars</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>LLV260700102987</t>
+        </is>
+      </c>
+      <c r="E536" s="3" t="n">
+        <v>46229.42507789352</v>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>Simple Assault</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>ASSAULT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>3500 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J536" t="n">
+        <v>36.11731907946647</v>
+      </c>
+      <c r="K536" t="n">
+        <v>-115.1747388395123</v>
+      </c>
+      <c r="L536" t="n">
+        <v>175.7</v>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 26, 2026, 176 m from The Forum Shops at Caesars (3500 S LAS VEGAS BLVD). Case #LLV260700102987 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>The Forum Shops at Caesars</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>LLV260700102865</t>
+        </is>
+      </c>
+      <c r="E537" s="3" t="n">
+        <v>46229.3777397338</v>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>Trespass of Real Property</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>3500 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J537" t="n">
+        <v>36.1170578909413</v>
+      </c>
+      <c r="K537" t="n">
+        <v>-115.1741161397651</v>
+      </c>
+      <c r="L537" t="n">
+        <v>235.2</v>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>Trespass of real property on Jul 26, 2026, 235 m from The Forum Shops at Caesars (3500 S LAS VEGAS BLVD). Case #LLV260700102865 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>The Forum Shops at Caesars</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>LLV260700102596</t>
+        </is>
+      </c>
+      <c r="E538" s="3" t="n">
+        <v>46229.30750309028</v>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>3500 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J538" t="n">
+        <v>36.11695368432775</v>
+      </c>
+      <c r="K538" t="n">
+        <v>-115.1740045401824</v>
+      </c>
+      <c r="L538" t="n">
+        <v>247.4</v>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 26, 2026, 247 m from The Forum Shops at Caesars (3500 S LAS VEGAS BLVD). Case #LLV260700102596 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>The Forum Shops at Caesars</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>LLV260700102840</t>
+        </is>
+      </c>
+      <c r="E539" s="3" t="n">
+        <v>46229.36774001158</v>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>S LAS VEGAS BLVD &amp; CAESARS PALACE DR</t>
+        </is>
+      </c>
+      <c r="J539" t="n">
+        <v>36.11736365932026</v>
+      </c>
+      <c r="K539" t="n">
+        <v>-115.1726925161043</v>
+      </c>
+      <c r="L539" t="n">
+        <v>359</v>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 26, 2026, 359 m from The Forum Shops at Caesars (S LAS VEGAS BLVD &amp; CAESARS PALACE DR). Case #LLV260700102840 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>The Forum Shops at Caesars</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>LLV260700100233</t>
+        </is>
+      </c>
+      <c r="E540" s="3" t="n">
+        <v>46228.81579209491</v>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>Destruction/Damage/Vandalism of Property</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>DESTRUCTION/DAMAGE/VANDALISM OF PROPERTY</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>400 W FLAMINGO RD</t>
+        </is>
+      </c>
+      <c r="J540" t="n">
+        <v>36.11440363140287</v>
+      </c>
+      <c r="K540" t="n">
+        <v>-115.1728667657516</v>
+      </c>
+      <c r="L540" t="n">
+        <v>482.5</v>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>Destruction/damage/vandalism of property on Jul 25, 2026, 482 m from The Forum Shops at Caesars (400 W FLAMINGO RD). Case #LLV260700100233 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>The Forum Shops at Caesars</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>LLV260700099767</t>
+        </is>
+      </c>
+      <c r="E541" s="3" t="n">
+        <v>46228.67075015046</v>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>Trespass of Real Property</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>3300 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J541" t="n">
+        <v>36.12177061943648</v>
+      </c>
+      <c r="K541" t="n">
+        <v>-115.1714678581325</v>
+      </c>
+      <c r="L541" t="n">
+        <v>671.1</v>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>Trespass of real property on Jul 25, 2026, 671 m from The Forum Shops at Caesars (3300 S LAS VEGAS BLVD). Case #LLV260700099767 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>The Forum Shops at Caesars</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>LLV260700099246</t>
+        </is>
+      </c>
+      <c r="E542" s="3" t="n">
+        <v>46228.45050413194</v>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>Trespass of Real Property</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>3700 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J542" t="n">
+        <v>36.11057101116696</v>
+      </c>
+      <c r="K542" t="n">
+        <v>-115.1761183999585</v>
+      </c>
+      <c r="L542" t="n">
+        <v>766.9</v>
+      </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>Trespass of real property on Jul 25, 2026, 767 m from The Forum Shops at Caesars (3700 S LAS VEGAS BLVD). Case #LLV260700099246 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>The Forum Shops at Caesars</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>LLV260700099368</t>
+        </is>
+      </c>
+      <c r="E543" s="3" t="n">
+        <v>46228.56055555555</v>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>False Pretenses/Swindle/Confidence Game</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>FRAUD OFFENSES</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>3700 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J543" t="n">
+        <v>36.11045502553304</v>
+      </c>
+      <c r="K543" t="n">
+        <v>-115.1764700026846</v>
+      </c>
+      <c r="L543" t="n">
+        <v>778.4</v>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>False pretenses/swindle/confidence game on Jul 25, 2026, 778 m from The Forum Shops at Caesars (3700 S LAS VEGAS BLVD). Case #LLV260700099368 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>The Forum Shops at Caesars</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>LLV260700102948</t>
+        </is>
+      </c>
+      <c r="E544" s="3" t="n">
+        <v>46229.40803371528</v>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>Simple Assault</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>ASSAULT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>3700 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J544" t="n">
+        <v>36.11009780070533</v>
+      </c>
+      <c r="K544" t="n">
+        <v>-115.1756791808693</v>
+      </c>
+      <c r="L544" t="n">
+        <v>822.8</v>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 26, 2026, 823 m from The Forum Shops at Caesars (3700 S LAS VEGAS BLVD). Case #LLV260700102948 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>The Forum Shops at Caesars</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>LLV260700102908</t>
+        </is>
+      </c>
+      <c r="E545" s="3" t="n">
+        <v>46229.39162488426</v>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>Trespass of Real Property</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>3700 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J545" t="n">
+        <v>36.109816508108</v>
+      </c>
+      <c r="K545" t="n">
+        <v>-115.1752634203852</v>
+      </c>
+      <c r="L545" t="n">
+        <v>858.7</v>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>Trespass of real property on Jul 26, 2026, 859 m from The Forum Shops at Caesars (3700 S LAS VEGAS BLVD). Case #LLV260700102908 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>The Forum Shops at Caesars</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>LLV260700102376</t>
+        </is>
+      </c>
+      <c r="E546" s="3" t="n">
+        <v>46229.26850439815</v>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>Trespass of Real Property</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>3700 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J546" t="n">
+        <v>36.10952339284594</v>
+      </c>
+      <c r="K546" t="n">
+        <v>-115.1757603243095</v>
+      </c>
+      <c r="L546" t="n">
+        <v>885.6</v>
+      </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>Trespass of real property on Jul 26, 2026, 886 m from The Forum Shops at Caesars (3700 S LAS VEGAS BLVD). Case #LLV260700102376 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>The Forum Shops at Caesars</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>LLV260700100373</t>
+        </is>
+      </c>
+      <c r="E547" s="3" t="n">
+        <v>46228.86391959491</v>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>Credit Card/Automatic Teller Fraud</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>FRAUD OFFENSES</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>3600 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J547" t="n">
+        <v>36.10964909179242</v>
+      </c>
+      <c r="K547" t="n">
+        <v>-115.1717081572878</v>
+      </c>
+      <c r="L547" t="n">
+        <v>976.3</v>
+      </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>Credit card/automatic teller fraud on Jul 25, 2026, 976 m from The Forum Shops at Caesars (3600 S LAS VEGAS BLVD). Case #LLV260700100373 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>The Forum Shops at Caesars</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>LLV260700103048</t>
+        </is>
+      </c>
+      <c r="E548" s="3" t="n">
+        <v>46229.4527658912</v>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>Trespass of Real Property</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>3700 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J548" t="n">
+        <v>36.10810116479229</v>
+      </c>
+      <c r="K548" t="n">
+        <v>-115.1763287441091</v>
+      </c>
+      <c r="L548" t="n">
+        <v>1040.4</v>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>Trespass of real property on Jul 26, 2026, 1040 m from The Forum Shops at Caesars (3700 S LAS VEGAS BLVD). Case #LLV260700103048 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>The Forum Shops at Caesars</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>LLV260700102332</t>
+        </is>
+      </c>
+      <c r="E549" s="3" t="n">
+        <v>46229.26111111111</v>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Simple Assault</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>ASSAULT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>LAS VEGAS BLVD &amp; W HARMON AVE</t>
+        </is>
+      </c>
+      <c r="J549" t="n">
+        <v>36.10856523975185</v>
+      </c>
+      <c r="K549" t="n">
+        <v>-115.1729787498052</v>
+      </c>
+      <c r="L549" t="n">
+        <v>1042.9</v>
+      </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 26, 2026, 1043 m from The Forum Shops at Caesars (LAS VEGAS BLVD &amp; W HARMON AVE). Case #LLV260700102332 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>The Forum Shops at Caesars</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>LLV260700102610</t>
+        </is>
+      </c>
+      <c r="E550" s="3" t="n">
+        <v>46229.31013295139</v>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>3300 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J550" t="n">
+        <v>36.12270519273537</v>
+      </c>
+      <c r="K550" t="n">
+        <v>-115.1676811122252</v>
+      </c>
+      <c r="L550" t="n">
+        <v>997.8</v>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 26, 2026, 998 m from The Forum Shops at Caesars (3300 S LAS VEGAS BLVD). Case #LLV260700102610 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>The Forum Shops at Caesars</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>LLV260700099478</t>
+        </is>
+      </c>
+      <c r="E551" s="3" t="n">
+        <v>46228.56054621527</v>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>Motor Vehicle Theft</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>MOTOR VEHICLE THEFT</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>3600 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J551" t="n">
+        <v>36.10933960033531</v>
+      </c>
+      <c r="K551" t="n">
+        <v>-115.1699156668243</v>
+      </c>
+      <c r="L551" t="n">
+        <v>1088.1</v>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 25, 2026, 1088 m from The Forum Shops at Caesars (3600 S LAS VEGAS BLVD). Case #LLV260700099478 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>The Forum Shops at Caesars</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>LLV260700100442</t>
+        </is>
+      </c>
+      <c r="E552" s="3" t="n">
+        <v>46228.88731006945</v>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>Motor Vehicle Theft</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>MOTOR VEHICLE THEFT</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>3200 W Harmon Ave</t>
+        </is>
+      </c>
+      <c r="J552" t="n">
+        <v>36.10877706599933</v>
+      </c>
+      <c r="K552" t="n">
+        <v>-115.1829397712671</v>
+      </c>
+      <c r="L552" t="n">
+        <v>1116.3</v>
+      </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 25, 2026, 1116 m from The Forum Shops at Caesars (3200 W Harmon Ave). Case #LLV260700100442 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>The Forum Shops at Caesars</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>LLV260700101587</t>
+        </is>
+      </c>
+      <c r="E553" s="3" t="n">
+        <v>46229.13058788195</v>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>SANDS AVE &amp; S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J553" t="n">
+        <v>36.12613102874734</v>
+      </c>
+      <c r="K553" t="n">
+        <v>-115.1688644072716</v>
+      </c>
+      <c r="L553" t="n">
+        <v>1193.7</v>
+      </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 26, 2026, 1194 m from The Forum Shops at Caesars (SANDS AVE &amp; S LAS VEGAS BLVD). Case #LLV260700101587 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>The Forum Shops at Caesars</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>LLV260700100734</t>
+        </is>
+      </c>
+      <c r="E554" s="3" t="n">
+        <v>46229.01319444444</v>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>Trespass of Real Property</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>3700 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J554" t="n">
+        <v>36.10622671487162</v>
+      </c>
+      <c r="K554" t="n">
+        <v>-115.1732496569539</v>
+      </c>
+      <c r="L554" t="n">
+        <v>1285.9</v>
+      </c>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>Trespass of real property on Jul 26, 2026, 1286 m from The Forum Shops at Caesars (3700 S LAS VEGAS BLVD). Case #LLV260700100734 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>The Forum Shops at Caesars</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>SHOPSATCAESARS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>LLV260700099132</t>
+        </is>
+      </c>
+      <c r="E555" s="3" t="n">
+        <v>46228.41107017361</v>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>Drug/narcotic Violations</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>DRUG/NARCOTIC OFFENSES</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>TUSCANY CASINO DR &amp; E FLAMINGO RD</t>
+        </is>
+      </c>
+      <c r="J555" t="n">
+        <v>36.11404615795168</v>
+      </c>
+      <c r="K555" t="n">
+        <v>-115.1595625535794</v>
+      </c>
+      <c r="L555" t="n">
+        <v>1584.3</v>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>Drug/narcotic violations on Jul 25, 2026, 1584 m from The Forum Shops at Caesars (TUSCANY CASINO DR &amp; E FLAMINGO RD). Case #LLV260700099132 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>LLV260700102332</t>
+        </is>
+      </c>
+      <c r="E556" s="3" t="n">
+        <v>46229.26111111111</v>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>Simple Assault</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>ASSAULT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>LAS VEGAS BLVD &amp; W HARMON AVE</t>
+        </is>
+      </c>
+      <c r="J556" t="n">
+        <v>36.10856523975185</v>
+      </c>
+      <c r="K556" t="n">
+        <v>-115.1729787498052</v>
+      </c>
+      <c r="L556" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 26, 2026, 104 m from The Shops at Crystals (LAS VEGAS BLVD &amp; W HARMON AVE). Case #LLV260700102332 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>LLV260700102948</t>
+        </is>
+      </c>
+      <c r="E557" s="3" t="n">
+        <v>46229.40803371528</v>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>All Other Larceny</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>LARCENY/THEFT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>3700 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J557" t="n">
+        <v>36.10971079828387</v>
+      </c>
+      <c r="K557" t="n">
+        <v>-115.1752607872438</v>
+      </c>
+      <c r="L557" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>All other larceny on Jul 26, 2026, 188 m from The Shops at Crystals (3700 S LAS VEGAS BLVD). Case #LLV260700102948 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>LLV260700102908</t>
+        </is>
+      </c>
+      <c r="E558" s="3" t="n">
+        <v>46229.39162488426</v>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>Trespass of Real Property</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>3700 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J558" t="n">
+        <v>36.109816508108</v>
+      </c>
+      <c r="K558" t="n">
+        <v>-115.1752634203852</v>
+      </c>
+      <c r="L558" t="n">
+        <v>197.5</v>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>Trespass of real property on Jul 26, 2026, 197 m from The Shops at Crystals (3700 S LAS VEGAS BLVD). Case #LLV260700102908 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>LLV260700102376</t>
+        </is>
+      </c>
+      <c r="E559" s="3" t="n">
+        <v>46229.26850439815</v>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>Trespass of Real Property</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>3700 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J559" t="n">
+        <v>36.10952339284594</v>
+      </c>
+      <c r="K559" t="n">
+        <v>-115.1757603243095</v>
+      </c>
+      <c r="L559" t="n">
+        <v>201.4</v>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>Trespass of real property on Jul 26, 2026, 201 m from The Shops at Crystals (3700 S LAS VEGAS BLVD). Case #LLV260700102376 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>LLV260700103048</t>
+        </is>
+      </c>
+      <c r="E560" s="3" t="n">
+        <v>46229.4527658912</v>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>Trespass of Real Property</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>3700 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J560" t="n">
+        <v>36.10810116479229</v>
+      </c>
+      <c r="K560" t="n">
+        <v>-115.1763287441091</v>
+      </c>
+      <c r="L560" t="n">
+        <v>202.4</v>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>Trespass of real property on Jul 26, 2026, 202 m from The Shops at Crystals (3700 S LAS VEGAS BLVD). Case #LLV260700103048 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>LLV260700100734</t>
+        </is>
+      </c>
+      <c r="E561" s="3" t="n">
+        <v>46229.01319444444</v>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Trespass of Real Property</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>3700 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J561" t="n">
+        <v>36.10622671487162</v>
+      </c>
+      <c r="K561" t="n">
+        <v>-115.1732496569539</v>
+      </c>
+      <c r="L561" t="n">
+        <v>244.1</v>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>Trespass of real property on Jul 26, 2026, 244 m from The Shops at Crystals (3700 S LAS VEGAS BLVD). Case #LLV260700100734 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>LLV260700100373</t>
+        </is>
+      </c>
+      <c r="E562" s="3" t="n">
+        <v>46228.86391959491</v>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>Credit Card/Automatic Teller Fraud</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>FRAUD OFFENSES</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>3600 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J562" t="n">
+        <v>36.10964909179242</v>
+      </c>
+      <c r="K562" t="n">
+        <v>-115.1717081572878</v>
+      </c>
+      <c r="L562" t="n">
+        <v>260.5</v>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>Credit card/automatic teller fraud on Jul 25, 2026, 260 m from The Shops at Crystals (3600 S LAS VEGAS BLVD). Case #LLV260700100373 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>LLV260700099246</t>
+        </is>
+      </c>
+      <c r="E563" s="3" t="n">
+        <v>46228.45050413194</v>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>Trespass of Real Property</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>3700 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J563" t="n">
+        <v>36.11057101116696</v>
+      </c>
+      <c r="K563" t="n">
+        <v>-115.1761183999585</v>
+      </c>
+      <c r="L563" t="n">
+        <v>310.1</v>
+      </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>Trespass of real property on Jul 25, 2026, 310 m from The Shops at Crystals (3700 S LAS VEGAS BLVD). Case #LLV260700099246 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>LLV260700099368</t>
+        </is>
+      </c>
+      <c r="E564" s="3" t="n">
+        <v>46228.56055555555</v>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>False Pretenses/Swindle/Confidence Game</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>FRAUD OFFENSES</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>3700 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J564" t="n">
+        <v>36.11045502553304</v>
+      </c>
+      <c r="K564" t="n">
+        <v>-115.1764700026846</v>
+      </c>
+      <c r="L564" t="n">
+        <v>319.9</v>
+      </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>False pretenses/swindle/confidence game on Jul 25, 2026, 320 m from The Shops at Crystals (3700 S LAS VEGAS BLVD). Case #LLV260700099368 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>LLV260700099478</t>
+        </is>
+      </c>
+      <c r="E565" s="3" t="n">
+        <v>46228.56054621527</v>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Motor Vehicle Theft</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>MOTOR VEHICLE THEFT</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>3600 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J565" t="n">
+        <v>36.10933960033531</v>
+      </c>
+      <c r="K565" t="n">
+        <v>-115.1699156668243</v>
+      </c>
+      <c r="L565" t="n">
+        <v>392</v>
+      </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 25, 2026, 392 m from The Shops at Crystals (3600 S LAS VEGAS BLVD). Case #LLV260700099478 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>LLV260700100233</t>
+        </is>
+      </c>
+      <c r="E566" s="3" t="n">
+        <v>46228.81579209491</v>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Destruction/Damage/Vandalism of Property</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>DESTRUCTION/DAMAGE/VANDALISM OF PROPERTY</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>400 W FLAMINGO RD</t>
+        </is>
+      </c>
+      <c r="J566" t="n">
+        <v>36.11440363140287</v>
+      </c>
+      <c r="K566" t="n">
+        <v>-115.1728667657516</v>
+      </c>
+      <c r="L566" t="n">
+        <v>686</v>
+      </c>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>Destruction/damage/vandalism of property on Jul 25, 2026, 686 m from The Shops at Crystals (400 W FLAMINGO RD). Case #LLV260700100233 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>LLV260700103131</t>
+        </is>
+      </c>
+      <c r="E567" s="3" t="n">
+        <v>46229.49368055556</v>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>All Other Larceny</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>LARCENY/THEFT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>3700 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J567" t="n">
+        <v>36.10190075110259</v>
+      </c>
+      <c r="K567" t="n">
+        <v>-115.1743821470215</v>
+      </c>
+      <c r="L567" t="n">
+        <v>713.6</v>
+      </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>All other larceny on Jul 26, 2026, 714 m from The Shops at Crystals (3700 S LAS VEGAS BLVD). Case #LLV260700103131 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>LLV260700100275</t>
+        </is>
+      </c>
+      <c r="E568" s="3" t="n">
+        <v>46228.83145185185</v>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>All Other Larceny</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>LARCENY/THEFT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>3700 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J568" t="n">
+        <v>36.10442519052311</v>
+      </c>
+      <c r="K568" t="n">
+        <v>-115.1682967800051</v>
+      </c>
+      <c r="L568" t="n">
+        <v>676.7</v>
+      </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>All other larceny on Jul 25, 2026, 677 m from The Shops at Crystals (3700 S LAS VEGAS BLVD). Case #LLV260700100275 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>LLV260700099335</t>
+        </is>
+      </c>
+      <c r="E569" s="3" t="n">
+        <v>46228.48560748842</v>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>All Other Larceny</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>LARCENY/THEFT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>3500 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J569" t="n">
+        <v>36.11687308181964</v>
+      </c>
+      <c r="K569" t="n">
+        <v>-115.1750785479665</v>
+      </c>
+      <c r="L569" t="n">
+        <v>955.8</v>
+      </c>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>All other larceny on Jul 25, 2026, 956 m from The Shops at Crystals (3500 S LAS VEGAS BLVD). Case #LLV260700099335 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>LLV260700102596</t>
+        </is>
+      </c>
+      <c r="E570" s="3" t="n">
+        <v>46229.30750309028</v>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>3500 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J570" t="n">
+        <v>36.11695368432775</v>
+      </c>
+      <c r="K570" t="n">
+        <v>-115.1740045401824</v>
+      </c>
+      <c r="L570" t="n">
+        <v>960.7</v>
+      </c>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 26, 2026, 961 m from The Shops at Crystals (3500 S LAS VEGAS BLVD). Case #LLV260700102596 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>LLV260700102865</t>
+        </is>
+      </c>
+      <c r="E571" s="3" t="n">
+        <v>46229.3777397338</v>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Trespass of Real Property</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>3500 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J571" t="n">
+        <v>36.1170578909413</v>
+      </c>
+      <c r="K571" t="n">
+        <v>-115.1741161397651</v>
+      </c>
+      <c r="L571" t="n">
+        <v>972.3</v>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>Trespass of real property on Jul 26, 2026, 972 m from The Shops at Crystals (3500 S LAS VEGAS BLVD). Case #LLV260700102865 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>LLV260700100442</t>
+        </is>
+      </c>
+      <c r="E572" s="3" t="n">
+        <v>46228.88731006945</v>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Motor Vehicle Theft</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>MOTOR VEHICLE THEFT</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>3200 W Harmon Ave</t>
+        </is>
+      </c>
+      <c r="J572" t="n">
+        <v>36.10877706599933</v>
+      </c>
+      <c r="K572" t="n">
+        <v>-115.1829397712671</v>
+      </c>
+      <c r="L572" t="n">
+        <v>796.6</v>
+      </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 25, 2026, 797 m from The Shops at Crystals (3200 W Harmon Ave). Case #LLV260700100442 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>LLV260700102987</t>
+        </is>
+      </c>
+      <c r="E573" s="3" t="n">
+        <v>46229.42507789352</v>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Simple Assault</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>ASSAULT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>3500 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J573" t="n">
+        <v>36.11731907946647</v>
+      </c>
+      <c r="K573" t="n">
+        <v>-115.1747388395123</v>
+      </c>
+      <c r="L573" t="n">
+        <v>1003</v>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 26, 2026, 1003 m from The Shops at Crystals (3500 S LAS VEGAS BLVD). Case #LLV260700102987 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>LLV260700102840</t>
+        </is>
+      </c>
+      <c r="E574" s="3" t="n">
+        <v>46229.36774001158</v>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>S LAS VEGAS BLVD &amp; CAESARS PALACE DR</t>
+        </is>
+      </c>
+      <c r="J574" t="n">
+        <v>36.11736365932026</v>
+      </c>
+      <c r="K574" t="n">
+        <v>-115.1726925161043</v>
+      </c>
+      <c r="L574" t="n">
+        <v>1014.1</v>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 26, 2026, 1014 m from The Shops at Crystals (S LAS VEGAS BLVD &amp; CAESARS PALACE DR). Case #LLV260700102840 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>LLV260700099955</t>
+        </is>
+      </c>
+      <c r="E575" s="3" t="n">
+        <v>46228.73026982639</v>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>100 E Tropicana Ave</t>
+        </is>
+      </c>
+      <c r="J575" t="n">
+        <v>36.10139614658136</v>
+      </c>
+      <c r="K575" t="n">
+        <v>-115.1653400497766</v>
+      </c>
+      <c r="L575" t="n">
+        <v>1099.9</v>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 25, 2026, 1100 m from The Shops at Crystals (100 E Tropicana Ave). Case #LLV260700099955 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>LLV260700100213</t>
+        </is>
+      </c>
+      <c r="E576" s="3" t="n">
+        <v>46228.80969305555</v>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Simple Assault</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>ASSAULT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>3900 S Las Vegas Blvd</t>
+        </is>
+      </c>
+      <c r="J576" t="n">
+        <v>36.0957792642059</v>
+      </c>
+      <c r="K576" t="n">
+        <v>-115.1728941764399</v>
+      </c>
+      <c r="L576" t="n">
+        <v>1398</v>
+      </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 25, 2026, 1398 m from The Shops at Crystals (3900 S Las Vegas Blvd). Case #LLV260700100213 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>LLV260700101649</t>
+        </is>
+      </c>
+      <c r="E577" s="3" t="n">
+        <v>46229.13857630787</v>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Stolen Property Offenses</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>STOLEN PROPERTY OFFENSES</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>5000 KOVAL LN</t>
+        </is>
+      </c>
+      <c r="J577" t="n">
+        <v>36.09861122820531</v>
+      </c>
+      <c r="K577" t="n">
+        <v>-115.165012918165</v>
+      </c>
+      <c r="L577" t="n">
+        <v>1352.5</v>
+      </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>Stolen property offenses on Jul 26, 2026, 1352 m from The Shops at Crystals (5000 KOVAL LN). Case #LLV260700101649 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>LLV260700099767</t>
+        </is>
+      </c>
+      <c r="E578" s="3" t="n">
+        <v>46228.67075015046</v>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Trespass of Real Property</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>3300 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J578" t="n">
+        <v>36.12177061943648</v>
+      </c>
+      <c r="K578" t="n">
+        <v>-115.1714678581325</v>
+      </c>
+      <c r="L578" t="n">
+        <v>1514.7</v>
+      </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>Trespass of real property on Jul 25, 2026, 1515 m from The Shops at Crystals (3300 S LAS VEGAS BLVD). Case #LLV260700099767 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>LLV260700100086</t>
+        </is>
+      </c>
+      <c r="E579" s="3" t="n">
+        <v>46228.7722264699</v>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Simple Assault</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>ASSAULT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>3400 W TROPICANA AVE</t>
+        </is>
+      </c>
+      <c r="J579" t="n">
+        <v>36.10032761931003</v>
+      </c>
+      <c r="K579" t="n">
+        <v>-115.1859900281356</v>
+      </c>
+      <c r="L579" t="n">
+        <v>1389.8</v>
+      </c>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 25, 2026, 1390 m from The Shops at Crystals (3400 W TROPICANA AVE). Case #LLV260700100086 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>The Shops at Crystals</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>SHOPSCRYSTALS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>LLV260700099132</t>
+        </is>
+      </c>
+      <c r="E580" s="3" t="n">
+        <v>46228.41107017361</v>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Drug/narcotic Violations</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>DRUG/NARCOTIC OFFENSES</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>TUSCANY CASINO DR &amp; E FLAMINGO RD</t>
+        </is>
+      </c>
+      <c r="J580" t="n">
+        <v>36.11404615795168</v>
+      </c>
+      <c r="K580" t="n">
+        <v>-115.1595625535794</v>
+      </c>
+      <c r="L580" t="n">
+        <v>1452.4</v>
+      </c>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>Drug/narcotic violations on Jul 25, 2026, 1452 m from The Shops at Crystals (TUSCANY CASINO DR &amp; E FLAMINGO RD). Case #LLV260700099132 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Encore at Wynn Las Vegas</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>LLV260700099413</t>
+        </is>
+      </c>
+      <c r="E581" s="3" t="n">
+        <v>46228.52763457176</v>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Trespass of Real Property</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>3100 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J581" t="n">
+        <v>36.1297628128203</v>
+      </c>
+      <c r="K581" t="n">
+        <v>-115.1654142990722</v>
+      </c>
+      <c r="L581" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>Trespass of real property on Jul 25, 2026, 30 m from Encore at Wynn Las Vegas (3100 S LAS VEGAS BLVD). Case #LLV260700099413 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Encore at Wynn Las Vegas</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>LLV260700100242</t>
+        </is>
+      </c>
+      <c r="E582" s="3" t="n">
+        <v>46228.81746612269</v>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>Destruction/Damage/Vandalism of Property</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>DESTRUCTION/DAMAGE/VANDALISM OF PROPERTY</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>3000 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J582" t="n">
+        <v>36.13253259819938</v>
+      </c>
+      <c r="K582" t="n">
+        <v>-115.1627187481995</v>
+      </c>
+      <c r="L582" t="n">
+        <v>364.9</v>
+      </c>
+      <c r="M582" t="inlineStr">
+        <is>
+          <t>Destruction/damage/vandalism of property on Jul 25, 2026, 365 m from Encore at Wynn Las Vegas (3000 S LAS VEGAS BLVD). Case #LLV260700100242 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Encore at Wynn Las Vegas</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>LLV260700101587</t>
+        </is>
+      </c>
+      <c r="E583" s="3" t="n">
+        <v>46229.13058788195</v>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>SANDS AVE &amp; S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J583" t="n">
+        <v>36.12613102874734</v>
+      </c>
+      <c r="K583" t="n">
+        <v>-115.1688644072716</v>
+      </c>
+      <c r="L583" t="n">
+        <v>536.1</v>
+      </c>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 26, 2026, 536 m from Encore at Wynn Las Vegas (SANDS AVE &amp; S LAS VEGAS BLVD). Case #LLV260700101587 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Encore at Wynn Las Vegas</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>LLV260700100619</t>
+        </is>
+      </c>
+      <c r="E584" s="3" t="n">
+        <v>46228.94140790509</v>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>Theft From Motor Vehicle</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>LARCENY/THEFT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>3000 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J584" t="n">
+        <v>36.13463272556923</v>
+      </c>
+      <c r="K584" t="n">
+        <v>-115.1689195366479</v>
+      </c>
+      <c r="L584" t="n">
+        <v>629.8</v>
+      </c>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>Theft from motor vehicle on Jul 25, 2026, 630 m from Encore at Wynn Las Vegas (3000 S LAS VEGAS BLVD). Case #LLV260700100619 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Encore at Wynn Las Vegas</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>LLV260700102610</t>
+        </is>
+      </c>
+      <c r="E585" s="3" t="n">
+        <v>46229.31013295139</v>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>3300 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J585" t="n">
+        <v>36.12270519273537</v>
+      </c>
+      <c r="K585" t="n">
+        <v>-115.1676811122252</v>
+      </c>
+      <c r="L585" t="n">
+        <v>830.4</v>
+      </c>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 26, 2026, 830 m from Encore at Wynn Las Vegas (3300 S LAS VEGAS BLVD). Case #LLV260700102610 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Encore at Wynn Las Vegas</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>LLV260700101795</t>
+        </is>
+      </c>
+      <c r="E586" s="3" t="n">
+        <v>46229.16637627315</v>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>S LAS VEGAS BLVD &amp; CIRCUS CIRCUS DR</t>
+        </is>
+      </c>
+      <c r="J586" t="n">
+        <v>36.13680990955322</v>
+      </c>
+      <c r="K586" t="n">
+        <v>-115.1616647514288</v>
+      </c>
+      <c r="L586" t="n">
+        <v>830.5</v>
+      </c>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 26, 2026, 830 m from Encore at Wynn Las Vegas (S LAS VEGAS BLVD &amp; CIRCUS CIRCUS DR). Case #LLV260700101795 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Encore at Wynn Las Vegas</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>LLV260700099952</t>
+        </is>
+      </c>
+      <c r="E587" s="3" t="n">
+        <v>46228.75069444445</v>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>Theft From Motor Vehicle</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>LARCENY/THEFT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>2800 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J587" t="n">
+        <v>36.1377704302845</v>
+      </c>
+      <c r="K587" t="n">
+        <v>-115.1675335183679</v>
+      </c>
+      <c r="L587" t="n">
+        <v>904.2</v>
+      </c>
+      <c r="M587" t="inlineStr">
+        <is>
+          <t>Theft from motor vehicle on Jul 25, 2026, 904 m from Encore at Wynn Las Vegas (2800 S LAS VEGAS BLVD). Case #LLV260700099952 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Encore at Wynn Las Vegas</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>LLV260700101084</t>
+        </is>
+      </c>
+      <c r="E588" s="3" t="n">
+        <v>46229.03793769676</v>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>Simple Assault</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>ASSAULT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>2700 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J588" t="n">
+        <v>36.13758804215176</v>
+      </c>
+      <c r="K588" t="n">
+        <v>-115.1590244775813</v>
+      </c>
+      <c r="L588" t="n">
+        <v>1016.6</v>
+      </c>
+      <c r="M588" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 26, 2026, 1017 m from Encore at Wynn Las Vegas (2700 S LAS VEGAS BLVD). Case #LLV260700101084 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Encore at Wynn Las Vegas</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>LLV260700099767</t>
+        </is>
+      </c>
+      <c r="E589" s="3" t="n">
+        <v>46228.67075015046</v>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>Trespass of Real Property</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>3300 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J589" t="n">
+        <v>36.12177061943648</v>
+      </c>
+      <c r="K589" t="n">
+        <v>-115.1714678581325</v>
+      </c>
+      <c r="L589" t="n">
+        <v>1067.2</v>
+      </c>
+      <c r="M589" t="inlineStr">
+        <is>
+          <t>Trespass of real property on Jul 25, 2026, 1067 m from Encore at Wynn Las Vegas (3300 S LAS VEGAS BLVD). Case #LLV260700099767 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Encore at Wynn Las Vegas</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>LLV260700101630</t>
+        </is>
+      </c>
+      <c r="E590" s="3" t="n">
+        <v>46229.13695686343</v>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>Destruction/Damage/Vandalism of Property</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>DESTRUCTION/DAMAGE/VANDALISM OF PROPERTY</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>Highland Dr &amp; Presidio Ave</t>
+        </is>
+      </c>
+      <c r="J590" t="n">
+        <v>36.14083813844527</v>
+      </c>
+      <c r="K590" t="n">
+        <v>-115.170670972927</v>
+      </c>
+      <c r="L590" t="n">
+        <v>1317.1</v>
+      </c>
+      <c r="M590" t="inlineStr">
+        <is>
+          <t>Destruction/damage/vandalism of property on Jul 26, 2026, 1317 m from Encore at Wynn Las Vegas (Highland Dr &amp; Presidio Ave). Case #LLV260700101630 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Encore at Wynn Las Vegas</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>LLV260700102714</t>
+        </is>
+      </c>
+      <c r="E591" s="3" t="n">
+        <v>46229.51539351852</v>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>Drug Equipment Violations</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>DRUG/NARCOTIC OFFENSES</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>2900 Westwood Dr</t>
+        </is>
+      </c>
+      <c r="J591" t="n">
+        <v>36.13578722218833</v>
+      </c>
+      <c r="K591" t="n">
+        <v>-115.1767464675433</v>
+      </c>
+      <c r="L591" t="n">
+        <v>1234.5</v>
+      </c>
+      <c r="M591" t="inlineStr">
+        <is>
+          <t>Drug equipment violations on Jul 26, 2026, 1235 m from Encore at Wynn Las Vegas (2900 Westwood Dr). Case #LLV260700102714 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Encore at Wynn Las Vegas</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>LLV260700101101</t>
+        </is>
+      </c>
+      <c r="E592" s="3" t="n">
+        <v>46229.04129552083</v>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>Simple Assault</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>ASSAULT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>3600 Paradise Rd</t>
+        </is>
+      </c>
+      <c r="J592" t="n">
+        <v>36.12246287364957</v>
+      </c>
+      <c r="K592" t="n">
+        <v>-115.154300014731</v>
+      </c>
+      <c r="L592" t="n">
+        <v>1273.7</v>
+      </c>
+      <c r="M592" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 26, 2026, 1274 m from Encore at Wynn Las Vegas (3600 Paradise Rd). Case #LLV260700101101 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Encore at Wynn Las Vegas</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>LLV260700102840</t>
+        </is>
+      </c>
+      <c r="E593" s="3" t="n">
+        <v>46229.36774001158</v>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>S LAS VEGAS BLVD &amp; CAESARS PALACE DR</t>
+        </is>
+      </c>
+      <c r="J593" t="n">
+        <v>36.11736365932026</v>
+      </c>
+      <c r="K593" t="n">
+        <v>-115.1726925161043</v>
+      </c>
+      <c r="L593" t="n">
+        <v>1549.3</v>
+      </c>
+      <c r="M593" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 26, 2026, 1549 m from Encore at Wynn Las Vegas (S LAS VEGAS BLVD &amp; CAESARS PALACE DR). Case #LLV260700102840 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Encore at Wynn Las Vegas</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>ENCOREWYNNVEGAS:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>LLV260700099779</t>
+        </is>
+      </c>
+      <c r="E594" s="3" t="n">
+        <v>46228.67524945602</v>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>Aggravated Assault</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>ASSAULT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>500 E TWAIN AVE</t>
+        </is>
+      </c>
+      <c r="J594" t="n">
+        <v>36.12139069355136</v>
+      </c>
+      <c r="K594" t="n">
+        <v>-115.1521736318877</v>
+      </c>
+      <c r="L594" t="n">
+        <v>1496.8</v>
+      </c>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>Aggravated assault on Jul 25, 2026, 1497 m from Encore at Wynn Las Vegas (500 E TWAIN AVE). Case #LLV260700099779 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Las Vegas Convention Center</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>LLV260700101084</t>
+        </is>
+      </c>
+      <c r="E595" s="3" t="n">
+        <v>46229.03793769676</v>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>Simple Assault</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>ASSAULT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>2700 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J595" t="n">
+        <v>36.13758804215176</v>
+      </c>
+      <c r="K595" t="n">
+        <v>-115.1590244775813</v>
+      </c>
+      <c r="L595" t="n">
+        <v>880.5</v>
+      </c>
+      <c r="M595" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 26, 2026, 880 m from Las Vegas Convention Center (2700 S LAS VEGAS BLVD). Case #LLV260700101084 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Las Vegas Convention Center</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>LLV260700099541</t>
+        </is>
+      </c>
+      <c r="E596" s="3" t="n">
+        <v>46228.59047017361</v>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>Simple Assault</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>ASSAULT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>2600 LYNNWOOD ST</t>
+        </is>
+      </c>
+      <c r="J596" t="n">
+        <v>36.14146729525472</v>
+      </c>
+      <c r="K596" t="n">
+        <v>-115.1504365576298</v>
+      </c>
+      <c r="L596" t="n">
+        <v>1060.7</v>
+      </c>
+      <c r="M596" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 25, 2026, 1061 m from Las Vegas Convention Center (2600 LYNNWOOD ST). Case #LLV260700099541 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Las Vegas Convention Center</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>LLV260700101101</t>
+        </is>
+      </c>
+      <c r="E597" s="3" t="n">
+        <v>46229.04129552083</v>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Simple Assault</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>ASSAULT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>3600 Paradise Rd</t>
+        </is>
+      </c>
+      <c r="J597" t="n">
+        <v>36.12246287364957</v>
+      </c>
+      <c r="K597" t="n">
+        <v>-115.154300014731</v>
+      </c>
+      <c r="L597" t="n">
+        <v>1081.4</v>
+      </c>
+      <c r="M597" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 26, 2026, 1081 m from Las Vegas Convention Center (3600 Paradise Rd). Case #LLV260700101101 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Las Vegas Convention Center</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>LLV260700099735</t>
+        </is>
+      </c>
+      <c r="E598" s="3" t="n">
+        <v>46228.65902777778</v>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>Drug/narcotic Violations</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>QUALITY_OF_LIFE</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>DRUG/NARCOTIC OFFENSES</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>2600 LYNNWOOD ST</t>
+        </is>
+      </c>
+      <c r="J598" t="n">
+        <v>36.14208373569374</v>
+      </c>
+      <c r="K598" t="n">
+        <v>-115.1501035601041</v>
+      </c>
+      <c r="L598" t="n">
+        <v>1132.9</v>
+      </c>
+      <c r="M598" t="inlineStr">
+        <is>
+          <t>Drug/narcotic violations on Jul 25, 2026, 1133 m from Las Vegas Convention Center (2600 LYNNWOOD ST). Case #LLV260700099735 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Las Vegas Convention Center</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>LLV260700099779</t>
+        </is>
+      </c>
+      <c r="E599" s="3" t="n">
+        <v>46228.67524945602</v>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>Aggravated Assault</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>ASSAULT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>500 E TWAIN AVE</t>
+        </is>
+      </c>
+      <c r="J599" t="n">
+        <v>36.12139069355136</v>
+      </c>
+      <c r="K599" t="n">
+        <v>-115.1521736318877</v>
+      </c>
+      <c r="L599" t="n">
+        <v>1181.8</v>
+      </c>
+      <c r="M599" t="inlineStr">
+        <is>
+          <t>Aggravated assault on Jul 25, 2026, 1182 m from Las Vegas Convention Center (500 E TWAIN AVE). Case #LLV260700099779 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Las Vegas Convention Center</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>LLV260700100242</t>
+        </is>
+      </c>
+      <c r="E600" s="3" t="n">
+        <v>46228.81746612269</v>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Destruction/Damage/Vandalism of Property</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>DESTRUCTION/DAMAGE/VANDALISM OF PROPERTY</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>3000 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J600" t="n">
+        <v>36.13253259819938</v>
+      </c>
+      <c r="K600" t="n">
+        <v>-115.1627187481995</v>
+      </c>
+      <c r="L600" t="n">
+        <v>959.3</v>
+      </c>
+      <c r="M600" t="inlineStr">
+        <is>
+          <t>Destruction/damage/vandalism of property on Jul 25, 2026, 959 m from Las Vegas Convention Center (3000 S LAS VEGAS BLVD). Case #LLV260700100242 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Las Vegas Convention Center</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>LLV260700101795</t>
+        </is>
+      </c>
+      <c r="E601" s="3" t="n">
+        <v>46229.16637627315</v>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>S LAS VEGAS BLVD &amp; CIRCUS CIRCUS DR</t>
+        </is>
+      </c>
+      <c r="J601" t="n">
+        <v>36.13680990955322</v>
+      </c>
+      <c r="K601" t="n">
+        <v>-115.1616647514288</v>
+      </c>
+      <c r="L601" t="n">
+        <v>1014.2</v>
+      </c>
+      <c r="M601" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 26, 2026, 1014 m from Las Vegas Convention Center (S LAS VEGAS BLVD &amp; CIRCUS CIRCUS DR). Case #LLV260700101795 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Las Vegas Convention Center</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>LLV260700101104</t>
+        </is>
+      </c>
+      <c r="E602" s="3" t="n">
+        <v>46229.04232230324</v>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>Simple Assault</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>ASSAULT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>700 E Twain Ave</t>
+        </is>
+      </c>
+      <c r="J602" t="n">
+        <v>36.12164799653186</v>
+      </c>
+      <c r="K602" t="n">
+        <v>-115.1480163381353</v>
+      </c>
+      <c r="L602" t="n">
+        <v>1208.8</v>
+      </c>
+      <c r="M602" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 26, 2026, 1209 m from Las Vegas Convention Center (700 E Twain Ave). Case #LLV260700101104 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Las Vegas Convention Center</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>LLV260700103115</t>
+        </is>
+      </c>
+      <c r="E603" s="3" t="n">
+        <v>46229.48666423611</v>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>Driving Under the Influence</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>PARADISE RD &amp; E SAHARA AVE</t>
+        </is>
+      </c>
+      <c r="J603" t="n">
+        <v>36.1438859219674</v>
+      </c>
+      <c r="K603" t="n">
+        <v>-115.1543299305438</v>
+      </c>
+      <c r="L603" t="n">
+        <v>1335.3</v>
+      </c>
+      <c r="M603" t="inlineStr">
+        <is>
+          <t>Driving under the influence on Jul 26, 2026, 1335 m from Las Vegas Convention Center (PARADISE RD &amp; E SAHARA AVE). Case #LLV260700103115 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Las Vegas Convention Center</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>LLV260700099413</t>
+        </is>
+      </c>
+      <c r="E604" s="3" t="n">
+        <v>46228.52763457176</v>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>Trespass of Real Property</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>3100 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J604" t="n">
+        <v>36.1297628128203</v>
+      </c>
+      <c r="K604" t="n">
+        <v>-115.1654142990722</v>
+      </c>
+      <c r="L604" t="n">
+        <v>1225.6</v>
+      </c>
+      <c r="M604" t="inlineStr">
+        <is>
+          <t>Trespass of real property on Jul 25, 2026, 1226 m from Las Vegas Convention Center (3100 S LAS VEGAS BLVD). Case #LLV260700099413 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Las Vegas Convention Center</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>LLV260700103026</t>
+        </is>
+      </c>
+      <c r="E605" s="3" t="n">
+        <v>46229.44455266204</v>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>Simple Assault</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>VIOLENT</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>ASSAULT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>3900 Paradise Rd</t>
+        </is>
+      </c>
+      <c r="J605" t="n">
+        <v>36.11802592290677</v>
+      </c>
+      <c r="K605" t="n">
+        <v>-115.154694636731</v>
+      </c>
+      <c r="L605" t="n">
+        <v>1573.8</v>
+      </c>
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 26, 2026, 1574 m from Las Vegas Convention Center (3900 Paradise Rd). Case #LLV260700103026 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Las Vegas Convention Center</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>LLV260700100182</t>
+        </is>
+      </c>
+      <c r="E606" s="3" t="n">
+        <v>46228.79930555556</v>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>All Other Offenses</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>GROUP "B" OFFENSES</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>S Las Vegas Blvd &amp; Bob Stupak Ave</t>
+        </is>
+      </c>
+      <c r="J606" t="n">
+        <v>36.14602814286643</v>
+      </c>
+      <c r="K606" t="n">
+        <v>-115.1557771838872</v>
+      </c>
+      <c r="L606" t="n">
+        <v>1593.3</v>
+      </c>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 25, 2026, 1593 m from Las Vegas Convention Center (S Las Vegas Blvd &amp; Bob Stupak Ave). Case #LLV260700100182 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Las Vegas Convention Center</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>LLV260700099952</t>
+        </is>
+      </c>
+      <c r="E607" s="3" t="n">
+        <v>46228.75069444445</v>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>Theft From Motor Vehicle</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>LARCENY/THEFT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>2800 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J607" t="n">
+        <v>36.1377704302845</v>
+      </c>
+      <c r="K607" t="n">
+        <v>-115.1675335183679</v>
+      </c>
+      <c r="L607" t="n">
+        <v>1530.1</v>
+      </c>
+      <c r="M607" t="inlineStr">
+        <is>
+          <t>Theft from motor vehicle on Jul 25, 2026, 1530 m from Las Vegas Convention Center (2800 S LAS VEGAS BLVD). Case #LLV260700099952 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Las Vegas Convention Center</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>VEGASCONVENTION:LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>LLV260700100619</t>
+        </is>
+      </c>
+      <c r="E608" s="3" t="n">
+        <v>46228.94140790509</v>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>Theft From Motor Vehicle</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>PROPERTY</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>LARCENY/THEFT OFFENSES</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>3000 S LAS VEGAS BLVD</t>
+        </is>
+      </c>
+      <c r="J608" t="n">
+        <v>36.13463272556923</v>
+      </c>
+      <c r="K608" t="n">
+        <v>-115.1689195366479</v>
+      </c>
+      <c r="L608" t="n">
+        <v>1542.1</v>
+      </c>
+      <c r="M608" t="inlineStr">
+        <is>
+          <t>Theft from motor vehicle on Jul 25, 2026, 1542 m from Las Vegas Convention Center (3000 S LAS VEGAS BLVD). Case #LLV260700100619 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M530"/>
+  <autoFilter ref="A1:M608"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -34264,11 +39192,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34291,7 +39219,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:49:29.028322+00:00</t>
+          <t>2026-08-01 09:51:46.734489+00:00</t>
         </is>
       </c>
     </row>
@@ -34323,7 +39251,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-25 09:49:29.028322+00:00</t>
+          <t>2026-07-25 09:51:46.734489+00:00</t>
         </is>
       </c>
     </row>
@@ -34334,7 +39262,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>529</v>
+        <v>607</v>
       </c>
     </row>
     <row r="7">
@@ -34344,7 +39272,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
@@ -34355,7 +39283,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CASTLETON, LENOX, THEDOMAIN</t>
+          <t>CASTLETON, COLLEGE, LENOX, THEDOMAIN</t>
         </is>
       </c>
     </row>
@@ -34683,8 +39611,80 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>source:VEGASNORTHPO/LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>OK fetched=2 truncated=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>source:VEGASSOUTHPO/LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>OK fetched=2 truncated=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>source:SHOPSATCAESARS/LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>OK fetched=44 truncated=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>source:SHOPSCRYSTALS/LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>OK fetched=49 truncated=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>source:ENCOREWYNNVEGAS/LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>OK fetched=28 truncated=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>source:VEGASCONVENTION/LVMPD Reported NIBRS Crimes</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>OK fetched=20 truncated=False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B35"/>
+  <autoFilter ref="A1:B41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>